--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -39817,6 +39817,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1716">
+      <c r="A1716" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1716" t="n">
+        <v>21483</v>
+      </c>
+      <c r="C1716" t="n">
+        <v>38.0200004577637</v>
+      </c>
+      <c r="D1716" t="n">
+        <v>37.439998626709</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>37.7799987792969</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>37.6599998474121</v>
+      </c>
+      <c r="G1716" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -39840,6 +39840,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1717">
+      <c r="A1717" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>31494</v>
+      </c>
+      <c r="C1717" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>36.439998626709</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>37.1800003051758</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>36.3800010681152</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -39851,7 +39851,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="D1717" t="n">
-        <v>36.439998626709</v>
+        <v>36.3800010681152</v>
       </c>
       <c r="E1717" t="n">
         <v>37.1800003051758</v>
@@ -39860,6 +39860,29 @@
         <v>36.3800010681152</v>
       </c>
       <c r="G1717" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1718" t="n">
+        <v>25174</v>
+      </c>
+      <c r="C1718" t="n">
+        <v>37.0800018310547</v>
+      </c>
+      <c r="D1718" t="n">
+        <v>36.2400016784668</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>37.0400009155273</v>
+      </c>
+      <c r="G1718" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -39886,6 +39886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1719">
+      <c r="A1719" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>17605</v>
+      </c>
+      <c r="C1719" t="n">
+        <v>37.2200012207031</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>36.7599983215332</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>37.1800003051758</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>37.060001373291</v>
+      </c>
+      <c r="G1719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -39727,22 +39727,22 @@
     </row>
     <row r="1712">
       <c r="A1712" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1712" t="n">
-        <v>46634</v>
+        <v>37572</v>
       </c>
       <c r="C1712" t="n">
-        <v>39.8600006103516</v>
+        <v>39.9000015258789</v>
       </c>
       <c r="D1712" t="n">
-        <v>38.7200012207031</v>
+        <v>38.6199989318848</v>
       </c>
       <c r="E1712" t="n">
-        <v>38.7200012207031</v>
+        <v>38.7999992370605</v>
       </c>
       <c r="F1712" t="n">
-        <v>39.3800010681152</v>
+        <v>39.2400016784668</v>
       </c>
       <c r="G1712" t="s">
         <v>7</v>
@@ -39750,22 +39750,22 @@
     </row>
     <row r="1713">
       <c r="A1713" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1713" t="n">
-        <v>17072</v>
+        <v>46634</v>
       </c>
       <c r="C1713" t="n">
-        <v>39.8400001525879</v>
+        <v>39.8600006103516</v>
       </c>
       <c r="D1713" t="n">
-        <v>38.4799995422363</v>
+        <v>38.7200012207031</v>
       </c>
       <c r="E1713" t="n">
-        <v>39.2000007629395</v>
+        <v>38.7200012207031</v>
       </c>
       <c r="F1713" t="n">
-        <v>39.0400009155273</v>
+        <v>39.3800010681152</v>
       </c>
       <c r="G1713" t="s">
         <v>7</v>
@@ -39773,22 +39773,22 @@
     </row>
     <row r="1714">
       <c r="A1714" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1714" t="n">
-        <v>15160</v>
+        <v>17072</v>
       </c>
       <c r="C1714" t="n">
-        <v>39.0999984741211</v>
+        <v>39.8400001525879</v>
       </c>
       <c r="D1714" t="n">
-        <v>38.1599998474121</v>
+        <v>38.4799995422363</v>
       </c>
       <c r="E1714" t="n">
-        <v>38.5200004577637</v>
+        <v>39.2000007629395</v>
       </c>
       <c r="F1714" t="n">
-        <v>38.1599998474121</v>
+        <v>39.0400009155273</v>
       </c>
       <c r="G1714" t="s">
         <v>7</v>
@@ -39796,22 +39796,22 @@
     </row>
     <row r="1715">
       <c r="A1715" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1715" t="n">
-        <v>15711</v>
+        <v>15160</v>
       </c>
       <c r="C1715" t="n">
-        <v>38.6599998474121</v>
+        <v>39.0999984741211</v>
       </c>
       <c r="D1715" t="n">
-        <v>37.7000007629395</v>
+        <v>38.1599998474121</v>
       </c>
       <c r="E1715" t="n">
-        <v>38.6399993896484</v>
+        <v>38.5200004577637</v>
       </c>
       <c r="F1715" t="n">
-        <v>38.2799987792969</v>
+        <v>38.1599998474121</v>
       </c>
       <c r="G1715" t="s">
         <v>7</v>
@@ -39819,22 +39819,22 @@
     </row>
     <row r="1716">
       <c r="A1716" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1716" t="n">
-        <v>21483</v>
+        <v>15711</v>
       </c>
       <c r="C1716" t="n">
-        <v>38.0200004577637</v>
+        <v>38.6599998474121</v>
       </c>
       <c r="D1716" t="n">
-        <v>37.439998626709</v>
+        <v>37.7000007629395</v>
       </c>
       <c r="E1716" t="n">
-        <v>37.7799987792969</v>
+        <v>38.6399993896484</v>
       </c>
       <c r="F1716" t="n">
-        <v>37.6599998474121</v>
+        <v>38.2799987792969</v>
       </c>
       <c r="G1716" t="s">
         <v>7</v>
@@ -39842,22 +39842,22 @@
     </row>
     <row r="1717">
       <c r="A1717" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1717" t="n">
-        <v>31494</v>
+        <v>21483</v>
       </c>
       <c r="C1717" t="n">
-        <v>37.7999992370605</v>
+        <v>38.0200004577637</v>
       </c>
       <c r="D1717" t="n">
-        <v>36.3800010681152</v>
+        <v>37.439998626709</v>
       </c>
       <c r="E1717" t="n">
-        <v>37.1800003051758</v>
+        <v>37.7799987792969</v>
       </c>
       <c r="F1717" t="n">
-        <v>36.3800010681152</v>
+        <v>37.6599998474121</v>
       </c>
       <c r="G1717" t="s">
         <v>7</v>
@@ -39865,22 +39865,22 @@
     </row>
     <row r="1718">
       <c r="A1718" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1718" t="n">
-        <v>25174</v>
+        <v>31494</v>
       </c>
       <c r="C1718" t="n">
-        <v>37.0800018310547</v>
+        <v>37.7999992370605</v>
       </c>
       <c r="D1718" t="n">
-        <v>36.2400016784668</v>
+        <v>36.3800010681152</v>
       </c>
       <c r="E1718" t="n">
-        <v>36.5</v>
+        <v>37.1800003051758</v>
       </c>
       <c r="F1718" t="n">
-        <v>37.0400009155273</v>
+        <v>36.3800010681152</v>
       </c>
       <c r="G1718" t="s">
         <v>7</v>
@@ -39888,24 +39888,47 @@
     </row>
     <row r="1719">
       <c r="A1719" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1719" t="n">
-        <v>17605</v>
+        <v>25174</v>
       </c>
       <c r="C1719" t="n">
-        <v>37.2200012207031</v>
+        <v>37.0800018310547</v>
       </c>
       <c r="D1719" t="n">
-        <v>36.7599983215332</v>
+        <v>36.2400016784668</v>
       </c>
       <c r="E1719" t="n">
-        <v>37.1800003051758</v>
+        <v>36.5</v>
       </c>
       <c r="F1719" t="n">
-        <v>37.060001373291</v>
+        <v>37.0400009155273</v>
       </c>
       <c r="G1719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1720" t="n">
+        <v>36599</v>
+      </c>
+      <c r="C1720" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1720" t="n">
+        <v>36.4199981689453</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>36.6800003051758</v>
+      </c>
+      <c r="G1720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025457382202</v>
+        <v>13.6025447845459</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.416880607605</v>
+        <v>13.4168796539307</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818502426147</v>
+        <v>13.3818511962891</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479248046875</v>
+        <v>13.7479238510132</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934637069702</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9248323440552</v>
+        <v>13.9248313903809</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390054702759</v>
+        <v>13.8390045166016</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896373748779</v>
+        <v>13.9896383285522</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370918273926</v>
+        <v>13.9370908737183</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598617553711</v>
+        <v>13.9598627090454</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073143005371</v>
+        <v>13.9073152542114</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G18" t="n">
-        <v>13.9423475265503</v>
+        <v>13.942346572876</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260717391968</v>
+        <v>15.3260726928711</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916864395142</v>
+        <v>14.8916873931885</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757614135742</v>
+        <v>14.9757633209229</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730653762817</v>
+        <v>14.4730663299561</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.644718170166</v>
+        <v>14.6447191238403</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628793716431</v>
+        <v>14.2628812789917</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609676361084</v>
+        <v>14.3609685897827</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006067276001</v>
+        <v>14.8006057739258</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443956375122</v>
+        <v>14.8443965911865</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655763626099</v>
+        <v>14.7655773162842</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6236991882324</v>
+        <v>14.6237001419067</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633392333984</v>
+        <v>15.0633411407471</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.136905670166</v>
+        <v>15.1369028091431</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.2698860168457</v>
+        <v>14.26988697052</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270685195923</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527196884155</v>
+        <v>12.9527206420898</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781856536865</v>
+        <v>13.4781847000122</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868530273438</v>
+        <v>9.80868625640869</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837593078613</v>
+        <v>9.45837688446045</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96619033813477</v>
+        <v>8.96618938446045</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58260154724121</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58260154724121</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032096862793</v>
+        <v>8.69032001495361</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415332794189</v>
+        <v>8.92415237426758</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500961303711</v>
+        <v>9.04500865936279</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.3532829284668</v>
+        <v>9.35328197479248</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968856811523</v>
+        <v>10.596884727478</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070707321167</v>
+        <v>10.8070697784424</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878046035767</v>
+        <v>10.7878036499023</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353925704956</v>
+        <v>11.735390663147</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898517608643</v>
+        <v>11.6898508071899</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068826675415</v>
+        <v>12.0068836212158</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229694366455</v>
+        <v>11.8229703903198</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325347900391</v>
+        <v>11.3325357437134</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.933180809021</v>
+        <v>10.9331827163696</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.947193145752</v>
+        <v>10.9471940994263</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655170440674</v>
+        <v>10.4655179977417</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.3866987228394</v>
+        <v>10.386697769165</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691825866699</v>
+        <v>10.3691816329956</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078775405884</v>
+        <v>10.3078784942627</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465744018555</v>
+        <v>10.2465734481812</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616926193237</v>
+        <v>10.6616916656494</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008718490601</v>
+        <v>10.3008728027344</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.381443977356</v>
+        <v>10.3814430236816</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>11.3412942886353</v>
+        <v>11.3412933349609</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955907821655</v>
+        <v>11.3955926895142</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565723419189</v>
+        <v>11.6565732955933</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119766235352</v>
+        <v>12.1119756698608</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834657669067</v>
+        <v>12.3834667205811</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727954864502</v>
+        <v>12.4727945327759</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506706237793</v>
+        <v>12.0506715774536</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258272171021</v>
+        <v>12.2258262634277</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922233581543</v>
+        <v>12.3922243118286</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205724716187</v>
+        <v>12.220573425293</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.2959995269775</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5200862884521</v>
+        <v>12.5200872421265</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.3100357055664</v>
+        <v>13.3100366592407</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930067062378</v>
+        <v>12.9930057525635</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.786322593689</v>
+        <v>12.7863235473633</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119512557983</v>
+        <v>13.211950302124</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976144790649</v>
+        <v>13.3976154327393</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361486434937</v>
+        <v>13.436149597168</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>13.3030309677124</v>
+        <v>13.3030300140381</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>13.2680006027222</v>
+        <v>13.2679986953735</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805835723877</v>
+        <v>13.0805816650391</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606695175171</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501609802246</v>
+        <v>13.4501600265503</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.049054145813</v>
+        <v>13.0490550994873</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504854202271</v>
+        <v>13.2504835128784</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821746826172</v>
+        <v>13.1821727752686</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606695175171</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620979309082</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135385513306</v>
+        <v>13.3135404586792</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277135848999</v>
+        <v>13.2277145385742</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555784225464</v>
+        <v>13.3555765151978</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348819732666</v>
+        <v>13.1348829269409</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823335647583</v>
+        <v>13.0823345184326</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484344482422</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309192657471</v>
+        <v>12.3309183120728</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393533706665</v>
+        <v>12.5393543243408</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094169616699</v>
+        <v>12.6094160079956</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484344482422</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097394943237</v>
+        <v>12.4097385406494</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909313201904</v>
+        <v>13.1909322738647</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.686619758606</v>
+        <v>13.6866207122803</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620979309082</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>13.2680006027222</v>
+        <v>13.2679986953735</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493541717529</v>
+        <v>13.9493532180786</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445827484131</v>
+        <v>13.6445837020874</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971282958984</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>13.679612159729</v>
+        <v>13.679615020752</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531513214111</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531513214111</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955137252808</v>
+        <v>14.6955165863037</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G217" t="n">
-        <v>14.1175022125244</v>
+        <v>14.117504119873</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>13.9248323440552</v>
+        <v>13.9248313903809</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.3117895126343</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592430114746</v>
+        <v>13.2592420578003</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.3117895126343</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.101601600647</v>
+        <v>13.1016035079956</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620979309082</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>13.679612159729</v>
+        <v>13.679615020752</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270685195923</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022222518921</v>
+        <v>13.8022232055664</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270685195923</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971282958984</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197364807129</v>
+        <v>13.8197383880615</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079368591309</v>
+        <v>14.6079359054565</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G274" t="n">
-        <v>14.3977518081665</v>
+        <v>14.3977508544922</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401113510132</v>
+        <v>14.2401103973389</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276901245117</v>
+        <v>14.3276891708374</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729036331177</v>
+        <v>14.572904586792</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311676025391</v>
+        <v>15.4311656951904</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989912033081</v>
+        <v>15.7989931106567</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165044784546</v>
+        <v>15.8165054321289</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397342681885</v>
+        <v>16.6397361755371</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>16.4295501708984</v>
+        <v>16.4295463562012</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024658203125</v>
+        <v>16.9024696350098</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753852844238</v>
+        <v>17.3753890991211</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592975616455</v>
+        <v>17.5593013763428</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220310211182</v>
+        <v>17.8220329284668</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906681060791</v>
+        <v>17.6906661987305</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.252779006958</v>
+        <v>17.2527770996094</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468772888184</v>
+        <v>17.646879196167</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228397369385</v>
+        <v>17.3228416442871</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979972839355</v>
+        <v>17.4979953765869</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.172342300415</v>
+        <v>18.1723442077637</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108520507812</v>
+        <v>19.3108501434326</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173706054688</v>
+        <v>19.6173725128174</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925300598145</v>
+        <v>19.7925281524658</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611633300781</v>
+        <v>19.6611614227295</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729610443115</v>
+        <v>18.8729648590088</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167537689209</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546390533447</v>
+        <v>19.3546409606934</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167537689209</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799457550049</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.212646484375</v>
+        <v>20.2126445770264</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793781280518</v>
+        <v>20.0793762207031</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905300140381</v>
+        <v>19.9905261993408</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345737457275</v>
+        <v>20.8345756530762</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684135437012</v>
+        <v>19.7684116363525</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461059570312</v>
+        <v>19.9461078643799</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.835521697998</v>
+        <v>18.8355236053467</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.746675491333</v>
+        <v>18.7466735839844</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>19.6351413726807</v>
+        <v>19.6351432800293</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.523609161377</v>
+        <v>20.5236110687256</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905300140381</v>
+        <v>19.9905261993408</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570686340332</v>
+        <v>20.2570667266846</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570686340332</v>
+        <v>20.2570667266846</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>23.2778625488281</v>
+        <v>23.2778606414795</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>23.233434677124</v>
+        <v>23.2334365844727</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>23.2778625488281</v>
+        <v>23.2778606414795</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.144588470459</v>
+        <v>23.1445903778076</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>24.25</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5453472137451</v>
+        <v>21.5453491210938</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5897731781006</v>
+        <v>21.5897693634033</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5009269714355</v>
+        <v>21.5009250640869</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011161804199</v>
+        <v>21.1011142730713</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901515960693</v>
+        <v>20.7901496887207</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.8789978027344</v>
+        <v>20.8789958953857</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5</v>
       </c>
       <c r="G398" t="n">
-        <v>21.7674655914307</v>
+        <v>21.7674674987793</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.5897731781006</v>
+        <v>21.5897693634033</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.25</v>
       </c>
       <c r="G403" t="n">
-        <v>21.5453472137451</v>
+        <v>21.5453491210938</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>21.4120769500732</v>
+        <v>21.4120788574219</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459167480469</v>
+        <v>20.3459148406982</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.5</v>
       </c>
       <c r="G411" t="n">
-        <v>21.7674655914307</v>
+        <v>21.7674674987793</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115112304688</v>
+        <v>22.6115093231201</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224739074707</v>
+        <v>22.9224720001221</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551746368408</v>
+        <v>24.2551765441895</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663303375244</v>
+        <v>24.1663284301758</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5443992614746</v>
+        <v>23.5444011688232</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886341094971</v>
+        <v>23.9886360168457</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772930145264</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215259552002</v>
+        <v>24.9215278625488</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438335418701</v>
+        <v>24.7438316345215</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324905395508</v>
+        <v>25.2324886322021</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205799102783</v>
+        <v>26.9205780029297</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536609649658</v>
+        <v>27.4536571502686</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425071716309</v>
+        <v>27.5425090789795</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975154876709</v>
+        <v>28.6975135803223</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.296760559082</v>
+        <v>30.2967567443848</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.6965675354004</v>
+        <v>30.696569442749</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527130126953</v>
+        <v>29.4527149200439</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744529724121</v>
+        <v>30.4744472503662</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646217346191</v>
+        <v>27.7646255493164</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311660766602</v>
+        <v>28.0311641693115</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311660766602</v>
+        <v>28.0311641693115</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423198699951</v>
+        <v>27.9423179626465</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.4753952026367</v>
+        <v>28.4753971099854</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406112670898</v>
+        <v>31.5406093597412</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627296447754</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629169464111</v>
+        <v>31.362922668457</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G476" t="n">
-        <v>33.8506278991699</v>
+        <v>33.8506240844727</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956253051758</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.7173538208008</v>
+        <v>33.717357635498</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942932128906</v>
+        <v>35.4942970275879</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617797851562</v>
+        <v>33.7617835998535</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>37.75</v>
       </c>
       <c r="G487" t="n">
-        <v>33.539665222168</v>
+        <v>33.5396690368652</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398544311523</v>
+        <v>33.1398582458496</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844696044922</v>
+        <v>32.7844657897949</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404239654541</v>
+        <v>31.9404258728027</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852264404297</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852264404297</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956253051758</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071517944336</v>
+        <v>31.8071537017822</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627296447754</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>36</v>
       </c>
       <c r="G512" t="n">
-        <v>31.9848461151123</v>
+        <v>31.984842300415</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510139465332</v>
+        <v>33.0510101318359</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508171081543</v>
+        <v>33.4508209228516</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.473503112793</v>
+        <v>32.4735069274902</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.473503112793</v>
+        <v>32.4735069274902</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.317554473877</v>
+        <v>33.3175506591797</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960018157959</v>
+        <v>31.8959999084473</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840873718262</v>
+        <v>33.5840911865234</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842765808105</v>
+        <v>33.1842727661133</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>34.4725608825684</v>
+        <v>34.4725570678711</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>40.5</v>
       </c>
       <c r="G537" t="n">
-        <v>35.9829521179199</v>
+        <v>35.9829483032227</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956253051758</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279457092285</v>
+        <v>34.8279495239258</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275634765625</v>
+        <v>35.6275672912598</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>34.9612159729004</v>
+        <v>34.9612197875977</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655696868896</v>
+        <v>25.7655715942383</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882556915283</v>
+        <v>24.788257598877</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190662384033</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184986114502</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519580841064</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623550415039</v>
+        <v>32.5623512268066</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298397064209</v>
+        <v>30.8298435211182</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408004760742</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186840057373</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>33.8506278991699</v>
+        <v>33.8506240844727</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>32.1181221008301</v>
+        <v>32.1181144714355</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744529724121</v>
+        <v>30.4744472503662</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186840057373</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>35</v>
       </c>
       <c r="G597" t="n">
-        <v>31.096378326416</v>
+        <v>31.0963802337646</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519580841064</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740745544434</v>
+        <v>31.2740726470947</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629169464111</v>
+        <v>31.362922668457</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408004760742</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.9640522003174</v>
+        <v>28.964054107666</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859832763672</v>
+        <v>29.5859813690186</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596549987793</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828468322754</v>
+        <v>32.3828544616699</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658050537109</v>
+        <v>33.9658088684082</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9758014678955</v>
+        <v>31.9757995605469</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903427124023</v>
+        <v>30.8903465270996</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094326019287</v>
+        <v>30.7094345092773</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903427124023</v>
+        <v>30.8903465270996</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189785003662</v>
+        <v>30.6189746856689</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426189422607</v>
+        <v>31.3426208496094</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737495422363</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260219573975</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766948699951</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766948699951</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>28.8551082611084</v>
+        <v>28.8551063537598</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601036071777</v>
+        <v>27.8601055145264</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787467956543</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260219573975</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355697631836</v>
+        <v>30.9355735778809</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9808006286621</v>
+        <v>30.9807987213135</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832935333252</v>
+        <v>30.4832992553711</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787467956543</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G679" t="n">
-        <v>29.714427947998</v>
+        <v>29.7144298553467</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048858642578</v>
+        <v>29.8048839569092</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596549987793</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123779296875</v>
+        <v>28.3123798370361</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>28.4028339385986</v>
+        <v>28.40283203125</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>28.3576068878174</v>
+        <v>28.357608795166</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567115783691</v>
+        <v>32.1567077636719</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G702" t="n">
-        <v>29.714427947998</v>
+        <v>29.7144298553467</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314697265625</v>
+        <v>28.1314716339111</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048858642578</v>
+        <v>29.8048839569092</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119331359863</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596549987793</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210342407227</v>
+        <v>32.0210304260254</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998905181885</v>
+        <v>30.7998886108398</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119331359863</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832935333252</v>
+        <v>30.4832992553711</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737495422363</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094326019287</v>
+        <v>30.7094345092773</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235271453857</v>
+        <v>31.5235233306885</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>35</v>
       </c>
       <c r="G758" t="n">
-        <v>31.6592102050781</v>
+        <v>31.6592121124268</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>32.4733085632324</v>
+        <v>32.4733009338379</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803443908691</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521648406982</v>
+        <v>31.2521629333496</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803443908691</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>34.5085372924805</v>
+        <v>34.5085411071777</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442184448242</v>
+        <v>34.6442222595215</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608154296875</v>
+        <v>34.9608116149902</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658050537109</v>
+        <v>33.9658088684082</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558143615723</v>
+        <v>35.9558181762695</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674179077148</v>
+        <v>37.2674140930176</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.227180480957</v>
+        <v>36.2271766662598</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.0914993286133</v>
+        <v>36.091495513916</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.0914993286133</v>
+        <v>36.091495513916</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.5437774658203</v>
+        <v>36.543773651123</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.905590057373</v>
+        <v>36.9055938720703</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.5840034484863</v>
+        <v>37.5839996337891</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433288574219</v>
+        <v>38.4433250427246</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3981018066406</v>
+        <v>38.3980979919434</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8956031799316</v>
+        <v>38.8955993652344</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910545349121</v>
+        <v>37.9910507202148</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649154663086</v>
+        <v>37.7649116516113</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9006004333496</v>
+        <v>37.9005928039551</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>38.4885559082031</v>
+        <v>38.4885520935059</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367263793945</v>
+        <v>36.1367301940918</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342239379883</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.9105911254883</v>
+        <v>35.910587310791</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>37.5840034484863</v>
+        <v>37.5839996337891</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101425170898</v>
+        <v>37.8101463317871</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>37.5840034484863</v>
+        <v>37.5839996337891</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342239379883</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.0462684631348</v>
+        <v>36.046272277832</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>36.7331314086914</v>
+        <v>36.7331352233887</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354713439941</v>
+        <v>36.1354751586914</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.618335723877</v>
+        <v>34.6183395385742</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.215991973877</v>
+        <v>35.2159957885742</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.5723609924316</v>
+        <v>34.5723571777344</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850952148438</v>
+        <v>33.2850914001465</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471672058105</v>
+        <v>33.1471710205078</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>35</v>
       </c>
       <c r="G921" t="n">
-        <v>32.1817169189453</v>
+        <v>32.1817207336426</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>35</v>
       </c>
       <c r="G926" t="n">
-        <v>32.1817169189453</v>
+        <v>32.1817207336426</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424911499023</v>
+        <v>34.3424873352051</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965126037598</v>
+        <v>34.2965202331543</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>32.9632759094238</v>
+        <v>32.9632720947266</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>32.5954818725586</v>
+        <v>32.5954856872559</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G964" t="n">
-        <v>32.2736663818359</v>
+        <v>32.2736625671387</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380840301514</v>
+        <v>31.5380802154541</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>33.0552253723145</v>
+        <v>33.0552215576172</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>32.5954818725586</v>
+        <v>32.5954856872559</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9172973632812</v>
+        <v>32.9173049926758</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9172973632812</v>
+        <v>32.9173049926758</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347076416016</v>
+        <v>30.4347095489502</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541851043701</v>
+        <v>31.3541870117188</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783443450928</v>
+        <v>31.0783424377441</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G992" t="n">
-        <v>30.8944473266602</v>
+        <v>30.8944492340088</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G994" t="n">
-        <v>32.9632759094238</v>
+        <v>32.9632720947266</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861259460449</v>
+        <v>34.9861221313477</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>40.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>37.2388458251953</v>
+        <v>37.238842010498</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>39.1697463989258</v>
+        <v>39.169750213623</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>39.2157211303711</v>
+        <v>39.2157249450684</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>42.75</v>
       </c>
       <c r="G1028" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1029" t="n">
-        <v>39.1697463989258</v>
+        <v>39.169750213623</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1035" t="n">
-        <v>38.0203971862793</v>
+        <v>38.0204010009766</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>38.2042961120605</v>
+        <v>38.2042922973633</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>39.2157211303711</v>
+        <v>39.2157249450684</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996162414551</v>
+        <v>39.3996200561523</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>42.75</v>
       </c>
       <c r="G1048" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>40.2731246948242</v>
+        <v>40.273120880127</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>40.6409149169922</v>
+        <v>40.6409111022949</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650703430176</v>
+        <v>40.3650741577148</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>39.1697463989258</v>
+        <v>39.169750213623</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>40.4110450744629</v>
+        <v>40.4110412597656</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627304077148</v>
+        <v>40.9627265930176</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>42.75</v>
       </c>
       <c r="G1067" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>42.25</v>
       </c>
       <c r="G1068" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100105285645</v>
+        <v>38.7100067138672</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>42.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>41.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>37.9284515380859</v>
+        <v>37.9284553527832</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1100" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>42.25</v>
       </c>
       <c r="G1101" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1102" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>38.2042961120605</v>
+        <v>38.2042922973633</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858551025391</v>
+        <v>38.9858589172363</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727058410645</v>
+        <v>39.4727020263672</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900825500488</v>
+        <v>39.1900787353516</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082176208496</v>
+        <v>39.7082214355469</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842903137207</v>
+        <v>39.2842864990234</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379447937012</v>
+        <v>40.0379409790039</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452537536621</v>
+        <v>41.5452499389648</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437370300293</v>
+        <v>39.9437408447266</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132514953613</v>
+        <v>38.8132553100586</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522842407227</v>
+        <v>36.5522880554199</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993881225586</v>
+        <v>36.5993919372559</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376663208008</v>
+        <v>33.5376625061035</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202896118164</v>
+        <v>33.8202857971191</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275985717773</v>
+        <v>35.3275947570801</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238010406494</v>
+        <v>31.3238048553467</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890399932861</v>
+        <v>31.8890419006348</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419399261475</v>
+        <v>31.8419380187988</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804946899414</v>
+        <v>35.2804908752441</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391792297363</v>
+        <v>35.1391830444336</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558013916016</v>
+        <v>34.0558052062988</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160140991211</v>
+        <v>35.5160102844238</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.0233192443848</v>
+        <v>37.023323059082</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739402770996</v>
+        <v>34.5739440917969</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955924987793</v>
+        <v>32.5955963134766</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099395751953</v>
+        <v>29.1099376678467</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164920806885</v>
+        <v>29.8164901733398</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643543243408</v>
+        <v>30.6643524169922</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832496643066</v>
+        <v>31.9832515716553</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.3492546081543</v>
+        <v>33.349250793457</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041454315186</v>
+        <v>29.2041473388672</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207675933838</v>
+        <v>28.1207656860352</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844898223877</v>
+        <v>27.0844917297363</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902839660645</v>
+        <v>26.9902820587158</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779373168945</v>
+        <v>26.3779392242432</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829711914062</v>
+        <v>25.4829730987549</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011119842529</v>
+        <v>26.0011100769043</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.388765335083</v>
+        <v>25.3887672424316</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003517150879</v>
+        <v>25.2003536224365</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.1895236968994</v>
+        <v>26.189525604248</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076644897461</v>
+        <v>26.7076625823975</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.6968364715576</v>
+        <v>27.696834564209</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -45144,6 +45144,32 @@
         <v>36.8199996948242</v>
       </c>
       <c r="H1722" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>24071</v>
+      </c>
+      <c r="C1723" t="n">
+        <v>37.439998626709</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>36.5800018310547</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>36.7799987792969</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>36.7999992370605</v>
+      </c>
+      <c r="G1723" t="n">
+        <v>36.7999992370605</v>
+      </c>
+      <c r="H1723" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4168796539307</v>
+        <v>13.4168825149536</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818511962891</v>
+        <v>13.3818492889404</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479238510132</v>
+        <v>13.7479248046875</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.001898765564</v>
+        <v>14.0018997192383</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810424804688</v>
+        <v>13.8810434341431</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934637069702</v>
+        <v>13.7934656143188</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9248313903809</v>
+        <v>13.9248294830322</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390045166016</v>
+        <v>13.8390054702759</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896383285522</v>
+        <v>13.9896373748779</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370908737183</v>
+        <v>13.9370918273926</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598627090454</v>
+        <v>13.9598617553711</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073152542114</v>
+        <v>13.9073162078857</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948930740356</v>
+        <v>13.9948921203613</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963214874268</v>
+        <v>14.1963205337524</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130289077759</v>
+        <v>14.7130298614502</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692409515381</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260726928711</v>
+        <v>15.3260717391968</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881855010986</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916873931885</v>
+        <v>14.8916864395142</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757633209229</v>
+        <v>14.9757623672485</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730663299561</v>
+        <v>14.4730653762817</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881855010986</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881855010986</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378751754761</v>
+        <v>14.5378742218018</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.355712890625</v>
+        <v>14.3557119369507</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628812789917</v>
+        <v>14.2628793716431</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609685897827</v>
+        <v>14.360969543457</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006057739258</v>
+        <v>14.8006076812744</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443965911865</v>
+        <v>14.8443956375122</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692409515381</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655773162842</v>
+        <v>14.7655763626099</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633411407471</v>
+        <v>15.0633401870728</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369028091431</v>
+        <v>15.1369066238403</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1262588500977</v>
+        <v>14.126259803772</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.44153881073</v>
+        <v>14.4415378570557</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089063644409</v>
+        <v>14.0089054107666</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527206420898</v>
+        <v>12.9527187347412</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781847000122</v>
+        <v>13.4781866073608</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>11.0347728729248</v>
+        <v>11.0347719192505</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868625640869</v>
+        <v>9.80868721008301</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837688446045</v>
+        <v>9.45837593078613</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58260154724121</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651382446289</v>
+        <v>8.76651287078857</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58260154724121</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494094848633</v>
+        <v>8.54494190216064</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6701774597168</v>
+        <v>8.67017841339111</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032001495361</v>
+        <v>8.69032096862793</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415237426758</v>
+        <v>8.92415142059326</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500865936279</v>
+        <v>9.04501152038574</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328197479248</v>
+        <v>9.35328388214111</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921142578125</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070697784424</v>
+        <v>10.8070707321167</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156656265259</v>
+        <v>10.9156665802002</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748962402344</v>
+        <v>11.1748952865601</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878036499023</v>
+        <v>10.7878017425537</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.735390663147</v>
+        <v>11.7353916168213</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898508071899</v>
+        <v>11.6898517608643</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068836212158</v>
+        <v>12.0068826675415</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0347728729248</v>
+        <v>11.0347719192505</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331827163696</v>
+        <v>10.9331817626953</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143999099731</v>
+        <v>10.6143989562988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655179977417</v>
+        <v>10.4655170440674</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078784942627</v>
+        <v>10.3078775405884</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465734481812</v>
+        <v>10.2465744018555</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075559616089</v>
+        <v>10.5075550079346</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616916656494</v>
+        <v>10.6616907119751</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008728027344</v>
+        <v>10.3008718490601</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093059539795</v>
+        <v>10.5093069076538</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220262527466</v>
+        <v>11.3220272064209</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955926895142</v>
+        <v>11.3955907821655</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119756698608</v>
+        <v>12.1119766235352</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834667205811</v>
+        <v>12.3834657669067</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727945327759</v>
+        <v>12.4727935791016</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506715774536</v>
+        <v>12.0506706237793</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258262634277</v>
+        <v>12.2258281707764</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922243118286</v>
+        <v>12.3922233581543</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.220573425293</v>
+        <v>12.2205715179443</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.760048866272</v>
+        <v>12.7600498199463</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614782333374</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901498794556</v>
+        <v>12.5901489257812</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976154327393</v>
+        <v>13.3976135253906</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>13.2679986953735</v>
+        <v>13.2679996490479</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805816650391</v>
+        <v>13.0805826187134</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606704711914</v>
+        <v>13.4606695175171</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501600265503</v>
+        <v>13.4501609802246</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928440093994</v>
+        <v>13.0928449630737</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490550994873</v>
+        <v>13.0490560531616</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772415161133</v>
+        <v>12.9772424697876</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821727752686</v>
+        <v>13.1821746826172</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.0019998550415</v>
       </c>
       <c r="G149" t="n">
-        <v>13.1383857727051</v>
+        <v>13.1383848190308</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606704711914</v>
+        <v>13.4606695175171</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620979309082</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324831008911</v>
+        <v>13.5324850082397</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135404586792</v>
+        <v>13.3135395050049</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.469428062439</v>
+        <v>13.4694271087646</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555765151978</v>
+        <v>13.3555774688721</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348829269409</v>
+        <v>13.1348819732666</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.4307584762573</v>
+        <v>12.430757522583</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097385406494</v>
+        <v>12.409740447998</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909322738647</v>
+        <v>13.1909313201904</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620979309082</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>13.2679986953735</v>
+        <v>13.2679996490479</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445837020874</v>
+        <v>13.6445827484131</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971282958984</v>
+        <v>13.6971311569214</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>13.679615020752</v>
+        <v>13.6796140670776</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920372009277</v>
+        <v>13.5920362472534</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G197" t="n">
-        <v>13.2942724227905</v>
+        <v>13.2942733764648</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614782333374</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767572402954</v>
+        <v>13.2767562866211</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.3101720809937</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531513214111</v>
+        <v>14.8531522750854</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531513214111</v>
+        <v>14.8531522750854</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751417160034</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751417160034</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.730544090271</v>
+        <v>14.7305431365967</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955165863037</v>
+        <v>14.6955137252808</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452014923096</v>
+        <v>14.3452024459839</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G217" t="n">
-        <v>14.117504119873</v>
+        <v>14.1175022125244</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>13.9248313903809</v>
+        <v>13.9248294830322</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1016035079956</v>
+        <v>13.1016025543213</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620979309082</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>13.679615020752</v>
+        <v>13.6796140670776</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022232055664</v>
+        <v>13.8022222518921</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869422912598</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971282958984</v>
+        <v>13.6971311569214</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773778915405</v>
+        <v>13.9773788452148</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.1525325775146</v>
+        <v>14.152533531189</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.3101720809937</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751417160034</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.2576274871826</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079359054565</v>
+        <v>14.6079349517822</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276891708374</v>
+        <v>14.3276882171631</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.2576274871826</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.203462600708</v>
+        <v>15.2034635543823</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311656951904</v>
+        <v>15.4311666488647</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989931106567</v>
+        <v>15.7989921569824</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165054321289</v>
+        <v>15.8165044784546</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814750671387</v>
+        <v>15.7814769744873</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712900161743</v>
+        <v>15.5712909698486</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317844390869</v>
+        <v>16.1317863464355</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397361755371</v>
+        <v>16.6397342681885</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>16.4295463562012</v>
+        <v>16.4295501708984</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024696350098</v>
+        <v>16.9024677276611</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403549194336</v>
+        <v>17.3403568267822</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753890991211</v>
+        <v>17.3753852844238</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5593013763428</v>
+        <v>17.5592994689941</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.2527770996094</v>
+        <v>17.252779006958</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.646879196167</v>
+        <v>17.6468753814697</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228416442871</v>
+        <v>17.3228397369385</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979953765869</v>
+        <v>17.4979934692383</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108501434326</v>
+        <v>19.3108463287354</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173725128174</v>
+        <v>19.617374420166</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611614227295</v>
+        <v>19.6611633300781</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.2232723236084</v>
+        <v>19.223274230957</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729648590088</v>
+        <v>18.8729629516602</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167537689209</v>
+        <v>18.9167518615723</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.2232723236084</v>
+        <v>19.223274230957</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546409606934</v>
+        <v>19.3546390533447</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167537689209</v>
+        <v>18.9167518615723</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912868499756</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912868499756</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799438476562</v>
+        <v>18.8799457550049</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.2126445770264</v>
+        <v>20.2126483917236</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903408050537</v>
+        <v>20.3903427124023</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>20.1237983703613</v>
+        <v>20.12380027771</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572597503662</v>
+        <v>19.8572616577148</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905261993408</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345756530762</v>
+        <v>20.8345737457275</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.8355236053467</v>
+        <v>18.835521697998</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.7466735839844</v>
+        <v>18.7466773986816</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910976409912</v>
+        <v>18.7910995483398</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>20.1237983703613</v>
+        <v>20.12380027771</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905261993408</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455364227295</v>
+        <v>21.1455383300781</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G370" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>21.9451599121094</v>
+        <v>21.9451580047607</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>21.9451599121094</v>
+        <v>21.9451580047607</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5897693634033</v>
+        <v>21.5897731781006</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011142730713</v>
+        <v>21.1011161804199</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566921234131</v>
+        <v>21.0566902160645</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.8789958953857</v>
+        <v>20.8789978027344</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5</v>
       </c>
       <c r="G398" t="n">
-        <v>21.7674674987793</v>
+        <v>21.7674655914307</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.5897693634033</v>
+        <v>21.5897731781006</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G405" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459148406982</v>
+        <v>20.3459167480469</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>21.6341953277588</v>
+        <v>21.6341972351074</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.5</v>
       </c>
       <c r="G411" t="n">
-        <v>21.7674674987793</v>
+        <v>21.7674655914307</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>21.9451599121094</v>
+        <v>21.9451580047607</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115093231201</v>
+        <v>22.6115112304688</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3893947601318</v>
+        <v>22.3893928527832</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>22.3893947601318</v>
+        <v>22.3893928527832</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113220214844</v>
+        <v>23.0113201141357</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886360168457</v>
+        <v>23.9886341094971</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772930145264</v>
+        <v>24.4772911071777</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774803161621</v>
+        <v>24.0774822235107</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215278625488</v>
+        <v>24.9215240478516</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661373138428</v>
+        <v>24.5661392211914</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326797485352</v>
+        <v>24.8326778411865</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324886322021</v>
+        <v>25.2324905395508</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103740692139</v>
+        <v>25.0103721618652</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205780029297</v>
+        <v>26.9205799102783</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536571502686</v>
+        <v>27.4536609649658</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425090789795</v>
+        <v>27.5425071716309</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300308227539</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.696569442749</v>
+        <v>30.6965656280518</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417503356934</v>
+        <v>29.1417484283447</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300308227539</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744472503662</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>28.1200103759766</v>
+        <v>28.1200122833252</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646255493164</v>
+        <v>27.7646236419678</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867401123047</v>
+        <v>27.986743927002</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867401123047</v>
+        <v>27.986743927002</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.1644344329834</v>
+        <v>28.164436340332</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857959747314</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406093597412</v>
+        <v>31.5406131744385</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.762731552124</v>
+        <v>31.7627296447754</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.362922668457</v>
+        <v>31.3629188537598</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G476" t="n">
-        <v>33.8506240844727</v>
+        <v>33.8506278991699</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956253051758</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.717357635498</v>
+        <v>33.7173614501953</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398582458496</v>
+        <v>33.1398506164551</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844657897949</v>
+        <v>32.7844696044922</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954322814941</v>
+        <v>33.0954284667969</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179290771484</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634883880615</v>
+        <v>30.1634864807129</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404258728027</v>
+        <v>31.9404239654541</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852245330811</v>
+        <v>31.1852226257324</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852245330811</v>
+        <v>31.1852226257324</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956253051758</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071537017822</v>
+        <v>31.8071517944336</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.762731552124</v>
+        <v>31.7627296447754</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>36</v>
       </c>
       <c r="G512" t="n">
-        <v>31.984842300415</v>
+        <v>31.9848461151123</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510101318359</v>
+        <v>33.0510063171387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508209228516</v>
+        <v>33.4508171081543</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.4735069274902</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.4735069274902</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954322814941</v>
+        <v>33.0954284667969</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729354858398</v>
+        <v>33.6729393005371</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.294864654541</v>
+        <v>34.2948608398438</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8959999084473</v>
+        <v>31.8960018157959</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179290771484</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060127258301</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G535" t="n">
-        <v>33.228702545166</v>
+        <v>33.2287063598633</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>34.4725570678711</v>
+        <v>34.4725532531738</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>40.5</v>
       </c>
       <c r="G537" t="n">
-        <v>35.9829483032227</v>
+        <v>35.9829521179199</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956253051758</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279495239258</v>
+        <v>34.8279457092285</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060127258301</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.294864654541</v>
+        <v>34.2948608398438</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714218139648</v>
+        <v>36.8714179992676</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>34.9612197875977</v>
+        <v>34.9612121582031</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655715942383</v>
+        <v>25.7655696868896</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.788257598877</v>
+        <v>24.7882556915283</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.3430728912354</v>
+        <v>26.343074798584</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184986114502</v>
+        <v>31.3184947967529</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519580841064</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623512268066</v>
+        <v>32.5623550415039</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298435211182</v>
+        <v>30.8298397064209</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408004760742</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>33.8506240844727</v>
+        <v>33.8506278991699</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744472503662</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521453857422</v>
+        <v>30.6521434783936</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521453857422</v>
+        <v>30.6521434783936</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>35</v>
       </c>
       <c r="G597" t="n">
-        <v>31.0963802337646</v>
+        <v>31.096378326416</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519580841064</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740726470947</v>
+        <v>31.2740688323975</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.362922668457</v>
+        <v>31.3629188537598</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408004760742</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.964054107666</v>
+        <v>28.9640560150146</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859813690186</v>
+        <v>29.5859832763672</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857959747314</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621517181396</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621517181396</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828544616699</v>
+        <v>32.3828468322754</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9757995605469</v>
+        <v>31.9758014678955</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094345092773</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617088317871</v>
+        <v>31.1617107391357</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898979187012</v>
+        <v>32.7898941040039</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189746856689</v>
+        <v>30.6189765930176</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G630" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164836883545</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260219573975</v>
+        <v>31.0260238647461</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766948699951</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766948699951</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601055145264</v>
+        <v>27.8601036071777</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787467956543</v>
+        <v>29.5787506103516</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214752197266</v>
+        <v>30.1214771270752</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260219573975</v>
+        <v>31.0260238647461</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>30.6642055511475</v>
+        <v>30.6642093658447</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476104736328</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355735778809</v>
+        <v>30.9355716705322</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9807987213135</v>
+        <v>30.9808006286621</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832992553711</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787467956543</v>
+        <v>29.5787506103516</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048839569092</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>32.25</v>
       </c>
       <c r="G683" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>28.4480628967285</v>
+        <v>28.4480609893799</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123798370361</v>
+        <v>28.3123779296875</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>28.40283203125</v>
+        <v>28.4028339385986</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>28.357608795166</v>
+        <v>28.3576068878174</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762500762939</v>
+        <v>30.0762481689453</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567077636719</v>
+        <v>32.1567115783691</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.7194271087646</v>
+        <v>28.719425201416</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G708" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364650726318</v>
+        <v>27.1364669799805</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314716339111</v>
+        <v>28.1314697265625</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>32.25</v>
       </c>
       <c r="G714" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048839569092</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430656433105</v>
+        <v>29.4430675506592</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G728" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621517181396</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476104736328</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401222229004</v>
+        <v>31.8401165008545</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998886108398</v>
+        <v>30.7998847961426</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832992553711</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094345092773</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235233306885</v>
+        <v>31.5235290527344</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164836883545</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>35</v>
       </c>
       <c r="G758" t="n">
-        <v>31.6592121124268</v>
+        <v>31.6592102050781</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>32.4733009338379</v>
+        <v>32.4733047485352</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853492736816</v>
+        <v>31.885347366333</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969451904297</v>
+        <v>33.1969413757324</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803443908691</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521629333496</v>
+        <v>31.252161026001</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803443908691</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.920581817627</v>
+        <v>33.9205856323242</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608116149902</v>
+        <v>34.9608192443848</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035400390625</v>
+        <v>35.5035438537598</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558181762695</v>
+        <v>35.9558143615723</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578681945801</v>
+        <v>37.3578643798828</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674140930176</v>
+        <v>37.2674102783203</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.091495513916</v>
+        <v>36.0915031433105</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.091495513916</v>
+        <v>36.0915031433105</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.543773651123</v>
+        <v>36.5437774658203</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.5839996337891</v>
+        <v>37.5840034484863</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433250427246</v>
+        <v>38.4433288574219</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3980979919434</v>
+        <v>38.3980941772461</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>43.5499992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>39.3931007385254</v>
+        <v>39.3931045532227</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860534667969</v>
+        <v>38.9860572814941</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910507202148</v>
+        <v>37.9910545349121</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649116516113</v>
+        <v>37.7649154663086</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9005928039551</v>
+        <v>37.9006042480469</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367301940918</v>
+        <v>36.1367263793945</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G842" t="n">
-        <v>36.2724075317383</v>
+        <v>36.2724113464355</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342239379883</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.910587310791</v>
+        <v>35.9105911254883</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387763977051</v>
+        <v>37.5387725830078</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>37.5839996337891</v>
+        <v>37.5840034484863</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101463317871</v>
+        <v>37.8101425170898</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>37.6292304992676</v>
+        <v>37.6292343139648</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>37.5839996337891</v>
+        <v>37.5840034484863</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>40.75</v>
       </c>
       <c r="G856" t="n">
-        <v>36.8603668212891</v>
+        <v>36.8603706359863</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342239379883</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.046272277832</v>
+        <v>36.0462684631348</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>36.7331352233887</v>
+        <v>36.7331314086914</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354751586914</v>
+        <v>36.1354713439941</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>35.5378112792969</v>
+        <v>35.5378150939941</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>38</v>
       </c>
       <c r="G883" t="n">
-        <v>34.9401512145996</v>
+        <v>34.9401550292969</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.6183395385742</v>
+        <v>34.6183319091797</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.5723571777344</v>
+        <v>34.5723609924316</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>35.5378112792969</v>
+        <v>35.5378150939941</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>38.25</v>
       </c>
       <c r="G896" t="n">
-        <v>35.1700210571289</v>
+        <v>35.1700172424316</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>38</v>
       </c>
       <c r="G904" t="n">
-        <v>34.9401512145996</v>
+        <v>34.9401550292969</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850914001465</v>
+        <v>33.2850952148438</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471710205078</v>
+        <v>33.1471672058105</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>35</v>
       </c>
       <c r="G921" t="n">
-        <v>32.1817207336426</v>
+        <v>32.1817169189453</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>35</v>
       </c>
       <c r="G926" t="n">
-        <v>32.1817207336426</v>
+        <v>32.1817169189453</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575614929199</v>
+        <v>32.4575653076172</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.5</v>
       </c>
       <c r="G934" t="n">
-        <v>34.480411529541</v>
+        <v>34.4804153442383</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G937" t="n">
-        <v>35.0780754089355</v>
+        <v>35.0780715942383</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>35.2619705200195</v>
+        <v>35.2619667053223</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965202331543</v>
+        <v>34.2965126037598</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>32.5954856872559</v>
+        <v>32.5954818725586</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.503532409668</v>
+        <v>32.5035362243652</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380802154541</v>
+        <v>31.5380821228027</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G972" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>32.5954856872559</v>
+        <v>32.5954818725586</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6069068908691</v>
+        <v>33.6069107055664</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9173049926758</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9173049926758</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>30.7565269470215</v>
+        <v>30.7565288543701</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541870117188</v>
+        <v>31.3541889190674</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783424377441</v>
+        <v>31.0783443450928</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>35.3079414367676</v>
+        <v>35.3079452514648</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>35.8136558532715</v>
+        <v>35.8136596679688</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861221313477</v>
+        <v>34.9861259460449</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>35.8136558532715</v>
+        <v>35.8136596679688</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1017" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>40.75</v>
       </c>
       <c r="G1018" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>40.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>37.238842010498</v>
+        <v>37.2388458251953</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>42</v>
       </c>
       <c r="G1024" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>39.2157249450684</v>
+        <v>39.2157211303711</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1029" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>42.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>38.2502708435059</v>
+        <v>38.2502746582031</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>38.2042922973633</v>
+        <v>38.2042961120605</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>39.2157249450684</v>
+        <v>39.2157211303711</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>42.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>42.5</v>
       </c>
       <c r="G1047" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>44</v>
       </c>
       <c r="G1051" t="n">
-        <v>40.4570159912109</v>
+        <v>40.4570198059082</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1052" t="n">
-        <v>41.3305206298828</v>
+        <v>41.3305244445801</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>40.273120880127</v>
+        <v>40.2731246948242</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>40.6409111022949</v>
+        <v>40.6409149169922</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650741577148</v>
+        <v>40.3650703430176</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>41.3305206298828</v>
+        <v>41.3305244445801</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442893981934</v>
+        <v>41.7442855834961</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>42</v>
       </c>
       <c r="G1071" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100067138672</v>
+        <v>38.7100105285645</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>41.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>37.9284553527832</v>
+        <v>37.9284515380859</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>42</v>
       </c>
       <c r="G1087" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>40.75</v>
       </c>
       <c r="G1092" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>38.7559852600098</v>
+        <v>38.7559814453125</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1097" t="n">
-        <v>37.744556427002</v>
+        <v>37.7445602416992</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>38.2042922973633</v>
+        <v>38.2042961120605</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>42</v>
       </c>
       <c r="G1120" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858589172363</v>
+        <v>38.9858551025391</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>39.905330657959</v>
+        <v>39.9053344726562</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>44.4500007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>40.8707847595215</v>
+        <v>40.8707809448242</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>45.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>42.066104888916</v>
+        <v>42.0661010742188</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727020263672</v>
+        <v>39.4727058410645</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900787353516</v>
+        <v>39.1900825500488</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082214355469</v>
+        <v>39.7082176208496</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842864990234</v>
+        <v>39.2842903137207</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379409790039</v>
+        <v>40.0379447937012</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452499389648</v>
+        <v>41.5452537536621</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437408447266</v>
+        <v>39.9437370300293</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132553100586</v>
+        <v>38.8132514953613</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522880554199</v>
+        <v>36.5522842407227</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993919372559</v>
+        <v>36.5993881225586</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376625061035</v>
+        <v>33.5376663208008</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202857971191</v>
+        <v>33.8202896118164</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275947570801</v>
+        <v>35.3275985717773</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238048553467</v>
+        <v>31.3238010406494</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890419006348</v>
+        <v>31.8890399932861</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419380187988</v>
+        <v>31.8419399261475</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804908752441</v>
+        <v>35.2804946899414</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391830444336</v>
+        <v>35.1391792297363</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558052062988</v>
+        <v>34.0558013916016</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160102844238</v>
+        <v>35.5160140991211</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.023323059082</v>
+        <v>37.0233192443848</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739440917969</v>
+        <v>34.5739402770996</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955963134766</v>
+        <v>32.5955924987793</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099376678467</v>
+        <v>29.1099395751953</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164901733398</v>
+        <v>29.8164920806885</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643524169922</v>
+        <v>30.6643543243408</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832515716553</v>
+        <v>31.9832496643066</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.349250793457</v>
+        <v>33.3492546081543</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041473388672</v>
+        <v>29.2041454315186</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207656860352</v>
+        <v>28.1207675933838</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844917297363</v>
+        <v>27.0844898223877</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902820587158</v>
+        <v>26.9902839660645</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779392242432</v>
+        <v>26.3779373168945</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829730987549</v>
+        <v>25.4829711914062</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011100769043</v>
+        <v>26.0011119842529</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.3887672424316</v>
+        <v>25.388765335083</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003536224365</v>
+        <v>25.2003517150879</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.189525604248</v>
+        <v>26.1895236968994</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076625823975</v>
+        <v>26.7076644897461</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.696834564209</v>
+        <v>27.6968364715576</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -45170,6 +45170,32 @@
         <v>36.7999992370605</v>
       </c>
       <c r="H1723" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1724" t="n">
+        <v>17258</v>
+      </c>
+      <c r="C1724" t="n">
+        <v>37</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>36.4000015258789</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>36.7599983215332</v>
+      </c>
+      <c r="G1724" t="n">
+        <v>36.7599983215332</v>
+      </c>
+      <c r="H1724" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4168825149536</v>
+        <v>13.4168815612793</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818492889404</v>
+        <v>13.3818502426147</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479248046875</v>
+        <v>13.7479238510132</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.0018997192383</v>
+        <v>14.001898765564</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810434341431</v>
+        <v>13.8810424804688</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934656143188</v>
+        <v>13.7934646606445</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9248294830322</v>
+        <v>13.9248313903809</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370918273926</v>
+        <v>13.9370927810669</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948921203613</v>
+        <v>13.9948930740356</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130298614502</v>
+        <v>14.7130279541016</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692399978638</v>
+        <v>14.6692409515381</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071281433105</v>
+        <v>15.1071252822876</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260717391968</v>
+        <v>15.3260707855225</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463083267212</v>
+        <v>14.7463102340698</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916864395142</v>
+        <v>14.8916883468628</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.6447191238403</v>
+        <v>14.644718170166</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905815124512</v>
+        <v>14.4905824661255</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557119369507</v>
+        <v>14.3557138442993</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628793716431</v>
+        <v>14.2628784179688</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.360969543457</v>
+        <v>14.3609676361084</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006076812744</v>
+        <v>14.8006067276001</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443956375122</v>
+        <v>14.8443946838379</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692399978638</v>
+        <v>14.6692409515381</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237001419067</v>
+        <v>14.6236991882324</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708292007446</v>
+        <v>14.7708282470703</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633401870728</v>
+        <v>15.0633392333984</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369066238403</v>
+        <v>15.136905670166</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.126259803772</v>
+        <v>14.1262588500977</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.4415378570557</v>
+        <v>14.44153881073</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527187347412</v>
+        <v>12.9527206420898</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781866073608</v>
+        <v>13.4781856536865</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320251464844</v>
+        <v>12.7320241928101</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.071418762207</v>
+        <v>10.0714197158813</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>11.0347719192505</v>
+        <v>11.0347728729248</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868721008301</v>
+        <v>9.80868530273438</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96618938446045</v>
+        <v>8.96619033813477</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58259963989258</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58259963989258</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494190216064</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.67017841339111</v>
+        <v>8.6701774597168</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415142059326</v>
+        <v>8.92415332794189</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04501152038574</v>
+        <v>9.04500961303711</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328388214111</v>
+        <v>9.35328197479248</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921142578125</v>
+        <v>10.2921133041382</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.596884727478</v>
+        <v>10.5968856811523</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070707321167</v>
+        <v>10.8070697784424</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748952865601</v>
+        <v>11.1748962402344</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878017425537</v>
+        <v>10.787802696228</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353916168213</v>
+        <v>11.7353925704956</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229703903198</v>
+        <v>11.8229694366455</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325357437134</v>
+        <v>11.3325347900391</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0347719192505</v>
+        <v>11.0347728729248</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331817626953</v>
+        <v>10.933180809021</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471940994263</v>
+        <v>10.9471950531006</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655170440674</v>
+        <v>10.4655179977417</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078775405884</v>
+        <v>10.3078784942627</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075550079346</v>
+        <v>10.5075540542603</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616907119751</v>
+        <v>10.6616916656494</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220272064209</v>
+        <v>11.3220262527466</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955907821655</v>
+        <v>11.3955917358398</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667583465576</v>
+        <v>11.8667593002319</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119766235352</v>
+        <v>12.1119756698608</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727935791016</v>
+        <v>12.4727954864502</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506706237793</v>
+        <v>12.0506725311279</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258281707764</v>
+        <v>12.2258262634277</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205715179443</v>
+        <v>12.2205724716187</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.2959995269775</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5200872421265</v>
+        <v>12.5200853347778</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.7600498199463</v>
+        <v>12.7600507736206</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614772796631</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930057525635</v>
+        <v>12.9930067062378</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.7863235473633</v>
+        <v>12.786322593689</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901489257812</v>
+        <v>12.5901498794556</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.211950302124</v>
+        <v>13.2119512557983</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976135253906</v>
+        <v>13.3976144790649</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.436149597168</v>
+        <v>13.4361476898193</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681623458862</v>
+        <v>13.1681613922119</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805826187134</v>
+        <v>13.0805835723877</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501609802246</v>
+        <v>13.4501600265503</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979370117188</v>
+        <v>13.1979360580444</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928449630737</v>
+        <v>13.0928440093994</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490560531616</v>
+        <v>13.049054145813</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772424697876</v>
+        <v>12.9772415161133</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504835128784</v>
+        <v>13.2504854202271</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821746826172</v>
+        <v>13.1821737289429</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324850082397</v>
+        <v>13.5324840545654</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309183120728</v>
+        <v>12.3309202194214</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673789978027</v>
+        <v>12.5673799514771</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393543243408</v>
+        <v>12.5393533706665</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.430757522583</v>
+        <v>12.4307584762573</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.409740447998</v>
+        <v>12.4097394943237</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132169723511</v>
+        <v>13.5132160186768</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.6866207122803</v>
+        <v>13.686619758606</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493532180786</v>
+        <v>13.9493541717529</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>14.0999870300293</v>
+        <v>14.0999879837036</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>14.0999870300293</v>
+        <v>14.0999879837036</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445827484131</v>
+        <v>13.6445817947388</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971311569214</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920362472534</v>
+        <v>13.5920372009277</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614772796631</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767562866211</v>
+        <v>13.2767572402954</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.467812538147</v>
+        <v>14.4678134918213</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751417160034</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751417160034</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0999870300293</v>
+        <v>14.0999879837036</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.7305431365967</v>
+        <v>14.7305450439453</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452024459839</v>
+        <v>14.3452014923096</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>13.9248294830322</v>
+        <v>13.9248313903809</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022222518921</v>
+        <v>13.8022232055664</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971311569214</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197383880615</v>
+        <v>13.8197374343872</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773788452148</v>
+        <v>13.9773778915405</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.152533531189</v>
+        <v>14.1525325775146</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751417160034</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576265335083</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079349517822</v>
+        <v>14.6079368591309</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401103973389</v>
+        <v>14.2401113510132</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276882171631</v>
+        <v>14.3276901245117</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576265335083</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034635543823</v>
+        <v>15.2034645080566</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311666488647</v>
+        <v>15.4311656951904</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114133834839</v>
+        <v>15.7114152908325</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989921569824</v>
+        <v>15.7989912033081</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888042449951</v>
+        <v>15.5888061523438</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165044784546</v>
+        <v>15.816502571106</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712909698486</v>
+        <v>15.5712900161743</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397342681885</v>
+        <v>16.6397361755371</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973747253418</v>
+        <v>16.7973728179932</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024677276611</v>
+        <v>16.9024658203125</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403568267822</v>
+        <v>17.3403549194336</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753852844238</v>
+        <v>17.3753890991211</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592994689941</v>
+        <v>17.5592975616455</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906661987305</v>
+        <v>17.6906681060791</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.515510559082</v>
+        <v>17.5155086517334</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228397369385</v>
+        <v>17.3228416442871</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.7273139953613</v>
+        <v>16.7273120880127</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979934692383</v>
+        <v>17.4979972839355</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.1723442077637</v>
+        <v>18.1723403930664</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>18.1285533905029</v>
+        <v>18.1285552978516</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0919055938721</v>
+        <v>19.0919075012207</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108463287354</v>
+        <v>19.3108520507812</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415981292725</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356964111328</v>
+        <v>19.1356983184814</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0919055938721</v>
+        <v>19.0919075012207</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.617374420166</v>
+        <v>19.6173706054688</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925281524658</v>
+        <v>19.7925300598145</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>19.0919055938721</v>
+        <v>19.0919075012207</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415981292725</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.391284942627</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.391284942627</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799457550049</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797565460205</v>
+        <v>19.2797546386719</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.2126483917236</v>
+        <v>20.212646484375</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903427124023</v>
+        <v>20.3903408050537</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>23</v>
       </c>
       <c r="G351" t="n">
-        <v>20.4347629547119</v>
+        <v>20.4347648620605</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>20.12380027771</v>
+        <v>20.1237983703613</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572616577148</v>
+        <v>19.8572597503662</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793762207031</v>
+        <v>20.0793781280518</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684116363525</v>
+        <v>19.7684135437012</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.7466773986816</v>
+        <v>18.746675491333</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910995483398</v>
+        <v>18.7910976409912</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>20.12380027771</v>
+        <v>20.1237983703613</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455383300781</v>
+        <v>21.1455364227295</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G370" t="n">
-        <v>21.2788105010986</v>
+        <v>21.27880859375</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890144348145</v>
+        <v>23.1890125274658</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.8336277008057</v>
+        <v>22.833625793457</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563117980957</v>
+        <v>21.8563137054443</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5897731781006</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5009250640869</v>
+        <v>21.5009269714355</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566902160645</v>
+        <v>21.0566921234131</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901496887207</v>
+        <v>20.7901515960693</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.8789978027344</v>
+        <v>20.878999710083</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>21.2788105010986</v>
+        <v>21.27880859375</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.5897731781006</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G405" t="n">
-        <v>21.2788105010986</v>
+        <v>21.27880859375</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115112304688</v>
+        <v>22.6115093231201</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561206817627</v>
+        <v>22.2561187744141</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551765441895</v>
+        <v>24.2551746368408</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663284301758</v>
+        <v>24.1663303375244</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444011688232</v>
+        <v>23.5443992614746</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>23.6332473754883</v>
+        <v>23.6332492828369</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215240478516</v>
+        <v>24.9215259552002</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438316345215</v>
+        <v>24.7438354492188</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326778411865</v>
+        <v>24.8326797485352</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103721618652</v>
+        <v>25.0103740692139</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205799102783</v>
+        <v>26.9205780029297</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536609649658</v>
+        <v>27.4536628723145</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975135803223</v>
+        <v>28.6975154876709</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300308227539</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.6965656280518</v>
+        <v>30.696569442749</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417484283447</v>
+        <v>29.1417503356934</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527149200439</v>
+        <v>29.4527130126953</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300308227539</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311660766602</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311660766602</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423179626465</v>
+        <v>27.9423198699951</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.4753971099854</v>
+        <v>28.4753952026367</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.986743927002</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.986743927002</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.2305965423584</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863616943359</v>
+        <v>28.7863636016846</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857978820801</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.74098777771</v>
+        <v>30.7409896850586</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406131744385</v>
+        <v>31.5406112670898</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627296447754</v>
+        <v>31.7627258300781</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629188537598</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402366638184</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513885498047</v>
+        <v>32.2513847351074</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.7173614501953</v>
+        <v>33.717357635498</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398506164551</v>
+        <v>33.1398544311523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065879821777</v>
+        <v>33.0065841674805</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619728088379</v>
+        <v>33.3619689941406</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179290771484</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634864807129</v>
+        <v>30.1634883880615</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402366638184</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627296447754</v>
+        <v>31.7627258300781</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510063171387</v>
+        <v>33.0510101318359</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402366638184</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619728088379</v>
+        <v>33.3619689941406</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729393005371</v>
+        <v>33.6729316711426</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283241271973</v>
+        <v>34.0283203125</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179290771484</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842727661133</v>
+        <v>33.1842765808105</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394721984863</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060127258301</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G535" t="n">
-        <v>33.2287063598633</v>
+        <v>33.228702545166</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>34.4725532531738</v>
+        <v>34.4725608825684</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394721984863</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060127258301</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394721984863</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882556915283</v>
+        <v>24.7882537841797</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.2305965423584</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190662384033</v>
+        <v>30.1190643310547</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519523620605</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623550415039</v>
+        <v>32.5623512268066</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298397064209</v>
+        <v>30.8298377990723</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408042907715</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186840057373</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>32.1181144714355</v>
+        <v>32.1181182861328</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513885498047</v>
+        <v>32.2513847351074</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521415710449</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521415710449</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186840057373</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519523620605</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740688323975</v>
+        <v>31.2740745544434</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629188537598</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408042907715</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863616943359</v>
+        <v>28.7863636016846</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.9640560150146</v>
+        <v>28.964054107666</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857978820801</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621517181396</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264724731445</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621517181396</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094326019287</v>
+        <v>30.7094345092773</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>34.5</v>
       </c>
       <c r="G625" t="n">
-        <v>31.2069358825684</v>
+        <v>31.2069320678711</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617107391357</v>
+        <v>31.1617088317871</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898941040039</v>
+        <v>32.7898979187012</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426208496094</v>
+        <v>31.3426189422607</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5737495422363</v>
+        <v>30.573751449585</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907875061035</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766967773438</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766967773438</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>28.8551063537598</v>
+        <v>28.8551082611084</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907875061035</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214771270752</v>
+        <v>30.1214752197266</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>30.6642093658447</v>
+        <v>30.6642055511475</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285224914551</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476104736328</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355716705322</v>
+        <v>30.9355697631836</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9808006286621</v>
+        <v>30.9807987213135</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G679" t="n">
-        <v>29.7144298553467</v>
+        <v>29.714427947998</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>28.4480609893799</v>
+        <v>28.4480628967285</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907875061035</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>28.4028339385986</v>
+        <v>28.40283203125</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285224914551</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762481689453</v>
+        <v>30.0762500762939</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G702" t="n">
-        <v>29.7144298553467</v>
+        <v>29.714427947998</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.719425201416</v>
+        <v>28.7194271087646</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957866668701</v>
+        <v>27.9957885742188</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364669799805</v>
+        <v>27.1364650726318</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264724731445</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119331359863</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430675506592</v>
+        <v>29.4430637359619</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264724731445</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264724731445</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621517181396</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907875061035</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264724731445</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476104736328</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285224914551</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401165008545</v>
+        <v>31.8401222229004</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210304260254</v>
+        <v>32.0210342407227</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998847961426</v>
+        <v>30.7998886108398</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119331359863</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.5737495422363</v>
+        <v>30.573751449585</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094326019287</v>
+        <v>30.7094345092773</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235290527344</v>
+        <v>31.5235271453857</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.885347366333</v>
+        <v>31.8853454589844</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969413757324</v>
+        <v>33.1969451904297</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.252161026001</v>
+        <v>31.2521648406982</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064872741699</v>
+        <v>33.1064834594727</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301315307617</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301315307617</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301315307617</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442222595215</v>
+        <v>34.6442184448242</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608192443848</v>
+        <v>34.9608154296875</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130859375</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130859375</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035438537598</v>
+        <v>35.5035400390625</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392288208008</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578643798828</v>
+        <v>37.3578681945801</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674102783203</v>
+        <v>37.2674140930176</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.408088684082</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.2271766662598</v>
+        <v>36.227180480957</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.0915031433105</v>
+        <v>36.0914993286133</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.0915031433105</v>
+        <v>36.0914993286133</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G812" t="n">
-        <v>36.7699127197266</v>
+        <v>36.7699089050293</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.9055938720703</v>
+        <v>36.905590057373</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433288574219</v>
+        <v>38.4433250427246</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312805175781</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3980941772461</v>
+        <v>38.3981018066406</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8955993652344</v>
+        <v>38.8956069946289</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860572814941</v>
+        <v>38.9860534667969</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312805175781</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9006042480469</v>
+        <v>37.9005966186523</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.1819534301758</v>
+        <v>36.1819496154785</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.865364074707</v>
+        <v>35.8653678894043</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392288208008</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.865364074707</v>
+        <v>35.8653678894043</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.1819534301758</v>
+        <v>36.1819496154785</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.408088684082</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.1819534301758</v>
+        <v>36.1819496154785</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342277526855</v>
+        <v>36.6342315673828</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387725830078</v>
+        <v>37.5387763977051</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>37.6292343139648</v>
+        <v>37.6292304992676</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744613647461</v>
+        <v>37.6744575500488</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>40.75</v>
       </c>
       <c r="G856" t="n">
-        <v>36.8603706359863</v>
+        <v>36.8603630065918</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342277526855</v>
+        <v>36.6342315673828</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.0462684631348</v>
+        <v>36.046272277832</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.408088684082</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>36.7699127197266</v>
+        <v>36.7699089050293</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>40</v>
       </c>
       <c r="G866" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354713439941</v>
+        <v>36.1354675292969</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>35.5378150939941</v>
+        <v>35.5378112792969</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>38</v>
       </c>
       <c r="G883" t="n">
-        <v>34.9401550292969</v>
+        <v>34.9401512145996</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.6183319091797</v>
+        <v>34.618335723877</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.2159957885742</v>
+        <v>35.215991973877</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>35.5378150939941</v>
+        <v>35.5378112792969</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>38.25</v>
       </c>
       <c r="G896" t="n">
-        <v>35.1700172424316</v>
+        <v>35.1700210571289</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.5263862609863</v>
+        <v>34.5263824462891</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>34.5263862609863</v>
+        <v>34.5263824462891</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>38</v>
       </c>
       <c r="G904" t="n">
-        <v>34.9401550292969</v>
+        <v>34.9401512145996</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G906" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>34.112621307373</v>
+        <v>34.1126174926758</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850952148438</v>
+        <v>33.2850914001465</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471672058105</v>
+        <v>33.1471710205078</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424873352051</v>
+        <v>34.3424911499023</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G937" t="n">
-        <v>35.0780715942383</v>
+        <v>35.0780754089355</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>34.112621307373</v>
+        <v>34.1126174926758</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.5035362243652</v>
+        <v>32.503532409668</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380821228027</v>
+        <v>31.5380840301514</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>30.7565288543701</v>
+        <v>30.7565269470215</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347095489502</v>
+        <v>30.4347114562988</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541889190674</v>
+        <v>31.3541851043701</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783443450928</v>
+        <v>31.0783462524414</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>35.3079452514648</v>
+        <v>35.3079414367676</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>35.8136596679688</v>
+        <v>35.8136558532715</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861259460449</v>
+        <v>34.9861221313477</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>35.8136596679688</v>
+        <v>35.8136558532715</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>40.75</v>
       </c>
       <c r="G1018" t="n">
-        <v>37.4687194824219</v>
+        <v>37.4687156677246</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>37.6526107788086</v>
+        <v>37.6526145935059</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>42</v>
       </c>
       <c r="G1024" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>42.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>39.0778045654297</v>
+        <v>39.0778007507324</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616958618164</v>
+        <v>39.2616996765137</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>42.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>39.0778045654297</v>
+        <v>39.0778007507324</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996200561523</v>
+        <v>39.3996162414551</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>42.5</v>
       </c>
       <c r="G1047" t="n">
-        <v>39.0778045654297</v>
+        <v>39.0778007507324</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1052" t="n">
-        <v>41.3305244445801</v>
+        <v>41.3305206298828</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650703430176</v>
+        <v>40.3650741577148</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627265930176</v>
+        <v>40.9627304077148</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>41.3305244445801</v>
+        <v>41.3305206298828</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442855834961</v>
+        <v>41.7442893981934</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>42</v>
       </c>
       <c r="G1071" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100105285645</v>
+        <v>38.7100067138672</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>40</v>
       </c>
       <c r="G1083" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365097045898</v>
+        <v>37.8365058898926</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422241210938</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>42</v>
       </c>
       <c r="G1087" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>40.75</v>
       </c>
       <c r="G1092" t="n">
-        <v>37.4687194824219</v>
+        <v>37.4687156677246</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>38.7559814453125</v>
+        <v>38.7559852600098</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227447509766</v>
+        <v>37.4227409362793</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227447509766</v>
+        <v>37.4227409362793</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365097045898</v>
+        <v>37.8365058898926</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>42</v>
       </c>
       <c r="G1120" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>39.9053344726562</v>
+        <v>39.905330657959</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>45.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>42.0661010742188</v>
+        <v>42.066104888916</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616958618164</v>
+        <v>39.2616996765137</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422241210938</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -45196,6 +45196,32 @@
         <v>36.7599983215332</v>
       </c>
       <c r="H1724" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1725" t="n">
+        <v>48903</v>
+      </c>
+      <c r="C1725" t="n">
+        <v>37.060001373291</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>36.1800003051758</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>36.7200012207031</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>36.4799995422363</v>
+      </c>
+      <c r="G1725" t="n">
+        <v>36.4799995422363</v>
+      </c>
+      <c r="H1725" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025447845459</v>
+        <v>13.6025457382202</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818502426147</v>
+        <v>13.3818492889404</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.001898765564</v>
+        <v>14.0018997192383</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810424804688</v>
+        <v>13.8810434341431</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934665679932</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390054702759</v>
+        <v>13.8390045166016</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370927810669</v>
+        <v>13.9370918273926</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073162078857</v>
+        <v>13.9073152542114</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.8722848892212</v>
+        <v>13.8722839355469</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948930740356</v>
+        <v>13.9948921203613</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130279541016</v>
+        <v>14.7130298614502</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071252822876</v>
+        <v>15.1071281433105</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260707855225</v>
+        <v>15.3260726928711</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463102340698</v>
+        <v>14.7463073730469</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916883468628</v>
+        <v>14.8916873931885</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757623672485</v>
+        <v>14.9757614135742</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.644718170166</v>
+        <v>14.6447200775146</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905824661255</v>
+        <v>14.4905815124512</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557138442993</v>
+        <v>14.355712890625</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628784179688</v>
+        <v>14.2628803253174</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006067276001</v>
+        <v>14.8006076812744</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443946838379</v>
+        <v>14.8443965911865</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655763626099</v>
+        <v>14.7655754089355</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6236991882324</v>
+        <v>14.6237001419067</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708282470703</v>
+        <v>14.7708301544189</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633392333984</v>
+        <v>15.0633401870728</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.136905670166</v>
+        <v>15.1369066238403</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987457275391</v>
+        <v>12.6987438201904</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111679077148</v>
+        <v>12.6111669540405</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781856536865</v>
+        <v>13.4781875610352</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320241928101</v>
+        <v>12.7320251464844</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602369308472</v>
+        <v>11.5602378845215</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0714197158813</v>
+        <v>10.071418762207</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868530273438</v>
+        <v>9.80868625640869</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>9.63353061676025</v>
+        <v>9.63353157043457</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806465148926</v>
+        <v>9.10806560516357</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96619033813477</v>
+        <v>8.96618938446045</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58259963989258</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651287078857</v>
+        <v>8.76651382446289</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58259963989258</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494094848633</v>
+        <v>8.54494190216064</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6701774597168</v>
+        <v>8.67017841339111</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500961303711</v>
+        <v>9.04501056671143</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328197479248</v>
+        <v>9.35328388214111</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921142578125</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968856811523</v>
+        <v>10.596884727478</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748962402344</v>
+        <v>11.1748952865601</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.787802696228</v>
+        <v>10.7878046035767</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353925704956</v>
+        <v>11.7353935241699</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898517608643</v>
+        <v>11.6898508071899</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068826675415</v>
+        <v>12.0068836212158</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229694366455</v>
+        <v>11.8229703903198</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.933180809021</v>
+        <v>10.9331827163696</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471950531006</v>
+        <v>10.9471940994263</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143989562988</v>
+        <v>10.6143999099731</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655179977417</v>
+        <v>10.4655170440674</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.386697769165</v>
+        <v>10.3866968154907</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691816329956</v>
+        <v>10.3691835403442</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078784942627</v>
+        <v>10.3078775405884</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075540542603</v>
+        <v>10.5075550079346</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008718490601</v>
+        <v>10.3008728027344</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.3814430236816</v>
+        <v>10.381443977356</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093069076538</v>
+        <v>10.5093059539795</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667593002319</v>
+        <v>11.8667573928833</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119756698608</v>
+        <v>12.1119766235352</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834657669067</v>
+        <v>12.3834667205811</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727954864502</v>
+        <v>12.4727945327759</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506725311279</v>
+        <v>12.0506706237793</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258262634277</v>
+        <v>12.2258272171021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922233581543</v>
+        <v>12.3922243118286</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.2959995269775</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5200853347778</v>
+        <v>12.5200862884521</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.7600507736206</v>
+        <v>12.7600498199463</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.786322593689</v>
+        <v>12.7863216400146</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119512557983</v>
+        <v>13.2119493484497</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681613922119</v>
+        <v>13.1681604385376</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979360580444</v>
+        <v>13.1979370117188</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.049054145813</v>
+        <v>13.0490560531616</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504854202271</v>
+        <v>13.2504835128784</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.0019998550415</v>
       </c>
       <c r="G149" t="n">
-        <v>13.1383848190308</v>
+        <v>13.1383838653564</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324840545654</v>
+        <v>13.5324831008911</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135395050049</v>
+        <v>13.3135385513306</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277145385742</v>
+        <v>13.2277135848999</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555774688721</v>
+        <v>13.3555765151978</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348819732666</v>
+        <v>13.1348810195923</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987457275391</v>
+        <v>12.6987438201904</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309202194214</v>
+        <v>12.3309183120728</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.4307584762573</v>
+        <v>12.430757522583</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909313201904</v>
+        <v>13.1909303665161</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132160186768</v>
+        <v>13.5132179260254</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G174" t="n">
-        <v>13.653341293335</v>
+        <v>13.6533393859863</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493541717529</v>
+        <v>13.9493532180786</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>14.0999879837036</v>
+        <v>14.099986076355</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>14.0999879837036</v>
+        <v>14.099986076355</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G191" t="n">
-        <v>13.8722848892212</v>
+        <v>13.8722839355469</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445817947388</v>
+        <v>13.6445837020874</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920372009277</v>
+        <v>13.5920362472534</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321605682373</v>
+        <v>13.732159614563</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531522750854</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531522750854</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.4678134918213</v>
+        <v>14.4678115844727</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0999879837036</v>
+        <v>14.099986076355</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.7305450439453</v>
+        <v>14.7305431365967</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955137252808</v>
+        <v>14.6955146789551</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452014923096</v>
+        <v>14.3452033996582</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592420578003</v>
+        <v>13.259241104126</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1016025543213</v>
+        <v>13.101601600647</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321605682373</v>
+        <v>13.732159614563</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022232055664</v>
+        <v>13.8022222518921</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.5745220184326</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.1525325775146</v>
+        <v>14.152533531189</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079368591309</v>
+        <v>14.6079349517822</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401113510132</v>
+        <v>14.2401103973389</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276901245117</v>
+        <v>14.3276882171631</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.572904586792</v>
+        <v>14.5729036331177</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114152908325</v>
+        <v>15.7114133834839</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989912033081</v>
+        <v>15.7989921569824</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.816502571106</v>
+        <v>15.8165073394775</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814769744873</v>
+        <v>15.781476020813</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712900161743</v>
+        <v>15.5712890625</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317863464355</v>
+        <v>16.1317844390869</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973728179932</v>
+        <v>16.7973766326904</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024658203125</v>
+        <v>16.9024677276611</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403549194336</v>
+        <v>17.3403568267822</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753890991211</v>
+        <v>17.3753871917725</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592975616455</v>
+        <v>17.5592994689941</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906681060791</v>
+        <v>17.6906661987305</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468753814697</v>
+        <v>17.6468772888184</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.5155086517334</v>
+        <v>17.5155124664307</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228416442871</v>
+        <v>17.3228397369385</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979972839355</v>
+        <v>17.4979953765869</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409736633301</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.1723403930664</v>
+        <v>18.172342300415</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108520507812</v>
+        <v>19.3108501434326</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356983184814</v>
+        <v>19.1356945037842</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="n">
-        <v>19.2670612335205</v>
+        <v>19.2670631408691</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173706054688</v>
+        <v>19.6173725128174</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925300598145</v>
+        <v>19.7925281524658</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7487392425537</v>
+        <v>19.7487373352051</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>18.9605407714844</v>
+        <v>18.9605388641357</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409736633301</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409736633301</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799438476562</v>
+        <v>18.8799457550049</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797546386719</v>
+        <v>19.2797565460205</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572597503662</v>
+        <v>19.8572616577148</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684135437012</v>
+        <v>19.7684116363525</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461078643799</v>
+        <v>19.9461097717285</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.746675491333</v>
+        <v>18.7466773986816</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455364227295</v>
+        <v>21.1455383300781</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3005466461182</v>
+        <v>22.3005447387695</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.833625793457</v>
+        <v>22.8336277008057</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563137054443</v>
+        <v>21.8563117980957</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>24.25</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5453491210938</v>
+        <v>21.5453510284424</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5009269714355</v>
+        <v>21.5009250640869</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011161804199</v>
+        <v>21.1011142730713</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566921234131</v>
+        <v>21.0566902160645</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>20.7013034820557</v>
+        <v>20.701301574707</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>20.7013034820557</v>
+        <v>20.701301574707</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901515960693</v>
+        <v>20.7901496887207</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.6124591827393</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.878999710083</v>
+        <v>20.8789978027344</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.6124591827393</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.25</v>
       </c>
       <c r="G403" t="n">
-        <v>21.5453491210938</v>
+        <v>21.5453510284424</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>21.4120788574219</v>
+        <v>21.4120769500732</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.6124591827393</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.6124591827393</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>21.6341972351074</v>
+        <v>21.6341953277588</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>22.3005466461182</v>
+        <v>22.3005447387695</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>22.3005466461182</v>
+        <v>22.3005447387695</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115093231201</v>
+        <v>22.6115112304688</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561187744141</v>
+        <v>22.2561206817627</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5226631164551</v>
+        <v>22.5226650238037</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224720001221</v>
+        <v>22.9224739074707</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113201141357</v>
+        <v>23.0113220214844</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663303375244</v>
+        <v>24.1663284301758</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>23.6332492828369</v>
+        <v>23.6332473754883</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886341094971</v>
+        <v>23.9886360168457</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772891998291</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774822235107</v>
+        <v>24.0774803161621</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215259552002</v>
+        <v>24.9215240478516</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661392211914</v>
+        <v>24.5661373138428</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438354492188</v>
+        <v>24.7438316345215</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103740692139</v>
+        <v>25.0103721618652</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207710266113</v>
+        <v>26.5207691192627</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536628723145</v>
+        <v>27.4536609649658</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425071716309</v>
+        <v>27.5425052642822</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975154876709</v>
+        <v>28.6975135803223</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300308227539</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967567443848</v>
+        <v>30.2967586517334</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.696569442749</v>
+        <v>30.6965656280518</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527130126953</v>
+        <v>29.4527149200439</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300308227539</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>28.1200122833252</v>
+        <v>28.1200103759766</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311660766602</v>
+        <v>28.0311641693115</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311660766602</v>
+        <v>28.0311641693115</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423198699951</v>
+        <v>27.9423179626465</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.4753952026367</v>
+        <v>28.4753971099854</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857978820801</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296485900879</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406112670898</v>
+        <v>31.5406131744385</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627258300781</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629207611084</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.162540435791</v>
+        <v>32.1625480651855</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956176757812</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942970275879</v>
+        <v>35.4942932128906</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617835998535</v>
+        <v>33.7617874145508</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065841674805</v>
+        <v>33.0065879821777</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.162540435791</v>
+        <v>32.1625480651855</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634883880615</v>
+        <v>30.1634864807129</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296485900879</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956176757812</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177360534668</v>
+        <v>32.9177322387695</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627258300781</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510101318359</v>
+        <v>33.0510063171387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508171081543</v>
+        <v>33.4508209228516</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290809631348</v>
+        <v>32.429084777832</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729316711426</v>
+        <v>33.6729354858398</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283203125</v>
+        <v>34.0283241271973</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960018157959</v>
+        <v>31.8959999084473</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394721984863</v>
+        <v>33.9394760131836</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G535" t="n">
-        <v>33.228702545166</v>
+        <v>33.2287063598633</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>34.4725608825684</v>
+        <v>34.4725532531738</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727462768555</v>
+        <v>34.0727424621582</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290809631348</v>
+        <v>32.429084777832</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394721984863</v>
+        <v>33.9394760131836</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956176757812</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394721984863</v>
+        <v>33.9394760131836</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.4054489135742</v>
+        <v>35.405445098877</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714179992676</v>
+        <v>36.8714141845703</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655696868896</v>
+        <v>25.7655715942383</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882537841797</v>
+        <v>24.7882556915283</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873077392578</v>
+        <v>26.7873096466064</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190662384033</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184967041016</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519523620605</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623512268066</v>
+        <v>32.5623550415039</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298377990723</v>
+        <v>30.8298397064209</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186840057373</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>32.1181182861328</v>
+        <v>32.1181144714355</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521415710449</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521415710449</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186840057373</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519523620605</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740745544434</v>
+        <v>31.2740688323975</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629207611084</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.964054107666</v>
+        <v>28.9640560150146</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857978820801</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621517181396</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621517181396</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094345092773</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>34.5</v>
       </c>
       <c r="G625" t="n">
-        <v>31.2069320678711</v>
+        <v>31.2069358825684</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617088317871</v>
+        <v>31.1617107391357</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898979187012</v>
+        <v>32.7898941040039</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426189422607</v>
+        <v>31.3426208496094</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737495422363</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907875061035</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>28.8551082611084</v>
+        <v>28.8551063537598</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907875061035</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214752197266</v>
+        <v>30.1214771270752</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>30.6642055511475</v>
+        <v>30.6642093658447</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476104736328</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355697631836</v>
+        <v>30.9355716705322</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9807987213135</v>
+        <v>30.9808006286621</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G679" t="n">
-        <v>29.714427947998</v>
+        <v>29.7144298553467</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>28.4480628967285</v>
+        <v>28.4480609893799</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907875061035</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>28.40283203125</v>
+        <v>28.4028339385986</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762500762939</v>
+        <v>30.0762481689453</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G702" t="n">
-        <v>29.714427947998</v>
+        <v>29.7144298553467</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.7194271087646</v>
+        <v>28.719425201416</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957885742188</v>
+        <v>27.9957866668701</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364650726318</v>
+        <v>27.1364669799805</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430637359619</v>
+        <v>29.4430675506592</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621517181396</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907875061035</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264724731445</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476104736328</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401222229004</v>
+        <v>31.8401165008545</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210342407227</v>
+        <v>32.0210304260254</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998886108398</v>
+        <v>30.7998847961426</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737495422363</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094345092773</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235271453857</v>
+        <v>31.5235290527344</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853454589844</v>
+        <v>31.885347366333</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969451904297</v>
+        <v>33.1969413757324</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521648406982</v>
+        <v>31.252161026001</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064834594727</v>
+        <v>33.1064872741699</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442184448242</v>
+        <v>34.6442222595215</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608154296875</v>
+        <v>34.9608192443848</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130859375</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130859375</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035400390625</v>
+        <v>35.5035438537598</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392288208008</v>
+        <v>35.6392250061035</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578681945801</v>
+        <v>37.3578643798828</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674140930176</v>
+        <v>37.2674102783203</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.227180480957</v>
+        <v>36.2271766662598</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.0914993286133</v>
+        <v>36.0915031433105</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.0914993286133</v>
+        <v>36.0915031433105</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G812" t="n">
-        <v>36.7699089050293</v>
+        <v>36.7699127197266</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.905590057373</v>
+        <v>36.9055938720703</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433250427246</v>
+        <v>38.4433288574219</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3981018066406</v>
+        <v>38.3980941772461</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8956069946289</v>
+        <v>38.8955993652344</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860534667969</v>
+        <v>38.9860572814941</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9005966186523</v>
+        <v>37.9006042480469</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.1819496154785</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.8653678894043</v>
+        <v>35.865364074707</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392288208008</v>
+        <v>35.6392250061035</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.8653678894043</v>
+        <v>35.865364074707</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.1819496154785</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.1819496154785</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387763977051</v>
+        <v>37.5387725830078</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>37.6292304992676</v>
+        <v>37.6292343139648</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744575500488</v>
+        <v>37.6744613647461</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>40.75</v>
       </c>
       <c r="G856" t="n">
-        <v>36.8603630065918</v>
+        <v>36.8603706359863</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.046272277832</v>
+        <v>36.0462684631348</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>36.7699089050293</v>
+        <v>36.7699127197266</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>40</v>
       </c>
       <c r="G866" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354675292969</v>
+        <v>36.1354713439941</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>35.5378112792969</v>
+        <v>35.5378150939941</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>38</v>
       </c>
       <c r="G883" t="n">
-        <v>34.9401512145996</v>
+        <v>34.9401550292969</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.618335723877</v>
+        <v>34.6183319091797</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.215991973877</v>
+        <v>35.2159957885742</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>35.5378112792969</v>
+        <v>35.5378150939941</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>38.25</v>
       </c>
       <c r="G896" t="n">
-        <v>35.1700210571289</v>
+        <v>35.1700172424316</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.5263824462891</v>
+        <v>34.5263862609863</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>34.5263824462891</v>
+        <v>34.5263862609863</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>38</v>
       </c>
       <c r="G904" t="n">
-        <v>34.9401512145996</v>
+        <v>34.9401550292969</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G906" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>34.1126174926758</v>
+        <v>34.112621307373</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850914001465</v>
+        <v>33.2850952148438</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471710205078</v>
+        <v>33.1471672058105</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424911499023</v>
+        <v>34.3424873352051</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G937" t="n">
-        <v>35.0780754089355</v>
+        <v>35.0780715942383</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>34.1126174926758</v>
+        <v>34.112621307373</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.503532409668</v>
+        <v>32.5035362243652</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380840301514</v>
+        <v>31.5380821228027</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>30.7565269470215</v>
+        <v>30.7565288543701</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347114562988</v>
+        <v>30.4347095489502</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541851043701</v>
+        <v>31.3541889190674</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783462524414</v>
+        <v>31.0783443450928</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>35.3079414367676</v>
+        <v>35.3079452514648</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>35.8136558532715</v>
+        <v>35.8136596679688</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861221313477</v>
+        <v>34.9861259460449</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>35.8136558532715</v>
+        <v>35.8136596679688</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>40.75</v>
       </c>
       <c r="G1018" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>37.6526145935059</v>
+        <v>37.6526107788086</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>42</v>
       </c>
       <c r="G1024" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>42.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985816955566</v>
+        <v>37.6985855102539</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>42.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996162414551</v>
+        <v>39.3996200561523</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>42.5</v>
       </c>
       <c r="G1047" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1052" t="n">
-        <v>41.3305206298828</v>
+        <v>41.3305244445801</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650741577148</v>
+        <v>40.3650703430176</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627304077148</v>
+        <v>40.9627265930176</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>41.3305206298828</v>
+        <v>41.3305244445801</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442893981934</v>
+        <v>41.7442855834961</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>42</v>
       </c>
       <c r="G1071" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100067138672</v>
+        <v>38.7100105285645</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985816955566</v>
+        <v>37.6985855102539</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>40</v>
       </c>
       <c r="G1083" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422241210938</v>
+        <v>38.3422203063965</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>42</v>
       </c>
       <c r="G1087" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>40.75</v>
       </c>
       <c r="G1092" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>38.7559852600098</v>
+        <v>38.7559814453125</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>42</v>
       </c>
       <c r="G1120" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>39.905330657959</v>
+        <v>39.9053344726562</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>45.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>42.066104888916</v>
+        <v>42.0661010742188</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422241210938</v>
+        <v>38.3422203063965</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -45222,6 +45222,32 @@
         <v>36.4799995422363</v>
       </c>
       <c r="H1725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1726" t="n">
+        <v>16299</v>
+      </c>
+      <c r="C1726" t="n">
+        <v>36.939998626709</v>
+      </c>
+      <c r="D1726" t="n">
+        <v>36.1199989318848</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>36.939998626709</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>36.5999984741211</v>
+      </c>
+      <c r="G1726" t="n">
+        <v>36.5999984741211</v>
+      </c>
+      <c r="H1726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025457382202</v>
+        <v>13.6025438308716</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4168815612793</v>
+        <v>13.4168796539307</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818492889404</v>
+        <v>13.3818511962891</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479257583618</v>
+        <v>13.7479248046875</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.001898765564</v>
+        <v>14.0018997192383</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810434341431</v>
+        <v>13.8810424804688</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934637069702</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9248304367065</v>
+        <v>13.9248313903809</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896383285522</v>
+        <v>13.9896392822266</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598608016968</v>
+        <v>13.9598617553711</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915510177612</v>
+        <v>13.8915529251099</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073162078857</v>
+        <v>13.9073152542114</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G18" t="n">
-        <v>13.942346572876</v>
+        <v>13.9423456192017</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.99489402771</v>
+        <v>13.9948930740356</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130279541016</v>
+        <v>14.7130270004272</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692419052124</v>
+        <v>14.6692390441895</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071281433105</v>
+        <v>15.1071271896362</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881816864014</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463083267212</v>
+        <v>14.7463073730469</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916873931885</v>
+        <v>14.8916864395142</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757614135742</v>
+        <v>14.9757623672485</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730653762817</v>
+        <v>14.4730644226074</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881816864014</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881816864014</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378751754761</v>
+        <v>14.5378761291504</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905824661255</v>
+        <v>14.4905815124512</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557138442993</v>
+        <v>14.3557119369507</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628803253174</v>
+        <v>14.2628812789917</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609666824341</v>
+        <v>14.3609676361084</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>14.6604833602905</v>
+        <v>14.6604824066162</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006076812744</v>
+        <v>14.8006057739258</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443956375122</v>
+        <v>14.8443965911865</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692419052124</v>
+        <v>14.6692390441895</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237001419067</v>
+        <v>14.6236991882324</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708301544189</v>
+        <v>14.7708292007446</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369066238403</v>
+        <v>15.136905670166</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1262578964233</v>
+        <v>14.1262588500977</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.26988697052</v>
+        <v>14.2698879241943</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987457275391</v>
+        <v>12.6987447738647</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527196884155</v>
+        <v>12.9527206420898</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602378845215</v>
+        <v>11.5602359771729</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0714197158813</v>
+        <v>10.071418762207</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868625640869</v>
+        <v>9.80868530273438</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>9.63353157043457</v>
+        <v>9.63353061676025</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806560516357</v>
+        <v>9.10806465148926</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96618938446045</v>
+        <v>8.96619033813477</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58259963989258</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651382446289</v>
+        <v>8.76651287078857</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58259963989258</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494190216064</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.67017841339111</v>
+        <v>8.6701774597168</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032096862793</v>
+        <v>8.69032192230225</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415332794189</v>
+        <v>8.92415142059326</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328197479248</v>
+        <v>9.3532829284668</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G79" t="n">
-        <v>9.82620239257812</v>
+        <v>9.82620143890381</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921152114868</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968837738037</v>
+        <v>10.596884727478</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156665802002</v>
+        <v>10.9156656265259</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>11.288745880127</v>
+        <v>11.2887477874756</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748962402344</v>
+        <v>11.1748971939087</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878017425537</v>
+        <v>10.787802696228</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.8079996109009</v>
       </c>
       <c r="G87" t="n">
-        <v>11.2169322967529</v>
+        <v>11.2169313430786</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353935241699</v>
+        <v>11.7353925704956</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068826675415</v>
+        <v>12.0068836212158</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331817626953</v>
+        <v>10.9331827163696</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471950531006</v>
+        <v>10.9471940994263</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143999099731</v>
+        <v>10.6143989562988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.465518951416</v>
+        <v>10.4655179977417</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465744018555</v>
+        <v>10.2465734481812</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616907119751</v>
+        <v>10.6616916656494</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008718490601</v>
+        <v>10.3008728027344</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.3814430236816</v>
+        <v>10.381443977356</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>11.3412942886353</v>
+        <v>11.3412923812866</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955907821655</v>
+        <v>11.3955917358398</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726591110229</v>
+        <v>11.4726600646973</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667573928833</v>
+        <v>11.8667593002319</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727954864502</v>
+        <v>12.4727945327759</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922233581543</v>
+        <v>12.3922243118286</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205724716187</v>
+        <v>12.220573425293</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.2959995269775</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5200862884521</v>
+        <v>12.5200872421265</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.760048866272</v>
+        <v>12.7600498199463</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.310037612915</v>
+        <v>13.3100357055664</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930067062378</v>
+        <v>12.9930057525635</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.786322593689</v>
+        <v>12.7863235473633</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901489257812</v>
+        <v>12.5901498794556</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976135253906</v>
+        <v>13.3976144790649</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.5272302627563</v>
+        <v>13.5272283554077</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>13.2679996490479</v>
+        <v>13.2679977416992</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805826187134</v>
+        <v>13.0805816650391</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606714248657</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928449630737</v>
+        <v>13.0928430557251</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772415161133</v>
+        <v>12.9772424697876</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821737289429</v>
+        <v>13.1821727752686</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606714248657</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135385513306</v>
+        <v>13.3135404586792</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.469428062439</v>
+        <v>13.4694290161133</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277135848999</v>
+        <v>13.2277145385742</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555765151978</v>
+        <v>13.3555755615234</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348819732666</v>
+        <v>13.1348829269409</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823354721069</v>
+        <v>13.0823335647583</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987457275391</v>
+        <v>12.6987447738647</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484344482422</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309202194214</v>
+        <v>12.3309192657471</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673789978027</v>
+        <v>12.5673799514771</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393533706665</v>
+        <v>12.5393543243408</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094150543213</v>
+        <v>12.6094160079956</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484344482422</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.409740447998</v>
+        <v>12.4097394943237</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="n">
-        <v>13.1366319656372</v>
+        <v>13.1366329193115</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909313201904</v>
+        <v>13.1909322738647</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132179260254</v>
+        <v>13.5132169723511</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.686619758606</v>
+        <v>13.6866207122803</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>13.2679996490479</v>
+        <v>13.2679977416992</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493541717529</v>
+        <v>13.9493532180786</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G183" t="n">
-        <v>13.7847061157227</v>
+        <v>13.784707069397</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971292495728</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920362472534</v>
+        <v>13.5920372009277</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1366319656372</v>
+        <v>13.1366329193115</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767581939697</v>
+        <v>13.2767572402954</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531513214111</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531513214111</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.4678134918213</v>
+        <v>14.467812538147</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955127716064</v>
+        <v>14.6955156326294</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G217" t="n">
-        <v>14.1175022125244</v>
+        <v>14.1175031661987</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>13.9248304367065</v>
+        <v>13.9248313903809</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G232" t="n">
-        <v>13.7847061157227</v>
+        <v>13.784707069397</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869422912598</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.5745191574097</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971292495728</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197374343872</v>
+        <v>13.8197383880615</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773769378662</v>
+        <v>13.9773778915405</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.2576274871826</v>
+        <v>14.2576265335083</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G274" t="n">
-        <v>14.3977518081665</v>
+        <v>14.3977499008179</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401103973389</v>
+        <v>14.2401113510132</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.2576274871826</v>
+        <v>14.2576265335083</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729055404663</v>
+        <v>14.572904586792</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034635543823</v>
+        <v>15.2034645080566</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311656951904</v>
+        <v>15.4311637878418</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114143371582</v>
+        <v>15.7114133834839</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989921569824</v>
+        <v>15.7989931106567</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888042449951</v>
+        <v>15.5888023376465</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814750671387</v>
+        <v>15.78147315979</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317863464355</v>
+        <v>16.1317844390869</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397380828857</v>
+        <v>16.6397361755371</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>16.4295501708984</v>
+        <v>16.4295482635498</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973728179932</v>
+        <v>16.7973747253418</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024658203125</v>
+        <v>16.9024696350098</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403568267822</v>
+        <v>17.3403549194336</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5593013763428</v>
+        <v>17.5592994689941</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220310211182</v>
+        <v>17.8220329284668</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906642913818</v>
+        <v>17.6906661987305</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228397369385</v>
+        <v>17.3228416442871</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.7273120880127</v>
+        <v>16.72731590271</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.172342300415</v>
+        <v>18.1723442077637</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853832244873</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21.5</v>
       </c>
       <c r="G311" t="n">
-        <v>18.8291759490967</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356945037842</v>
+        <v>19.1356964111328</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.5</v>
       </c>
       <c r="G314" t="n">
-        <v>18.8291759490967</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21.5</v>
       </c>
       <c r="G317" t="n">
-        <v>18.8291759490967</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853832244873</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="n">
-        <v>19.2670631408691</v>
+        <v>19.2670612335205</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173725128174</v>
+        <v>19.6173706054688</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925281524658</v>
+        <v>19.7925262451172</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794834136963</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611633300781</v>
+        <v>19.6611614227295</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232704162598</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232704162598</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853832244873</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.5</v>
       </c>
       <c r="G336" t="n">
-        <v>18.8291759490967</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794834136963</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>18.9605388641357</v>
+        <v>18.9605407714844</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912887573242</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912887573242</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799457550049</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797546386719</v>
+        <v>19.2797565460205</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.212646484375</v>
+        <v>20.2126445770264</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>23</v>
       </c>
       <c r="G351" t="n">
-        <v>20.4347648620605</v>
+        <v>20.4347629547119</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793762207031</v>
+        <v>20.0793743133545</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345737457275</v>
+        <v>20.8345756530762</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684135437012</v>
+        <v>19.7684116363525</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.8355197906494</v>
+        <v>18.835521697998</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.746675491333</v>
+        <v>18.7466735839844</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>19.4574489593506</v>
+        <v>19.457447052002</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5236110687256</v>
+        <v>20.5236129760742</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455383300781</v>
+        <v>21.1455364227295</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>23.2334384918213</v>
+        <v>23.2334365844727</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890125274658</v>
+        <v>23.1890144348145</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.144588470459</v>
+        <v>23.1445903778076</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.8336277008057</v>
+        <v>22.833625793457</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011123657227</v>
+        <v>21.1011161804199</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566921234131</v>
+        <v>21.0566940307617</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901515960693</v>
+        <v>20.7901496887207</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.8789978027344</v>
+        <v>20.878999710083</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.5</v>
       </c>
       <c r="G398" t="n">
-        <v>21.767463684082</v>
+        <v>21.7674655914307</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>21.4120769500732</v>
+        <v>21.4120788574219</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.5</v>
       </c>
       <c r="G411" t="n">
-        <v>21.767463684082</v>
+        <v>21.7674655914307</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561206817627</v>
+        <v>22.2561225891113</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5226650238037</v>
+        <v>22.5226631164551</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113220214844</v>
+        <v>23.0113201141357</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551746368408</v>
+        <v>24.2551765441895</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663303375244</v>
+        <v>24.1663284301758</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5443992614746</v>
+        <v>23.5444011688232</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772930145264</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>24.1219062805176</v>
+        <v>24.1219043731689</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774803161621</v>
+        <v>24.0774822235107</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215259552002</v>
+        <v>24.9215278625488</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>27.5</v>
       </c>
       <c r="G432" t="n">
-        <v>24.4328670501709</v>
+        <v>24.4328708648682</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326797485352</v>
+        <v>24.8326816558838</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324905395508</v>
+        <v>25.2324886322021</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205799102783</v>
+        <v>26.9205760955811</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536628723145</v>
+        <v>27.4536590576172</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425033569336</v>
+        <v>27.5425090789795</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300270080566</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967548370361</v>
+        <v>30.2967529296875</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636795043945</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417484283447</v>
+        <v>29.1417503356934</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527149200439</v>
+        <v>29.4527168273926</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748294830322</v>
+        <v>29.6748332977295</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300270080566</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744529724121</v>
+        <v>30.4744510650635</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>28.1200103759766</v>
+        <v>28.1200122833252</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646217346191</v>
+        <v>27.764627456665</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.164436340332</v>
+        <v>28.1644344329834</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525218963623</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409915924072</v>
+        <v>30.74098777771</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>37</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8733177185059</v>
+        <v>32.8733139038086</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402290344238</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.717357635498</v>
+        <v>33.7173614501953</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617874145508</v>
+        <v>33.7617835998535</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398544311523</v>
+        <v>33.1398582458496</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065879821777</v>
+        <v>33.0065841674805</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288955688477</v>
+        <v>32.8288879394531</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844734191895</v>
+        <v>32.7844657897949</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404277801514</v>
+        <v>31.9404220581055</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402290344238</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>37</v>
       </c>
       <c r="G508" t="n">
-        <v>32.8733177185059</v>
+        <v>32.8733139038086</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177322387695</v>
+        <v>32.9177360534668</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071517944336</v>
+        <v>31.8071537017822</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.4734992980957</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.4734992980957</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402290344238</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288955688477</v>
+        <v>32.8288879394531</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290809631348</v>
+        <v>32.4290771484375</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729354858398</v>
+        <v>33.6729393005371</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283241271973</v>
+        <v>34.0283279418945</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8959999084473</v>
+        <v>31.8960037231445</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840873718262</v>
+        <v>33.5840911865234</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727462768555</v>
+        <v>34.0727424621582</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290809631348</v>
+        <v>32.4290771484375</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279418945312</v>
+        <v>34.8279457092285</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275672912598</v>
+        <v>35.6275634765625</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721748352051</v>
+        <v>35.2721786499023</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>36.7381477355957</v>
+        <v>36.738151550293</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>34.3837089538574</v>
+        <v>34.3837127685547</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>34.9612159729004</v>
+        <v>34.9612121582031</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655715942383</v>
+        <v>25.7655696868896</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873096466064</v>
+        <v>26.7873058319092</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190662384033</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525218963623</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184967041016</v>
+        <v>31.3184928894043</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519580841064</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623588562012</v>
+        <v>32.5623512268066</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298358917236</v>
+        <v>30.8298397064209</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186820983887</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744529724121</v>
+        <v>30.4744510650635</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521453857422</v>
+        <v>30.6521434783936</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636795043945</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521453857422</v>
+        <v>30.6521434783936</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186820983887</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519580841064</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.964054107666</v>
+        <v>28.9640560150146</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859832763672</v>
+        <v>29.5859851837158</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828468322754</v>
+        <v>32.3828506469727</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>32.9255790710449</v>
+        <v>32.9255828857422</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9758033752441</v>
+        <v>31.9757995605469</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.890344619751</v>
+        <v>30.8903427124023</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094345092773</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617069244385</v>
+        <v>31.1617126464844</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.890344619751</v>
+        <v>30.8903427124023</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189785003662</v>
+        <v>30.6189765930176</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G630" t="n">
-        <v>31.1164798736572</v>
+        <v>31.1164817810059</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426189422607</v>
+        <v>31.3426208496094</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G650" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339683532715</v>
+        <v>27.6339664459229</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>28.0862426757812</v>
+        <v>28.0862407684326</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>29.6692008972168</v>
+        <v>29.6692028045654</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787467956543</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214771270752</v>
+        <v>30.1214790344238</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>30.6642055511475</v>
+        <v>30.6642093658447</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355697631836</v>
+        <v>30.9355735778809</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023891448975</v>
+        <v>30.3023872375488</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832954406738</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787467956543</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048858642578</v>
+        <v>29.8048839569092</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>32.25</v>
       </c>
       <c r="G683" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G685" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123798370361</v>
+        <v>28.3123779296875</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505615234375</v>
+        <v>27.9505596160889</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567077636719</v>
+        <v>32.1567115783691</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>28.0862426757812</v>
+        <v>28.0862407684326</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G706" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G708" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957885742188</v>
+        <v>27.9957866668701</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314697265625</v>
+        <v>28.1314678192139</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>32.25</v>
       </c>
       <c r="G714" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048858642578</v>
+        <v>29.8048839569092</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430637359619</v>
+        <v>29.4430656433105</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G728" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401203155518</v>
+        <v>31.8401184082031</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210304260254</v>
+        <v>32.0210342407227</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998886108398</v>
+        <v>30.7998867034912</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832954406738</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094345092773</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235290527344</v>
+        <v>31.5235271453857</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>31.1164798736572</v>
+        <v>31.1164817810059</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>35</v>
       </c>
       <c r="G758" t="n">
-        <v>31.6592102050781</v>
+        <v>31.6592082977295</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G763" t="n">
-        <v>32.2019386291504</v>
+        <v>32.2019348144531</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.885347366333</v>
+        <v>31.8853454589844</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G766" t="n">
-        <v>32.2019386291504</v>
+        <v>32.2019348144531</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521629333496</v>
+        <v>31.2521648406982</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>32.5185356140137</v>
+        <v>32.5185317993164</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064834594727</v>
+        <v>33.1064872741699</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.875358581543</v>
+        <v>33.8753547668457</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.875358581543</v>
+        <v>33.8753547668457</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442222595215</v>
+        <v>34.6442184448242</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608154296875</v>
+        <v>34.9608116149902</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035400390625</v>
+        <v>35.5035438537598</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558143615723</v>
+        <v>35.9558181762695</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392211914062</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674102783203</v>
+        <v>37.2674140930176</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.408088684082</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.227180480957</v>
+        <v>36.2271766662598</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.543773651123</v>
+        <v>36.5437774658203</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3628616333008</v>
+        <v>36.362865447998</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.7246856689453</v>
+        <v>36.724681854248</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.9055938720703</v>
+        <v>36.905590057373</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>41.25</v>
       </c>
       <c r="G819" t="n">
-        <v>37.3126411437988</v>
+        <v>37.3126373291016</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433288574219</v>
+        <v>38.4433250427246</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312881469727</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3981056213379</v>
+        <v>38.3980979919434</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8956031799316</v>
+        <v>38.8955993652344</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>39.6192398071289</v>
+        <v>39.6192436218262</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>43.5499992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>39.3931007385254</v>
+        <v>39.3931045532227</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860534667969</v>
+        <v>38.9860496520996</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312881469727</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910545349121</v>
+        <v>37.9910507202148</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649154663086</v>
+        <v>37.7649116516113</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.1819534301758</v>
+        <v>36.181957244873</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392211914062</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.1819534301758</v>
+        <v>36.181957244873</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.408088684082</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.1819534301758</v>
+        <v>36.181957244873</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.910587310791</v>
+        <v>35.9105911254883</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387802124023</v>
+        <v>37.5387763977051</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.7246856689453</v>
+        <v>36.724681854248</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>37.6292304992676</v>
+        <v>37.6292343139648</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>36.3628616333008</v>
+        <v>36.362865447998</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.408088684082</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>40</v>
       </c>
       <c r="G866" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>36.7331352233887</v>
+        <v>36.7331314086914</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354751586914</v>
+        <v>36.1354675292969</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.6183395385742</v>
+        <v>34.618335723877</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.2159957885742</v>
+        <v>35.215991973877</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.5723571777344</v>
+        <v>34.5723609924316</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.5263862609863</v>
+        <v>34.5263824462891</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>34.5263862609863</v>
+        <v>34.5263824462891</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G906" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>34.112621307373</v>
+        <v>34.1126174926758</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>35</v>
       </c>
       <c r="G921" t="n">
-        <v>32.1817207336426</v>
+        <v>32.1817169189453</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>35</v>
       </c>
       <c r="G926" t="n">
-        <v>32.1817207336426</v>
+        <v>32.1817169189453</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575614929199</v>
+        <v>32.4575653076172</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424873352051</v>
+        <v>34.3424911499023</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>37.5</v>
       </c>
       <c r="G934" t="n">
-        <v>34.480411529541</v>
+        <v>34.4804153442383</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>35.2619705200195</v>
+        <v>35.2619667053223</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965202331543</v>
+        <v>34.2965126037598</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>34.112621307373</v>
+        <v>34.1126174926758</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>32.5954856872559</v>
+        <v>32.5954818725586</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380802154541</v>
+        <v>31.5380840301514</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G972" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>32.5954856872559</v>
+        <v>32.5954818725586</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6069068908691</v>
+        <v>33.6069107055664</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9173049926758</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9173049926758</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347095489502</v>
+        <v>30.4347114562988</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541870117188</v>
+        <v>31.3541851043701</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783424377441</v>
+        <v>31.0783462524414</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1017" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>40.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>37.238842010498</v>
+        <v>37.2388458251953</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>37.6526107788086</v>
+        <v>37.6526145935059</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>39.2157249450684</v>
+        <v>39.2157211303711</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1029" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616958618164</v>
+        <v>39.2616996765137</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>38.2502708435059</v>
+        <v>38.2502746582031</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>38.2042922973633</v>
+        <v>38.2042961120605</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>39.2157249450684</v>
+        <v>39.2157211303711</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996200561523</v>
+        <v>39.3996162414551</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>44</v>
       </c>
       <c r="G1051" t="n">
-        <v>40.4570159912109</v>
+        <v>40.4570198059082</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>40.273120880127</v>
+        <v>40.2731246948242</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>40.6409111022949</v>
+        <v>40.6409149169922</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627265930176</v>
+        <v>40.9627304077148</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>41.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>37.9284553527832</v>
+        <v>37.9284515380859</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>40</v>
       </c>
       <c r="G1083" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422241210938</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1097" t="n">
-        <v>37.744556427002</v>
+        <v>37.7445602416992</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>40</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>38.2042922973633</v>
+        <v>38.2042961120605</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858589172363</v>
+        <v>38.9858551025391</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>44.4500007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>40.8707847595215</v>
+        <v>40.8707809448242</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616958618164</v>
+        <v>39.2616996765137</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422241210938</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727020263672</v>
+        <v>39.4727058410645</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900787353516</v>
+        <v>39.1900825500488</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082214355469</v>
+        <v>39.7082176208496</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842864990234</v>
+        <v>39.2842903137207</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379409790039</v>
+        <v>40.0379447937012</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452499389648</v>
+        <v>41.5452537536621</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437408447266</v>
+        <v>39.9437370300293</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132553100586</v>
+        <v>38.8132514953613</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522880554199</v>
+        <v>36.5522842407227</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993919372559</v>
+        <v>36.5993881225586</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376625061035</v>
+        <v>33.5376663208008</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202857971191</v>
+        <v>33.8202896118164</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275947570801</v>
+        <v>35.3275985717773</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238048553467</v>
+        <v>31.3238010406494</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890419006348</v>
+        <v>31.8890399932861</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419380187988</v>
+        <v>31.8419399261475</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804908752441</v>
+        <v>35.2804946899414</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391830444336</v>
+        <v>35.1391792297363</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558052062988</v>
+        <v>34.0558013916016</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160102844238</v>
+        <v>35.5160140991211</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.023323059082</v>
+        <v>37.0233192443848</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739440917969</v>
+        <v>34.5739402770996</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955963134766</v>
+        <v>32.5955924987793</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099376678467</v>
+        <v>29.1099395751953</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164901733398</v>
+        <v>29.8164920806885</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643524169922</v>
+        <v>30.6643543243408</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832515716553</v>
+        <v>31.9832496643066</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.349250793457</v>
+        <v>33.3492546081543</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041473388672</v>
+        <v>29.2041454315186</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207656860352</v>
+        <v>28.1207675933838</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844917297363</v>
+        <v>27.0844898223877</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902820587158</v>
+        <v>26.9902839660645</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779392242432</v>
+        <v>26.3779373168945</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829730987549</v>
+        <v>25.4829711914062</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011100769043</v>
+        <v>26.0011119842529</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.3887672424316</v>
+        <v>25.388765335083</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003536224365</v>
+        <v>25.2003517150879</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.189525604248</v>
+        <v>26.1895236968994</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076625823975</v>
+        <v>26.7076644897461</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.696834564209</v>
+        <v>27.6968364715576</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -45300,6 +45300,32 @@
         <v>36.5400009155273</v>
       </c>
       <c r="H1728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>27486</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>37.2400016784668</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>36.439998626709</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>36.5400009155273</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G1729" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="H1729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -40201,8 +40201,31 @@
       <c r="E1732" t="n">
         <v>36</v>
       </c>
-      <c r="F1732"/>
+      <c r="F1732" t="n">
+        <v>35.7000007629395</v>
+      </c>
       <c r="G1732" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1733" t="n">
+        <v>28577</v>
+      </c>
+      <c r="C1733" t="n">
+        <v>36.6399993896484</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>35.6800003051758</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>35.7200012207031</v>
+      </c>
+      <c r="F1733"/>
+      <c r="G1733" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -40224,8 +40224,31 @@
       <c r="E1733" t="n">
         <v>35.7200012207031</v>
       </c>
-      <c r="F1733"/>
+      <c r="F1733" t="n">
+        <v>36.0999984741211</v>
+      </c>
       <c r="G1733" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>18271</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>36.1599998474121</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>35.6399993896484</v>
+      </c>
+      <c r="F1734"/>
+      <c r="G1734" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -40247,8 +40247,31 @@
       <c r="E1734" t="n">
         <v>35.6399993896484</v>
       </c>
-      <c r="F1734"/>
+      <c r="F1734" t="n">
+        <v>35.5400009155273</v>
+      </c>
       <c r="G1734" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1735" t="n">
+        <v>24999</v>
+      </c>
+      <c r="C1735" t="n">
+        <v>35.5400009155273</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>34.9000015258789</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>35.5400009155273</v>
+      </c>
+      <c r="F1735"/>
+      <c r="G1735" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -40270,8 +40270,31 @@
       <c r="E1735" t="n">
         <v>35.5400009155273</v>
       </c>
-      <c r="F1735"/>
+      <c r="F1735" t="n">
+        <v>35.0200004577637</v>
+      </c>
       <c r="G1735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1736" t="n">
+        <v>27495</v>
+      </c>
+      <c r="C1736" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="D1736" t="n">
+        <v>34.8800010681152</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>34.9799995422363</v>
+      </c>
+      <c r="F1736"/>
+      <c r="G1736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -40300,6 +40300,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1737" t="n">
+        <v>23083</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>35.1399993896484</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>34.7000007629395</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>34.7200012207031</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>34.9000015258789</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818511962891</v>
+        <v>13.3818502426147</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479248046875</v>
+        <v>13.7479238510132</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.0018997192383</v>
+        <v>14.001898765564</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934637069702</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390045166016</v>
+        <v>13.8390054702759</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370908737183</v>
+        <v>13.9370927810669</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915529251099</v>
+        <v>13.8915519714355</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073152542114</v>
+        <v>13.9073143005371</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G18" t="n">
-        <v>13.942346572876</v>
+        <v>13.9423475265503</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963205337524</v>
+        <v>14.1963214874268</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130279541016</v>
+        <v>14.7130270004272</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692380905151</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916873931885</v>
+        <v>14.8916864395142</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730644226074</v>
+        <v>14.4730653762817</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378751754761</v>
+        <v>14.5378761291504</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.644718170166</v>
+        <v>14.6447191238403</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905815124512</v>
+        <v>14.4905824661255</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557119369507</v>
+        <v>14.3557138442993</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628803253174</v>
+        <v>14.2628793716431</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006057739258</v>
+        <v>14.8006067276001</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692380905151</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6236991882324</v>
+        <v>14.6237001419067</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708292007446</v>
+        <v>14.770827293396</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633392333984</v>
+        <v>15.0633411407471</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.2698879241943</v>
+        <v>14.26988697052</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.44153881073</v>
+        <v>14.4415397644043</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320241928101</v>
+        <v>12.7320251464844</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868625640869</v>
+        <v>9.80868530273438</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837593078613</v>
+        <v>9.45837688446045</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651382446289</v>
+        <v>8.76651287078857</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415237426758</v>
+        <v>8.92415142059326</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500961303711</v>
+        <v>9.04501056671143</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921142578125</v>
+        <v>10.2921133041382</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>11.2887487411499</v>
+        <v>11.2887477874756</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748952865601</v>
+        <v>11.1748971939087</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878046035767</v>
+        <v>10.7878036499023</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353916168213</v>
+        <v>11.7353925704956</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898527145386</v>
+        <v>11.6898508071899</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229694366455</v>
+        <v>11.8229684829712</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325357437134</v>
+        <v>11.3325366973877</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655179977417</v>
+        <v>10.4655170440674</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078784942627</v>
+        <v>10.3078775405884</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075559616089</v>
+        <v>10.5075550079346</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008718490601</v>
+        <v>10.3008728027344</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.381443977356</v>
+        <v>10.3814430236816</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093059539795</v>
+        <v>10.5093050003052</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955907821655</v>
+        <v>11.3955917358398</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726600646973</v>
+        <v>11.4726591110229</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565732955933</v>
+        <v>11.6565723419189</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667593002319</v>
+        <v>11.8667583465576</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119766235352</v>
+        <v>12.1119756698608</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506715774536</v>
+        <v>12.0506706237793</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922243118286</v>
+        <v>12.3922233581543</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205715179443</v>
+        <v>12.2205724716187</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>14.2959995269775</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5200872421265</v>
+        <v>12.5200862884521</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.3100357055664</v>
+        <v>13.3100366592407</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901498794556</v>
+        <v>12.5901508331299</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119493484497</v>
+        <v>13.211950302124</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361476898193</v>
+        <v>13.4361486434937</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>13.3030309677124</v>
+        <v>13.3030300140381</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.527229309082</v>
+        <v>13.5272302627563</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>13.2679986953735</v>
+        <v>13.2680006027222</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681623458862</v>
+        <v>13.1681613922119</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501609802246</v>
+        <v>13.4501600265503</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979360580444</v>
+        <v>13.1979351043701</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490560531616</v>
+        <v>13.0490550994873</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504835128784</v>
+        <v>13.2504844665527</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821737289429</v>
+        <v>13.1821718215942</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.0019998550415</v>
       </c>
       <c r="G149" t="n">
-        <v>13.1383848190308</v>
+        <v>13.1383838653564</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.469428062439</v>
+        <v>13.4694290161133</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277135848999</v>
+        <v>13.2277145385742</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555765151978</v>
+        <v>13.3555755615234</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.430757522583</v>
+        <v>12.4307584762573</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.409740447998</v>
+        <v>12.4097394943237</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="n">
-        <v>13.1366319656372</v>
+        <v>13.1366329193115</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909322738647</v>
+        <v>13.1909313201904</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132179260254</v>
+        <v>13.5132160186768</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G174" t="n">
-        <v>13.6533403396606</v>
+        <v>13.653341293335</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>13.2679986953735</v>
+        <v>13.2680006027222</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445837020874</v>
+        <v>13.6445827484131</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1366319656372</v>
+        <v>13.1366329193115</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321605682373</v>
+        <v>13.7321615219116</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101711273193</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.7305431365967</v>
+        <v>14.730544090271</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G217" t="n">
-        <v>14.1175031661987</v>
+        <v>14.1175022125244</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>14.0474395751953</v>
+        <v>14.0474405288696</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117895126343</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592420578003</v>
+        <v>13.259241104126</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117895126343</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321605682373</v>
+        <v>13.7321615219116</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022232055664</v>
+        <v>13.8022222518921</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197383880615</v>
+        <v>13.8197393417358</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773778915405</v>
+        <v>13.9773788452148</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>14.0474395751953</v>
+        <v>14.0474405288696</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101711273193</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627195358276</v>
+        <v>14.362717628479</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576274871826</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079359054565</v>
+        <v>14.6079368591309</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401094436646</v>
+        <v>14.2401113510132</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276891708374</v>
+        <v>14.3276882171631</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576274871826</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729055404663</v>
+        <v>14.5729036331177</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034645080566</v>
+        <v>15.2034635543823</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311647415161</v>
+        <v>15.4311656951904</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114143371582</v>
+        <v>15.7114124298096</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989931106567</v>
+        <v>15.7989912033081</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888061523438</v>
+        <v>15.5888032913208</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165054321289</v>
+        <v>15.8165035247803</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.78147315979</v>
+        <v>15.7814769744873</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712890625</v>
+        <v>15.5712900161743</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317863464355</v>
+        <v>16.1317844390869</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024677276611</v>
+        <v>16.9024658203125</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753852844238</v>
+        <v>17.3753871917725</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220310211182</v>
+        <v>17.8220348358154</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906661987305</v>
+        <v>17.6906681060791</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.2527770996094</v>
+        <v>17.252779006958</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.5155124664307</v>
+        <v>17.515510559082</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228435516357</v>
+        <v>17.3228416442871</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0919036865234</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21.5</v>
       </c>
       <c r="G311" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415962219238</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.5</v>
       </c>
       <c r="G314" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0919036865234</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21.5</v>
       </c>
       <c r="G317" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173725128174</v>
+        <v>19.6173706054688</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794815063477</v>
+        <v>19.1794853210449</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7487411499023</v>
+        <v>19.7487392425537</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611614227295</v>
+        <v>19.6611633300781</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729629516602</v>
+        <v>18.8729610443115</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167537689209</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>19.0919036865234</v>
+        <v>19.0919055938721</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.5</v>
       </c>
       <c r="G336" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415962219238</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167537689209</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794815063477</v>
+        <v>19.1794853210449</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>18.960542678833</v>
+        <v>18.9605407714844</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912868499756</v>
+        <v>18.3912887573242</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912868499756</v>
+        <v>18.3912887573242</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799419403076</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797565460205</v>
+        <v>19.2797546386719</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.2126445770264</v>
+        <v>20.212646484375</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572597503662</v>
+        <v>19.8572616577148</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345737457275</v>
+        <v>20.8345756530762</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.835521697998</v>
+        <v>18.8355236053467</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.7466716766357</v>
+        <v>18.746675491333</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910976409912</v>
+        <v>18.7910957336426</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>19.6351432800293</v>
+        <v>19.6351413726807</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>19.4574489593506</v>
+        <v>19.457447052002</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455383300781</v>
+        <v>21.1455364227295</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G370" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890144348145</v>
+        <v>23.1890163421631</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.1445922851562</v>
+        <v>23.1445903778076</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.833625793457</v>
+        <v>22.8336277008057</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563117980957</v>
+        <v>21.8563137054443</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>24.25</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5453472137451</v>
+        <v>21.5453510284424</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5897693634033</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011142730713</v>
+        <v>21.1011161804199</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>20.7013034820557</v>
+        <v>20.701301574707</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>20.7013034820557</v>
+        <v>20.701301574707</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901496887207</v>
+        <v>20.7901477813721</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680313110352</v>
+        <v>20.5680351257324</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.5897693634033</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.25</v>
       </c>
       <c r="G403" t="n">
-        <v>21.5453472137451</v>
+        <v>21.5453510284424</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>21.4120788574219</v>
+        <v>21.4120769500732</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G405" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>21.6341934204102</v>
+        <v>21.6341953277588</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115074157715</v>
+        <v>22.6115093231201</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3893947601318</v>
+        <v>22.3893928527832</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>22.3893947601318</v>
+        <v>22.3893928527832</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224720001221</v>
+        <v>22.9224739074707</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113220214844</v>
+        <v>23.0113201141357</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663284301758</v>
+        <v>24.1663303375244</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444011688232</v>
+        <v>23.5444030761719</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772930145264</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774803161621</v>
+        <v>24.0774822235107</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215259552002</v>
+        <v>24.9215278625488</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661373138428</v>
+        <v>24.5661392211914</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326797485352</v>
+        <v>24.8326816558838</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103740692139</v>
+        <v>25.0103721618652</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207691192627</v>
+        <v>26.5207710266113</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205780029297</v>
+        <v>26.9205799102783</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.430025100708</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967567443848</v>
+        <v>30.2967548370361</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.696569442749</v>
+        <v>30.6965656280518</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417503356934</v>
+        <v>29.1417484283447</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748332977295</v>
+        <v>29.6748294830322</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.430025100708</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>28.1200103759766</v>
+        <v>28.1200122833252</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646255493164</v>
+        <v>27.7646236419678</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423160552979</v>
+        <v>27.9423179626465</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.230598449707</v>
+        <v>29.2306003570557</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.1644344329834</v>
+        <v>28.164436340332</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525199890137</v>
+        <v>29.8525218963623</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.74098777771</v>
+        <v>30.7409896850586</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406093597412</v>
+        <v>31.5406131744385</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.762731552124</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629188537598</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402366638184</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513885498047</v>
+        <v>32.251392364502</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.7173614501953</v>
+        <v>33.717357635498</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>37.75</v>
       </c>
       <c r="G487" t="n">
-        <v>33.5396690368652</v>
+        <v>33.539665222168</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398582458496</v>
+        <v>33.1398544311523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065879821777</v>
+        <v>33.0065841674805</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288955688477</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404296875</v>
+        <v>31.9404220581055</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402366638184</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852245330811</v>
+        <v>31.1852226257324</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852245330811</v>
+        <v>31.1852226257324</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177360534668</v>
+        <v>32.9177398681641</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.762731552124</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.4735069274902</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.4735069274902</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402328491211</v>
+        <v>32.3402366638184</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288955688477</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290809631348</v>
+        <v>32.429084777832</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.3175506591797</v>
+        <v>33.3175468444824</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842765808105</v>
+        <v>33.1842727661133</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>34.4725570678711</v>
+        <v>34.4725608825684</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>40.5</v>
       </c>
       <c r="G537" t="n">
-        <v>35.9829483032227</v>
+        <v>35.9829521179199</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290809631348</v>
+        <v>32.429084777832</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281311035156</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279495239258</v>
+        <v>34.8279457092285</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281311035156</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275672912598</v>
+        <v>35.6275634765625</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281311035156</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.405445098877</v>
+        <v>35.4054489135742</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714218139648</v>
+        <v>36.8714179992676</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>39.3499984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>34.9612159729004</v>
+        <v>34.9612121582031</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530914306641</v>
+        <v>28.6530933380127</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655715942383</v>
+        <v>25.7655696868896</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.788257598877</v>
+        <v>24.7882556915283</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.3430728912354</v>
+        <v>26.343074798584</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873077392578</v>
+        <v>26.7873096466064</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.230598449707</v>
+        <v>29.2306003570557</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190624237061</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525199890137</v>
+        <v>29.8525218963623</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184986114502</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623512268066</v>
+        <v>32.5623550415039</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408004760742</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186840057373</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281311035156</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513885498047</v>
+        <v>32.251392364502</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186840057373</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740726470947</v>
+        <v>31.2740707397461</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629188537598</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294612884521</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408004760742</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859851837158</v>
+        <v>29.5859832763672</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405632019043</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596607208252</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828544616699</v>
+        <v>32.3828506469727</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>32.9255790710449</v>
+        <v>32.9255828857422</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9757995605469</v>
+        <v>31.9758033752441</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>30.1667022705078</v>
+        <v>30.1667041778564</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898979187012</v>
+        <v>32.7898941040039</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189746856689</v>
+        <v>30.6189785003662</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426208496094</v>
+        <v>31.3426170349121</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260219573975</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.1667022705078</v>
+        <v>30.1667041778564</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646560668945</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601055145264</v>
+        <v>27.8601036071777</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646560668945</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>29.6692028045654</v>
+        <v>29.6692008972168</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978404998779</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405632019043</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260219573975</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355735778809</v>
+        <v>30.9355697631836</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G679" t="n">
-        <v>29.7144298553467</v>
+        <v>29.714427947998</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978404998779</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596607208252</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123798370361</v>
+        <v>28.3123779296875</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646560668945</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G696" t="n">
-        <v>28.40283203125</v>
+        <v>28.4028339385986</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>28.357608795166</v>
+        <v>28.3576068878174</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762500762939</v>
+        <v>30.0762481689453</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567077636719</v>
+        <v>32.1567115783691</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G702" t="n">
-        <v>29.7144298553467</v>
+        <v>29.714427947998</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119293212891</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978404998779</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646560668945</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596607208252</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405632019043</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401222229004</v>
+        <v>31.8401184082031</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119293212891</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>30.1667022705078</v>
+        <v>30.1667041778564</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G763" t="n">
-        <v>32.2019386291504</v>
+        <v>32.2019348144531</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G766" t="n">
-        <v>32.2019386291504</v>
+        <v>32.2019348144531</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969451904297</v>
+        <v>33.1969413757324</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803443908691</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521629333496</v>
+        <v>31.2521591186523</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803443908691</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442222595215</v>
+        <v>34.6442184448242</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674140930176</v>
+        <v>37.2674102783203</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.2271766662598</v>
+        <v>36.227180480957</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.091495513916</v>
+        <v>36.0914993286133</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.091495513916</v>
+        <v>36.0914993286133</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.543773651123</v>
+        <v>36.5437774658203</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8955993652344</v>
+        <v>38.8956031799316</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9005928039551</v>
+        <v>37.9005966186523</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>38.4885520935059</v>
+        <v>38.4885559082031</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342239379883</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342239379883</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952110290527</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952110290527</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.6183395385742</v>
+        <v>34.618335723877</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.2159957885742</v>
+        <v>35.215991973877</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.5723571777344</v>
+        <v>34.5723609924316</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G903" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>35.5837898254395</v>
+        <v>35.5837860107422</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850914001465</v>
+        <v>33.2850952148438</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471710205078</v>
+        <v>33.1471672058105</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>32.089771270752</v>
+        <v>32.0897750854492</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>31.9978218078613</v>
+        <v>31.9978256225586</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575614929199</v>
+        <v>32.4575576782227</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965202331543</v>
+        <v>34.296516418457</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448310852051</v>
+        <v>33.7448272705078</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.503532409668</v>
+        <v>32.5035362243652</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380802154541</v>
+        <v>31.5380840301514</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9173049926758</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9173049926758</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347095489502</v>
+        <v>30.4347076416016</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G992" t="n">
-        <v>30.8944492340088</v>
+        <v>30.8944473266602</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861221313477</v>
+        <v>34.9861259460449</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952110290527</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>40.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>37.238842010498</v>
+        <v>37.2388458251953</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1029" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>39.353645324707</v>
+        <v>39.3536415100098</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>38.8939056396484</v>
+        <v>38.8939018249512</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>39.7674102783203</v>
+        <v>39.767406463623</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650741577148</v>
+        <v>40.3650703430176</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>39.169750213623</v>
+        <v>39.1697463989258</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>38.8939056396484</v>
+        <v>38.8939018249512</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>40.4110412597656</v>
+        <v>40.4110450744629</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>43.25</v>
       </c>
       <c r="G1062" t="n">
-        <v>39.7674102783203</v>
+        <v>39.767406463623</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442893981934</v>
+        <v>41.7442855834961</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100067138672</v>
+        <v>38.7100105285645</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009254455566</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824806213379</v>
+        <v>37.8824768066406</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952110290527</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858589172363</v>
+        <v>38.9858551025391</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -45586,6 +45586,32 @@
         <v>35.5400009155273</v>
       </c>
       <c r="H1739" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1740" t="n">
+        <v>25502</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>35.7799987792969</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>35.0999984741211</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>35.2200012207031</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>35.439998626709</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>35.439998626709</v>
+      </c>
+      <c r="H1740" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025447845459</v>
+        <v>13.6025438308716</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.416880607605</v>
+        <v>13.4168815612793</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818502426147</v>
+        <v>13.3818492889404</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479238510132</v>
+        <v>13.7479248046875</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810434341431</v>
+        <v>13.8810424804688</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934637069702</v>
+        <v>13.7934646606445</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9248313903809</v>
+        <v>13.9248304367065</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390054702759</v>
+        <v>13.8390064239502</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370927810669</v>
+        <v>13.9370899200439</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598617553711</v>
+        <v>13.9598627090454</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915519714355</v>
+        <v>13.8915529251099</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073143005371</v>
+        <v>13.9073162078857</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948921203613</v>
+        <v>13.9948930740356</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963214874268</v>
+        <v>14.1963195800781</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130270004272</v>
+        <v>14.7130279541016</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692399978638</v>
+        <v>14.6692390441895</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071271896362</v>
+        <v>15.1071262359619</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260717391968</v>
+        <v>15.3260726928711</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881855010986</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463083267212</v>
+        <v>14.7463073730469</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916864395142</v>
+        <v>14.8916883468628</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757623672485</v>
+        <v>14.9757633209229</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730653762817</v>
+        <v>14.4730663299561</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G31" t="n">
-        <v>14.5203580856323</v>
+        <v>14.5203590393066</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881855010986</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881855010986</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378761291504</v>
+        <v>14.5378751754761</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905824661255</v>
+        <v>14.4905815124512</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557138442993</v>
+        <v>14.3557119369507</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628793716431</v>
+        <v>14.2628803253174</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.362717628479</v>
+        <v>14.362720489502</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609666824341</v>
+        <v>14.3609685897827</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006067276001</v>
+        <v>14.8006086349487</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692399978638</v>
+        <v>14.6692390441895</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237001419067</v>
+        <v>14.6237010955811</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.770827293396</v>
+        <v>14.7708292007446</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633411407471</v>
+        <v>15.0633392333984</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369047164917</v>
+        <v>15.1369066238403</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.4415397644043</v>
+        <v>14.4415378570557</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111669540405</v>
+        <v>12.6111679077148</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781856536865</v>
+        <v>13.4781875610352</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320251464844</v>
+        <v>12.7320241928101</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602369308472</v>
+        <v>11.5602359771729</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0714178085327</v>
+        <v>10.0714197158813</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868530273438</v>
+        <v>9.80868625640869</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>9.63353061676025</v>
+        <v>9.63352966308594</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837688446045</v>
+        <v>9.45837497711182</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806560516357</v>
+        <v>9.10806465148926</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96618938446045</v>
+        <v>8.96619033813477</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58259963989258</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651287078857</v>
+        <v>8.76651382446289</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58259963989258</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494285583496</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032096862793</v>
+        <v>8.69032192230225</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04501056671143</v>
+        <v>9.04500865936279</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921142578125</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968837738037</v>
+        <v>10.596884727478</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070697784424</v>
+        <v>10.807071685791</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156656265259</v>
+        <v>10.9156665802002</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>11.2887477874756</v>
+        <v>11.2887468338013</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748971939087</v>
+        <v>11.1748962402344</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878036499023</v>
+        <v>10.7878017425537</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.8079996109009</v>
       </c>
       <c r="G87" t="n">
-        <v>11.2169322967529</v>
+        <v>11.2169332504272</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898508071899</v>
+        <v>11.6898517608643</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068836212158</v>
+        <v>12.0068826675415</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229684829712</v>
+        <v>11.8229694366455</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331817626953</v>
+        <v>10.9331836700439</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143999099731</v>
+        <v>10.6143989562988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655170440674</v>
+        <v>10.4655179977417</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.3866968154907</v>
+        <v>10.3866987228394</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691825866699</v>
+        <v>10.3691816329956</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465724945068</v>
+        <v>10.2465734481812</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008728027344</v>
+        <v>10.3008718490601</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.3814430236816</v>
+        <v>10.381443977356</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093050003052</v>
+        <v>10.5093059539795</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>11.3412923812866</v>
+        <v>11.3412933349609</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220262527466</v>
+        <v>11.3220272064209</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726591110229</v>
+        <v>11.4726600646973</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667583465576</v>
+        <v>11.8667593002319</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506706237793</v>
+        <v>12.0506715774536</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258262634277</v>
+        <v>12.2258272171021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930067062378</v>
+        <v>12.9930057525635</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.7863235473633</v>
+        <v>12.7863245010376</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901508331299</v>
+        <v>12.5901498794556</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.5272302627563</v>
+        <v>13.527229309082</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681613922119</v>
+        <v>13.1681604385376</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606704711914</v>
+        <v>13.4606695175171</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501600265503</v>
+        <v>13.4501609802246</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979351043701</v>
+        <v>13.1979370117188</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928440093994</v>
+        <v>13.0928449630737</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490550994873</v>
+        <v>13.0490560531616</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504844665527</v>
+        <v>13.2504835128784</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821718215942</v>
+        <v>13.1821727752686</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.0019998550415</v>
       </c>
       <c r="G149" t="n">
-        <v>13.1383838653564</v>
+        <v>13.1383848190308</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606704711914</v>
+        <v>13.4606695175171</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324840545654</v>
+        <v>13.5324831008911</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135395050049</v>
+        <v>13.3135404586792</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.4694290161133</v>
+        <v>13.469428062439</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555755615234</v>
+        <v>13.3555765151978</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348819732666</v>
+        <v>13.1348810195923</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823354721069</v>
+        <v>13.0823335647583</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673789978027</v>
+        <v>12.5673799514771</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.4307584762573</v>
+        <v>12.430757522583</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097394943237</v>
+        <v>12.4097385406494</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="n">
-        <v>13.1366329193115</v>
+        <v>13.1366338729858</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132160186768</v>
+        <v>13.5132169723511</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493532180786</v>
+        <v>13.9493541717529</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445827484131</v>
+        <v>13.6445817947388</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971292495728</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920362472534</v>
+        <v>13.5920372009277</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G197" t="n">
-        <v>13.2942724227905</v>
+        <v>13.2942714691162</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1366329193115</v>
+        <v>13.1366338729858</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767562866211</v>
+        <v>13.2767572402954</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.3101711273193</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531503677368</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531503677368</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.467812538147</v>
+        <v>14.4678134918213</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.730544090271</v>
+        <v>14.7305450439453</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.362717628479</v>
+        <v>14.362720489502</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955156326294</v>
+        <v>14.6955127716064</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.362717628479</v>
+        <v>14.362720489502</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452024459839</v>
+        <v>14.3452014923096</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>14.0474405288696</v>
+        <v>14.0474414825439</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>13.9248313903809</v>
+        <v>13.9248304367065</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.3117895126343</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.259241104126</v>
+        <v>13.2592430114746</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.3117895126343</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219755172729</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219755172729</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219755172729</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971292495728</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197393417358</v>
+        <v>13.8197374343872</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773788452148</v>
+        <v>13.9773769378662</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>14.0474405288696</v>
+        <v>14.0474414825439</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.1525316238403</v>
+        <v>14.1525325775146</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.3101711273193</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.362717628479</v>
+        <v>14.362720489502</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.2576274871826</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028429031372</v>
+        <v>14.5028409957886</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028429031372</v>
+        <v>14.5028409957886</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079368591309</v>
+        <v>14.6079349517822</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401113510132</v>
+        <v>14.2401094436646</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.2576274871826</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729036331177</v>
+        <v>14.572904586792</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034635543823</v>
+        <v>15.2034645080566</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114124298096</v>
+        <v>15.7114152908325</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989912033081</v>
+        <v>15.7989902496338</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165035247803</v>
+        <v>15.8165054321289</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814769744873</v>
+        <v>15.7814750671387</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712900161743</v>
+        <v>15.5712919235229</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317844390869</v>
+        <v>16.1317863464355</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397361755371</v>
+        <v>16.6397342681885</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>16.4295482635498</v>
+        <v>16.4295520782471</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973766326904</v>
+        <v>16.7973747253418</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024658203125</v>
+        <v>16.9024677276611</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753871917725</v>
+        <v>17.3753852844238</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906681060791</v>
+        <v>17.6906642913818</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.252779006958</v>
+        <v>17.2527809143066</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468772888184</v>
+        <v>17.646879196167</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.7273139953613</v>
+        <v>16.7273120880127</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.172342300415</v>
+        <v>18.1723442077637</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108501434326</v>
+        <v>19.310848236084</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21.5</v>
       </c>
       <c r="G311" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356945037842</v>
+        <v>19.1356964111328</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.5</v>
       </c>
       <c r="G314" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21.5</v>
       </c>
       <c r="G317" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="n">
-        <v>19.2670612335205</v>
+        <v>19.2670593261719</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173706054688</v>
+        <v>19.6173725128174</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925281524658</v>
+        <v>19.7925262451172</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.2232723236084</v>
+        <v>19.2232761383057</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729610443115</v>
+        <v>18.8729629516602</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167537689209</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.2232723236084</v>
+        <v>19.2232761383057</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>21.5</v>
       </c>
       <c r="G336" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546390533447</v>
+        <v>19.3546371459961</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167537689209</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912887573242</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912887573242</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572616577148</v>
+        <v>19.8572597503662</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905281066895</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345756530762</v>
+        <v>20.8345737457275</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461078643799</v>
+        <v>19.9461059570312</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.8355236053467</v>
+        <v>18.835521697998</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.746675491333</v>
+        <v>18.7466735839844</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910957336426</v>
+        <v>18.7910976409912</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>19.6351413726807</v>
+        <v>19.6351432800293</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>19.457447052002</v>
+        <v>19.4574489593506</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5236110687256</v>
+        <v>20.523609161377</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905281066895</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455364227295</v>
+        <v>21.1455383300781</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890163421631</v>
+        <v>23.1890144348145</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.1445903778076</v>
+        <v>23.144588470459</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563137054443</v>
+        <v>21.8563117980957</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>24.25</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5453510284424</v>
+        <v>21.5453472137451</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.589771270752</v>
+        <v>21.5897693634033</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011161804199</v>
+        <v>21.1011142730713</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>20.701301574707</v>
+        <v>20.7013034820557</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>20.701301574707</v>
+        <v>20.7013034820557</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901477813721</v>
+        <v>20.7901496887207</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680351257324</v>
+        <v>20.5680313110352</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.589771270752</v>
+        <v>21.5897693634033</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.25</v>
       </c>
       <c r="G403" t="n">
-        <v>21.5453510284424</v>
+        <v>21.5453472137451</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459148406982</v>
+        <v>20.3459167480469</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3893928527832</v>
+        <v>22.3893947601318</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561206817627</v>
+        <v>22.2561225891113</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5226631164551</v>
+        <v>22.5226650238037</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>22.3893928527832</v>
+        <v>22.3893947601318</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224739074707</v>
+        <v>22.9224720001221</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113201141357</v>
+        <v>23.0113182067871</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551765441895</v>
+        <v>24.2551746368408</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663303375244</v>
+        <v>24.1663284301758</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>23.6332473754883</v>
+        <v>23.6332492828369</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215278625488</v>
+        <v>24.9215259552002</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438316345215</v>
+        <v>24.7438335418701</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324886322021</v>
+        <v>25.2324905395508</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103721618652</v>
+        <v>25.0103740692139</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207710266113</v>
+        <v>26.5207691192627</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536590576172</v>
+        <v>27.4536609649658</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975135803223</v>
+        <v>28.6975154876709</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300289154053</v>
+        <v>30.430025100708</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967548370361</v>
+        <v>30.2967529296875</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.6965656280518</v>
+        <v>30.6965675354004</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636775970459</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417484283447</v>
+        <v>29.1417503356934</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527149200439</v>
+        <v>29.4527187347412</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748294830322</v>
+        <v>29.6748332977295</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300289154053</v>
+        <v>30.430025100708</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744510650635</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>28.1200122833252</v>
+        <v>28.1200103759766</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.4753952026367</v>
+        <v>28.4753971099854</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867420196533</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867420196533</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.2306003570557</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525218963623</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409896850586</v>
+        <v>30.7409915924072</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406131744385</v>
+        <v>31.5406112670898</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627277374268</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G476" t="n">
-        <v>33.8506240844727</v>
+        <v>33.8506278991699</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.251392364502</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.717357635498</v>
+        <v>33.7173614501953</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>37.75</v>
       </c>
       <c r="G487" t="n">
-        <v>33.539665222168</v>
+        <v>33.5396614074707</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398544311523</v>
+        <v>33.1398506164551</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288955688477</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844657897949</v>
+        <v>32.7844696044922</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>33.806209564209</v>
+        <v>33.8062057495117</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>33.806209564209</v>
+        <v>33.8062057495117</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179290771484</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634883880615</v>
+        <v>30.1634864807129</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852226257324</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852226257324</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071537017822</v>
+        <v>31.8071556091309</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627277374268</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510101318359</v>
+        <v>33.0510063171387</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508209228516</v>
+        <v>33.4508171081543</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288955688477</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.429084777832</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.3175468444824</v>
+        <v>33.3175506591797</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283203125</v>
+        <v>34.0283279418945</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8959999084473</v>
+        <v>31.8960018157959</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179290771484</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840911865234</v>
+        <v>33.5840873718262</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842727661133</v>
+        <v>33.1842765808105</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G535" t="n">
-        <v>33.228702545166</v>
+        <v>33.2287063598633</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>34.4725608825684</v>
+        <v>34.4725570678711</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>31.4517669677734</v>
+        <v>31.4517650604248</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.429084777832</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281311035156</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281311035156</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281311035156</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>33.806209564209</v>
+        <v>33.8062057495117</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721748352051</v>
+        <v>35.2721786499023</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>36.738151550293</v>
+        <v>36.7381477355957</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714179992676</v>
+        <v>36.8714218139648</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>34.3837089538574</v>
+        <v>34.3837127685547</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530933380127</v>
+        <v>28.6530914306641</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655696868896</v>
+        <v>25.7655715942383</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882556915283</v>
+        <v>24.7882537841797</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873096466064</v>
+        <v>26.7873077392578</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.2306003570557</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525218963623</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519580841064</v>
+        <v>31.0519542694092</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623550415039</v>
+        <v>32.5623512268066</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408004760742</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281311035156</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>33.8506240844727</v>
+        <v>33.8506278991699</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>32.1181182861328</v>
+        <v>32.1181221008301</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.251392364502</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>31.4517669677734</v>
+        <v>31.4517650604248</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744510650635</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636775970459</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>35</v>
       </c>
       <c r="G597" t="n">
-        <v>31.0963802337646</v>
+        <v>31.096378326416</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519580841064</v>
+        <v>31.0519542694092</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740707397461</v>
+        <v>31.2740745544434</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408004760742</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.964054107666</v>
+        <v>28.9640560150146</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859832763672</v>
+        <v>29.5859851837158</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596607208252</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828506469727</v>
+        <v>32.3828468322754</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110359191895</v>
+        <v>34.0110321044922</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>32.9255828857422</v>
+        <v>32.9255790710449</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>30.1667041778564</v>
+        <v>30.1667022705078</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617088317871</v>
+        <v>31.1617069244385</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G630" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164798736572</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426170349121</v>
+        <v>31.3426189422607</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5737495422363</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260257720947</v>
+        <v>31.0260276794434</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.1667041778564</v>
+        <v>30.1667022705078</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766948699951</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646560668945</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766948699951</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>28.8551063537598</v>
+        <v>28.8551082611084</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>32</v>
       </c>
       <c r="G644" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601036071777</v>
+        <v>27.8601055145264</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646560668945</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>32</v>
       </c>
       <c r="G648" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>32</v>
       </c>
       <c r="G651" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339664459229</v>
+        <v>27.6339683532715</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787467956543</v>
+        <v>29.5787487030029</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214752197266</v>
+        <v>30.1214771270752</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978404998779</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260257720947</v>
+        <v>31.0260276794434</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023872375488</v>
+        <v>30.3023891448975</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832992553711</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787467956543</v>
+        <v>29.5787487030029</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978404998779</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048839569092</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596607208252</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>32</v>
       </c>
       <c r="G691" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123779296875</v>
+        <v>28.3123798370361</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505596160889</v>
+        <v>27.9505615234375</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646560668945</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762481689453</v>
+        <v>30.0762500762939</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567115783691</v>
+        <v>32.1567077636719</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957866668701</v>
+        <v>27.9957885742188</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314716339111</v>
+        <v>28.1314697265625</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048839569092</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119293212891</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>32</v>
       </c>
       <c r="G719" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978404998779</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430656433105</v>
+        <v>29.4430637359619</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646560668945</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596607208252</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>32</v>
       </c>
       <c r="G735" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401184082031</v>
+        <v>31.8401203155518</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119293212891</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>30.1667041778564</v>
+        <v>30.1667022705078</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832992553711</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.5737495422363</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235233306885</v>
+        <v>31.5235290527344</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164798736572</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>35</v>
       </c>
       <c r="G758" t="n">
-        <v>31.6592121124268</v>
+        <v>31.6592102050781</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>32.4733009338379</v>
+        <v>32.4733047485352</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G763" t="n">
-        <v>32.2019348144531</v>
+        <v>32.2019386291504</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853492736816</v>
+        <v>31.885347366333</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G766" t="n">
-        <v>32.2019348144531</v>
+        <v>32.2019386291504</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969413757324</v>
+        <v>33.1969451904297</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521591186523</v>
+        <v>31.2521629333496</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>32.5185317993164</v>
+        <v>32.5185356140137</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.920581817627</v>
+        <v>33.9205856323242</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064872741699</v>
+        <v>33.1064834594727</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919479370117</v>
+        <v>34.1919441223145</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.8753547668457</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919479370117</v>
+        <v>34.1919441223145</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110359191895</v>
+        <v>34.0110321044922</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.8753547668457</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442184448242</v>
+        <v>34.6442222595215</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608116149902</v>
+        <v>34.9608154296875</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558181762695</v>
+        <v>35.9558143615723</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.5437774658203</v>
+        <v>36.543773651123</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>36.362865447998</v>
+        <v>36.3628616333008</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.724681854248</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>37.5839996337891</v>
+        <v>37.5840034484863</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433250427246</v>
+        <v>38.4433288574219</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3980979919434</v>
+        <v>38.3981056213379</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910507202148</v>
+        <v>37.9910545349121</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649116516113</v>
+        <v>37.7649154663086</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>38.4885559082031</v>
+        <v>38.4885520935059</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367301940918</v>
+        <v>36.1367263793945</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G842" t="n">
-        <v>36.2724075317383</v>
+        <v>36.2724113464355</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387763977051</v>
+        <v>37.5387802124023</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.724681854248</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>37.5839996337891</v>
+        <v>37.5840034484863</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101463317871</v>
+        <v>37.8101425170898</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G855" t="n">
-        <v>37.5839996337891</v>
+        <v>37.5840034484863</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>36.362865447998</v>
+        <v>36.3628616333008</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.618335723877</v>
+        <v>34.6183395385742</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.215991973877</v>
+        <v>35.2159957885742</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>34.5723609924316</v>
+        <v>34.5723571777344</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G903" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>35.5837860107422</v>
+        <v>35.5837898254395</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850952148438</v>
+        <v>33.2850914001465</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471672058105</v>
+        <v>33.1471710205078</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>32.0897750854492</v>
+        <v>32.089771270752</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>31.9978256225586</v>
+        <v>31.9978218078613</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575576782227</v>
+        <v>32.4575614929199</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.296516418457</v>
+        <v>34.2965202331543</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448272705078</v>
+        <v>33.7448310852051</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.5035362243652</v>
+        <v>32.503532409668</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380840301514</v>
+        <v>31.5380802154541</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9173011779785</v>
+        <v>32.9173049926758</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9173011779785</v>
+        <v>32.9173049926758</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347076416016</v>
+        <v>30.4347095489502</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G992" t="n">
-        <v>30.8944473266602</v>
+        <v>30.8944492340088</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861259460449</v>
+        <v>34.9861221313477</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>40.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>37.2388458251953</v>
+        <v>37.238842010498</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>39.1697463989258</v>
+        <v>39.169750213623</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1029" t="n">
-        <v>39.1697463989258</v>
+        <v>39.169750213623</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>39.3536415100098</v>
+        <v>39.353645324707</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>43.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>39.767406463623</v>
+        <v>39.7674102783203</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650703430176</v>
+        <v>40.3650741577148</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>42.5999984741211</v>
       </c>
       <c r="G1059" t="n">
-        <v>39.1697463989258</v>
+        <v>39.169750213623</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>40.4110450744629</v>
+        <v>40.4110412597656</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>43.25</v>
       </c>
       <c r="G1062" t="n">
-        <v>39.767406463623</v>
+        <v>39.7674102783203</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442855834961</v>
+        <v>41.7442893981934</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100105285645</v>
+        <v>38.7100067138672</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009254455566</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365097045898</v>
+        <v>37.8365058898926</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824768066406</v>
+        <v>37.8824806213379</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227447509766</v>
+        <v>37.4227409362793</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227447509766</v>
+        <v>37.4227409362793</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365097045898</v>
+        <v>37.8365058898926</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858551025391</v>
+        <v>38.9858589172363</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -45612,6 +45612,32 @@
         <v>35.439998626709</v>
       </c>
       <c r="H1740" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1741" t="n">
+        <v>13260</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>36.1399993896484</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>35.4799995422363</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>35.4799995422363</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>36.0200004577637</v>
+      </c>
+      <c r="G1741" t="n">
+        <v>36.0200004577637</v>
+      </c>
+      <c r="H1741" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025457382202</v>
+        <v>13.6025447845459</v>
       </c>
       <c r="H2" t="n">
         <v>487001</v>
@@ -485,7 +485,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818492889404</v>
+        <v>13.3818502426147</v>
       </c>
       <c r="H4" t="n">
         <v>54824</v>
@@ -543,7 +543,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.001898765564</v>
+        <v>14.0018997192383</v>
       </c>
       <c r="H6" t="n">
         <v>24177</v>
@@ -572,7 +572,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810424804688</v>
+        <v>13.8810434341431</v>
       </c>
       <c r="H7" t="n">
         <v>41257</v>
@@ -601,7 +601,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H8" t="n">
         <v>32860</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934656143188</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -659,7 +659,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9248313903809</v>
+        <v>13.9248304367065</v>
       </c>
       <c r="H10" t="n">
         <v>61964</v>
@@ -746,7 +746,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370927810669</v>
+        <v>13.9370908737183</v>
       </c>
       <c r="H13" t="n">
         <v>8422</v>
@@ -804,7 +804,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915519714355</v>
+        <v>13.8915529251099</v>
       </c>
       <c r="H15" t="n">
         <v>15065</v>
@@ -862,7 +862,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.8722839355469</v>
+        <v>13.8722848892212</v>
       </c>
       <c r="H17" t="n">
         <v>116007</v>
@@ -978,7 +978,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963205337524</v>
+        <v>14.1963214874268</v>
       </c>
       <c r="H21" t="n">
         <v>76030</v>
@@ -1007,7 +1007,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130279541016</v>
+        <v>14.7130289077759</v>
       </c>
       <c r="H22" t="n">
         <v>147663</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071281433105</v>
+        <v>15.1071271896362</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1152,7 +1152,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463073730469</v>
+        <v>14.7463083267212</v>
       </c>
       <c r="H27" t="n">
         <v>68742</v>
@@ -1181,7 +1181,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916864395142</v>
+        <v>14.8916873931885</v>
       </c>
       <c r="H28" t="n">
         <v>63118</v>
@@ -1239,7 +1239,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730653762817</v>
+        <v>14.4730663299561</v>
       </c>
       <c r="H30" t="n">
         <v>42455</v>
@@ -1268,7 +1268,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G31" t="n">
-        <v>14.520357131958</v>
+        <v>14.5203580856323</v>
       </c>
       <c r="H31" t="n">
         <v>43925</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881855010986</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1355,7 +1355,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378742218018</v>
+        <v>14.5378751754761</v>
       </c>
       <c r="H34" t="n">
         <v>28201</v>
@@ -1413,7 +1413,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905824661255</v>
+        <v>14.4905815124512</v>
       </c>
       <c r="H36" t="n">
         <v>29716</v>
@@ -1442,7 +1442,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.355712890625</v>
+        <v>14.3557119369507</v>
       </c>
       <c r="H37" t="n">
         <v>37432</v>
@@ -1500,7 +1500,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H39" t="n">
         <v>17569</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609666824341</v>
+        <v>14.360969543457</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006057739258</v>
+        <v>14.8006076812744</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1616,7 +1616,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443965911865</v>
+        <v>14.8443956375122</v>
       </c>
       <c r="H43" t="n">
         <v>115888</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.136905670166</v>
+        <v>15.1369066238403</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1819,7 +1819,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1262578964233</v>
+        <v>14.1262588500977</v>
       </c>
       <c r="H50" t="n">
         <v>74499</v>
@@ -1877,7 +1877,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.4415397644043</v>
+        <v>14.4415378570557</v>
       </c>
       <c r="H52" t="n">
         <v>18751</v>
@@ -1906,7 +1906,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089073181152</v>
+        <v>14.0089054107666</v>
       </c>
       <c r="H53" t="n">
         <v>23213</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -1993,7 +1993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H56" t="n">
         <v>23379</v>
@@ -2051,7 +2051,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527196884155</v>
+        <v>12.9527206420898</v>
       </c>
       <c r="H58" t="n">
         <v>30556</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111669540405</v>
+        <v>12.6111688613892</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320251464844</v>
+        <v>12.7320241928101</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0714197158813</v>
+        <v>10.071418762207</v>
       </c>
       <c r="H63" t="n">
         <v>21708</v>
@@ -2283,7 +2283,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>9.63353157043457</v>
+        <v>9.63353061676025</v>
       </c>
       <c r="H66" t="n">
         <v>74779</v>
@@ -2370,7 +2370,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96619033813477</v>
+        <v>8.96618938446045</v>
       </c>
       <c r="H69" t="n">
         <v>122433</v>
@@ -2399,7 +2399,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58259963989258</v>
       </c>
       <c r="H70" t="n">
         <v>24355</v>
@@ -2457,7 +2457,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58260059356689</v>
+        <v>8.58259963989258</v>
       </c>
       <c r="H72" t="n">
         <v>30457</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494190216064</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2544,7 +2544,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032096862793</v>
+        <v>8.69032192230225</v>
       </c>
       <c r="H75" t="n">
         <v>14690</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500961303711</v>
+        <v>9.04500865936279</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2660,7 +2660,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G79" t="n">
-        <v>9.82620143890381</v>
+        <v>9.82620239257812</v>
       </c>
       <c r="H79" t="n">
         <v>19607</v>
@@ -2689,7 +2689,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921142578125</v>
       </c>
       <c r="H80" t="n">
         <v>20417</v>
@@ -2718,7 +2718,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968837738037</v>
+        <v>10.5968856811523</v>
       </c>
       <c r="H81" t="n">
         <v>17348</v>
@@ -2747,7 +2747,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070697784424</v>
+        <v>10.8070707321167</v>
       </c>
       <c r="H82" t="n">
         <v>3945</v>
@@ -2776,7 +2776,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156665802002</v>
+        <v>10.9156656265259</v>
       </c>
       <c r="H83" t="n">
         <v>6741</v>
@@ -2805,7 +2805,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>11.2887468338013</v>
+        <v>11.2887477874756</v>
       </c>
       <c r="H84" t="n">
         <v>6430</v>
@@ -2834,7 +2834,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748962402344</v>
+        <v>11.1748952865601</v>
       </c>
       <c r="H85" t="n">
         <v>4457</v>
@@ -2863,7 +2863,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.787802696228</v>
+        <v>10.7878036499023</v>
       </c>
       <c r="H86" t="n">
         <v>15151</v>
@@ -2892,7 +2892,7 @@
         <v>12.8079996109009</v>
       </c>
       <c r="G87" t="n">
-        <v>11.2169322967529</v>
+        <v>11.2169313430786</v>
       </c>
       <c r="H87" t="n">
         <v>10905</v>
@@ -2921,7 +2921,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353925704956</v>
+        <v>11.7353916168213</v>
       </c>
       <c r="H88" t="n">
         <v>24596</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229694366455</v>
+        <v>11.8229703903198</v>
       </c>
       <c r="H91" t="n">
         <v>16703</v>
@@ -3095,7 +3095,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331817626953</v>
+        <v>10.9331827163696</v>
       </c>
       <c r="H94" t="n">
         <v>46331</v>
@@ -3124,7 +3124,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471950531006</v>
+        <v>10.9471940994263</v>
       </c>
       <c r="H95" t="n">
         <v>49105</v>
@@ -3153,7 +3153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143989562988</v>
+        <v>10.6143999099731</v>
       </c>
       <c r="H96" t="n">
         <v>30171</v>
@@ -3211,7 +3211,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.3866968154907</v>
+        <v>10.386697769165</v>
       </c>
       <c r="H98" t="n">
         <v>22385</v>
@@ -3240,7 +3240,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691825866699</v>
+        <v>10.3691816329956</v>
       </c>
       <c r="H99" t="n">
         <v>11865</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078784942627</v>
+        <v>10.3078775405884</v>
       </c>
       <c r="H100" t="n">
         <v>7478</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465734481812</v>
+        <v>10.2465744018555</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3472,7 +3472,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>11.3412933349609</v>
+        <v>11.3412923812866</v>
       </c>
       <c r="H107" t="n">
         <v>39114</v>
@@ -3530,7 +3530,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955917358398</v>
+        <v>11.3955926895142</v>
       </c>
       <c r="H109" t="n">
         <v>18584</v>
@@ -3588,7 +3588,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565732955933</v>
+        <v>11.6565723419189</v>
       </c>
       <c r="H111" t="n">
         <v>27521</v>
@@ -3704,7 +3704,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727945327759</v>
+        <v>12.4727954864502</v>
       </c>
       <c r="H115" t="n">
         <v>41546</v>
@@ -3733,7 +3733,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506715774536</v>
+        <v>12.0506706237793</v>
       </c>
       <c r="H116" t="n">
         <v>330572</v>
@@ -3762,7 +3762,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258262634277</v>
+        <v>12.2258272171021</v>
       </c>
       <c r="H117" t="n">
         <v>24996</v>
@@ -3878,7 +3878,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.760048866272</v>
+        <v>12.7600479125977</v>
       </c>
       <c r="H121" t="n">
         <v>53970</v>
@@ -3907,7 +3907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H122" t="n">
         <v>27467</v>
@@ -3936,7 +3936,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.310037612915</v>
+        <v>13.3100366592407</v>
       </c>
       <c r="H123" t="n">
         <v>25697</v>
@@ -3965,7 +3965,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930067062378</v>
+        <v>12.9930057525635</v>
       </c>
       <c r="H124" t="n">
         <v>20213</v>
@@ -3994,7 +3994,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.786322593689</v>
+        <v>12.7863235473633</v>
       </c>
       <c r="H125" t="n">
         <v>14042</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901498794556</v>
+        <v>12.5901489257812</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4052,7 +4052,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H127" t="n">
         <v>96046</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119512557983</v>
+        <v>13.211950302124</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4168,7 +4168,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361476898193</v>
+        <v>13.4361486434937</v>
       </c>
       <c r="H131" t="n">
         <v>17251</v>
@@ -4226,7 +4226,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.5272283554077</v>
+        <v>13.5272302627563</v>
       </c>
       <c r="H133" t="n">
         <v>18810</v>
@@ -4255,7 +4255,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H134" t="n">
         <v>10358</v>
@@ -4313,7 +4313,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H136" t="n">
         <v>7773</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681613922119</v>
+        <v>13.1681604385376</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4400,7 +4400,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.080584526062</v>
+        <v>13.0805826187134</v>
       </c>
       <c r="H139" t="n">
         <v>13088</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H140" t="n">
         <v>6887</v>
@@ -4458,7 +4458,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606695175171</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H141" t="n">
         <v>4654</v>
@@ -4516,7 +4516,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979370117188</v>
+        <v>13.1979360580444</v>
       </c>
       <c r="H143" t="n">
         <v>3314</v>
@@ -4574,7 +4574,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490550994873</v>
+        <v>13.0490560531616</v>
       </c>
       <c r="H145" t="n">
         <v>1877</v>
@@ -4603,7 +4603,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772415161133</v>
+        <v>12.9772424697876</v>
       </c>
       <c r="H146" t="n">
         <v>4221</v>
@@ -4748,7 +4748,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606695175171</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H151" t="n">
         <v>14307</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4806,7 +4806,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324840545654</v>
+        <v>13.5324831008911</v>
       </c>
       <c r="H153" t="n">
         <v>9502</v>
@@ -4864,7 +4864,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.469428062439</v>
+        <v>13.4694261550903</v>
       </c>
       <c r="H155" t="n">
         <v>2209</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277145385742</v>
+        <v>13.2277135848999</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4922,7 +4922,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555774688721</v>
+        <v>13.3555765151978</v>
       </c>
       <c r="H157" t="n">
         <v>9479</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348810195923</v>
+        <v>13.1348829269409</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -5067,7 +5067,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309211730957</v>
+        <v>12.3309192657471</v>
       </c>
       <c r="H162" t="n">
         <v>17829</v>
@@ -5096,7 +5096,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673780441284</v>
+        <v>12.5673789978027</v>
       </c>
       <c r="H163" t="n">
         <v>11473</v>
@@ -5125,7 +5125,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393533706665</v>
+        <v>12.5393552780151</v>
       </c>
       <c r="H164" t="n">
         <v>30378</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H171" t="n">
         <v>7984</v>
@@ -5357,7 +5357,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132169723511</v>
+        <v>13.5132160186768</v>
       </c>
       <c r="H172" t="n">
         <v>10655</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5531,7 +5531,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044574737549</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H178" t="n">
         <v>14964</v>
@@ -5908,7 +5908,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G191" t="n">
-        <v>13.8722839355469</v>
+        <v>13.8722848892212</v>
       </c>
       <c r="H191" t="n">
         <v>17918</v>
@@ -5966,7 +5966,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H193" t="n">
         <v>36033</v>
@@ -6024,7 +6024,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>13.6796131134033</v>
+        <v>13.6796140670776</v>
       </c>
       <c r="H195" t="n">
         <v>5114</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H199" t="n">
         <v>7759</v>
@@ -6198,7 +6198,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H201" t="n">
         <v>43057</v>
@@ -6285,7 +6285,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531513214111</v>
       </c>
       <c r="H204" t="n">
         <v>59951</v>
@@ -6314,7 +6314,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531513214111</v>
       </c>
       <c r="H205" t="n">
         <v>52305</v>
@@ -6343,7 +6343,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.467812538147</v>
+        <v>14.4678134918213</v>
       </c>
       <c r="H206" t="n">
         <v>39648</v>
@@ -6372,7 +6372,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H207" t="n">
         <v>18020</v>
@@ -6401,7 +6401,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H208" t="n">
         <v>11562</v>
@@ -6546,7 +6546,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H213" t="n">
         <v>3813</v>
@@ -6575,7 +6575,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955146789551</v>
+        <v>14.6955137252808</v>
       </c>
       <c r="H214" t="n">
         <v>13259</v>
@@ -6604,7 +6604,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H215" t="n">
         <v>13883</v>
@@ -6633,7 +6633,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452024459839</v>
+        <v>14.3452014923096</v>
       </c>
       <c r="H216" t="n">
         <v>9351</v>
@@ -6662,7 +6662,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G217" t="n">
-        <v>14.1175022125244</v>
+        <v>14.1175031661987</v>
       </c>
       <c r="H217" t="n">
         <v>5382</v>
@@ -6720,7 +6720,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>13.9248313903809</v>
+        <v>13.9248304367065</v>
       </c>
       <c r="H219" t="n">
         <v>22685</v>
@@ -6749,7 +6749,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H220" t="n">
         <v>11900</v>
@@ -6778,7 +6778,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H221" t="n">
         <v>2428</v>
@@ -6807,7 +6807,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H222" t="n">
         <v>6474</v>
@@ -6836,7 +6836,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044574737549</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H223" t="n">
         <v>17777</v>
@@ -6865,7 +6865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.3117895126343</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H224" t="n">
         <v>45360</v>
@@ -6923,7 +6923,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.3117895126343</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H226" t="n">
         <v>5423</v>
@@ -6981,7 +6981,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H228" t="n">
         <v>2543</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219755172729</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7039,7 +7039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H230" t="n">
         <v>2511</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7126,7 +7126,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H233" t="n">
         <v>26206</v>
@@ -7155,7 +7155,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H234" t="n">
         <v>16461</v>
@@ -7184,7 +7184,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H235" t="n">
         <v>16963</v>
@@ -7213,7 +7213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H236" t="n">
         <v>8277</v>
@@ -7242,7 +7242,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H237" t="n">
         <v>17203</v>
@@ -7271,7 +7271,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H238" t="n">
         <v>12067</v>
@@ -7300,7 +7300,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>13.6796131134033</v>
+        <v>13.6796140670776</v>
       </c>
       <c r="H239" t="n">
         <v>20611</v>
@@ -7329,7 +7329,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H240" t="n">
         <v>23600</v>
@@ -7358,7 +7358,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H241" t="n">
         <v>4135</v>
@@ -7387,7 +7387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H242" t="n">
         <v>10822</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7445,7 +7445,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H244" t="n">
         <v>25909</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219755172729</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7503,7 +7503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H246" t="n">
         <v>7116</v>
@@ -7532,7 +7532,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H247" t="n">
         <v>18668</v>
@@ -7561,7 +7561,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H248" t="n">
         <v>7591</v>
@@ -7590,7 +7590,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H249" t="n">
         <v>4482</v>
@@ -7648,7 +7648,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H251" t="n">
         <v>2749</v>
@@ -7677,7 +7677,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H252" t="n">
         <v>3351</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022222518921</v>
+        <v>13.8022232055664</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7764,7 +7764,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H255" t="n">
         <v>3852</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7822,7 +7822,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H257" t="n">
         <v>7773</v>
@@ -7851,7 +7851,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496747970581</v>
       </c>
       <c r="H258" t="n">
         <v>4171</v>
@@ -7880,7 +7880,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H259" t="n">
         <v>10259</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219755172729</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7967,7 +7967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197374343872</v>
+        <v>13.8197383880615</v>
       </c>
       <c r="H262" t="n">
         <v>19414</v>
@@ -8054,7 +8054,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.152533531189</v>
+        <v>14.1525325775146</v>
       </c>
       <c r="H265" t="n">
         <v>11125</v>
@@ -8141,7 +8141,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H268" t="n">
         <v>16682</v>
@@ -8170,7 +8170,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H269" t="n">
         <v>28438</v>
@@ -8199,7 +8199,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576265335083</v>
       </c>
       <c r="H270" t="n">
         <v>5152</v>
@@ -8228,7 +8228,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028429031372</v>
+        <v>14.5028419494629</v>
       </c>
       <c r="H271" t="n">
         <v>6060</v>
@@ -8257,7 +8257,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028429031372</v>
+        <v>14.5028419494629</v>
       </c>
       <c r="H272" t="n">
         <v>8570</v>
@@ -8315,7 +8315,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G274" t="n">
-        <v>14.3977499008179</v>
+        <v>14.3977508544922</v>
       </c>
       <c r="H274" t="n">
         <v>5498</v>
@@ -8344,7 +8344,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401113510132</v>
+        <v>14.2401103973389</v>
       </c>
       <c r="H275" t="n">
         <v>14243</v>
@@ -8373,7 +8373,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276891708374</v>
+        <v>14.3276882171631</v>
       </c>
       <c r="H276" t="n">
         <v>6927</v>
@@ -8402,7 +8402,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576265335083</v>
       </c>
       <c r="H277" t="n">
         <v>6898</v>
@@ -8431,7 +8431,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729055404663</v>
+        <v>14.5729036331177</v>
       </c>
       <c r="H278" t="n">
         <v>26113</v>
@@ -8489,7 +8489,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311666488647</v>
+        <v>15.4311656951904</v>
       </c>
       <c r="H280" t="n">
         <v>50717</v>
@@ -8518,7 +8518,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114114761353</v>
+        <v>15.7114133834839</v>
       </c>
       <c r="H281" t="n">
         <v>48160</v>
@@ -8547,7 +8547,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989892959595</v>
+        <v>15.7989912033081</v>
       </c>
       <c r="H282" t="n">
         <v>60104</v>
@@ -8605,7 +8605,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165044784546</v>
+        <v>15.8165035247803</v>
       </c>
       <c r="H284" t="n">
         <v>60606</v>
@@ -8692,7 +8692,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317863464355</v>
+        <v>16.1317844390869</v>
       </c>
       <c r="H287" t="n">
         <v>34304</v>
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397361755371</v>
+        <v>16.6397380828857</v>
       </c>
       <c r="H288" t="n">
         <v>19711</v>
@@ -8779,7 +8779,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973747253418</v>
+        <v>16.7973766326904</v>
       </c>
       <c r="H290" t="n">
         <v>32844</v>
@@ -8866,7 +8866,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753871917725</v>
+        <v>17.3753852844238</v>
       </c>
       <c r="H293" t="n">
         <v>29298</v>
@@ -8895,7 +8895,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592975616455</v>
+        <v>17.5592994689941</v>
       </c>
       <c r="H294" t="n">
         <v>17437</v>
@@ -8953,7 +8953,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906681060791</v>
+        <v>17.6906661987305</v>
       </c>
       <c r="H296" t="n">
         <v>36908</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.2527770996094</v>
+        <v>17.2527809143066</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9011,7 +9011,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468753814697</v>
+        <v>17.646879196167</v>
       </c>
       <c r="H298" t="n">
         <v>49334</v>
@@ -9040,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.5155086517334</v>
+        <v>17.5155124664307</v>
       </c>
       <c r="H299" t="n">
         <v>21074</v>
@@ -9069,7 +9069,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228397369385</v>
+        <v>17.3228416442871</v>
       </c>
       <c r="H300" t="n">
         <v>7964</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979972839355</v>
+        <v>17.4979953765869</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9156,7 +9156,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409736633301</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H303" t="n">
         <v>51778</v>
@@ -9214,7 +9214,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>18.1285533905029</v>
+        <v>18.1285552978516</v>
       </c>
       <c r="H305" t="n">
         <v>35889</v>
@@ -9272,7 +9272,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>18.7853870391846</v>
+        <v>18.7853851318359</v>
       </c>
       <c r="H307" t="n">
         <v>24097</v>
@@ -9330,7 +9330,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422206878662</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H309" t="n">
         <v>14880</v>
@@ -9359,7 +9359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422206878662</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H310" t="n">
         <v>34531</v>
@@ -9533,7 +9533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422206878662</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H316" t="n">
         <v>27872</v>
@@ -9591,7 +9591,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>18.7853870391846</v>
+        <v>18.7853851318359</v>
       </c>
       <c r="H318" t="n">
         <v>14808</v>
@@ -9620,7 +9620,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="n">
-        <v>19.2670631408691</v>
+        <v>19.2670612335205</v>
       </c>
       <c r="H319" t="n">
         <v>26626</v>
@@ -9707,7 +9707,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422206878662</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H322" t="n">
         <v>48797</v>
@@ -9736,7 +9736,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794815063477</v>
       </c>
       <c r="H323" t="n">
         <v>9282</v>
@@ -9765,7 +9765,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7487373352051</v>
+        <v>19.7487392425537</v>
       </c>
       <c r="H324" t="n">
         <v>38949</v>
@@ -9823,7 +9823,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H326" t="n">
         <v>15812</v>
@@ -9852,7 +9852,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H327" t="n">
         <v>7040</v>
@@ -9910,7 +9910,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729629516602</v>
+        <v>18.8729648590088</v>
       </c>
       <c r="H329" t="n">
         <v>14665</v>
@@ -9968,7 +9968,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.0481204986572</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H331" t="n">
         <v>11487</v>
@@ -10055,7 +10055,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.0481204986572</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H334" t="n">
         <v>5987</v>
@@ -10084,7 +10084,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.7853870391846</v>
+        <v>18.7853851318359</v>
       </c>
       <c r="H335" t="n">
         <v>17649</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546409606934</v>
+        <v>19.3546390533447</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10229,7 +10229,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794815063477</v>
       </c>
       <c r="H340" t="n">
         <v>8629</v>
@@ -10287,7 +10287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409736633301</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H342" t="n">
         <v>48534</v>
@@ -10316,7 +10316,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409736633301</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H343" t="n">
         <v>22326</v>
@@ -10345,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.391284942627</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H344" t="n">
         <v>18146</v>
@@ -10374,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.391284942627</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H345" t="n">
         <v>7042</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799457550049</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10432,7 +10432,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797546386719</v>
+        <v>19.2797565460205</v>
       </c>
       <c r="H347" t="n">
         <v>18924</v>
@@ -10490,7 +10490,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.212646484375</v>
+        <v>20.2126445770264</v>
       </c>
       <c r="H349" t="n">
         <v>34567</v>
@@ -10519,7 +10519,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903388977051</v>
+        <v>20.3903408050537</v>
       </c>
       <c r="H350" t="n">
         <v>39422</v>
@@ -10548,7 +10548,7 @@
         <v>23</v>
       </c>
       <c r="G351" t="n">
-        <v>20.4347648620605</v>
+        <v>20.4347629547119</v>
       </c>
       <c r="H351" t="n">
         <v>25210</v>
@@ -10606,7 +10606,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572578430176</v>
+        <v>19.8572597503662</v>
       </c>
       <c r="H353" t="n">
         <v>50006</v>
@@ -10635,7 +10635,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793762207031</v>
+        <v>20.0793743133545</v>
       </c>
       <c r="H354" t="n">
         <v>30645</v>
@@ -10664,7 +10664,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905281066895</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H355" t="n">
         <v>20044</v>
@@ -10693,7 +10693,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345737457275</v>
+        <v>20.8345756530762</v>
       </c>
       <c r="H356" t="n">
         <v>39582</v>
@@ -10751,7 +10751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461059570312</v>
+        <v>19.9461078643799</v>
       </c>
       <c r="H358" t="n">
         <v>49210</v>
@@ -10809,7 +10809,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.746675491333</v>
+        <v>18.7466735839844</v>
       </c>
       <c r="H360" t="n">
         <v>21783</v>
@@ -10954,7 +10954,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.523609161377</v>
+        <v>20.5236129760742</v>
       </c>
       <c r="H365" t="n">
         <v>43029</v>
@@ -10983,7 +10983,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905281066895</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H366" t="n">
         <v>12885</v>
@@ -11128,7 +11128,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>21.9451580047607</v>
+        <v>21.9451599121094</v>
       </c>
       <c r="H371" t="n">
         <v>40746</v>
@@ -11157,7 +11157,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>22.3005485534668</v>
+        <v>22.3005466461182</v>
       </c>
       <c r="H372" t="n">
         <v>57393</v>
@@ -11331,7 +11331,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.8336277008057</v>
+        <v>22.833625793457</v>
       </c>
       <c r="H378" t="n">
         <v>26713</v>
@@ -11389,7 +11389,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>21.9451580047607</v>
+        <v>21.9451599121094</v>
       </c>
       <c r="H380" t="n">
         <v>63715</v>
@@ -11505,7 +11505,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5897693634033</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H384" t="n">
         <v>31931</v>
@@ -11534,7 +11534,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5009269714355</v>
+        <v>21.5009250640869</v>
       </c>
       <c r="H385" t="n">
         <v>66958</v>
@@ -11592,7 +11592,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011142730713</v>
+        <v>21.1011161804199</v>
       </c>
       <c r="H387" t="n">
         <v>8616</v>
@@ -11708,7 +11708,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901515960693</v>
+        <v>20.7901496887207</v>
       </c>
       <c r="H391" t="n">
         <v>21903</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11824,7 +11824,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.8789978027344</v>
+        <v>20.878999710083</v>
       </c>
       <c r="H395" t="n">
         <v>27666</v>
@@ -11998,7 +11998,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.5897693634033</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H401" t="n">
         <v>37886</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12346,7 +12346,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>21.9451580047607</v>
+        <v>21.9451599121094</v>
       </c>
       <c r="H413" t="n">
         <v>51382</v>
@@ -12375,7 +12375,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>22.3005485534668</v>
+        <v>22.3005466461182</v>
       </c>
       <c r="H414" t="n">
         <v>72981</v>
@@ -12404,7 +12404,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>22.3005485534668</v>
+        <v>22.3005466461182</v>
       </c>
       <c r="H415" t="n">
         <v>35324</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115112304688</v>
+        <v>22.6115093231201</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12491,7 +12491,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561206817627</v>
+        <v>22.2561225891113</v>
       </c>
       <c r="H418" t="n">
         <v>18147</v>
@@ -12578,7 +12578,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224739074707</v>
+        <v>22.9224720001221</v>
       </c>
       <c r="H421" t="n">
         <v>20723</v>
@@ -12636,7 +12636,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551727294922</v>
+        <v>24.2551765441895</v>
       </c>
       <c r="H423" t="n">
         <v>80709</v>
@@ -12665,7 +12665,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663303375244</v>
+        <v>24.1663284301758</v>
       </c>
       <c r="H424" t="n">
         <v>33528</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444030761719</v>
+        <v>23.5444011688232</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12723,7 +12723,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>23.6332492828369</v>
+        <v>23.6332473754883</v>
       </c>
       <c r="H426" t="n">
         <v>20089</v>
@@ -12752,7 +12752,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886360168457</v>
+        <v>23.9886341094971</v>
       </c>
       <c r="H427" t="n">
         <v>21987</v>
@@ -12781,7 +12781,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772930145264</v>
       </c>
       <c r="H428" t="n">
         <v>27149</v>
@@ -12839,7 +12839,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774803161621</v>
+        <v>24.0774822235107</v>
       </c>
       <c r="H430" t="n">
         <v>23999</v>
@@ -12868,7 +12868,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215240478516</v>
+        <v>24.9215278625488</v>
       </c>
       <c r="H431" t="n">
         <v>25118</v>
@@ -12897,7 +12897,7 @@
         <v>27.5</v>
       </c>
       <c r="G432" t="n">
-        <v>24.4328689575195</v>
+        <v>24.4328708648682</v>
       </c>
       <c r="H432" t="n">
         <v>17561</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661373138428</v>
+        <v>24.5661392211914</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -12984,7 +12984,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326797485352</v>
+        <v>24.8326816558838</v>
       </c>
       <c r="H435" t="n">
         <v>15025</v>
@@ -13042,7 +13042,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103721618652</v>
+        <v>25.0103740692139</v>
       </c>
       <c r="H437" t="n">
         <v>16754</v>
@@ -13071,7 +13071,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H438" t="n">
         <v>49309</v>
@@ -13100,7 +13100,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H439" t="n">
         <v>22024</v>
@@ -13158,7 +13158,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207710266113</v>
+        <v>26.5207691192627</v>
       </c>
       <c r="H441" t="n">
         <v>28926</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425071716309</v>
+        <v>27.5425090789795</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13303,7 +13303,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975154876709</v>
+        <v>28.6975135803223</v>
       </c>
       <c r="H446" t="n">
         <v>109999</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967548370361</v>
+        <v>30.2967529296875</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13419,7 +13419,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636775970459</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H450" t="n">
         <v>69374</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527130126953</v>
+        <v>29.4527168273926</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13506,7 +13506,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748275756836</v>
+        <v>29.6748332977295</v>
       </c>
       <c r="H453" t="n">
         <v>18449</v>
@@ -13564,7 +13564,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744529724121</v>
+        <v>30.4744510650635</v>
       </c>
       <c r="H455" t="n">
         <v>27798</v>
@@ -13622,7 +13622,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646255493164</v>
+        <v>27.764627456665</v>
       </c>
       <c r="H457" t="n">
         <v>101299</v>
@@ -13651,7 +13651,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H458" t="n">
         <v>38519</v>
@@ -13680,7 +13680,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H459" t="n">
         <v>26817</v>
@@ -13854,7 +13854,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H465" t="n">
         <v>29892</v>
@@ -13883,7 +13883,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.164436340332</v>
+        <v>28.1644344329834</v>
       </c>
       <c r="H466" t="n">
         <v>19936</v>
@@ -13941,7 +13941,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525238037109</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H468" t="n">
         <v>33525</v>
@@ -13970,7 +13970,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409896850586</v>
+        <v>30.74098777771</v>
       </c>
       <c r="H469" t="n">
         <v>41790</v>
@@ -14028,7 +14028,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406150817871</v>
+        <v>31.5406131744385</v>
       </c>
       <c r="H471" t="n">
         <v>48516</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627296447754</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14115,7 +14115,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.1625480651855</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H474" t="n">
         <v>26719</v>
@@ -14144,7 +14144,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H475" t="n">
         <v>22487</v>
@@ -14231,7 +14231,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402290344238</v>
       </c>
       <c r="H478" t="n">
         <v>49641</v>
@@ -14289,7 +14289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H480" t="n">
         <v>25306</v>
@@ -14318,7 +14318,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H481" t="n">
         <v>18772</v>
@@ -14347,7 +14347,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.717357635498</v>
+        <v>33.7173614501953</v>
       </c>
       <c r="H482" t="n">
         <v>45662</v>
@@ -14376,7 +14376,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H483" t="n">
         <v>61904</v>
@@ -14405,7 +14405,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942970275879</v>
+        <v>35.4942932128906</v>
       </c>
       <c r="H484" t="n">
         <v>95655</v>
@@ -14434,7 +14434,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H485" t="n">
         <v>147072</v>
@@ -14463,7 +14463,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617797851562</v>
+        <v>33.7617835998535</v>
       </c>
       <c r="H486" t="n">
         <v>58518</v>
@@ -14521,7 +14521,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398506164551</v>
+        <v>33.1398582458496</v>
       </c>
       <c r="H488" t="n">
         <v>34481</v>
@@ -14579,7 +14579,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H490" t="n">
         <v>30081</v>
@@ -14608,7 +14608,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H491" t="n">
         <v>10757</v>
@@ -14637,7 +14637,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288879394531</v>
       </c>
       <c r="H492" t="n">
         <v>26262</v>
@@ -14666,7 +14666,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844696044922</v>
+        <v>32.7844657897949</v>
       </c>
       <c r="H493" t="n">
         <v>16789</v>
@@ -14695,7 +14695,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H494" t="n">
         <v>20925</v>
@@ -14724,7 +14724,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H495" t="n">
         <v>56617</v>
@@ -14753,7 +14753,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H496" t="n">
         <v>24430</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14811,7 +14811,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.1625480651855</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H498" t="n">
         <v>32373</v>
@@ -14927,7 +14927,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404239654541</v>
+        <v>31.9404220581055</v>
       </c>
       <c r="H502" t="n">
         <v>44140</v>
@@ -14956,7 +14956,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402290344238</v>
       </c>
       <c r="H503" t="n">
         <v>22134</v>
@@ -14985,7 +14985,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852264404297</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H504" t="n">
         <v>25156</v>
@@ -15043,7 +15043,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852264404297</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H506" t="n">
         <v>14367</v>
@@ -15072,7 +15072,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H507" t="n">
         <v>36805</v>
@@ -15159,7 +15159,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071517944336</v>
+        <v>31.8071537017822</v>
       </c>
       <c r="H510" t="n">
         <v>24075</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627296447754</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15217,7 +15217,7 @@
         <v>36</v>
       </c>
       <c r="G512" t="n">
-        <v>31.9848499298096</v>
+        <v>31.9848461151123</v>
       </c>
       <c r="H512" t="n">
         <v>28137</v>
@@ -15275,7 +15275,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508171081543</v>
+        <v>33.4508209228516</v>
       </c>
       <c r="H514" t="n">
         <v>66935</v>
@@ -15304,7 +15304,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.4735069274902</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H515" t="n">
         <v>28750</v>
@@ -15333,7 +15333,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.4735069274902</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H516" t="n">
         <v>39270</v>
@@ -15362,7 +15362,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402366638184</v>
+        <v>32.3402290344238</v>
       </c>
       <c r="H517" t="n">
         <v>59170</v>
@@ -15391,7 +15391,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288879394531</v>
       </c>
       <c r="H518" t="n">
         <v>13845</v>
@@ -15420,7 +15420,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.429084777832</v>
+        <v>32.4290771484375</v>
       </c>
       <c r="H519" t="n">
         <v>27308</v>
@@ -15449,7 +15449,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.3175468444824</v>
+        <v>33.3175506591797</v>
       </c>
       <c r="H520" t="n">
         <v>18235</v>
@@ -15478,7 +15478,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H521" t="n">
         <v>16885</v>
@@ -15507,7 +15507,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H522" t="n">
         <v>24452</v>
@@ -15565,7 +15565,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H524" t="n">
         <v>40082</v>
@@ -15623,7 +15623,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283203125</v>
+        <v>34.0283279418945</v>
       </c>
       <c r="H526" t="n">
         <v>15120</v>
@@ -15652,7 +15652,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H527" t="n">
         <v>15724</v>
@@ -15710,7 +15710,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960018157959</v>
+        <v>31.8960037231445</v>
       </c>
       <c r="H529" t="n">
         <v>38776</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15768,7 +15768,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840873718262</v>
+        <v>33.5840911865234</v>
       </c>
       <c r="H531" t="n">
         <v>37158</v>
@@ -15797,7 +15797,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842727661133</v>
+        <v>33.1842765808105</v>
       </c>
       <c r="H532" t="n">
         <v>28931</v>
@@ -15826,7 +15826,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394721984863</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H533" t="n">
         <v>33489</v>
@@ -15855,7 +15855,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H534" t="n">
         <v>20804</v>
@@ -16087,7 +16087,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H542" t="n">
         <v>16501</v>
@@ -16116,7 +16116,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.429084777832</v>
+        <v>32.4290771484375</v>
       </c>
       <c r="H543" t="n">
         <v>43887</v>
@@ -16145,7 +16145,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394721984863</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H544" t="n">
         <v>89245</v>
@@ -16174,7 +16174,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H545" t="n">
         <v>71422</v>
@@ -16203,7 +16203,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H546" t="n">
         <v>50699</v>
@@ -16290,7 +16290,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279418945312</v>
+        <v>34.8279457092285</v>
       </c>
       <c r="H549" t="n">
         <v>115069</v>
@@ -16319,7 +16319,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H550" t="n">
         <v>59281</v>
@@ -16377,7 +16377,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275672912598</v>
+        <v>35.6275634765625</v>
       </c>
       <c r="H552" t="n">
         <v>107403</v>
@@ -16493,7 +16493,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H556" t="n">
         <v>29679</v>
@@ -16522,7 +16522,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>33.8062057495117</v>
+        <v>33.806209564209</v>
       </c>
       <c r="H557" t="n">
         <v>40431</v>
@@ -16551,7 +16551,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H558" t="n">
         <v>31513</v>
@@ -16580,7 +16580,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394721984863</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H559" t="n">
         <v>87892</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.405445098877</v>
+        <v>35.4054489135742</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16725,7 +16725,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>34.3837089538574</v>
+        <v>34.3837127685547</v>
       </c>
       <c r="H564" t="n">
         <v>118997</v>
@@ -16812,7 +16812,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>32.962158203125</v>
+        <v>32.9621620178223</v>
       </c>
       <c r="H567" t="n">
         <v>82672</v>
@@ -16841,7 +16841,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530914306641</v>
+        <v>28.6530933380127</v>
       </c>
       <c r="H568" t="n">
         <v>187078</v>
@@ -16870,7 +16870,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655715942383</v>
+        <v>25.7655696868896</v>
       </c>
       <c r="H569" t="n">
         <v>154319</v>
@@ -16899,7 +16899,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882556915283</v>
+        <v>24.788257598877</v>
       </c>
       <c r="H570" t="n">
         <v>115179</v>
@@ -16957,7 +16957,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873077392578</v>
+        <v>26.7873058319092</v>
       </c>
       <c r="H572" t="n">
         <v>79386</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190662384033</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17044,7 +17044,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525238037109</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H575" t="n">
         <v>71925</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184928894043</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186820983887</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17450,7 +17450,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H589" t="n">
         <v>67180</v>
@@ -17537,7 +17537,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744529724121</v>
+        <v>30.4744510650635</v>
       </c>
       <c r="H592" t="n">
         <v>28557</v>
@@ -17595,7 +17595,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636775970459</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H594" t="n">
         <v>35604</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186820983887</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17682,7 +17682,7 @@
         <v>35</v>
       </c>
       <c r="G597" t="n">
-        <v>31.0963802337646</v>
+        <v>31.096378326416</v>
       </c>
       <c r="H597" t="n">
         <v>23818</v>
@@ -17740,7 +17740,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740745544434</v>
+        <v>31.2740726470947</v>
       </c>
       <c r="H599" t="n">
         <v>22406</v>
@@ -17856,7 +17856,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H603" t="n">
         <v>26401</v>
@@ -17885,7 +17885,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.964054107666</v>
+        <v>28.9640560150146</v>
       </c>
       <c r="H604" t="n">
         <v>20198</v>
@@ -17914,7 +17914,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859832763672</v>
+        <v>29.5859851837158</v>
       </c>
       <c r="H605" t="n">
         <v>31886</v>
@@ -17972,7 +17972,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H607" t="n">
         <v>27177</v>
@@ -18001,7 +18001,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H608" t="n">
         <v>42611</v>
@@ -18059,7 +18059,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H610" t="n">
         <v>31377</v>
@@ -18088,7 +18088,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H611" t="n">
         <v>81317</v>
@@ -18117,7 +18117,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H612" t="n">
         <v>85415</v>
@@ -18204,7 +18204,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828468322754</v>
+        <v>32.3828506469727</v>
       </c>
       <c r="H615" t="n">
         <v>35851</v>
@@ -18233,7 +18233,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H616" t="n">
         <v>45928</v>
@@ -18291,7 +18291,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H618" t="n">
         <v>36011</v>
@@ -18320,7 +18320,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>32.9255790710449</v>
+        <v>32.9255828857422</v>
       </c>
       <c r="H619" t="n">
         <v>22834</v>
@@ -18349,7 +18349,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9758014678955</v>
+        <v>31.9757995605469</v>
       </c>
       <c r="H620" t="n">
         <v>19405</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903465270996</v>
+        <v>30.8903427124023</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18407,7 +18407,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.709436416626</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H622" t="n">
         <v>13020</v>
@@ -18436,7 +18436,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>30.0310230255127</v>
+        <v>30.0310249328613</v>
       </c>
       <c r="H623" t="n">
         <v>15007</v>
@@ -18523,7 +18523,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617088317871</v>
+        <v>31.1617126464844</v>
       </c>
       <c r="H626" t="n">
         <v>16502</v>
@@ -18552,7 +18552,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898979187012</v>
+        <v>32.7898941040039</v>
       </c>
       <c r="H627" t="n">
         <v>41583</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903465270996</v>
+        <v>30.8903427124023</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18610,7 +18610,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189785003662</v>
+        <v>30.6189765930176</v>
       </c>
       <c r="H629" t="n">
         <v>25073</v>
@@ -18668,7 +18668,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>30.0310230255127</v>
+        <v>30.0310249328613</v>
       </c>
       <c r="H631" t="n">
         <v>20315</v>
@@ -18697,7 +18697,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426189422607</v>
+        <v>31.3426208496094</v>
       </c>
       <c r="H632" t="n">
         <v>44384</v>
@@ -18726,7 +18726,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H633" t="n">
         <v>27780</v>
@@ -18755,7 +18755,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H634" t="n">
         <v>36768</v>
@@ -18813,7 +18813,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H636" t="n">
         <v>49552</v>
@@ -18842,7 +18842,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H637" t="n">
         <v>26649</v>
@@ -18987,7 +18987,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H642" t="n">
         <v>7805</v>
@@ -19016,7 +19016,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H643" t="n">
         <v>23506</v>
@@ -19045,7 +19045,7 @@
         <v>32</v>
       </c>
       <c r="G644" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H644" t="n">
         <v>31552</v>
@@ -19074,7 +19074,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601016998291</v>
+        <v>27.8601055145264</v>
       </c>
       <c r="H645" t="n">
         <v>17310</v>
@@ -19132,7 +19132,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H647" t="n">
         <v>19011</v>
@@ -19161,7 +19161,7 @@
         <v>32</v>
       </c>
       <c r="G648" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H648" t="n">
         <v>10722</v>
@@ -19190,7 +19190,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H649" t="n">
         <v>12887</v>
@@ -19219,7 +19219,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G650" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H650" t="n">
         <v>20929</v>
@@ -19248,7 +19248,7 @@
         <v>32</v>
       </c>
       <c r="G651" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H651" t="n">
         <v>18834</v>
@@ -19335,7 +19335,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H654" t="n">
         <v>70905</v>
@@ -19393,7 +19393,7 @@
         <v>33</v>
       </c>
       <c r="G656" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H656" t="n">
         <v>35738</v>
@@ -19451,7 +19451,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H658" t="n">
         <v>15664</v>
@@ -19480,7 +19480,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H659" t="n">
         <v>11969</v>
@@ -19509,7 +19509,7 @@
         <v>33</v>
       </c>
       <c r="G660" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H660" t="n">
         <v>20537</v>
@@ -19538,7 +19538,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H661" t="n">
         <v>16406</v>
@@ -19567,7 +19567,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787467956543</v>
       </c>
       <c r="H662" t="n">
         <v>11492</v>
@@ -19596,7 +19596,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214752197266</v>
+        <v>30.1214790344238</v>
       </c>
       <c r="H663" t="n">
         <v>13226</v>
@@ -19654,7 +19654,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H665" t="n">
         <v>5963</v>
@@ -19683,7 +19683,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H666" t="n">
         <v>41810</v>
@@ -19712,7 +19712,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0310230255127</v>
+        <v>30.0310249328613</v>
       </c>
       <c r="H667" t="n">
         <v>20516</v>
@@ -19741,7 +19741,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H668" t="n">
         <v>37372</v>
@@ -19770,7 +19770,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H669" t="n">
         <v>27479</v>
@@ -19799,7 +19799,7 @@
         <v>33</v>
       </c>
       <c r="G670" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H670" t="n">
         <v>16306</v>
@@ -19828,7 +19828,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>30.6642055511475</v>
+        <v>30.6642093658447</v>
       </c>
       <c r="H671" t="n">
         <v>28977</v>
@@ -19857,7 +19857,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285205841064</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H672" t="n">
         <v>11102</v>
@@ -19886,7 +19886,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H673" t="n">
         <v>12485</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355697631836</v>
+        <v>30.9355735778809</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19944,7 +19944,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9807968139648</v>
+        <v>30.9807987213135</v>
       </c>
       <c r="H675" t="n">
         <v>14000</v>
@@ -20031,7 +20031,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787467956543</v>
       </c>
       <c r="H678" t="n">
         <v>13528</v>
@@ -20118,7 +20118,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H681" t="n">
         <v>24865</v>
@@ -20147,7 +20147,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048820495605</v>
+        <v>29.8048839569092</v>
       </c>
       <c r="H682" t="n">
         <v>13128</v>
@@ -20176,7 +20176,7 @@
         <v>32.25</v>
       </c>
       <c r="G683" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H683" t="n">
         <v>7419</v>
@@ -20234,7 +20234,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G685" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H685" t="n">
         <v>7357</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H687" t="n">
         <v>31220</v>
@@ -20321,7 +20321,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H688" t="n">
         <v>9866</v>
@@ -20350,7 +20350,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H689" t="n">
         <v>6251</v>
@@ -20379,7 +20379,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H690" t="n">
         <v>13325</v>
@@ -20408,7 +20408,7 @@
         <v>32</v>
       </c>
       <c r="G691" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H691" t="n">
         <v>11145</v>
@@ -20437,7 +20437,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H692" t="n">
         <v>20442</v>
@@ -20495,7 +20495,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505577087402</v>
+        <v>27.9505596160889</v>
       </c>
       <c r="H694" t="n">
         <v>28033</v>
@@ -20611,7 +20611,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H698" t="n">
         <v>35920</v>
@@ -20640,7 +20640,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285205841064</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H699" t="n">
         <v>56297</v>
@@ -20669,7 +20669,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762481689453</v>
+        <v>30.0762500762939</v>
       </c>
       <c r="H700" t="n">
         <v>23460</v>
@@ -20756,7 +20756,7 @@
         <v>33</v>
       </c>
       <c r="G703" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H703" t="n">
         <v>24157</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.719425201416</v>
+        <v>28.7194271087646</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20843,7 +20843,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G706" t="n">
-        <v>29.0360164642334</v>
+        <v>29.0360145568848</v>
       </c>
       <c r="H706" t="n">
         <v>10664</v>
@@ -20872,7 +20872,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H707" t="n">
         <v>13065</v>
@@ -20901,7 +20901,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G708" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H708" t="n">
         <v>15124</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314716339111</v>
+        <v>28.1314678192139</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21017,7 +21017,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289730072021</v>
       </c>
       <c r="H712" t="n">
         <v>33341</v>
@@ -21046,7 +21046,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H713" t="n">
         <v>37089</v>
@@ -21075,7 +21075,7 @@
         <v>32.25</v>
       </c>
       <c r="G714" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H714" t="n">
         <v>28119</v>
@@ -21104,7 +21104,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048820495605</v>
+        <v>29.8048839569092</v>
       </c>
       <c r="H715" t="n">
         <v>26731</v>
@@ -21162,7 +21162,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119293212891</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H717" t="n">
         <v>59213</v>
@@ -21191,7 +21191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H718" t="n">
         <v>15926</v>
@@ -21220,7 +21220,7 @@
         <v>32</v>
       </c>
       <c r="G719" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H719" t="n">
         <v>25143</v>
@@ -21307,7 +21307,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H722" t="n">
         <v>27650</v>
@@ -21481,7 +21481,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G728" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H728" t="n">
         <v>20050</v>
@@ -21539,7 +21539,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H730" t="n">
         <v>19631</v>
@@ -21626,7 +21626,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H733" t="n">
         <v>36285</v>
@@ -21655,7 +21655,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H734" t="n">
         <v>19361</v>
@@ -21684,7 +21684,7 @@
         <v>32</v>
       </c>
       <c r="G735" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H735" t="n">
         <v>17587</v>
@@ -21742,7 +21742,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H737" t="n">
         <v>13524</v>
@@ -21800,7 +21800,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H739" t="n">
         <v>12783</v>
@@ -21829,7 +21829,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H740" t="n">
         <v>25796</v>
@@ -21858,7 +21858,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H741" t="n">
         <v>14572</v>
@@ -21887,7 +21887,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285205841064</v>
+        <v>30.5285224914551</v>
       </c>
       <c r="H742" t="n">
         <v>22513</v>
@@ -21974,7 +21974,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401222229004</v>
+        <v>31.8401184082031</v>
       </c>
       <c r="H745" t="n">
         <v>20993</v>
@@ -22061,7 +22061,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119293212891</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H748" t="n">
         <v>18927</v>
@@ -22148,7 +22148,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H751" t="n">
         <v>7222</v>
@@ -22177,7 +22177,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.709436416626</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H752" t="n">
         <v>15924</v>
@@ -22351,7 +22351,7 @@
         <v>35</v>
       </c>
       <c r="G758" t="n">
-        <v>31.6592102050781</v>
+        <v>31.6592082977295</v>
       </c>
       <c r="H758" t="n">
         <v>36492</v>
@@ -22525,7 +22525,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853492736816</v>
+        <v>31.8853454589844</v>
       </c>
       <c r="H764" t="n">
         <v>11653</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803558349609</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22670,7 +22670,7 @@
         <v>35.5</v>
       </c>
       <c r="G769" t="n">
-        <v>32.1114883422852</v>
+        <v>32.1114845275879</v>
       </c>
       <c r="H769" t="n">
         <v>44649</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.252161026001</v>
+        <v>31.2521648406982</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803558349609</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637626647949</v>
+        <v>32.5637588500977</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -22902,7 +22902,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H777" t="n">
         <v>22186</v>
@@ -22931,7 +22931,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.9205780029297</v>
+        <v>33.9205856323242</v>
       </c>
       <c r="H778" t="n">
         <v>24835</v>
@@ -22960,7 +22960,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H779" t="n">
         <v>8669</v>
@@ -23018,7 +23018,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H781" t="n">
         <v>27307</v>
@@ -23047,7 +23047,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.8753509521484</v>
+        <v>33.8753547668457</v>
       </c>
       <c r="H782" t="n">
         <v>27238</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23134,7 +23134,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H785" t="n">
         <v>16126</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301315307617</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23221,7 +23221,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.8753509521484</v>
+        <v>33.8753547668457</v>
       </c>
       <c r="H788" t="n">
         <v>10901</v>
@@ -23250,7 +23250,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>34.5085372924805</v>
+        <v>34.5085411071777</v>
       </c>
       <c r="H789" t="n">
         <v>22080</v>
@@ -23337,7 +23337,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608154296875</v>
+        <v>34.9608116149902</v>
       </c>
       <c r="H792" t="n">
         <v>32491</v>
@@ -23366,7 +23366,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>34.101490020752</v>
+        <v>34.1014938354492</v>
       </c>
       <c r="H793" t="n">
         <v>25794</v>
@@ -23395,7 +23395,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H794" t="n">
         <v>32389</v>
@@ -23511,7 +23511,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558143615723</v>
+        <v>35.9558181762695</v>
       </c>
       <c r="H798" t="n">
         <v>25747</v>
@@ -23540,7 +23540,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392211914062</v>
       </c>
       <c r="H799" t="n">
         <v>12129</v>
@@ -23627,7 +23627,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H802" t="n">
         <v>24522</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578720092773</v>
+        <v>37.3578681945801</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23714,7 +23714,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H805" t="n">
         <v>20586</v>
@@ -23801,7 +23801,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.227180480957</v>
+        <v>36.2271766662598</v>
       </c>
       <c r="H808" t="n">
         <v>31459</v>
@@ -24033,7 +24033,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.7246780395508</v>
+        <v>36.724681854248</v>
       </c>
       <c r="H816" t="n">
         <v>28980</v>
@@ -24062,7 +24062,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.9055938720703</v>
+        <v>36.905590057373</v>
       </c>
       <c r="H817" t="n">
         <v>29508</v>
@@ -24120,7 +24120,7 @@
         <v>41.25</v>
       </c>
       <c r="G819" t="n">
-        <v>37.3126411437988</v>
+        <v>37.3126373291016</v>
       </c>
       <c r="H819" t="n">
         <v>39954</v>
@@ -24149,7 +24149,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433288574219</v>
+        <v>38.4433250427246</v>
       </c>
       <c r="H820" t="n">
         <v>48120</v>
@@ -24178,7 +24178,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312881469727</v>
       </c>
       <c r="H821" t="n">
         <v>71113</v>
@@ -24265,7 +24265,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>39.6192398071289</v>
+        <v>39.6192436218262</v>
       </c>
       <c r="H824" t="n">
         <v>41543</v>
@@ -24294,7 +24294,7 @@
         <v>43.5499992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>39.3931007385254</v>
+        <v>39.3931045532227</v>
       </c>
       <c r="H825" t="n">
         <v>40999</v>
@@ -24323,7 +24323,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860534667969</v>
+        <v>38.9860496520996</v>
       </c>
       <c r="H826" t="n">
         <v>26184</v>
@@ -24381,7 +24381,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312881469727</v>
       </c>
       <c r="H828" t="n">
         <v>29768</v>
@@ -24410,7 +24410,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H829" t="n">
         <v>35652</v>
@@ -24439,7 +24439,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H830" t="n">
         <v>38250</v>
@@ -24468,7 +24468,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910545349121</v>
+        <v>37.9910507202148</v>
       </c>
       <c r="H831" t="n">
         <v>31412</v>
@@ -24526,7 +24526,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649154663086</v>
+        <v>37.7649116516113</v>
       </c>
       <c r="H833" t="n">
         <v>30771</v>
@@ -24555,7 +24555,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9006004333496</v>
+        <v>37.9005966186523</v>
       </c>
       <c r="H834" t="n">
         <v>57165</v>
@@ -24584,7 +24584,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H835" t="n">
         <v>34627</v>
@@ -24613,7 +24613,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>38.4885559082031</v>
+        <v>38.4885520935059</v>
       </c>
       <c r="H836" t="n">
         <v>39749</v>
@@ -24642,7 +24642,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.1819534301758</v>
+        <v>36.181957244873</v>
       </c>
       <c r="H837" t="n">
         <v>119181</v>
@@ -24758,7 +24758,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392211914062</v>
       </c>
       <c r="H841" t="n">
         <v>39832</v>
@@ -24787,7 +24787,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G842" t="n">
-        <v>36.2724075317383</v>
+        <v>36.2724113464355</v>
       </c>
       <c r="H842" t="n">
         <v>29267</v>
@@ -24845,7 +24845,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.1819534301758</v>
+        <v>36.181957244873</v>
       </c>
       <c r="H844" t="n">
         <v>20530</v>
@@ -24903,7 +24903,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.1819534301758</v>
+        <v>36.181957244873</v>
       </c>
       <c r="H846" t="n">
         <v>26328</v>
@@ -24932,7 +24932,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H847" t="n">
         <v>16900</v>
@@ -25019,7 +25019,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.7246780395508</v>
+        <v>36.724681854248</v>
       </c>
       <c r="H850" t="n">
         <v>32977</v>
@@ -25106,7 +25106,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>37.6292304992676</v>
+        <v>37.6292343139648</v>
       </c>
       <c r="H853" t="n">
         <v>19600</v>
@@ -25135,7 +25135,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744651794434</v>
+        <v>37.6744613647461</v>
       </c>
       <c r="H854" t="n">
         <v>14320</v>
@@ -25193,7 +25193,7 @@
         <v>40.75</v>
       </c>
       <c r="G856" t="n">
-        <v>36.8603630065918</v>
+        <v>36.8603668212891</v>
       </c>
       <c r="H856" t="n">
         <v>25546</v>
@@ -25251,7 +25251,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>37.1317291259766</v>
+        <v>37.1317329406738</v>
       </c>
       <c r="H858" t="n">
         <v>14683</v>
@@ -25280,7 +25280,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H859" t="n">
         <v>12270</v>
@@ -25309,7 +25309,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.0462684631348</v>
+        <v>36.046272277832</v>
       </c>
       <c r="H860" t="n">
         <v>13910</v>
@@ -25425,7 +25425,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H864" t="n">
         <v>25714</v>
@@ -25483,7 +25483,7 @@
         <v>40</v>
       </c>
       <c r="G866" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H866" t="n">
         <v>9543</v>
@@ -25541,7 +25541,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H868" t="n">
         <v>14461</v>
@@ -25599,7 +25599,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H870" t="n">
         <v>19770</v>
@@ -25715,7 +25715,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H874" t="n">
         <v>12962</v>
@@ -25773,7 +25773,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H876" t="n">
         <v>14179</v>
@@ -25831,7 +25831,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354713439941</v>
+        <v>36.1354675292969</v>
       </c>
       <c r="H878" t="n">
         <v>14544</v>
@@ -26005,7 +26005,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H884" t="n">
         <v>74828</v>
@@ -26121,7 +26121,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H888" t="n">
         <v>18290</v>
@@ -26295,7 +26295,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H894" t="n">
         <v>19917</v>
@@ -26382,7 +26382,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.5263862609863</v>
+        <v>34.5263824462891</v>
       </c>
       <c r="H897" t="n">
         <v>12411</v>
@@ -26411,7 +26411,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>34.5263862609863</v>
+        <v>34.5263824462891</v>
       </c>
       <c r="H898" t="n">
         <v>8875</v>
@@ -26440,7 +26440,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H899" t="n">
         <v>12713</v>
@@ -26643,7 +26643,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G906" t="n">
-        <v>36.2274208068848</v>
+        <v>36.2274169921875</v>
       </c>
       <c r="H906" t="n">
         <v>30888</v>
@@ -26672,7 +26672,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>34.112621307373</v>
+        <v>34.1126174926758</v>
       </c>
       <c r="H907" t="n">
         <v>64157</v>
@@ -26759,7 +26759,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850952148438</v>
+        <v>33.2850914001465</v>
       </c>
       <c r="H910" t="n">
         <v>19988</v>
@@ -26933,7 +26933,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H916" t="n">
         <v>6480</v>
@@ -26962,7 +26962,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471672058105</v>
+        <v>33.1471710205078</v>
       </c>
       <c r="H917" t="n">
         <v>22126</v>
@@ -26991,7 +26991,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H918" t="n">
         <v>15454</v>
@@ -27252,7 +27252,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575614929199</v>
+        <v>32.4575653076172</v>
       </c>
       <c r="H927" t="n">
         <v>15137</v>
@@ -27310,7 +27310,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H929" t="n">
         <v>19875</v>
@@ -27455,7 +27455,7 @@
         <v>37.5</v>
       </c>
       <c r="G934" t="n">
-        <v>34.480411529541</v>
+        <v>34.4804153442383</v>
       </c>
       <c r="H934" t="n">
         <v>36101</v>
@@ -27571,7 +27571,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>35.2619705200195</v>
+        <v>35.2619667053223</v>
       </c>
       <c r="H938" t="n">
         <v>29216</v>
@@ -27629,7 +27629,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H940" t="n">
         <v>25107</v>
@@ -27687,7 +27687,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H942" t="n">
         <v>13115</v>
@@ -27832,7 +27832,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>33.8367767333984</v>
+        <v>33.8367729187012</v>
       </c>
       <c r="H947" t="n">
         <v>15677</v>
@@ -27890,7 +27890,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>34.112621307373</v>
+        <v>34.1126174926758</v>
       </c>
       <c r="H949" t="n">
         <v>58394</v>
@@ -28006,7 +28006,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H953" t="n">
         <v>30708</v>
@@ -28209,7 +28209,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>32.9632759094238</v>
+        <v>32.9632720947266</v>
       </c>
       <c r="H960" t="n">
         <v>35963</v>
@@ -28267,7 +28267,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H962" t="n">
         <v>19440</v>
@@ -28325,7 +28325,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G964" t="n">
-        <v>32.2736663818359</v>
+        <v>32.2736625671387</v>
       </c>
       <c r="H964" t="n">
         <v>19495</v>
@@ -28412,7 +28412,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H967" t="n">
         <v>23454</v>
@@ -28441,7 +28441,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357460021973</v>
+        <v>32.1357421875</v>
       </c>
       <c r="H968" t="n">
         <v>22355</v>
@@ -28528,7 +28528,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>33.0552253723145</v>
+        <v>33.0552215576172</v>
       </c>
       <c r="H971" t="n">
         <v>12593</v>
@@ -28557,7 +28557,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G972" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H972" t="n">
         <v>17502</v>
@@ -28731,7 +28731,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6069068908691</v>
+        <v>33.6069107055664</v>
       </c>
       <c r="H978" t="n">
         <v>13732</v>
@@ -28847,7 +28847,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9172973632812</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H982" t="n">
         <v>17608</v>
@@ -28876,7 +28876,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9172973632812</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H983" t="n">
         <v>19478</v>
@@ -29050,7 +29050,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347076416016</v>
+        <v>30.4347114562988</v>
       </c>
       <c r="H989" t="n">
         <v>20300</v>
@@ -29108,7 +29108,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783443450928</v>
+        <v>31.0783462524414</v>
       </c>
       <c r="H991" t="n">
         <v>22083</v>
@@ -29137,7 +29137,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G992" t="n">
-        <v>30.8944473266602</v>
+        <v>30.8944492340088</v>
       </c>
       <c r="H992" t="n">
         <v>20906</v>
@@ -29195,7 +29195,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G994" t="n">
-        <v>32.9632759094238</v>
+        <v>32.9632720947266</v>
       </c>
       <c r="H994" t="n">
         <v>25799</v>
@@ -29282,7 +29282,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H997" t="n">
         <v>21195</v>
@@ -29601,7 +29601,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861259460449</v>
+        <v>34.9861221313477</v>
       </c>
       <c r="H1008" t="n">
         <v>17929</v>
@@ -29775,7 +29775,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1014" t="n">
         <v>42877</v>
@@ -29862,7 +29862,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1017" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H1017" t="n">
         <v>16992</v>
@@ -30036,7 +30036,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>37.6526107788086</v>
+        <v>37.6526145935059</v>
       </c>
       <c r="H1023" t="n">
         <v>27323</v>
@@ -30181,7 +30181,7 @@
         <v>42.75</v>
       </c>
       <c r="G1028" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1028" t="n">
         <v>26762</v>
@@ -30326,7 +30326,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1033" t="n">
         <v>17293</v>
@@ -30355,7 +30355,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>38.2502708435059</v>
+        <v>38.2502746582031</v>
       </c>
       <c r="H1034" t="n">
         <v>34988</v>
@@ -30384,7 +30384,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1035" t="n">
-        <v>38.0203971862793</v>
+        <v>38.0204010009766</v>
       </c>
       <c r="H1035" t="n">
         <v>30679</v>
@@ -30413,7 +30413,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1036" t="n">
         <v>34011</v>
@@ -30442,7 +30442,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1037" t="n">
         <v>16755</v>
@@ -30500,7 +30500,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1039" t="n">
         <v>35974</v>
@@ -30616,7 +30616,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1043" t="n">
         <v>12351</v>
@@ -30761,7 +30761,7 @@
         <v>42.75</v>
       </c>
       <c r="G1048" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1048" t="n">
         <v>28234</v>
@@ -30790,7 +30790,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1049" t="n">
         <v>25230</v>
@@ -30848,7 +30848,7 @@
         <v>44</v>
       </c>
       <c r="G1051" t="n">
-        <v>40.4570159912109</v>
+        <v>40.4570198059082</v>
       </c>
       <c r="H1051" t="n">
         <v>26021</v>
@@ -30993,7 +30993,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650703430176</v>
+        <v>40.3650741577148</v>
       </c>
       <c r="H1056" t="n">
         <v>17856</v>
@@ -31022,7 +31022,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1057" t="n">
         <v>25708</v>
@@ -31051,7 +31051,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1058" t="n">
         <v>26015</v>
@@ -31109,7 +31109,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1060" t="n">
         <v>30816</v>
@@ -31138,7 +31138,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>40.4110450744629</v>
+        <v>40.4110412597656</v>
       </c>
       <c r="H1061" t="n">
         <v>51174</v>
@@ -31312,7 +31312,7 @@
         <v>42.75</v>
       </c>
       <c r="G1067" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1067" t="n">
         <v>57559</v>
@@ -31341,7 +31341,7 @@
         <v>42.25</v>
       </c>
       <c r="G1068" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1068" t="n">
         <v>39015</v>
@@ -31370,7 +31370,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1069" t="n">
         <v>40978</v>
@@ -31399,7 +31399,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1070" t="n">
         <v>24074</v>
@@ -31457,7 +31457,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1072" t="n">
         <v>20307</v>
@@ -31486,7 +31486,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100105285645</v>
+        <v>38.7100067138672</v>
       </c>
       <c r="H1073" t="n">
         <v>28907</v>
@@ -31515,7 +31515,7 @@
         <v>42.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1074" t="n">
         <v>19772</v>
@@ -31573,7 +31573,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1076" t="n">
         <v>35632</v>
@@ -31689,7 +31689,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1080" t="n">
         <v>21026</v>
@@ -31776,7 +31776,7 @@
         <v>40</v>
       </c>
       <c r="G1083" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1083" t="n">
         <v>25278</v>
@@ -31834,7 +31834,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422241210938</v>
       </c>
       <c r="H1085" t="n">
         <v>44926</v>
@@ -32066,7 +32066,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1093" t="n">
         <v>21149</v>
@@ -32124,7 +32124,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1095" t="n">
         <v>27027</v>
@@ -32182,7 +32182,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1097" t="n">
-        <v>37.744556427002</v>
+        <v>37.7445602416992</v>
       </c>
       <c r="H1097" t="n">
         <v>46557</v>
@@ -32211,7 +32211,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1098" t="n">
         <v>26751</v>
@@ -32240,7 +32240,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1099" t="n">
         <v>14005</v>
@@ -32269,7 +32269,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1100" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1100" t="n">
         <v>26546</v>
@@ -32298,7 +32298,7 @@
         <v>42.25</v>
       </c>
       <c r="G1101" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1101" t="n">
         <v>11787</v>
@@ -32327,7 +32327,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1102" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1102" t="n">
         <v>17758</v>
@@ -32385,7 +32385,7 @@
         <v>40</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1104" t="n">
         <v>28294</v>
@@ -32414,7 +32414,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952072143555</v>
+        <v>36.5952110290527</v>
       </c>
       <c r="H1105" t="n">
         <v>26729</v>
@@ -32443,7 +32443,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.7791061401367</v>
+        <v>36.779109954834</v>
       </c>
       <c r="H1106" t="n">
         <v>12511</v>
@@ -32936,7 +32936,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1123" t="n">
         <v>13686</v>
@@ -32994,7 +32994,7 @@
         <v>44.4500007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>40.8707847595215</v>
+        <v>40.8707809448242</v>
       </c>
       <c r="H1125" t="n">
         <v>59380</v>
@@ -33110,7 +33110,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422241210938</v>
       </c>
       <c r="H1129" t="n">
         <v>76007</v>
@@ -50864,6 +50864,64 @@
         <v>13288</v>
       </c>
       <c r="I1741" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1742" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>36.0200004577637</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>36.0200004577637</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>34.9799995422363</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>35.2799987792969</v>
+      </c>
+      <c r="G1742" t="n">
+        <v>35.2799987792969</v>
+      </c>
+      <c r="H1742" t="n">
+        <v>16285</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1743" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>35.0400009155273</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>35.0400009155273</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>33.3400001525879</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>34.4000015258789</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>34.4000015258789</v>
+      </c>
+      <c r="H1743" t="n">
+        <v>75514</v>
+      </c>
+      <c r="I1743" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025447845459</v>
+        <v>13.6025457382202</v>
       </c>
       <c r="H2" t="n">
         <v>487001</v>
@@ -485,7 +485,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818502426147</v>
+        <v>13.3818492889404</v>
       </c>
       <c r="H4" t="n">
         <v>54824</v>
@@ -601,7 +601,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H8" t="n">
         <v>32860</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934656143188</v>
+        <v>13.7934646606445</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -688,7 +688,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390054702759</v>
+        <v>13.8390064239502</v>
       </c>
       <c r="H11" t="n">
         <v>10789</v>
@@ -717,7 +717,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896383285522</v>
+        <v>13.9896392822266</v>
       </c>
       <c r="H12" t="n">
         <v>10618</v>
@@ -746,7 +746,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370908737183</v>
+        <v>13.9370918273926</v>
       </c>
       <c r="H13" t="n">
         <v>8422</v>
@@ -804,7 +804,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915529251099</v>
+        <v>13.8915519714355</v>
       </c>
       <c r="H15" t="n">
         <v>15065</v>
@@ -920,7 +920,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H19" t="n">
         <v>69364</v>
@@ -949,7 +949,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948930740356</v>
+        <v>13.9948921203613</v>
       </c>
       <c r="H20" t="n">
         <v>34939</v>
@@ -1036,7 +1036,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692409515381</v>
+        <v>14.6692419052124</v>
       </c>
       <c r="H23" t="n">
         <v>297347</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071271896362</v>
+        <v>15.1071281433105</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881864547729</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1152,7 +1152,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463083267212</v>
+        <v>14.7463092803955</v>
       </c>
       <c r="H27" t="n">
         <v>68742</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757623672485</v>
+        <v>14.9757614135742</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1239,7 +1239,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730663299561</v>
+        <v>14.4730653762817</v>
       </c>
       <c r="H30" t="n">
         <v>42455</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881864547729</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881864547729</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1413,7 +1413,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905815124512</v>
+        <v>14.4905824661255</v>
       </c>
       <c r="H36" t="n">
         <v>29716</v>
@@ -1442,7 +1442,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557119369507</v>
+        <v>14.355712890625</v>
       </c>
       <c r="H37" t="n">
         <v>37432</v>
@@ -1471,7 +1471,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628803253174</v>
+        <v>14.2628793716431</v>
       </c>
       <c r="H38" t="n">
         <v>11160</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.360969543457</v>
+        <v>14.3609685897827</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1558,7 +1558,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>14.6604833602905</v>
+        <v>14.6604814529419</v>
       </c>
       <c r="H41" t="n">
         <v>29941</v>
@@ -1645,7 +1645,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692409515381</v>
+        <v>14.6692419052124</v>
       </c>
       <c r="H44" t="n">
         <v>35731</v>
@@ -1674,7 +1674,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655754089355</v>
+        <v>14.7655763626099</v>
       </c>
       <c r="H45" t="n">
         <v>31415</v>
@@ -1703,7 +1703,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237010955811</v>
+        <v>14.6237001419067</v>
       </c>
       <c r="H46" t="n">
         <v>33733</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369066238403</v>
+        <v>15.1369047164917</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270685195923</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -1964,7 +1964,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H55" t="n">
         <v>37252</v>
@@ -1993,7 +1993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H56" t="n">
         <v>23379</v>
@@ -2051,7 +2051,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527206420898</v>
+        <v>12.9527196884155</v>
       </c>
       <c r="H58" t="n">
         <v>30556</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111688613892</v>
+        <v>12.6111679077148</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320241928101</v>
+        <v>12.7320232391357</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2167,7 +2167,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602369308472</v>
+        <v>11.5602378845215</v>
       </c>
       <c r="H62" t="n">
         <v>43479</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.071418762207</v>
+        <v>10.0714197158813</v>
       </c>
       <c r="H63" t="n">
         <v>21708</v>
@@ -2254,7 +2254,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868625640869</v>
+        <v>9.80868530273438</v>
       </c>
       <c r="H65" t="n">
         <v>49411</v>
@@ -2312,7 +2312,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837593078613</v>
+        <v>9.45837497711182</v>
       </c>
       <c r="H67" t="n">
         <v>48156</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806465148926</v>
+        <v>9.10806560516357</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2399,7 +2399,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>8.58259963989258</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H70" t="n">
         <v>24355</v>
@@ -2428,7 +2428,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651287078857</v>
+        <v>8.76651477813721</v>
       </c>
       <c r="H71" t="n">
         <v>44594</v>
@@ -2457,7 +2457,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G72" t="n">
-        <v>8.58259963989258</v>
+        <v>8.58260059356689</v>
       </c>
       <c r="H72" t="n">
         <v>30457</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494094848633</v>
+        <v>8.54494190216064</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2515,7 +2515,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6701774597168</v>
+        <v>8.67017841339111</v>
       </c>
       <c r="H74" t="n">
         <v>15416</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500865936279</v>
+        <v>9.04500961303711</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2631,7 +2631,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328197479248</v>
+        <v>9.35328388214111</v>
       </c>
       <c r="H78" t="n">
         <v>29100</v>
@@ -2660,7 +2660,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G79" t="n">
-        <v>9.82620239257812</v>
+        <v>9.82620143890381</v>
       </c>
       <c r="H79" t="n">
         <v>19607</v>
@@ -2718,7 +2718,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968856811523</v>
+        <v>10.5968837738037</v>
       </c>
       <c r="H81" t="n">
         <v>17348</v>
@@ -2776,7 +2776,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156656265259</v>
+        <v>10.9156665802002</v>
       </c>
       <c r="H83" t="n">
         <v>6741</v>
@@ -2805,7 +2805,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G84" t="n">
-        <v>11.2887477874756</v>
+        <v>11.2887468338013</v>
       </c>
       <c r="H84" t="n">
         <v>6430</v>
@@ -2863,7 +2863,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878036499023</v>
+        <v>10.787802696228</v>
       </c>
       <c r="H86" t="n">
         <v>15151</v>
@@ -2892,7 +2892,7 @@
         <v>12.8079996109009</v>
       </c>
       <c r="G87" t="n">
-        <v>11.2169313430786</v>
+        <v>11.2169322967529</v>
       </c>
       <c r="H87" t="n">
         <v>10905</v>
@@ -2950,7 +2950,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898517608643</v>
+        <v>11.6898508071899</v>
       </c>
       <c r="H89" t="n">
         <v>19363</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229703903198</v>
+        <v>11.8229694366455</v>
       </c>
       <c r="H91" t="n">
         <v>16703</v>
@@ -3037,7 +3037,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325357437134</v>
+        <v>11.3325347900391</v>
       </c>
       <c r="H92" t="n">
         <v>25713</v>
@@ -3124,7 +3124,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471940994263</v>
+        <v>10.947193145752</v>
       </c>
       <c r="H95" t="n">
         <v>49105</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078775405884</v>
+        <v>10.3078784942627</v>
       </c>
       <c r="H100" t="n">
         <v>7478</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465744018555</v>
+        <v>10.2465734481812</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3356,7 +3356,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616907119751</v>
+        <v>10.6616897583008</v>
       </c>
       <c r="H103" t="n">
         <v>12365</v>
@@ -3385,7 +3385,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008718490601</v>
+        <v>10.3008708953857</v>
       </c>
       <c r="H104" t="n">
         <v>32832</v>
@@ -3472,7 +3472,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>11.3412923812866</v>
+        <v>11.3412933349609</v>
       </c>
       <c r="H107" t="n">
         <v>39114</v>
@@ -3501,7 +3501,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220272064209</v>
+        <v>11.3220262527466</v>
       </c>
       <c r="H108" t="n">
         <v>36330</v>
@@ -3530,7 +3530,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955926895142</v>
+        <v>11.3955907821655</v>
       </c>
       <c r="H109" t="n">
         <v>18584</v>
@@ -3588,7 +3588,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565723419189</v>
+        <v>11.6565732955933</v>
       </c>
       <c r="H111" t="n">
         <v>27521</v>
@@ -3617,7 +3617,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667593002319</v>
+        <v>11.8667583465576</v>
       </c>
       <c r="H112" t="n">
         <v>27613</v>
@@ -3675,7 +3675,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834667205811</v>
+        <v>12.3834657669067</v>
       </c>
       <c r="H114" t="n">
         <v>29369</v>
@@ -3791,7 +3791,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922233581543</v>
+        <v>12.3922243118286</v>
       </c>
       <c r="H118" t="n">
         <v>16297</v>
@@ -3820,7 +3820,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205715179443</v>
+        <v>12.2205724716187</v>
       </c>
       <c r="H119" t="n">
         <v>70567</v>
@@ -3878,7 +3878,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.7600479125977</v>
+        <v>12.7600498199463</v>
       </c>
       <c r="H121" t="n">
         <v>53970</v>
@@ -3907,7 +3907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614782333374</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H122" t="n">
         <v>27467</v>
@@ -3936,7 +3936,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.3100366592407</v>
+        <v>13.310037612915</v>
       </c>
       <c r="H123" t="n">
         <v>25697</v>
@@ -3965,7 +3965,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930057525635</v>
+        <v>12.9930047988892</v>
       </c>
       <c r="H124" t="n">
         <v>20213</v>
@@ -3994,7 +3994,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.7863235473633</v>
+        <v>12.786322593689</v>
       </c>
       <c r="H125" t="n">
         <v>14042</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901489257812</v>
+        <v>12.5901479721069</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4081,7 +4081,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H128" t="n">
         <v>20883</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.211950302124</v>
+        <v>13.2119512557983</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4139,7 +4139,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976144790649</v>
+        <v>13.3976135253906</v>
       </c>
       <c r="H130" t="n">
         <v>7245</v>
@@ -4197,7 +4197,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>13.3030309677124</v>
+        <v>13.3030300140381</v>
       </c>
       <c r="H132" t="n">
         <v>11780</v>
@@ -4226,7 +4226,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.5272302627563</v>
+        <v>13.527229309082</v>
       </c>
       <c r="H133" t="n">
         <v>18810</v>
@@ -4313,7 +4313,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H136" t="n">
         <v>7773</v>
@@ -4342,7 +4342,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H137" t="n">
         <v>5525</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681604385376</v>
+        <v>13.1681623458862</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4487,7 +4487,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501609802246</v>
+        <v>13.4501600265503</v>
       </c>
       <c r="H142" t="n">
         <v>4891</v>
@@ -4516,7 +4516,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979360580444</v>
+        <v>13.1979370117188</v>
       </c>
       <c r="H143" t="n">
         <v>3314</v>
@@ -4545,7 +4545,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928440093994</v>
+        <v>13.0928449630737</v>
       </c>
       <c r="H144" t="n">
         <v>3240</v>
@@ -4574,7 +4574,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490560531616</v>
+        <v>13.0490550994873</v>
       </c>
       <c r="H145" t="n">
         <v>1877</v>
@@ -4603,7 +4603,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772424697876</v>
+        <v>12.977240562439</v>
       </c>
       <c r="H146" t="n">
         <v>4221</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504835128784</v>
+        <v>13.2504844665527</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4661,7 +4661,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821737289429</v>
+        <v>13.1821746826172</v>
       </c>
       <c r="H148" t="n">
         <v>863</v>
@@ -4719,7 +4719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H150" t="n">
         <v>1530</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4806,7 +4806,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324831008911</v>
+        <v>13.5324850082397</v>
       </c>
       <c r="H153" t="n">
         <v>9502</v>
@@ -4835,7 +4835,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135395050049</v>
+        <v>13.3135385513306</v>
       </c>
       <c r="H154" t="n">
         <v>2851</v>
@@ -4864,7 +4864,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.4694261550903</v>
+        <v>13.4694271087646</v>
       </c>
       <c r="H155" t="n">
         <v>2209</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277135848999</v>
+        <v>13.2277145385742</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348829269409</v>
+        <v>13.1348819732666</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -5067,7 +5067,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309192657471</v>
+        <v>12.3309202194214</v>
       </c>
       <c r="H162" t="n">
         <v>17829</v>
@@ -5125,7 +5125,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393552780151</v>
+        <v>12.5393543243408</v>
       </c>
       <c r="H164" t="n">
         <v>30378</v>
@@ -5183,7 +5183,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.4307584762573</v>
+        <v>12.430757522583</v>
       </c>
       <c r="H166" t="n">
         <v>16661</v>
@@ -5299,7 +5299,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909322738647</v>
+        <v>13.1909313201904</v>
       </c>
       <c r="H170" t="n">
         <v>36613</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H171" t="n">
         <v>7984</v>
@@ -5357,7 +5357,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132160186768</v>
+        <v>13.5132169723511</v>
       </c>
       <c r="H172" t="n">
         <v>10655</v>
@@ -5386,7 +5386,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.686619758606</v>
+        <v>13.6866216659546</v>
       </c>
       <c r="H173" t="n">
         <v>4657</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5502,7 +5502,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H177" t="n">
         <v>16366</v>
@@ -5560,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H179" t="n">
         <v>13803</v>
@@ -5589,7 +5589,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H180" t="n">
         <v>13692</v>
@@ -5647,7 +5647,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H182" t="n">
         <v>15865</v>
@@ -5676,7 +5676,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G183" t="n">
-        <v>13.784707069397</v>
+        <v>13.7847061157227</v>
       </c>
       <c r="H183" t="n">
         <v>22904</v>
@@ -5705,7 +5705,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H184" t="n">
         <v>25117</v>
@@ -5734,7 +5734,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>14.0999870300293</v>
+        <v>14.0999879837036</v>
       </c>
       <c r="H185" t="n">
         <v>23215</v>
@@ -5763,7 +5763,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H186" t="n">
         <v>9698</v>
@@ -5792,7 +5792,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H187" t="n">
         <v>24640</v>
@@ -5821,7 +5821,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H188" t="n">
         <v>35173</v>
@@ -5850,7 +5850,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H189" t="n">
         <v>28944</v>
@@ -5879,7 +5879,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>14.0999870300293</v>
+        <v>14.0999879837036</v>
       </c>
       <c r="H190" t="n">
         <v>9258</v>
@@ -5966,7 +5966,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H193" t="n">
         <v>36033</v>
@@ -5995,7 +5995,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971311569214</v>
       </c>
       <c r="H194" t="n">
         <v>8929</v>
@@ -6082,7 +6082,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G197" t="n">
-        <v>13.2942714691162</v>
+        <v>13.2942733764648</v>
       </c>
       <c r="H197" t="n">
         <v>21767</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614782333374</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H199" t="n">
         <v>7759</v>
@@ -6169,7 +6169,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767562866211</v>
+        <v>13.2767581939697</v>
       </c>
       <c r="H200" t="n">
         <v>6789</v>
@@ -6227,7 +6227,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H202" t="n">
         <v>32085</v>
@@ -6256,7 +6256,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.3101720809937</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H203" t="n">
         <v>21909</v>
@@ -6285,7 +6285,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531513214111</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H204" t="n">
         <v>59951</v>
@@ -6314,7 +6314,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531513214111</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H205" t="n">
         <v>52305</v>
@@ -6343,7 +6343,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.4678134918213</v>
+        <v>14.467812538147</v>
       </c>
       <c r="H206" t="n">
         <v>39648</v>
@@ -6372,7 +6372,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H207" t="n">
         <v>18020</v>
@@ -6401,7 +6401,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H208" t="n">
         <v>11562</v>
@@ -6430,7 +6430,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0999870300293</v>
+        <v>14.0999879837036</v>
       </c>
       <c r="H209" t="n">
         <v>15103</v>
@@ -6459,7 +6459,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H210" t="n">
         <v>16575</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H212" t="n">
         <v>5728</v>
@@ -6633,7 +6633,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452014923096</v>
+        <v>14.3452024459839</v>
       </c>
       <c r="H216" t="n">
         <v>9351</v>
@@ -6662,7 +6662,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G217" t="n">
-        <v>14.1175031661987</v>
+        <v>14.1175022125244</v>
       </c>
       <c r="H217" t="n">
         <v>5382</v>
@@ -6778,7 +6778,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H221" t="n">
         <v>2428</v>
@@ -6807,7 +6807,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H222" t="n">
         <v>6474</v>
@@ -6865,7 +6865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.3117876052856</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H224" t="n">
         <v>45360</v>
@@ -6923,7 +6923,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.3117876052856</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H226" t="n">
         <v>5423</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219755172729</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7039,7 +7039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H230" t="n">
         <v>2511</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7097,7 +7097,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G232" t="n">
-        <v>13.784707069397</v>
+        <v>13.7847061157227</v>
       </c>
       <c r="H232" t="n">
         <v>19127</v>
@@ -7155,7 +7155,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H234" t="n">
         <v>16461</v>
@@ -7184,7 +7184,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H235" t="n">
         <v>16963</v>
@@ -7213,7 +7213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H236" t="n">
         <v>8277</v>
@@ -7329,7 +7329,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H240" t="n">
         <v>23600</v>
@@ -7358,7 +7358,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H241" t="n">
         <v>4135</v>
@@ -7387,7 +7387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H242" t="n">
         <v>10822</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270685195923</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219755172729</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7503,7 +7503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H246" t="n">
         <v>7116</v>
@@ -7619,7 +7619,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H250" t="n">
         <v>41070</v>
@@ -7677,7 +7677,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H252" t="n">
         <v>3351</v>
@@ -7706,7 +7706,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H253" t="n">
         <v>8244</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022232055664</v>
+        <v>13.8022222518921</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7764,7 +7764,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H255" t="n">
         <v>3852</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270685195923</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7851,7 +7851,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496747970581</v>
+        <v>13.7496757507324</v>
       </c>
       <c r="H258" t="n">
         <v>4171</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219755172729</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7938,7 +7938,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971311569214</v>
       </c>
       <c r="H261" t="n">
         <v>11448</v>
@@ -7967,7 +7967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197383880615</v>
+        <v>13.8197364807129</v>
       </c>
       <c r="H262" t="n">
         <v>19414</v>
@@ -8083,7 +8083,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.3101720809937</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H266" t="n">
         <v>8011</v>
@@ -8112,7 +8112,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H267" t="n">
         <v>21797</v>
@@ -8141,7 +8141,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H268" t="n">
         <v>16682</v>
@@ -8228,7 +8228,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H271" t="n">
         <v>6060</v>
@@ -8257,7 +8257,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H272" t="n">
         <v>8570</v>
@@ -8286,7 +8286,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079359054565</v>
+        <v>14.6079368591309</v>
       </c>
       <c r="H273" t="n">
         <v>7891</v>
@@ -8344,7 +8344,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401103973389</v>
+        <v>14.2401113510132</v>
       </c>
       <c r="H275" t="n">
         <v>14243</v>
@@ -8373,7 +8373,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276882171631</v>
+        <v>14.3276891708374</v>
       </c>
       <c r="H276" t="n">
         <v>6927</v>
@@ -8431,7 +8431,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729036331177</v>
+        <v>14.572904586792</v>
       </c>
       <c r="H278" t="n">
         <v>26113</v>
@@ -8460,7 +8460,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.203462600708</v>
+        <v>15.2034635543823</v>
       </c>
       <c r="H279" t="n">
         <v>80397</v>
@@ -8489,7 +8489,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311656951904</v>
+        <v>15.4311666488647</v>
       </c>
       <c r="H280" t="n">
         <v>50717</v>
@@ -8547,7 +8547,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989912033081</v>
+        <v>15.7989921569824</v>
       </c>
       <c r="H282" t="n">
         <v>60104</v>
@@ -8576,7 +8576,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888042449951</v>
+        <v>15.5888051986694</v>
       </c>
       <c r="H283" t="n">
         <v>32761</v>
@@ -8605,7 +8605,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165035247803</v>
+        <v>15.8165044784546</v>
       </c>
       <c r="H284" t="n">
         <v>60606</v>
@@ -8634,7 +8634,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814750671387</v>
+        <v>15.7814769744873</v>
       </c>
       <c r="H285" t="n">
         <v>16215</v>
@@ -8663,7 +8663,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712909698486</v>
+        <v>15.5712919235229</v>
       </c>
       <c r="H286" t="n">
         <v>9069</v>
@@ -8692,7 +8692,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317844390869</v>
+        <v>16.1317863464355</v>
       </c>
       <c r="H287" t="n">
         <v>34304</v>
@@ -8779,7 +8779,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973766326904</v>
+        <v>16.7973728179932</v>
       </c>
       <c r="H290" t="n">
         <v>32844</v>
@@ -8837,7 +8837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403549194336</v>
+        <v>17.3403568267822</v>
       </c>
       <c r="H292" t="n">
         <v>108964</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.2527809143066</v>
+        <v>17.252779006958</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9011,7 +9011,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.646879196167</v>
+        <v>17.6468772888184</v>
       </c>
       <c r="H298" t="n">
         <v>49334</v>
@@ -9040,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.5155124664307</v>
+        <v>17.515510559082</v>
       </c>
       <c r="H299" t="n">
         <v>21074</v>
@@ -9069,7 +9069,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228416442871</v>
+        <v>17.3228378295898</v>
       </c>
       <c r="H300" t="n">
         <v>7964</v>
@@ -9098,7 +9098,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.7273120880127</v>
+        <v>16.7273139953613</v>
       </c>
       <c r="H301" t="n">
         <v>28487</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979953765869</v>
+        <v>17.4979972839355</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9156,7 +9156,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H303" t="n">
         <v>51778</v>
@@ -9185,7 +9185,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.172342300415</v>
+        <v>18.1723442077637</v>
       </c>
       <c r="H304" t="n">
         <v>46277</v>
@@ -9214,7 +9214,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>18.1285552978516</v>
+        <v>18.1285533905029</v>
       </c>
       <c r="H305" t="n">
         <v>35889</v>
@@ -9301,7 +9301,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108520507812</v>
+        <v>19.310848236084</v>
       </c>
       <c r="H308" t="n">
         <v>58530</v>
@@ -9649,7 +9649,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173725128174</v>
+        <v>19.6173706054688</v>
       </c>
       <c r="H320" t="n">
         <v>55008</v>
@@ -9678,7 +9678,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925300598145</v>
+        <v>19.7925243377686</v>
       </c>
       <c r="H321" t="n">
         <v>38533</v>
@@ -9736,7 +9736,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794815063477</v>
+        <v>19.1794853210449</v>
       </c>
       <c r="H323" t="n">
         <v>9282</v>
@@ -9823,7 +9823,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735816955566</v>
       </c>
       <c r="H326" t="n">
         <v>15812</v>
@@ -9852,7 +9852,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735816955566</v>
       </c>
       <c r="H327" t="n">
         <v>7040</v>
@@ -9881,7 +9881,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H328" t="n">
         <v>5122</v>
@@ -9910,7 +9910,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729648590088</v>
+        <v>18.8729610443115</v>
       </c>
       <c r="H329" t="n">
         <v>14665</v>
@@ -9939,7 +9939,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H330" t="n">
         <v>9202</v>
@@ -9968,7 +9968,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H331" t="n">
         <v>11487</v>
@@ -10026,7 +10026,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H333" t="n">
         <v>8384</v>
@@ -10055,7 +10055,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H334" t="n">
         <v>5987</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546390533447</v>
+        <v>19.3546371459961</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10200,7 +10200,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H339" t="n">
         <v>11503</v>
@@ -10229,7 +10229,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794815063477</v>
+        <v>19.1794853210449</v>
       </c>
       <c r="H340" t="n">
         <v>8629</v>
@@ -10287,7 +10287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H342" t="n">
         <v>48534</v>
@@ -10316,7 +10316,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H343" t="n">
         <v>22326</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799438476562</v>
+        <v>18.8799457550049</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10432,7 +10432,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797565460205</v>
+        <v>19.2797546386719</v>
       </c>
       <c r="H347" t="n">
         <v>18924</v>
@@ -10490,7 +10490,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.2126445770264</v>
+        <v>20.212646484375</v>
       </c>
       <c r="H349" t="n">
         <v>34567</v>
@@ -10519,7 +10519,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903408050537</v>
+        <v>20.3903427124023</v>
       </c>
       <c r="H350" t="n">
         <v>39422</v>
@@ -10548,7 +10548,7 @@
         <v>23</v>
       </c>
       <c r="G351" t="n">
-        <v>20.4347629547119</v>
+        <v>20.4347648620605</v>
       </c>
       <c r="H351" t="n">
         <v>25210</v>
@@ -10693,7 +10693,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G356" t="n">
-        <v>20.8345756530762</v>
+        <v>20.8345737457275</v>
       </c>
       <c r="H356" t="n">
         <v>39582</v>
@@ -10751,7 +10751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461078643799</v>
+        <v>19.9461059570312</v>
       </c>
       <c r="H358" t="n">
         <v>49210</v>
@@ -10780,7 +10780,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.835521697998</v>
+        <v>18.8355197906494</v>
       </c>
       <c r="H359" t="n">
         <v>57619</v>
@@ -10809,7 +10809,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.7466735839844</v>
+        <v>18.746675491333</v>
       </c>
       <c r="H360" t="n">
         <v>21783</v>
@@ -10838,7 +10838,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910976409912</v>
+        <v>18.7910995483398</v>
       </c>
       <c r="H361" t="n">
         <v>19501</v>
@@ -10867,7 +10867,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>19.6351432800293</v>
+        <v>19.6351413726807</v>
       </c>
       <c r="H362" t="n">
         <v>29703</v>
@@ -10896,7 +10896,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>19.457447052002</v>
+        <v>19.4574489593506</v>
       </c>
       <c r="H363" t="n">
         <v>18679</v>
@@ -10954,7 +10954,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5236129760742</v>
+        <v>20.5236110687256</v>
       </c>
       <c r="H365" t="n">
         <v>43029</v>
@@ -11012,7 +11012,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570686340332</v>
+        <v>20.2570667266846</v>
       </c>
       <c r="H367" t="n">
         <v>19035</v>
@@ -11041,7 +11041,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570686340332</v>
+        <v>20.2570667266846</v>
       </c>
       <c r="H368" t="n">
         <v>25835</v>
@@ -11331,7 +11331,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.833625793457</v>
+        <v>22.8336277008057</v>
       </c>
       <c r="H378" t="n">
         <v>26713</v>
@@ -11360,7 +11360,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H379" t="n">
         <v>1533317</v>
@@ -11418,7 +11418,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H381" t="n">
         <v>46241</v>
@@ -11447,7 +11447,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563117980957</v>
+        <v>21.8563098907471</v>
       </c>
       <c r="H382" t="n">
         <v>53898</v>
@@ -11563,7 +11563,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H386" t="n">
         <v>27193</v>
@@ -11592,7 +11592,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011161804199</v>
+        <v>21.1011142730713</v>
       </c>
       <c r="H387" t="n">
         <v>8616</v>
@@ -11621,7 +11621,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566940307617</v>
+        <v>21.0566921234131</v>
       </c>
       <c r="H388" t="n">
         <v>20039</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11882,7 +11882,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680332183838</v>
+        <v>20.5680351257324</v>
       </c>
       <c r="H397" t="n">
         <v>6449</v>
@@ -11911,7 +11911,7 @@
         <v>24.5</v>
       </c>
       <c r="G398" t="n">
-        <v>21.7674655914307</v>
+        <v>21.767463684082</v>
       </c>
       <c r="H398" t="n">
         <v>74119</v>
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H399" t="n">
         <v>85005</v>
@@ -12027,7 +12027,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H402" t="n">
         <v>58589</v>
@@ -12085,7 +12085,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G404" t="n">
-        <v>21.4120788574219</v>
+        <v>21.4120769500732</v>
       </c>
       <c r="H404" t="n">
         <v>17059</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12288,7 +12288,7 @@
         <v>24.5</v>
       </c>
       <c r="G411" t="n">
-        <v>21.7674655914307</v>
+        <v>21.767463684082</v>
       </c>
       <c r="H411" t="n">
         <v>36810</v>
@@ -12317,7 +12317,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H412" t="n">
         <v>32846</v>
@@ -12462,7 +12462,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3893928527832</v>
+        <v>22.3893947601318</v>
       </c>
       <c r="H417" t="n">
         <v>9809</v>
@@ -12549,7 +12549,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>22.3893928527832</v>
+        <v>22.3893947601318</v>
       </c>
       <c r="H420" t="n">
         <v>10509</v>
@@ -12607,7 +12607,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113201141357</v>
+        <v>23.0113220214844</v>
       </c>
       <c r="H422" t="n">
         <v>22051</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444011688232</v>
+        <v>23.5443992614746</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12752,7 +12752,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886341094971</v>
+        <v>23.9886322021484</v>
       </c>
       <c r="H427" t="n">
         <v>21987</v>
@@ -12781,7 +12781,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772930145264</v>
+        <v>24.4772911071777</v>
       </c>
       <c r="H428" t="n">
         <v>27149</v>
@@ -12810,7 +12810,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>24.1219043731689</v>
+        <v>24.1219024658203</v>
       </c>
       <c r="H429" t="n">
         <v>41301</v>
@@ -12868,7 +12868,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215278625488</v>
+        <v>24.9215259552002</v>
       </c>
       <c r="H431" t="n">
         <v>25118</v>
@@ -12897,7 +12897,7 @@
         <v>27.5</v>
       </c>
       <c r="G432" t="n">
-        <v>24.4328708648682</v>
+        <v>24.4328689575195</v>
       </c>
       <c r="H432" t="n">
         <v>17561</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661392211914</v>
+        <v>24.56614112854</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -12984,7 +12984,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326816558838</v>
+        <v>24.8326797485352</v>
       </c>
       <c r="H435" t="n">
         <v>15025</v>
@@ -13013,7 +13013,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324886322021</v>
+        <v>25.2324905395508</v>
       </c>
       <c r="H436" t="n">
         <v>14765</v>
@@ -13071,7 +13071,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H438" t="n">
         <v>49309</v>
@@ -13100,7 +13100,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H439" t="n">
         <v>22024</v>
@@ -13129,7 +13129,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H440" t="n">
         <v>28408</v>
@@ -13158,7 +13158,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207691192627</v>
+        <v>26.5207710266113</v>
       </c>
       <c r="H441" t="n">
         <v>28926</v>
@@ -13187,7 +13187,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H442" t="n">
         <v>23385</v>
@@ -13216,7 +13216,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205760955811</v>
+        <v>26.9205799102783</v>
       </c>
       <c r="H443" t="n">
         <v>23035</v>
@@ -13245,7 +13245,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536590576172</v>
+        <v>27.4536609649658</v>
       </c>
       <c r="H444" t="n">
         <v>42660</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425090789795</v>
+        <v>27.5425052642822</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13303,7 +13303,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975135803223</v>
+        <v>28.6975154876709</v>
       </c>
       <c r="H446" t="n">
         <v>109999</v>
@@ -13332,7 +13332,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300270080566</v>
+        <v>30.4300308227539</v>
       </c>
       <c r="H447" t="n">
         <v>138213</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967529296875</v>
+        <v>30.2967567443848</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13419,7 +13419,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636737823486</v>
+        <v>29.7636775970459</v>
       </c>
       <c r="H450" t="n">
         <v>69374</v>
@@ -13448,7 +13448,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417503356934</v>
+        <v>29.1417484283447</v>
       </c>
       <c r="H451" t="n">
         <v>55282</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527168273926</v>
+        <v>29.4527130126953</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13506,7 +13506,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748332977295</v>
+        <v>29.6748294830322</v>
       </c>
       <c r="H453" t="n">
         <v>18449</v>
@@ -13535,7 +13535,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300270080566</v>
+        <v>30.4300308227539</v>
       </c>
       <c r="H454" t="n">
         <v>27063</v>
@@ -13622,7 +13622,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.764627456665</v>
+        <v>27.7646217346191</v>
       </c>
       <c r="H457" t="n">
         <v>101299</v>
@@ -13651,7 +13651,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311622619629</v>
+        <v>28.0311641693115</v>
       </c>
       <c r="H458" t="n">
         <v>38519</v>
@@ -13680,7 +13680,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311622619629</v>
+        <v>28.0311641693115</v>
       </c>
       <c r="H459" t="n">
         <v>26817</v>
@@ -13738,7 +13738,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.4753971099854</v>
+        <v>28.475399017334</v>
       </c>
       <c r="H461" t="n">
         <v>73902</v>
@@ -13825,7 +13825,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.230598449707</v>
+        <v>29.2305965423584</v>
       </c>
       <c r="H464" t="n">
         <v>33973</v>
@@ -13883,7 +13883,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.1644344329834</v>
+        <v>28.1644382476807</v>
       </c>
       <c r="H466" t="n">
         <v>19936</v>
@@ -13912,7 +13912,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H467" t="n">
         <v>54363</v>
@@ -13941,7 +13941,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525199890137</v>
+        <v>29.8525218963623</v>
       </c>
       <c r="H468" t="n">
         <v>33525</v>
@@ -13970,7 +13970,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.74098777771</v>
+        <v>30.7409915924072</v>
       </c>
       <c r="H469" t="n">
         <v>41790</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627277374268</v>
+        <v>31.7627258300781</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14086,7 +14086,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H473" t="n">
         <v>41695</v>
@@ -14231,7 +14231,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G478" t="n">
-        <v>32.3402290344238</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H478" t="n">
         <v>49641</v>
@@ -14260,7 +14260,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H479" t="n">
         <v>24196</v>
@@ -14289,7 +14289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513885498047</v>
+        <v>32.2513847351074</v>
       </c>
       <c r="H480" t="n">
         <v>25306</v>
@@ -14405,7 +14405,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942932128906</v>
+        <v>35.4942970275879</v>
       </c>
       <c r="H484" t="n">
         <v>95655</v>
@@ -14434,7 +14434,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H485" t="n">
         <v>147072</v>
@@ -14521,7 +14521,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398582458496</v>
+        <v>33.1398544311523</v>
       </c>
       <c r="H488" t="n">
         <v>34481</v>
@@ -14550,7 +14550,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065841674805</v>
+        <v>33.0065879821777</v>
       </c>
       <c r="H489" t="n">
         <v>27315</v>
@@ -14637,7 +14637,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288879394531</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H492" t="n">
         <v>26262</v>
@@ -14666,7 +14666,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844657897949</v>
+        <v>32.7844696044922</v>
       </c>
       <c r="H493" t="n">
         <v>16789</v>
@@ -14724,7 +14724,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>33.806209564209</v>
+        <v>33.8062057495117</v>
       </c>
       <c r="H495" t="n">
         <v>56617</v>
@@ -14753,7 +14753,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>33.806209564209</v>
+        <v>33.8062057495117</v>
       </c>
       <c r="H496" t="n">
         <v>24430</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14840,7 +14840,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H499" t="n">
         <v>11923</v>
@@ -14927,7 +14927,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404220581055</v>
+        <v>31.9404239654541</v>
       </c>
       <c r="H502" t="n">
         <v>44140</v>
@@ -14956,7 +14956,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G503" t="n">
-        <v>32.3402290344238</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H503" t="n">
         <v>22134</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177360534668</v>
+        <v>32.9177398681641</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15159,7 +15159,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071537017822</v>
+        <v>31.8071517944336</v>
       </c>
       <c r="H510" t="n">
         <v>24075</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627277374268</v>
+        <v>31.7627258300781</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15304,7 +15304,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.473503112793</v>
+        <v>32.4734992980957</v>
       </c>
       <c r="H515" t="n">
         <v>28750</v>
@@ -15333,7 +15333,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.473503112793</v>
+        <v>32.4734992980957</v>
       </c>
       <c r="H516" t="n">
         <v>39270</v>
@@ -15362,7 +15362,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G517" t="n">
-        <v>32.3402290344238</v>
+        <v>32.3402328491211</v>
       </c>
       <c r="H517" t="n">
         <v>59170</v>
@@ -15391,7 +15391,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288879394531</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H518" t="n">
         <v>13845</v>
@@ -15420,7 +15420,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290771484375</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H519" t="n">
         <v>27308</v>
@@ -15449,7 +15449,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.3175506591797</v>
+        <v>33.317554473877</v>
       </c>
       <c r="H520" t="n">
         <v>18235</v>
@@ -15623,7 +15623,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283279418945</v>
+        <v>34.0283241271973</v>
       </c>
       <c r="H526" t="n">
         <v>15120</v>
@@ -15652,7 +15652,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H527" t="n">
         <v>15724</v>
@@ -15710,7 +15710,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960037231445</v>
+        <v>31.8960018157959</v>
       </c>
       <c r="H529" t="n">
         <v>38776</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15797,7 +15797,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842765808105</v>
+        <v>33.1842803955078</v>
       </c>
       <c r="H532" t="n">
         <v>28931</v>
@@ -15826,7 +15826,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394798278809</v>
+        <v>33.9394760131836</v>
       </c>
       <c r="H533" t="n">
         <v>33489</v>
@@ -15971,7 +15971,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727424621582</v>
+        <v>34.0727500915527</v>
       </c>
       <c r="H538" t="n">
         <v>33816</v>
@@ -16116,7 +16116,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290771484375</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H543" t="n">
         <v>43887</v>
@@ -16145,7 +16145,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394798278809</v>
+        <v>33.9394760131836</v>
       </c>
       <c r="H544" t="n">
         <v>89245</v>
@@ -16174,7 +16174,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H545" t="n">
         <v>71422</v>
@@ -16261,7 +16261,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H548" t="n">
         <v>151703</v>
@@ -16290,7 +16290,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279457092285</v>
+        <v>34.8279418945312</v>
       </c>
       <c r="H549" t="n">
         <v>115069</v>
@@ -16348,7 +16348,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H551" t="n">
         <v>43962</v>
@@ -16406,7 +16406,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H553" t="n">
         <v>48943</v>
@@ -16522,7 +16522,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>33.806209564209</v>
+        <v>33.8062057495117</v>
       </c>
       <c r="H557" t="n">
         <v>40431</v>
@@ -16580,7 +16580,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394798278809</v>
+        <v>33.9394760131836</v>
       </c>
       <c r="H559" t="n">
         <v>87892</v>
@@ -16609,7 +16609,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721786499023</v>
+        <v>35.2721748352051</v>
       </c>
       <c r="H560" t="n">
         <v>92873</v>
@@ -16638,7 +16638,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>36.738151550293</v>
+        <v>36.7381477355957</v>
       </c>
       <c r="H561" t="n">
         <v>96737</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.4054489135742</v>
+        <v>35.405445098877</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16696,7 +16696,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714218139648</v>
+        <v>36.8714256286621</v>
       </c>
       <c r="H563" t="n">
         <v>79980</v>
@@ -16725,7 +16725,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>34.3837127685547</v>
+        <v>34.3837089538574</v>
       </c>
       <c r="H564" t="n">
         <v>118997</v>
@@ -16928,7 +16928,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.343074798584</v>
+        <v>26.3430767059326</v>
       </c>
       <c r="H571" t="n">
         <v>102740</v>
@@ -16957,7 +16957,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873058319092</v>
+        <v>26.7873096466064</v>
       </c>
       <c r="H572" t="n">
         <v>79386</v>
@@ -16986,7 +16986,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.230598449707</v>
+        <v>29.2305965423584</v>
       </c>
       <c r="H573" t="n">
         <v>133949</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190662384033</v>
+        <v>30.1190643310547</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17044,7 +17044,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525199890137</v>
+        <v>29.8525218963623</v>
       </c>
       <c r="H575" t="n">
         <v>71925</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184928894043</v>
+        <v>31.3184947967529</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17189,7 +17189,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623512268066</v>
+        <v>32.5623550415039</v>
       </c>
       <c r="H580" t="n">
         <v>40631</v>
@@ -17247,7 +17247,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298397064209</v>
+        <v>30.8298358917236</v>
       </c>
       <c r="H582" t="n">
         <v>35488</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186820983887</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17334,7 +17334,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H585" t="n">
         <v>89419</v>
@@ -17450,7 +17450,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513885498047</v>
+        <v>32.2513847351074</v>
       </c>
       <c r="H589" t="n">
         <v>67180</v>
@@ -17479,7 +17479,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H590" t="n">
         <v>44682</v>
@@ -17595,7 +17595,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636737823486</v>
+        <v>29.7636775970459</v>
       </c>
       <c r="H594" t="n">
         <v>35604</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186820983887</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17769,7 +17769,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H600" t="n">
         <v>24723</v>
@@ -17885,7 +17885,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.9640560150146</v>
+        <v>28.9640522003174</v>
       </c>
       <c r="H604" t="n">
         <v>20198</v>
@@ -17914,7 +17914,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859851837158</v>
+        <v>29.5859832763672</v>
       </c>
       <c r="H605" t="n">
         <v>31886</v>
@@ -17943,7 +17943,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H606" t="n">
         <v>22611</v>
@@ -17972,7 +17972,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H607" t="n">
         <v>27177</v>
@@ -18030,7 +18030,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H609" t="n">
         <v>29532</v>
@@ -18088,7 +18088,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H611" t="n">
         <v>81317</v>
@@ -18117,7 +18117,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H612" t="n">
         <v>85415</v>
@@ -18146,7 +18146,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H613" t="n">
         <v>43669</v>
@@ -18175,7 +18175,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H614" t="n">
         <v>41499</v>
@@ -18204,7 +18204,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828506469727</v>
+        <v>32.3828468322754</v>
       </c>
       <c r="H615" t="n">
         <v>35851</v>
@@ -18233,7 +18233,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H616" t="n">
         <v>45928</v>
@@ -18320,7 +18320,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>32.9255828857422</v>
+        <v>32.9255790710449</v>
       </c>
       <c r="H619" t="n">
         <v>22834</v>
@@ -18349,7 +18349,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9757995605469</v>
+        <v>31.9758014678955</v>
       </c>
       <c r="H620" t="n">
         <v>19405</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903427124023</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18523,7 +18523,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617126464844</v>
+        <v>31.1617069244385</v>
       </c>
       <c r="H626" t="n">
         <v>16502</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903427124023</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18610,7 +18610,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189765930176</v>
+        <v>30.6189804077148</v>
       </c>
       <c r="H629" t="n">
         <v>25073</v>
@@ -18726,7 +18726,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5737533569336</v>
+        <v>30.573751449585</v>
       </c>
       <c r="H633" t="n">
         <v>27780</v>
@@ -18842,7 +18842,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H637" t="n">
         <v>26649</v>
@@ -18871,7 +18871,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766967773438</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H638" t="n">
         <v>56267</v>
@@ -18900,7 +18900,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H639" t="n">
         <v>19934</v>
@@ -18929,7 +18929,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766967773438</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H640" t="n">
         <v>27100</v>
@@ -18987,7 +18987,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H642" t="n">
         <v>7805</v>
@@ -19016,7 +19016,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>29.0812454223633</v>
+        <v>29.0812473297119</v>
       </c>
       <c r="H643" t="n">
         <v>23506</v>
@@ -19045,7 +19045,7 @@
         <v>32</v>
       </c>
       <c r="G644" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H644" t="n">
         <v>31552</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H646" t="n">
         <v>21557</v>
@@ -19132,7 +19132,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H647" t="n">
         <v>19011</v>
@@ -19161,7 +19161,7 @@
         <v>32</v>
       </c>
       <c r="G648" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H648" t="n">
         <v>10722</v>
@@ -19219,7 +19219,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G650" t="n">
-        <v>29.0360145568848</v>
+        <v>29.0360164642334</v>
       </c>
       <c r="H650" t="n">
         <v>20929</v>
@@ -19248,7 +19248,7 @@
         <v>32</v>
       </c>
       <c r="G651" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H651" t="n">
         <v>18834</v>
@@ -19306,7 +19306,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339664459229</v>
+        <v>27.6339683532715</v>
       </c>
       <c r="H653" t="n">
         <v>22878</v>
@@ -19335,7 +19335,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H654" t="n">
         <v>70905</v>
@@ -19364,7 +19364,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>28.0862407684326</v>
+        <v>28.0862426757812</v>
       </c>
       <c r="H655" t="n">
         <v>36534</v>
@@ -19451,7 +19451,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H658" t="n">
         <v>15664</v>
@@ -19538,7 +19538,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H661" t="n">
         <v>16406</v>
@@ -19567,7 +19567,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787467956543</v>
+        <v>29.5787506103516</v>
       </c>
       <c r="H662" t="n">
         <v>11492</v>
@@ -19596,7 +19596,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214790344238</v>
+        <v>30.1214771270752</v>
       </c>
       <c r="H663" t="n">
         <v>13226</v>
@@ -19625,7 +19625,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H664" t="n">
         <v>12292</v>
@@ -19654,7 +19654,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H665" t="n">
         <v>5963</v>
@@ -19741,7 +19741,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G668" t="n">
-        <v>29.0360145568848</v>
+        <v>29.0360164642334</v>
       </c>
       <c r="H668" t="n">
         <v>37372</v>
@@ -19828,7 +19828,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>30.6642093658447</v>
+        <v>30.6642055511475</v>
       </c>
       <c r="H671" t="n">
         <v>28977</v>
@@ -19857,7 +19857,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285224914551</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H672" t="n">
         <v>11102</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355735778809</v>
+        <v>30.935567855835</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19944,7 +19944,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9807987213135</v>
+        <v>30.9808006286621</v>
       </c>
       <c r="H675" t="n">
         <v>14000</v>
@@ -19973,7 +19973,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023872375488</v>
+        <v>30.3023891448975</v>
       </c>
       <c r="H676" t="n">
         <v>13444</v>
@@ -20002,7 +20002,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832973480225</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H677" t="n">
         <v>25987</v>
@@ -20031,7 +20031,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787467956543</v>
+        <v>29.5787506103516</v>
       </c>
       <c r="H678" t="n">
         <v>13528</v>
@@ -20089,7 +20089,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H680" t="n">
         <v>18879</v>
@@ -20118,7 +20118,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H681" t="n">
         <v>24865</v>
@@ -20147,7 +20147,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048839569092</v>
+        <v>29.8048877716064</v>
       </c>
       <c r="H682" t="n">
         <v>13128</v>
@@ -20205,7 +20205,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H684" t="n">
         <v>27461</v>
@@ -20234,7 +20234,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G685" t="n">
-        <v>29.0360145568848</v>
+        <v>29.0360164642334</v>
       </c>
       <c r="H685" t="n">
         <v>7357</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H687" t="n">
         <v>31220</v>
@@ -20321,7 +20321,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H688" t="n">
         <v>9866</v>
@@ -20350,7 +20350,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H689" t="n">
         <v>6251</v>
@@ -20408,7 +20408,7 @@
         <v>32</v>
       </c>
       <c r="G691" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H691" t="n">
         <v>11145</v>
@@ -20466,7 +20466,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123779296875</v>
+        <v>28.3123798370361</v>
       </c>
       <c r="H693" t="n">
         <v>18525</v>
@@ -20495,7 +20495,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505596160889</v>
+        <v>27.9505615234375</v>
       </c>
       <c r="H694" t="n">
         <v>28033</v>
@@ -20524,7 +20524,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H695" t="n">
         <v>25276</v>
@@ -20611,7 +20611,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H698" t="n">
         <v>35920</v>
@@ -20640,7 +20640,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285224914551</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H699" t="n">
         <v>56297</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.7194271087646</v>
+        <v>28.719425201416</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20814,7 +20814,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>28.0862407684326</v>
+        <v>28.0862426757812</v>
       </c>
       <c r="H705" t="n">
         <v>27391</v>
@@ -20843,7 +20843,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G706" t="n">
-        <v>29.0360145568848</v>
+        <v>29.0360164642334</v>
       </c>
       <c r="H706" t="n">
         <v>10664</v>
@@ -20872,7 +20872,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H707" t="n">
         <v>13065</v>
@@ -20901,7 +20901,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G708" t="n">
-        <v>29.0812454223633</v>
+        <v>29.0812473297119</v>
       </c>
       <c r="H708" t="n">
         <v>15124</v>
@@ -20930,7 +20930,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957866668701</v>
+        <v>27.9957885742188</v>
       </c>
       <c r="H709" t="n">
         <v>20930</v>
@@ -20959,7 +20959,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364650726318</v>
+        <v>27.1364669799805</v>
       </c>
       <c r="H710" t="n">
         <v>48790</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314678192139</v>
+        <v>28.1314697265625</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21017,7 +21017,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289730072021</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H712" t="n">
         <v>33341</v>
@@ -21104,7 +21104,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048839569092</v>
+        <v>29.8048877716064</v>
       </c>
       <c r="H715" t="n">
         <v>26731</v>
@@ -21133,7 +21133,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H716" t="n">
         <v>30596</v>
@@ -21162,7 +21162,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119331359863</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H717" t="n">
         <v>59213</v>
@@ -21191,7 +21191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H718" t="n">
         <v>15926</v>
@@ -21220,7 +21220,7 @@
         <v>32</v>
       </c>
       <c r="G719" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H719" t="n">
         <v>25143</v>
@@ -21249,7 +21249,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H720" t="n">
         <v>19906</v>
@@ -21394,7 +21394,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H725" t="n">
         <v>27078</v>
@@ -21452,7 +21452,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H727" t="n">
         <v>23140</v>
@@ -21481,7 +21481,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G728" t="n">
-        <v>29.0812454223633</v>
+        <v>29.0812473297119</v>
       </c>
       <c r="H728" t="n">
         <v>20050</v>
@@ -21539,7 +21539,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H730" t="n">
         <v>19631</v>
@@ -21568,7 +21568,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H731" t="n">
         <v>24208</v>
@@ -21597,7 +21597,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H732" t="n">
         <v>39155</v>
@@ -21655,7 +21655,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H734" t="n">
         <v>19361</v>
@@ -21684,7 +21684,7 @@
         <v>32</v>
       </c>
       <c r="G735" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H735" t="n">
         <v>17587</v>
@@ -21771,7 +21771,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H738" t="n">
         <v>31102</v>
@@ -21800,7 +21800,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H739" t="n">
         <v>12783</v>
@@ -21829,7 +21829,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H740" t="n">
         <v>25796</v>
@@ -21887,7 +21887,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285224914551</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H742" t="n">
         <v>22513</v>
@@ -21916,7 +21916,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H743" t="n">
         <v>39509</v>
@@ -21974,7 +21974,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401184082031</v>
+        <v>31.8401165008545</v>
       </c>
       <c r="H745" t="n">
         <v>20993</v>
@@ -22003,7 +22003,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210342407227</v>
+        <v>32.0210304260254</v>
       </c>
       <c r="H746" t="n">
         <v>23768</v>
@@ -22061,7 +22061,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119331359863</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H748" t="n">
         <v>18927</v>
@@ -22119,7 +22119,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832973480225</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H750" t="n">
         <v>5976</v>
@@ -22148,7 +22148,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.5737533569336</v>
+        <v>30.573751449585</v>
       </c>
       <c r="H751" t="n">
         <v>7222</v>
@@ -22206,7 +22206,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H753" t="n">
         <v>33549</v>
@@ -22235,7 +22235,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235271453857</v>
+        <v>31.5235290527344</v>
       </c>
       <c r="H754" t="n">
         <v>23044</v>
@@ -22293,7 +22293,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H756" t="n">
         <v>12661</v>
@@ -22351,7 +22351,7 @@
         <v>35</v>
       </c>
       <c r="G758" t="n">
-        <v>31.6592082977295</v>
+        <v>31.6592102050781</v>
       </c>
       <c r="H758" t="n">
         <v>36492</v>
@@ -22409,7 +22409,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H760" t="n">
         <v>38359</v>
@@ -22467,7 +22467,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H762" t="n">
         <v>46057</v>
@@ -22496,7 +22496,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G763" t="n">
-        <v>32.2019348144531</v>
+        <v>32.2019386291504</v>
       </c>
       <c r="H763" t="n">
         <v>35066</v>
@@ -22525,7 +22525,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853454589844</v>
+        <v>31.885347366333</v>
       </c>
       <c r="H764" t="n">
         <v>11653</v>
@@ -22583,7 +22583,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G766" t="n">
-        <v>32.2019348144531</v>
+        <v>32.2019386291504</v>
       </c>
       <c r="H766" t="n">
         <v>18901</v>
@@ -22612,7 +22612,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969451904297</v>
+        <v>33.1969413757324</v>
       </c>
       <c r="H767" t="n">
         <v>47582</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521648406982</v>
+        <v>31.252161026001</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637588500977</v>
+        <v>32.5637626647949</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -22873,7 +22873,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H776" t="n">
         <v>6543</v>
@@ -22902,7 +22902,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H777" t="n">
         <v>22186</v>
@@ -22960,7 +22960,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H779" t="n">
         <v>8669</v>
@@ -22989,7 +22989,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064872741699</v>
+        <v>33.1064834594727</v>
       </c>
       <c r="H780" t="n">
         <v>8743</v>
@@ -23047,7 +23047,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.8753547668457</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H782" t="n">
         <v>27238</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301315307617</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301315307617</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301315307617</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23221,7 +23221,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.8753547668457</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H788" t="n">
         <v>10901</v>
@@ -23279,7 +23279,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442184448242</v>
+        <v>34.6442222595215</v>
       </c>
       <c r="H790" t="n">
         <v>23430</v>
@@ -23337,7 +23337,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G792" t="n">
-        <v>34.9608116149902</v>
+        <v>34.9608154296875</v>
       </c>
       <c r="H792" t="n">
         <v>32491</v>
@@ -23366,7 +23366,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>34.1014938354492</v>
+        <v>34.101490020752</v>
       </c>
       <c r="H793" t="n">
         <v>25794</v>
@@ -23424,7 +23424,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H795" t="n">
         <v>28476</v>
@@ -23453,7 +23453,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H796" t="n">
         <v>22692</v>
@@ -23482,7 +23482,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035438537598</v>
+        <v>35.5035400390625</v>
       </c>
       <c r="H797" t="n">
         <v>15860</v>
@@ -23511,7 +23511,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558181762695</v>
+        <v>35.9558143615723</v>
       </c>
       <c r="H798" t="n">
         <v>25747</v>
@@ -23540,7 +23540,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392211914062</v>
+        <v>35.6392250061035</v>
       </c>
       <c r="H799" t="n">
         <v>12129</v>
@@ -23627,7 +23627,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H802" t="n">
         <v>24522</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578681945801</v>
+        <v>37.3578643798828</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23714,7 +23714,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G805" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H805" t="n">
         <v>20586</v>
@@ -23975,7 +23975,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>36.362865447998</v>
+        <v>36.3628616333008</v>
       </c>
       <c r="H814" t="n">
         <v>19882</v>
@@ -24033,7 +24033,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.724681854248</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H816" t="n">
         <v>28980</v>
@@ -24062,7 +24062,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.905590057373</v>
+        <v>36.9055938720703</v>
       </c>
       <c r="H817" t="n">
         <v>29508</v>
@@ -24120,7 +24120,7 @@
         <v>41.25</v>
       </c>
       <c r="G819" t="n">
-        <v>37.3126373291016</v>
+        <v>37.3126411437988</v>
       </c>
       <c r="H819" t="n">
         <v>39954</v>
@@ -24149,7 +24149,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433250427246</v>
+        <v>38.4433288574219</v>
       </c>
       <c r="H820" t="n">
         <v>48120</v>
@@ -24178,7 +24178,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312881469727</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H821" t="n">
         <v>71113</v>
@@ -24207,7 +24207,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3980979919434</v>
+        <v>38.3981018066406</v>
       </c>
       <c r="H822" t="n">
         <v>31744</v>
@@ -24236,7 +24236,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8955993652344</v>
+        <v>38.8956031799316</v>
       </c>
       <c r="H823" t="n">
         <v>45948</v>
@@ -24265,7 +24265,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>39.6192436218262</v>
+        <v>39.6192398071289</v>
       </c>
       <c r="H824" t="n">
         <v>41543</v>
@@ -24323,7 +24323,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860496520996</v>
+        <v>38.9860572814941</v>
       </c>
       <c r="H826" t="n">
         <v>26184</v>
@@ -24381,7 +24381,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312881469727</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H828" t="n">
         <v>29768</v>
@@ -24439,7 +24439,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H830" t="n">
         <v>38250</v>
@@ -24468,7 +24468,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910507202148</v>
+        <v>37.9910545349121</v>
       </c>
       <c r="H831" t="n">
         <v>31412</v>
@@ -24526,7 +24526,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649116516113</v>
+        <v>37.7649154663086</v>
       </c>
       <c r="H833" t="n">
         <v>30771</v>
@@ -24642,7 +24642,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.181957244873</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H837" t="n">
         <v>119181</v>
@@ -24700,7 +24700,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367263793945</v>
+        <v>36.1367301940918</v>
       </c>
       <c r="H839" t="n">
         <v>32321</v>
@@ -24729,7 +24729,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.865364074707</v>
+        <v>35.8653678894043</v>
       </c>
       <c r="H840" t="n">
         <v>24851</v>
@@ -24758,7 +24758,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392211914062</v>
+        <v>35.6392250061035</v>
       </c>
       <c r="H841" t="n">
         <v>39832</v>
@@ -24816,7 +24816,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.865364074707</v>
+        <v>35.8653678894043</v>
       </c>
       <c r="H843" t="n">
         <v>30983</v>
@@ -24845,7 +24845,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.181957244873</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H844" t="n">
         <v>20530</v>
@@ -24903,7 +24903,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.181957244873</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H846" t="n">
         <v>26328</v>
@@ -24961,7 +24961,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.9105911254883</v>
+        <v>35.910587310791</v>
       </c>
       <c r="H848" t="n">
         <v>26054</v>
@@ -24990,7 +24990,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387763977051</v>
+        <v>37.5387802124023</v>
       </c>
       <c r="H849" t="n">
         <v>30157</v>
@@ -25019,7 +25019,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.724681854248</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H850" t="n">
         <v>32977</v>
@@ -25077,7 +25077,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101425170898</v>
+        <v>37.8101387023926</v>
       </c>
       <c r="H852" t="n">
         <v>12442</v>
@@ -25106,7 +25106,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G853" t="n">
-        <v>37.6292343139648</v>
+        <v>37.6292304992676</v>
       </c>
       <c r="H853" t="n">
         <v>19600</v>
@@ -25222,7 +25222,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>36.362865447998</v>
+        <v>36.3628616333008</v>
       </c>
       <c r="H857" t="n">
         <v>13892</v>
@@ -25251,7 +25251,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G858" t="n">
-        <v>37.1317329406738</v>
+        <v>37.1317291259766</v>
       </c>
       <c r="H858" t="n">
         <v>14683</v>
@@ -25309,7 +25309,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.046272277832</v>
+        <v>36.0462684631348</v>
       </c>
       <c r="H860" t="n">
         <v>13910</v>
@@ -25425,7 +25425,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>36.8710556030273</v>
+        <v>36.8710517883301</v>
       </c>
       <c r="H864" t="n">
         <v>25714</v>
@@ -25483,7 +25483,7 @@
         <v>40</v>
       </c>
       <c r="G866" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H866" t="n">
         <v>9543</v>
@@ -25541,7 +25541,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H868" t="n">
         <v>14461</v>
@@ -25599,7 +25599,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G870" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H870" t="n">
         <v>19770</v>
@@ -25715,7 +25715,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H874" t="n">
         <v>12962</v>
@@ -25744,7 +25744,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H875" t="n">
         <v>10487</v>
@@ -25773,7 +25773,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H876" t="n">
         <v>14179</v>
@@ -25831,7 +25831,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354675292969</v>
+        <v>36.1354751586914</v>
       </c>
       <c r="H878" t="n">
         <v>14544</v>
@@ -26063,7 +26063,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.215991973877</v>
+        <v>35.2159957885742</v>
       </c>
       <c r="H886" t="n">
         <v>9003</v>
@@ -26179,7 +26179,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H890" t="n">
         <v>21938</v>
@@ -26208,7 +26208,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>34.6643104553223</v>
+        <v>34.664306640625</v>
       </c>
       <c r="H891" t="n">
         <v>21890</v>
@@ -26295,7 +26295,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H894" t="n">
         <v>19917</v>
@@ -26382,7 +26382,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G897" t="n">
-        <v>34.5263824462891</v>
+        <v>34.5263862609863</v>
       </c>
       <c r="H897" t="n">
         <v>12411</v>
@@ -26411,7 +26411,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G898" t="n">
-        <v>34.5263824462891</v>
+        <v>34.5263862609863</v>
       </c>
       <c r="H898" t="n">
         <v>8875</v>
@@ -26440,7 +26440,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H899" t="n">
         <v>12713</v>
@@ -26643,7 +26643,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G906" t="n">
-        <v>36.2274169921875</v>
+        <v>36.2274208068848</v>
       </c>
       <c r="H906" t="n">
         <v>30888</v>
@@ -26672,7 +26672,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>34.1126174926758</v>
+        <v>34.112621307373</v>
       </c>
       <c r="H907" t="n">
         <v>64157</v>
@@ -26701,7 +26701,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G908" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H908" t="n">
         <v>19888</v>
@@ -26759,7 +26759,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>33.2850914001465</v>
+        <v>33.2850952148438</v>
       </c>
       <c r="H910" t="n">
         <v>19988</v>
@@ -26788,7 +26788,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H911" t="n">
         <v>9666</v>
@@ -26817,7 +26817,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H912" t="n">
         <v>17366</v>
@@ -26875,7 +26875,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G914" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H914" t="n">
         <v>24076</v>
@@ -26933,7 +26933,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G916" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H916" t="n">
         <v>6480</v>
@@ -26962,7 +26962,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G917" t="n">
-        <v>33.1471710205078</v>
+        <v>33.1471672058105</v>
       </c>
       <c r="H917" t="n">
         <v>22126</v>
@@ -26991,7 +26991,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.0092506408691</v>
+        <v>33.0092468261719</v>
       </c>
       <c r="H918" t="n">
         <v>15454</v>
@@ -27020,7 +27020,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310699462891</v>
       </c>
       <c r="H919" t="n">
         <v>14186</v>
@@ -27049,7 +27049,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H920" t="n">
         <v>12456</v>
@@ -27194,7 +27194,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H925" t="n">
         <v>24388</v>
@@ -27281,7 +27281,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H928" t="n">
         <v>18700</v>
@@ -27310,7 +27310,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H929" t="n">
         <v>19875</v>
@@ -27339,7 +27339,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H930" t="n">
         <v>54293</v>
@@ -27368,7 +27368,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>34.6643104553223</v>
+        <v>34.664306640625</v>
       </c>
       <c r="H931" t="n">
         <v>102214</v>
@@ -27426,7 +27426,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424911499023</v>
+        <v>34.3424873352051</v>
       </c>
       <c r="H933" t="n">
         <v>31757</v>
@@ -27455,7 +27455,7 @@
         <v>37.5</v>
       </c>
       <c r="G934" t="n">
-        <v>34.4804153442383</v>
+        <v>34.480411529541</v>
       </c>
       <c r="H934" t="n">
         <v>36101</v>
@@ -27571,7 +27571,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>35.2619667053223</v>
+        <v>35.2619705200195</v>
       </c>
       <c r="H938" t="n">
         <v>29216</v>
@@ -27600,7 +27600,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965126037598</v>
+        <v>34.296516418457</v>
       </c>
       <c r="H939" t="n">
         <v>16255</v>
@@ -27629,7 +27629,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H940" t="n">
         <v>25107</v>
@@ -27687,7 +27687,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G942" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H942" t="n">
         <v>13115</v>
@@ -27832,7 +27832,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>33.8367729187012</v>
+        <v>33.8367767333984</v>
       </c>
       <c r="H947" t="n">
         <v>15677</v>
@@ -27890,7 +27890,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>34.1126174926758</v>
+        <v>34.112621307373</v>
       </c>
       <c r="H949" t="n">
         <v>58394</v>
@@ -27977,7 +27977,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H952" t="n">
         <v>8028</v>
@@ -28006,7 +28006,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>33.0092506408691</v>
+        <v>33.0092468261719</v>
       </c>
       <c r="H953" t="n">
         <v>30708</v>
@@ -28035,7 +28035,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H954" t="n">
         <v>10979</v>
@@ -28093,7 +28093,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448310852051</v>
+        <v>33.7448348999023</v>
       </c>
       <c r="H956" t="n">
         <v>7086</v>
@@ -28151,7 +28151,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H958" t="n">
         <v>18202</v>
@@ -28267,7 +28267,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H962" t="n">
         <v>19440</v>
@@ -28354,7 +28354,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H965" t="n">
         <v>16412</v>
@@ -28383,7 +28383,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380840301514</v>
+        <v>31.5380821228027</v>
       </c>
       <c r="H966" t="n">
         <v>27835</v>
@@ -28412,7 +28412,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H967" t="n">
         <v>23454</v>
@@ -28441,7 +28441,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>32.1357421875</v>
+        <v>32.1357460021973</v>
       </c>
       <c r="H968" t="n">
         <v>22355</v>
@@ -28470,7 +28470,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H969" t="n">
         <v>26969</v>
@@ -28557,7 +28557,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G972" t="n">
-        <v>33.0092506408691</v>
+        <v>33.0092468261719</v>
       </c>
       <c r="H972" t="n">
         <v>17502</v>
@@ -28644,7 +28644,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H975" t="n">
         <v>22418</v>
@@ -28673,7 +28673,7 @@
         <v>35.75</v>
       </c>
       <c r="G976" t="n">
-        <v>32.8713264465332</v>
+        <v>32.8713302612305</v>
       </c>
       <c r="H976" t="n">
         <v>23421</v>
@@ -28731,7 +28731,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6069107055664</v>
+        <v>33.6069068908691</v>
       </c>
       <c r="H978" t="n">
         <v>13732</v>
@@ -28789,7 +28789,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310699462891</v>
       </c>
       <c r="H980" t="n">
         <v>18596</v>
@@ -28818,7 +28818,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H981" t="n">
         <v>23720</v>
@@ -28934,7 +28934,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H985" t="n">
         <v>10944</v>
@@ -28963,7 +28963,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H986" t="n">
         <v>11601</v>
@@ -29021,7 +29021,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>30.7565269470215</v>
+        <v>30.7565288543701</v>
       </c>
       <c r="H988" t="n">
         <v>19829</v>
@@ -29050,7 +29050,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347114562988</v>
+        <v>30.4347095489502</v>
       </c>
       <c r="H989" t="n">
         <v>20300</v>
@@ -29079,7 +29079,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541851043701</v>
+        <v>31.3541889190674</v>
       </c>
       <c r="H990" t="n">
         <v>16205</v>
@@ -29108,7 +29108,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783462524414</v>
+        <v>31.0783424377441</v>
       </c>
       <c r="H991" t="n">
         <v>22083</v>
@@ -29253,7 +29253,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H996" t="n">
         <v>15814</v>
@@ -29398,7 +29398,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1001" t="n">
         <v>38594</v>
@@ -29456,7 +29456,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H1003" t="n">
         <v>52594</v>
@@ -29601,7 +29601,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>34.9861221313477</v>
+        <v>34.9861259460449</v>
       </c>
       <c r="H1008" t="n">
         <v>17929</v>
@@ -29630,7 +29630,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1009" t="n">
         <v>15324</v>
@@ -29659,7 +29659,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1010" t="n">
         <v>9446</v>
@@ -29717,7 +29717,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1012" t="n">
         <v>19550</v>
@@ -29775,7 +29775,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1014" t="n">
         <v>42877</v>
@@ -29862,7 +29862,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1017" t="n">
-        <v>36.8710556030273</v>
+        <v>36.8710517883301</v>
       </c>
       <c r="H1017" t="n">
         <v>16992</v>
@@ -29891,7 +29891,7 @@
         <v>40.75</v>
       </c>
       <c r="G1018" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1018" t="n">
         <v>22790</v>
@@ -30036,7 +30036,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G1023" t="n">
-        <v>37.6526145935059</v>
+        <v>37.6526107788086</v>
       </c>
       <c r="H1023" t="n">
         <v>27323</v>
@@ -30152,7 +30152,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1027" t="n">
         <v>33681</v>
@@ -30297,7 +30297,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1032" t="n">
         <v>26646</v>
@@ -30326,7 +30326,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1033" t="n">
         <v>17293</v>
@@ -30355,7 +30355,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>38.2502746582031</v>
+        <v>38.2502708435059</v>
       </c>
       <c r="H1034" t="n">
         <v>34988</v>
@@ -30471,7 +30471,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1038" t="n">
         <v>24399</v>
@@ -30500,7 +30500,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1039" t="n">
         <v>35974</v>
@@ -30529,7 +30529,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1040" t="n">
         <v>10126</v>
@@ -30674,7 +30674,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996162414551</v>
+        <v>39.3996200561523</v>
       </c>
       <c r="H1045" t="n">
         <v>13666</v>
@@ -30703,7 +30703,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1046" t="n">
         <v>27206</v>
@@ -30790,7 +30790,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>39.491569519043</v>
+        <v>39.4915657043457</v>
       </c>
       <c r="H1049" t="n">
         <v>25230</v>
@@ -30848,7 +30848,7 @@
         <v>44</v>
       </c>
       <c r="G1051" t="n">
-        <v>40.4570198059082</v>
+        <v>40.4570159912109</v>
       </c>
       <c r="H1051" t="n">
         <v>26021</v>
@@ -30993,7 +30993,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1056" t="n">
-        <v>40.3650741577148</v>
+        <v>40.3650703430176</v>
       </c>
       <c r="H1056" t="n">
         <v>17856</v>
@@ -31022,7 +31022,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>39.491569519043</v>
+        <v>39.4915657043457</v>
       </c>
       <c r="H1057" t="n">
         <v>25708</v>
@@ -31051,7 +31051,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1058" t="n">
         <v>26015</v>
@@ -31196,7 +31196,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627304077148</v>
+        <v>40.9627265930176</v>
       </c>
       <c r="H1063" t="n">
         <v>114652</v>
@@ -31283,7 +31283,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>40.5489654541016</v>
+        <v>40.5489616394043</v>
       </c>
       <c r="H1066" t="n">
         <v>41750</v>
@@ -31457,7 +31457,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1072" t="n">
         <v>20307</v>
@@ -31486,7 +31486,7 @@
         <v>42.0999984741211</v>
       </c>
       <c r="G1073" t="n">
-        <v>38.7100067138672</v>
+        <v>38.7100105285645</v>
       </c>
       <c r="H1073" t="n">
         <v>28907</v>
@@ -31602,7 +31602,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1077" t="n">
         <v>48482</v>
@@ -31631,7 +31631,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1078" t="n">
         <v>21323</v>
@@ -31776,7 +31776,7 @@
         <v>40</v>
       </c>
       <c r="G1083" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H1083" t="n">
         <v>25278</v>
@@ -31805,7 +31805,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1084" t="n">
         <v>33932</v>
@@ -31834,7 +31834,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422241210938</v>
+        <v>38.3422164916992</v>
       </c>
       <c r="H1085" t="n">
         <v>44926</v>
@@ -32037,7 +32037,7 @@
         <v>40.75</v>
       </c>
       <c r="G1092" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1092" t="n">
         <v>28651</v>
@@ -32095,7 +32095,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824806213379</v>
+        <v>37.8824844360352</v>
       </c>
       <c r="H1094" t="n">
         <v>23661</v>
@@ -32124,7 +32124,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1095" t="n">
         <v>27027</v>
@@ -32182,7 +32182,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1097" t="n">
-        <v>37.7445602416992</v>
+        <v>37.744556427002</v>
       </c>
       <c r="H1097" t="n">
         <v>46557</v>
@@ -32211,7 +32211,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1098" t="n">
         <v>26751</v>
@@ -32240,7 +32240,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1099" t="n">
         <v>14005</v>
@@ -32385,7 +32385,7 @@
         <v>40</v>
       </c>
       <c r="G1104" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H1104" t="n">
         <v>28294</v>
@@ -32414,7 +32414,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952110290527</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1105" t="n">
         <v>26729</v>
@@ -32443,7 +32443,7 @@
         <v>40</v>
       </c>
       <c r="G1106" t="n">
-        <v>36.779109954834</v>
+        <v>36.7791061401367</v>
       </c>
       <c r="H1106" t="n">
         <v>12511</v>
@@ -32501,7 +32501,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1108" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H1108" t="n">
         <v>21226</v>
@@ -32530,7 +32530,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1109" t="n">
         <v>25222</v>
@@ -32559,7 +32559,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1110" t="n">
-        <v>35.7217063903809</v>
+        <v>35.7217102050781</v>
       </c>
       <c r="H1110" t="n">
         <v>18379</v>
@@ -32588,7 +32588,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.7217063903809</v>
+        <v>35.7217102050781</v>
       </c>
       <c r="H1111" t="n">
         <v>13856</v>
@@ -32617,7 +32617,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1112" t="n">
         <v>49066</v>
@@ -32675,7 +32675,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1114" t="n">
         <v>12691</v>
@@ -32704,7 +32704,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1115" t="n">
         <v>9595</v>
@@ -32733,7 +32733,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1116" t="n">
         <v>18589</v>
@@ -32762,7 +32762,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1117" t="n">
         <v>12581</v>
@@ -32907,7 +32907,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858551025391</v>
+        <v>38.9858589172363</v>
       </c>
       <c r="H1122" t="n">
         <v>13057</v>
@@ -32936,7 +32936,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>39.491569519043</v>
+        <v>39.4915657043457</v>
       </c>
       <c r="H1123" t="n">
         <v>13686</v>
@@ -32965,7 +32965,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>39.905330657959</v>
+        <v>39.9053344726562</v>
       </c>
       <c r="H1124" t="n">
         <v>29851</v>
@@ -33023,7 +33023,7 @@
         <v>45.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>42.066104888916</v>
+        <v>42.0661010742188</v>
       </c>
       <c r="H1126" t="n">
         <v>38246</v>
@@ -33081,7 +33081,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1128" t="n">
         <v>49587</v>
@@ -33110,7 +33110,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422241210938</v>
+        <v>38.3422164916992</v>
       </c>
       <c r="H1129" t="n">
         <v>76007</v>
@@ -33197,7 +33197,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727058410645</v>
+        <v>39.4727020263672</v>
       </c>
       <c r="H1132" t="n">
         <v>28234</v>
@@ -33226,7 +33226,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900825500488</v>
+        <v>39.1900787353516</v>
       </c>
       <c r="H1133" t="n">
         <v>17044</v>
@@ -33371,7 +33371,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1138" t="n">
         <v>14887</v>
@@ -33429,7 +33429,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082176208496</v>
+        <v>39.7082214355469</v>
       </c>
       <c r="H1140" t="n">
         <v>25485</v>
@@ -33458,7 +33458,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842903137207</v>
+        <v>39.2842864990234</v>
       </c>
       <c r="H1141" t="n">
         <v>10680</v>
@@ -33487,7 +33487,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379447937012</v>
+        <v>40.0379409790039</v>
       </c>
       <c r="H1142" t="n">
         <v>21497</v>
@@ -33516,7 +33516,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1143" t="n">
         <v>17609</v>
@@ -33545,7 +33545,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452537536621</v>
+        <v>41.5452499389648</v>
       </c>
       <c r="H1144" t="n">
         <v>77350</v>
@@ -33661,7 +33661,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437370300293</v>
+        <v>39.9437408447266</v>
       </c>
       <c r="H1148" t="n">
         <v>26093</v>
@@ -33864,7 +33864,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132514953613</v>
+        <v>38.8132553100586</v>
       </c>
       <c r="H1155" t="n">
         <v>17325</v>
@@ -34154,7 +34154,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1165" t="n">
         <v>25025</v>
@@ -34212,7 +34212,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1167" t="n">
         <v>17311</v>
@@ -34241,7 +34241,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1168" t="n">
         <v>18709</v>
@@ -34270,7 +34270,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522842407227</v>
+        <v>36.5522880554199</v>
       </c>
       <c r="H1169" t="n">
         <v>7654</v>
@@ -34299,7 +34299,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1170" t="n">
         <v>11922</v>
@@ -34357,7 +34357,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993881225586</v>
+        <v>36.5993919372559</v>
       </c>
       <c r="H1172" t="n">
         <v>22854</v>
@@ -34444,7 +34444,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1175" t="n">
         <v>14281</v>
@@ -34589,7 +34589,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1180" t="n">
         <v>12217</v>
@@ -34647,7 +34647,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1182" t="n">
         <v>17442</v>
@@ -34763,7 +34763,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1186" t="n">
         <v>16678</v>
@@ -34850,7 +34850,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376663208008</v>
+        <v>33.5376625061035</v>
       </c>
       <c r="H1189" t="n">
         <v>13671</v>
@@ -34908,7 +34908,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202896118164</v>
+        <v>33.8202857971191</v>
       </c>
       <c r="H1191" t="n">
         <v>14410</v>
@@ -34937,7 +34937,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1192" t="n">
         <v>21211</v>
@@ -35053,7 +35053,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275985717773</v>
+        <v>35.3275947570801</v>
       </c>
       <c r="H1196" t="n">
         <v>18810</v>
@@ -35198,7 +35198,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1201" t="n">
         <v>10943</v>
@@ -35227,7 +35227,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1202" t="n">
         <v>13284</v>
@@ -35372,7 +35372,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1207" t="n">
         <v>86976</v>
@@ -35401,7 +35401,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1208" t="n">
         <v>107480</v>
@@ -35459,7 +35459,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238010406494</v>
+        <v>31.3238048553467</v>
       </c>
       <c r="H1210" t="n">
         <v>97335</v>
@@ -35517,7 +35517,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890399932861</v>
+        <v>31.8890419006348</v>
       </c>
       <c r="H1212" t="n">
         <v>19682</v>
@@ -35575,7 +35575,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1214" t="n">
         <v>32700</v>
@@ -35604,7 +35604,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1215" t="n">
         <v>71954</v>
@@ -35633,7 +35633,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419399261475</v>
+        <v>31.8419380187988</v>
       </c>
       <c r="H1216" t="n">
         <v>29272</v>
@@ -35662,7 +35662,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1217" t="n">
         <v>40121</v>
@@ -35691,7 +35691,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1218" t="n">
         <v>88062</v>
@@ -35720,7 +35720,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1219" t="n">
         <v>20873</v>
@@ -35807,7 +35807,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804946899414</v>
+        <v>35.2804908752441</v>
       </c>
       <c r="H1222" t="n">
         <v>55066</v>
@@ -35836,7 +35836,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391792297363</v>
+        <v>35.1391830444336</v>
       </c>
       <c r="H1223" t="n">
         <v>48119</v>
@@ -35952,7 +35952,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558013916016</v>
+        <v>34.0558052062988</v>
       </c>
       <c r="H1227" t="n">
         <v>33020</v>
@@ -36068,7 +36068,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1231" t="n">
         <v>27966</v>
@@ -36126,7 +36126,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160140991211</v>
+        <v>35.5160102844238</v>
       </c>
       <c r="H1233" t="n">
         <v>18372</v>
@@ -36155,7 +36155,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1234" t="n">
         <v>21216</v>
@@ -36271,7 +36271,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.0233192443848</v>
+        <v>37.023323059082</v>
       </c>
       <c r="H1238" t="n">
         <v>31944</v>
@@ -36329,7 +36329,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1240" t="n">
         <v>21979</v>
@@ -36358,7 +36358,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739402770996</v>
+        <v>34.5739440917969</v>
       </c>
       <c r="H1241" t="n">
         <v>36159</v>
@@ -36532,7 +36532,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955924987793</v>
+        <v>32.5955963134766</v>
       </c>
       <c r="H1247" t="n">
         <v>20275</v>
@@ -36619,7 +36619,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1250" t="n">
         <v>26995</v>
@@ -36735,7 +36735,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1254" t="n">
         <v>86029</v>
@@ -36938,7 +36938,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1261" t="n">
         <v>62483</v>
@@ -37083,7 +37083,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099395751953</v>
+        <v>29.1099376678467</v>
       </c>
       <c r="H1266" t="n">
         <v>42903</v>
@@ -37257,7 +37257,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1272" t="n">
         <v>69703</v>
@@ -37286,7 +37286,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1273" t="n">
         <v>51566</v>
@@ -37344,7 +37344,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1275" t="n">
         <v>39875</v>
@@ -37373,7 +37373,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1276" t="n">
         <v>33069</v>
@@ -37605,7 +37605,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164920806885</v>
+        <v>29.8164901733398</v>
       </c>
       <c r="H1284" t="n">
         <v>24216</v>
@@ -37663,7 +37663,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643543243408</v>
+        <v>30.6643524169922</v>
       </c>
       <c r="H1286" t="n">
         <v>27493</v>
@@ -37692,7 +37692,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1287" t="n">
         <v>27163</v>
@@ -37808,7 +37808,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1291" t="n">
         <v>50126</v>
@@ -37837,7 +37837,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1292" t="n">
         <v>15339</v>
@@ -37953,7 +37953,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1296" t="n">
         <v>31760</v>
@@ -38127,7 +38127,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832496643066</v>
+        <v>31.9832515716553</v>
       </c>
       <c r="H1302" t="n">
         <v>58973</v>
@@ -38156,7 +38156,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1303" t="n">
         <v>39498</v>
@@ -38330,7 +38330,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.3492546081543</v>
+        <v>33.349250793457</v>
       </c>
       <c r="H1309" t="n">
         <v>34631</v>
@@ -38417,7 +38417,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1312" t="n">
         <v>27726</v>
@@ -38533,7 +38533,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1316" t="n">
         <v>82490</v>
@@ -38562,7 +38562,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1317" t="n">
         <v>126426</v>
@@ -38707,7 +38707,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1322" t="n">
         <v>44000</v>
@@ -38765,7 +38765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1324" t="n">
         <v>42930</v>
@@ -38823,7 +38823,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1326" t="n">
         <v>38026</v>
@@ -38852,7 +38852,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1327" t="n">
         <v>61320</v>
@@ -38939,7 +38939,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041454315186</v>
+        <v>29.2041473388672</v>
       </c>
       <c r="H1330" t="n">
         <v>38634</v>
@@ -39113,7 +39113,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207675933838</v>
+        <v>28.1207656860352</v>
       </c>
       <c r="H1336" t="n">
         <v>109851</v>
@@ -39229,7 +39229,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1340" t="n">
         <v>55268</v>
@@ -39258,7 +39258,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1341" t="n">
         <v>36968</v>
@@ -39374,7 +39374,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844898223877</v>
+        <v>27.0844917297363</v>
       </c>
       <c r="H1345" t="n">
         <v>66714</v>
@@ -39432,7 +39432,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1347" t="n">
         <v>104150</v>
@@ -39519,7 +39519,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902839660645</v>
+        <v>26.9902820587158</v>
       </c>
       <c r="H1350" t="n">
         <v>33485</v>
@@ -39548,7 +39548,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779373168945</v>
+        <v>26.3779392242432</v>
       </c>
       <c r="H1351" t="n">
         <v>128641</v>
@@ -39606,7 +39606,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1353" t="n">
         <v>181757</v>
@@ -39635,7 +39635,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1354" t="n">
         <v>138211</v>
@@ -39664,7 +39664,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829711914062</v>
+        <v>25.4829730987549</v>
       </c>
       <c r="H1355" t="n">
         <v>105911</v>
@@ -39838,7 +39838,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011119842529</v>
+        <v>26.0011100769043</v>
       </c>
       <c r="H1361" t="n">
         <v>64528</v>
@@ -39867,7 +39867,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.388765335083</v>
+        <v>25.3887672424316</v>
       </c>
       <c r="H1362" t="n">
         <v>44652</v>
@@ -39896,7 +39896,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003517150879</v>
+        <v>25.2003536224365</v>
       </c>
       <c r="H1363" t="n">
         <v>43761</v>
@@ -39925,7 +39925,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.1895236968994</v>
+        <v>26.189525604248</v>
       </c>
       <c r="H1364" t="n">
         <v>45391</v>
@@ -39954,7 +39954,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076644897461</v>
+        <v>26.7076625823975</v>
       </c>
       <c r="H1365" t="n">
         <v>53357</v>
@@ -40157,7 +40157,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1372" t="n">
         <v>44289</v>
@@ -40215,7 +40215,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.6968364715576</v>
+        <v>27.696834564209</v>
       </c>
       <c r="H1374" t="n">
         <v>43847</v>
@@ -50919,9 +50919,38 @@
         <v>34.4000015258789</v>
       </c>
       <c r="H1743" t="n">
-        <v>75514</v>
+        <v>75558</v>
       </c>
       <c r="I1743" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1744" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1744" t="n">
+        <v>34</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>34.939998626709</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>34</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>35.0400009155273</v>
+      </c>
+      <c r="G1744" t="n">
+        <v>35.0400009155273</v>
+      </c>
+      <c r="H1744" t="n">
+        <v>24241</v>
+      </c>
+      <c r="I1744" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -485,7 +485,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818492889404</v>
+        <v>13.3818502426147</v>
       </c>
       <c r="H4" t="n">
         <v>54824</v>
@@ -514,7 +514,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479248046875</v>
+        <v>13.7479238510132</v>
       </c>
       <c r="H5" t="n">
         <v>18109</v>
@@ -688,7 +688,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390064239502</v>
+        <v>13.8390054702759</v>
       </c>
       <c r="H11" t="n">
         <v>10789</v>
@@ -775,7 +775,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598627090454</v>
+        <v>13.9598608016968</v>
       </c>
       <c r="H14" t="n">
         <v>75034</v>
@@ -804,7 +804,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915519714355</v>
+        <v>13.8915510177612</v>
       </c>
       <c r="H15" t="n">
         <v>15065</v>
@@ -920,7 +920,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H19" t="n">
         <v>69364</v>
@@ -949,7 +949,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948921203613</v>
+        <v>13.9948930740356</v>
       </c>
       <c r="H20" t="n">
         <v>34939</v>
@@ -978,7 +978,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963214874268</v>
+        <v>14.1963205337524</v>
       </c>
       <c r="H21" t="n">
         <v>76030</v>
@@ -1007,7 +1007,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130289077759</v>
+        <v>14.7130279541016</v>
       </c>
       <c r="H22" t="n">
         <v>147663</v>
@@ -1036,7 +1036,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692419052124</v>
+        <v>14.6692409515381</v>
       </c>
       <c r="H23" t="n">
         <v>297347</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071281433105</v>
+        <v>15.1071271896362</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881864547729</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1152,7 +1152,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463092803955</v>
+        <v>14.7463083267212</v>
       </c>
       <c r="H27" t="n">
         <v>68742</v>
@@ -1181,7 +1181,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916873931885</v>
+        <v>14.8916883468628</v>
       </c>
       <c r="H28" t="n">
         <v>63118</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757614135742</v>
+        <v>14.9757604598999</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1239,7 +1239,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730653762817</v>
+        <v>14.4730644226074</v>
       </c>
       <c r="H30" t="n">
         <v>42455</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881864547729</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881864547729</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1384,7 +1384,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.6447191238403</v>
+        <v>14.644718170166</v>
       </c>
       <c r="H35" t="n">
         <v>11249</v>
@@ -1413,7 +1413,7 @@
         <v>16.5459995269775</v>
       </c>
       <c r="G36" t="n">
-        <v>14.4905824661255</v>
+        <v>14.4905815124512</v>
       </c>
       <c r="H36" t="n">
         <v>29716</v>
@@ -1471,7 +1471,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628793716431</v>
+        <v>14.2628784179688</v>
       </c>
       <c r="H38" t="n">
         <v>11160</v>
@@ -1500,7 +1500,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H39" t="n">
         <v>17569</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609685897827</v>
+        <v>14.3609676361084</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1558,7 +1558,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>14.6604814529419</v>
+        <v>14.6604824066162</v>
       </c>
       <c r="H41" t="n">
         <v>29941</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006076812744</v>
+        <v>14.8006067276001</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1645,7 +1645,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692419052124</v>
+        <v>14.6692409515381</v>
       </c>
       <c r="H44" t="n">
         <v>35731</v>
@@ -1674,7 +1674,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655763626099</v>
+        <v>14.7655744552612</v>
       </c>
       <c r="H45" t="n">
         <v>31415</v>
@@ -1703,7 +1703,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237001419067</v>
+        <v>14.6236991882324</v>
       </c>
       <c r="H46" t="n">
         <v>33733</v>
@@ -1761,7 +1761,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633401870728</v>
+        <v>15.0633392333984</v>
       </c>
       <c r="H48" t="n">
         <v>87381</v>
@@ -1819,7 +1819,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1262588500977</v>
+        <v>14.126259803772</v>
       </c>
       <c r="H50" t="n">
         <v>74499</v>
@@ -1877,7 +1877,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.4415378570557</v>
+        <v>14.44153881073</v>
       </c>
       <c r="H52" t="n">
         <v>18751</v>
@@ -1906,7 +1906,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089054107666</v>
+        <v>14.0089044570923</v>
       </c>
       <c r="H53" t="n">
         <v>23213</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -2022,7 +2022,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H57" t="n">
         <v>15626</v>
@@ -2051,7 +2051,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527196884155</v>
+        <v>12.9527206420898</v>
       </c>
       <c r="H58" t="n">
         <v>30556</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111679077148</v>
+        <v>12.6111669540405</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320232391357</v>
+        <v>12.7320241928101</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2167,7 +2167,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602378845215</v>
+        <v>11.5602369308472</v>
       </c>
       <c r="H62" t="n">
         <v>43479</v>
@@ -2225,7 +2225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>11.0347719192505</v>
+        <v>11.0347738265991</v>
       </c>
       <c r="H64" t="n">
         <v>37959</v>
@@ -2312,7 +2312,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837497711182</v>
+        <v>9.45837688446045</v>
       </c>
       <c r="H67" t="n">
         <v>48156</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806560516357</v>
+        <v>9.10806465148926</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2370,7 +2370,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96618938446045</v>
+        <v>8.96619033813477</v>
       </c>
       <c r="H69" t="n">
         <v>122433</v>
@@ -2428,7 +2428,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651477813721</v>
+        <v>8.76651287078857</v>
       </c>
       <c r="H71" t="n">
         <v>44594</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494190216064</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2515,7 +2515,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.67017841339111</v>
+        <v>8.6701774597168</v>
       </c>
       <c r="H74" t="n">
         <v>15416</v>
@@ -2544,7 +2544,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032192230225</v>
+        <v>8.69032096862793</v>
       </c>
       <c r="H75" t="n">
         <v>14690</v>
@@ -2573,7 +2573,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415237426758</v>
+        <v>8.92415332794189</v>
       </c>
       <c r="H76" t="n">
         <v>26972</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500961303711</v>
+        <v>9.04501056671143</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2631,7 +2631,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328388214111</v>
+        <v>9.35328197479248</v>
       </c>
       <c r="H78" t="n">
         <v>29100</v>
@@ -2660,7 +2660,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G79" t="n">
-        <v>9.82620143890381</v>
+        <v>9.82620239257812</v>
       </c>
       <c r="H79" t="n">
         <v>19607</v>
@@ -2689,7 +2689,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921142578125</v>
+        <v>10.2921133041382</v>
       </c>
       <c r="H80" t="n">
         <v>20417</v>
@@ -2718,7 +2718,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968837738037</v>
+        <v>10.596884727478</v>
       </c>
       <c r="H81" t="n">
         <v>17348</v>
@@ -2747,7 +2747,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070707321167</v>
+        <v>10.8070697784424</v>
       </c>
       <c r="H82" t="n">
         <v>3945</v>
@@ -2776,7 +2776,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156665802002</v>
+        <v>10.9156656265259</v>
       </c>
       <c r="H83" t="n">
         <v>6741</v>
@@ -2834,7 +2834,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1748952865601</v>
+        <v>11.1748962402344</v>
       </c>
       <c r="H85" t="n">
         <v>4457</v>
@@ -2863,7 +2863,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.787802696228</v>
+        <v>10.7878036499023</v>
       </c>
       <c r="H86" t="n">
         <v>15151</v>
@@ -2921,7 +2921,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353916168213</v>
+        <v>11.7353935241699</v>
       </c>
       <c r="H88" t="n">
         <v>24596</v>
@@ -2979,7 +2979,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068826675415</v>
+        <v>12.0068817138672</v>
       </c>
       <c r="H90" t="n">
         <v>11410</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229694366455</v>
+        <v>11.8229703903198</v>
       </c>
       <c r="H91" t="n">
         <v>16703</v>
@@ -3037,7 +3037,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325347900391</v>
+        <v>11.3325357437134</v>
       </c>
       <c r="H92" t="n">
         <v>25713</v>
@@ -3066,7 +3066,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0347719192505</v>
+        <v>11.0347738265991</v>
       </c>
       <c r="H93" t="n">
         <v>52489</v>
@@ -3095,7 +3095,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331827163696</v>
+        <v>10.9331817626953</v>
       </c>
       <c r="H94" t="n">
         <v>46331</v>
@@ -3124,7 +3124,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.947193145752</v>
+        <v>10.9471950531006</v>
       </c>
       <c r="H95" t="n">
         <v>49105</v>
@@ -3240,7 +3240,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691816329956</v>
+        <v>10.3691825866699</v>
       </c>
       <c r="H99" t="n">
         <v>11865</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465734481812</v>
+        <v>10.2465744018555</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3356,7 +3356,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616897583008</v>
+        <v>10.6616907119751</v>
       </c>
       <c r="H103" t="n">
         <v>12365</v>
@@ -3385,7 +3385,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008708953857</v>
+        <v>10.3008718490601</v>
       </c>
       <c r="H104" t="n">
         <v>32832</v>
@@ -3414,7 +3414,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.381443977356</v>
+        <v>10.3814430236816</v>
       </c>
       <c r="H105" t="n">
         <v>19187</v>
@@ -3443,7 +3443,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093059539795</v>
+        <v>10.5093069076538</v>
       </c>
       <c r="H106" t="n">
         <v>15170</v>
@@ -3501,7 +3501,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220262527466</v>
+        <v>11.3220252990723</v>
       </c>
       <c r="H108" t="n">
         <v>36330</v>
@@ -3530,7 +3530,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955907821655</v>
+        <v>11.3955917358398</v>
       </c>
       <c r="H109" t="n">
         <v>18584</v>
@@ -3588,7 +3588,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565732955933</v>
+        <v>11.6565723419189</v>
       </c>
       <c r="H111" t="n">
         <v>27521</v>
@@ -3733,7 +3733,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506706237793</v>
+        <v>12.0506715774536</v>
       </c>
       <c r="H116" t="n">
         <v>330572</v>
@@ -3791,7 +3791,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922243118286</v>
+        <v>12.3922233581543</v>
       </c>
       <c r="H118" t="n">
         <v>16297</v>
@@ -3907,7 +3907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614772796631</v>
       </c>
       <c r="H122" t="n">
         <v>27467</v>
@@ -3936,7 +3936,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.310037612915</v>
+        <v>13.3100366592407</v>
       </c>
       <c r="H123" t="n">
         <v>25697</v>
@@ -3965,7 +3965,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930047988892</v>
+        <v>12.9930067062378</v>
       </c>
       <c r="H124" t="n">
         <v>20213</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901479721069</v>
+        <v>12.5901498794556</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119512557983</v>
+        <v>13.211950302124</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4139,7 +4139,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976135253906</v>
+        <v>13.3976144790649</v>
       </c>
       <c r="H130" t="n">
         <v>7245</v>
@@ -4168,7 +4168,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361486434937</v>
+        <v>13.4361476898193</v>
       </c>
       <c r="H131" t="n">
         <v>17251</v>
@@ -4197,7 +4197,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>13.3030300140381</v>
+        <v>13.3030309677124</v>
       </c>
       <c r="H132" t="n">
         <v>11780</v>
@@ -4226,7 +4226,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.527229309082</v>
+        <v>13.5272302627563</v>
       </c>
       <c r="H133" t="n">
         <v>18810</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681623458862</v>
+        <v>13.1681613922119</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4400,7 +4400,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805826187134</v>
+        <v>13.0805835723877</v>
       </c>
       <c r="H139" t="n">
         <v>13088</v>
@@ -4603,7 +4603,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.977240562439</v>
+        <v>12.9772415161133</v>
       </c>
       <c r="H146" t="n">
         <v>4221</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504844665527</v>
+        <v>13.2504854202271</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620979309082</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4835,7 +4835,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G154" t="n">
-        <v>13.3135385513306</v>
+        <v>13.3135395050049</v>
       </c>
       <c r="H154" t="n">
         <v>2851</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277145385742</v>
+        <v>13.2277135848999</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4922,7 +4922,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555765151978</v>
+        <v>13.3555774688721</v>
       </c>
       <c r="H157" t="n">
         <v>9479</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348819732666</v>
+        <v>13.1348810195923</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -4980,7 +4980,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823345184326</v>
+        <v>13.0823335647583</v>
       </c>
       <c r="H159" t="n">
         <v>22453</v>
@@ -5009,7 +5009,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H160" t="n">
         <v>8710</v>
@@ -5038,7 +5038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H161" t="n">
         <v>8576</v>
@@ -5096,7 +5096,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673789978027</v>
+        <v>12.5673799514771</v>
       </c>
       <c r="H163" t="n">
         <v>11473</v>
@@ -5125,7 +5125,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393543243408</v>
+        <v>12.5393533706665</v>
       </c>
       <c r="H164" t="n">
         <v>30378</v>
@@ -5154,7 +5154,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094160079956</v>
+        <v>12.6094169616699</v>
       </c>
       <c r="H165" t="n">
         <v>15675</v>
@@ -5212,7 +5212,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H167" t="n">
         <v>9897</v>
@@ -5241,7 +5241,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097394943237</v>
+        <v>12.4097385406494</v>
       </c>
       <c r="H168" t="n">
         <v>11733</v>
@@ -5270,7 +5270,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="n">
-        <v>13.1366329193115</v>
+        <v>13.1366338729858</v>
       </c>
       <c r="H169" t="n">
         <v>3414</v>
@@ -5386,7 +5386,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.6866216659546</v>
+        <v>13.686619758606</v>
       </c>
       <c r="H173" t="n">
         <v>4657</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620979309082</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5560,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H179" t="n">
         <v>13803</v>
@@ -5589,7 +5589,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H180" t="n">
         <v>13692</v>
@@ -5647,7 +5647,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H182" t="n">
         <v>15865</v>
@@ -5705,7 +5705,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H184" t="n">
         <v>25117</v>
@@ -5734,7 +5734,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>14.0999879837036</v>
+        <v>14.0999870300293</v>
       </c>
       <c r="H185" t="n">
         <v>23215</v>
@@ -5763,7 +5763,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H186" t="n">
         <v>9698</v>
@@ -5792,7 +5792,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H187" t="n">
         <v>24640</v>
@@ -5821,7 +5821,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H188" t="n">
         <v>35173</v>
@@ -5850,7 +5850,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H189" t="n">
         <v>28944</v>
@@ -5879,7 +5879,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>14.0999879837036</v>
+        <v>14.0999870300293</v>
       </c>
       <c r="H190" t="n">
         <v>9258</v>
@@ -5995,7 +5995,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971311569214</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H194" t="n">
         <v>8929</v>
@@ -6053,7 +6053,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920362472534</v>
+        <v>13.5920372009277</v>
       </c>
       <c r="H196" t="n">
         <v>10776</v>
@@ -6111,7 +6111,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1366329193115</v>
+        <v>13.1366338729858</v>
       </c>
       <c r="H198" t="n">
         <v>5996</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614772796631</v>
       </c>
       <c r="H199" t="n">
         <v>7759</v>
@@ -6169,7 +6169,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767581939697</v>
+        <v>13.2767562866211</v>
       </c>
       <c r="H200" t="n">
         <v>6789</v>
@@ -6227,7 +6227,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H202" t="n">
         <v>32085</v>
@@ -6256,7 +6256,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H203" t="n">
         <v>21909</v>
@@ -6285,7 +6285,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531522750854</v>
       </c>
       <c r="H204" t="n">
         <v>59951</v>
@@ -6314,7 +6314,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531532287598</v>
+        <v>14.8531522750854</v>
       </c>
       <c r="H205" t="n">
         <v>52305</v>
@@ -6343,7 +6343,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.467812538147</v>
+        <v>14.4678134918213</v>
       </c>
       <c r="H206" t="n">
         <v>39648</v>
@@ -6430,7 +6430,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0999879837036</v>
+        <v>14.0999870300293</v>
       </c>
       <c r="H209" t="n">
         <v>15103</v>
@@ -6459,7 +6459,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H210" t="n">
         <v>16575</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H212" t="n">
         <v>5728</v>
@@ -6546,7 +6546,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H213" t="n">
         <v>3813</v>
@@ -6604,7 +6604,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H215" t="n">
         <v>13883</v>
@@ -6894,7 +6894,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592420578003</v>
+        <v>13.259241104126</v>
       </c>
       <c r="H225" t="n">
         <v>9073</v>
@@ -6952,7 +6952,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1016025543213</v>
+        <v>13.1016035079956</v>
       </c>
       <c r="H227" t="n">
         <v>2440</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620988845825</v>
+        <v>13.6620979309082</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022222518921</v>
+        <v>13.8022232055664</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.6270685195923</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7938,7 +7938,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971311569214</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H261" t="n">
         <v>11448</v>
@@ -7996,7 +7996,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773778915405</v>
+        <v>13.9773769378662</v>
       </c>
       <c r="H263" t="n">
         <v>14625</v>
@@ -8083,7 +8083,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.310173034668</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H266" t="n">
         <v>8011</v>
@@ -8112,7 +8112,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H267" t="n">
         <v>21797</v>
@@ -8170,7 +8170,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H269" t="n">
         <v>28438</v>
@@ -8286,7 +8286,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079368591309</v>
+        <v>14.6079359054565</v>
       </c>
       <c r="H273" t="n">
         <v>7891</v>
@@ -8344,7 +8344,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>14.2401113510132</v>
+        <v>14.2401103973389</v>
       </c>
       <c r="H275" t="n">
         <v>14243</v>
@@ -8431,7 +8431,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.572904586792</v>
+        <v>14.5729036331177</v>
       </c>
       <c r="H278" t="n">
         <v>26113</v>
@@ -8489,7 +8489,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311666488647</v>
+        <v>15.4311647415161</v>
       </c>
       <c r="H280" t="n">
         <v>50717</v>
@@ -8518,7 +8518,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114133834839</v>
+        <v>15.7114152908325</v>
       </c>
       <c r="H281" t="n">
         <v>48160</v>
@@ -8605,7 +8605,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165044784546</v>
+        <v>15.8165054321289</v>
       </c>
       <c r="H284" t="n">
         <v>60606</v>
@@ -8634,7 +8634,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814769744873</v>
+        <v>15.7814779281616</v>
       </c>
       <c r="H285" t="n">
         <v>16215</v>
@@ -8663,7 +8663,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G286" t="n">
-        <v>15.5712919235229</v>
+        <v>15.5712900161743</v>
       </c>
       <c r="H286" t="n">
         <v>9069</v>
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397380828857</v>
+        <v>16.6397361755371</v>
       </c>
       <c r="H288" t="n">
         <v>19711</v>
@@ -8837,7 +8837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403568267822</v>
+        <v>17.3403549194336</v>
       </c>
       <c r="H292" t="n">
         <v>108964</v>
@@ -8866,7 +8866,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753852844238</v>
+        <v>17.3753871917725</v>
       </c>
       <c r="H293" t="n">
         <v>29298</v>
@@ -8895,7 +8895,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592994689941</v>
+        <v>17.5593013763428</v>
       </c>
       <c r="H294" t="n">
         <v>17437</v>
@@ -8953,7 +8953,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906661987305</v>
+        <v>17.6906642913818</v>
       </c>
       <c r="H296" t="n">
         <v>36908</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.252779006958</v>
+        <v>17.2527809143066</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9040,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.515510559082</v>
+        <v>17.5155086517334</v>
       </c>
       <c r="H299" t="n">
         <v>21074</v>
@@ -9069,7 +9069,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228378295898</v>
+        <v>17.3228416442871</v>
       </c>
       <c r="H300" t="n">
         <v>7964</v>
@@ -9098,7 +9098,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.7273139953613</v>
+        <v>16.7273120880127</v>
       </c>
       <c r="H301" t="n">
         <v>28487</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979972839355</v>
+        <v>17.4979953765869</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9185,7 +9185,7 @@
         <v>20.75</v>
       </c>
       <c r="G304" t="n">
-        <v>18.1723442077637</v>
+        <v>18.172342300415</v>
       </c>
       <c r="H304" t="n">
         <v>46277</v>
@@ -9214,7 +9214,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>18.1285533905029</v>
+        <v>18.1285552978516</v>
       </c>
       <c r="H305" t="n">
         <v>35889</v>
@@ -9272,7 +9272,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853870391846</v>
       </c>
       <c r="H307" t="n">
         <v>24097</v>
@@ -9301,7 +9301,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.310848236084</v>
+        <v>19.3108501434326</v>
       </c>
       <c r="H308" t="n">
         <v>58530</v>
@@ -9330,7 +9330,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H309" t="n">
         <v>14880</v>
@@ -9359,7 +9359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H310" t="n">
         <v>34531</v>
@@ -9388,7 +9388,7 @@
         <v>21.5</v>
       </c>
       <c r="G311" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H311" t="n">
         <v>24053</v>
@@ -9417,7 +9417,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415981292725</v>
       </c>
       <c r="H312" t="n">
         <v>23897</v>
@@ -9446,7 +9446,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356945037842</v>
+        <v>19.1356964111328</v>
       </c>
       <c r="H313" t="n">
         <v>16234</v>
@@ -9475,7 +9475,7 @@
         <v>21.5</v>
       </c>
       <c r="G314" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H314" t="n">
         <v>16356</v>
@@ -9533,7 +9533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H316" t="n">
         <v>27872</v>
@@ -9562,7 +9562,7 @@
         <v>21.5</v>
       </c>
       <c r="G317" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H317" t="n">
         <v>18086</v>
@@ -9591,7 +9591,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853870391846</v>
       </c>
       <c r="H318" t="n">
         <v>14808</v>
@@ -9678,7 +9678,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925243377686</v>
+        <v>19.7925281524658</v>
       </c>
       <c r="H321" t="n">
         <v>38533</v>
@@ -9707,7 +9707,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H322" t="n">
         <v>48797</v>
@@ -9736,7 +9736,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794834136963</v>
       </c>
       <c r="H323" t="n">
         <v>9282</v>
@@ -9794,7 +9794,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611614227295</v>
+        <v>19.6611652374268</v>
       </c>
       <c r="H325" t="n">
         <v>22459</v>
@@ -9823,7 +9823,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735816955566</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H326" t="n">
         <v>15812</v>
@@ -9852,7 +9852,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735816955566</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H327" t="n">
         <v>7040</v>
@@ -9881,7 +9881,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.2232723236084</v>
+        <v>19.223274230957</v>
       </c>
       <c r="H328" t="n">
         <v>5122</v>
@@ -9910,7 +9910,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729610443115</v>
+        <v>18.8729629516602</v>
       </c>
       <c r="H329" t="n">
         <v>14665</v>
@@ -9939,7 +9939,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167499542236</v>
+        <v>18.9167537689209</v>
       </c>
       <c r="H330" t="n">
         <v>9202</v>
@@ -9968,7 +9968,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H331" t="n">
         <v>11487</v>
@@ -10026,7 +10026,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.2232723236084</v>
+        <v>19.223274230957</v>
       </c>
       <c r="H333" t="n">
         <v>8384</v>
@@ -10055,7 +10055,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H334" t="n">
         <v>5987</v>
@@ -10084,7 +10084,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853870391846</v>
       </c>
       <c r="H335" t="n">
         <v>17649</v>
@@ -10113,7 +10113,7 @@
         <v>21.5</v>
       </c>
       <c r="G336" t="n">
-        <v>18.829174041748</v>
+        <v>18.8291759490967</v>
       </c>
       <c r="H336" t="n">
         <v>16890</v>
@@ -10142,7 +10142,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415981292725</v>
       </c>
       <c r="H337" t="n">
         <v>8572</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546371459961</v>
+        <v>19.3546390533447</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10200,7 +10200,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167499542236</v>
+        <v>18.9167537689209</v>
       </c>
       <c r="H339" t="n">
         <v>11503</v>
@@ -10229,7 +10229,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794834136963</v>
       </c>
       <c r="H340" t="n">
         <v>8629</v>
@@ -10345,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912868499756</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H344" t="n">
         <v>18146</v>
@@ -10374,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912868499756</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H345" t="n">
         <v>7042</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799457550049</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10490,7 +10490,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.212646484375</v>
+        <v>20.2126445770264</v>
       </c>
       <c r="H349" t="n">
         <v>34567</v>
@@ -10519,7 +10519,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903427124023</v>
+        <v>20.3903388977051</v>
       </c>
       <c r="H350" t="n">
         <v>39422</v>
@@ -10577,7 +10577,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>20.1237983703613</v>
+        <v>20.1237964630127</v>
       </c>
       <c r="H352" t="n">
         <v>39061</v>
@@ -10606,7 +10606,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572597503662</v>
+        <v>19.8572616577148</v>
       </c>
       <c r="H353" t="n">
         <v>50006</v>
@@ -10635,7 +10635,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793743133545</v>
+        <v>20.0793762207031</v>
       </c>
       <c r="H354" t="n">
         <v>30645</v>
@@ -10664,7 +10664,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905300140381</v>
+        <v>19.9905281066895</v>
       </c>
       <c r="H355" t="n">
         <v>20044</v>
@@ -10722,7 +10722,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684116363525</v>
+        <v>19.7684135437012</v>
       </c>
       <c r="H357" t="n">
         <v>47937</v>
@@ -10751,7 +10751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461059570312</v>
+        <v>19.9461097717285</v>
       </c>
       <c r="H358" t="n">
         <v>49210</v>
@@ -10780,7 +10780,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.8355197906494</v>
+        <v>18.835521697998</v>
       </c>
       <c r="H359" t="n">
         <v>57619</v>
@@ -10809,7 +10809,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.746675491333</v>
+        <v>18.7466773986816</v>
       </c>
       <c r="H360" t="n">
         <v>21783</v>
@@ -10838,7 +10838,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910995483398</v>
+        <v>18.7910957336426</v>
       </c>
       <c r="H361" t="n">
         <v>19501</v>
@@ -10867,7 +10867,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>19.6351413726807</v>
+        <v>19.6351432800293</v>
       </c>
       <c r="H362" t="n">
         <v>29703</v>
@@ -10925,7 +10925,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>20.1237983703613</v>
+        <v>20.1237964630127</v>
       </c>
       <c r="H364" t="n">
         <v>53805</v>
@@ -10983,7 +10983,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905300140381</v>
+        <v>19.9905281066895</v>
       </c>
       <c r="H366" t="n">
         <v>12885</v>
@@ -11012,7 +11012,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H367" t="n">
         <v>19035</v>
@@ -11041,7 +11041,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H368" t="n">
         <v>25835</v>
@@ -11273,7 +11273,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890144348145</v>
+        <v>23.1890125274658</v>
       </c>
       <c r="H376" t="n">
         <v>28296</v>
@@ -11331,7 +11331,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.8336277008057</v>
+        <v>22.833625793457</v>
       </c>
       <c r="H378" t="n">
         <v>26713</v>
@@ -11447,7 +11447,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563098907471</v>
+        <v>21.8563117980957</v>
       </c>
       <c r="H382" t="n">
         <v>53898</v>
@@ -11563,7 +11563,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H386" t="n">
         <v>27193</v>
@@ -11621,7 +11621,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566921234131</v>
+        <v>21.0566902160645</v>
       </c>
       <c r="H388" t="n">
         <v>20039</v>
@@ -11650,7 +11650,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>20.7013034820557</v>
+        <v>20.701301574707</v>
       </c>
       <c r="H389" t="n">
         <v>22114</v>
@@ -11679,7 +11679,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>20.7013034820557</v>
+        <v>20.701301574707</v>
       </c>
       <c r="H390" t="n">
         <v>27192</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11766,7 +11766,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.6124572753906</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H393" t="n">
         <v>23385</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11853,7 +11853,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.6124572753906</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H396" t="n">
         <v>21826</v>
@@ -11882,7 +11882,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680351257324</v>
+        <v>20.5680332183838</v>
       </c>
       <c r="H397" t="n">
         <v>6449</v>
@@ -11911,7 +11911,7 @@
         <v>24.5</v>
       </c>
       <c r="G398" t="n">
-        <v>21.767463684082</v>
+        <v>21.7674655914307</v>
       </c>
       <c r="H398" t="n">
         <v>74119</v>
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H399" t="n">
         <v>85005</v>
@@ -12143,7 +12143,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.6124572753906</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H406" t="n">
         <v>42941</v>
@@ -12201,7 +12201,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.6124572753906</v>
+        <v>20.612455368042</v>
       </c>
       <c r="H408" t="n">
         <v>17907</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12288,7 +12288,7 @@
         <v>24.5</v>
       </c>
       <c r="G411" t="n">
-        <v>21.767463684082</v>
+        <v>21.7674655914307</v>
       </c>
       <c r="H411" t="n">
         <v>36810</v>
@@ -12317,7 +12317,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H412" t="n">
         <v>32846</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115093231201</v>
+        <v>22.6115112304688</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12491,7 +12491,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561225891113</v>
+        <v>22.2561206817627</v>
       </c>
       <c r="H418" t="n">
         <v>18147</v>
@@ -12578,7 +12578,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224720001221</v>
+        <v>22.9224739074707</v>
       </c>
       <c r="H421" t="n">
         <v>20723</v>
@@ -12636,7 +12636,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551765441895</v>
+        <v>24.2551746368408</v>
       </c>
       <c r="H423" t="n">
         <v>80709</v>
@@ -12665,7 +12665,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663284301758</v>
+        <v>24.1663303375244</v>
       </c>
       <c r="H424" t="n">
         <v>33528</v>
@@ -12723,7 +12723,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>23.6332473754883</v>
+        <v>23.6332492828369</v>
       </c>
       <c r="H426" t="n">
         <v>20089</v>
@@ -12752,7 +12752,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886322021484</v>
+        <v>23.9886360168457</v>
       </c>
       <c r="H427" t="n">
         <v>21987</v>
@@ -12781,7 +12781,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772891998291</v>
       </c>
       <c r="H428" t="n">
         <v>27149</v>
@@ -12810,7 +12810,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>24.1219024658203</v>
+        <v>24.1219043731689</v>
       </c>
       <c r="H429" t="n">
         <v>41301</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.56614112854</v>
+        <v>24.5661373138428</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -12955,7 +12955,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438335418701</v>
+        <v>24.7438354492188</v>
       </c>
       <c r="H434" t="n">
         <v>22801</v>
@@ -12984,7 +12984,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326797485352</v>
+        <v>24.8326816558838</v>
       </c>
       <c r="H435" t="n">
         <v>15025</v>
@@ -13071,7 +13071,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H438" t="n">
         <v>49309</v>
@@ -13100,7 +13100,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H439" t="n">
         <v>22024</v>
@@ -13129,7 +13129,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H440" t="n">
         <v>28408</v>
@@ -13158,7 +13158,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207710266113</v>
+        <v>26.5207691192627</v>
       </c>
       <c r="H441" t="n">
         <v>28926</v>
@@ -13187,7 +13187,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H442" t="n">
         <v>23385</v>
@@ -13216,7 +13216,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205799102783</v>
+        <v>26.9205780029297</v>
       </c>
       <c r="H443" t="n">
         <v>23035</v>
@@ -13245,7 +13245,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536609649658</v>
+        <v>27.4536628723145</v>
       </c>
       <c r="H444" t="n">
         <v>42660</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967567443848</v>
+        <v>30.2967548370361</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13390,7 +13390,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.6965675354004</v>
+        <v>30.696569442749</v>
       </c>
       <c r="H449" t="n">
         <v>65084</v>
@@ -13448,7 +13448,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417484283447</v>
+        <v>29.1417503356934</v>
       </c>
       <c r="H451" t="n">
         <v>55282</v>
@@ -13564,7 +13564,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744510650635</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H455" t="n">
         <v>27798</v>
@@ -13593,7 +13593,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>28.1200122833252</v>
+        <v>28.1200103759766</v>
       </c>
       <c r="H456" t="n">
         <v>92553</v>
@@ -13622,7 +13622,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646217346191</v>
+        <v>27.7646236419678</v>
       </c>
       <c r="H457" t="n">
         <v>101299</v>
@@ -13738,7 +13738,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.475399017334</v>
+        <v>28.4753971099854</v>
       </c>
       <c r="H461" t="n">
         <v>73902</v>
@@ -13854,7 +13854,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863636016846</v>
       </c>
       <c r="H465" t="n">
         <v>29892</v>
@@ -13883,7 +13883,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.1644382476807</v>
+        <v>28.164436340332</v>
       </c>
       <c r="H466" t="n">
         <v>19936</v>
@@ -13912,7 +13912,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H467" t="n">
         <v>54363</v>
@@ -13970,7 +13970,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409915924072</v>
+        <v>30.7409934997559</v>
       </c>
       <c r="H469" t="n">
         <v>41790</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627258300781</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14086,7 +14086,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H473" t="n">
         <v>41695</v>
@@ -14115,7 +14115,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.162540435791</v>
+        <v>32.1625442504883</v>
       </c>
       <c r="H474" t="n">
         <v>26719</v>
@@ -14260,7 +14260,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H479" t="n">
         <v>24196</v>
@@ -14347,7 +14347,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.7173614501953</v>
+        <v>33.717357635498</v>
       </c>
       <c r="H482" t="n">
         <v>45662</v>
@@ -14376,7 +14376,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H483" t="n">
         <v>61904</v>
@@ -14405,7 +14405,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942970275879</v>
+        <v>35.4942932128906</v>
       </c>
       <c r="H484" t="n">
         <v>95655</v>
@@ -14463,7 +14463,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617835998535</v>
+        <v>33.7617874145508</v>
       </c>
       <c r="H486" t="n">
         <v>58518</v>
@@ -14521,7 +14521,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398544311523</v>
+        <v>33.1398582458496</v>
       </c>
       <c r="H488" t="n">
         <v>34481</v>
@@ -14608,7 +14608,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H491" t="n">
         <v>10757</v>
@@ -14637,7 +14637,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288955688477</v>
       </c>
       <c r="H492" t="n">
         <v>26262</v>
@@ -14666,7 +14666,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844696044922</v>
+        <v>32.7844734191895</v>
       </c>
       <c r="H493" t="n">
         <v>16789</v>
@@ -14695,7 +14695,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954322814941</v>
+        <v>33.0954284667969</v>
       </c>
       <c r="H494" t="n">
         <v>20925</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14811,7 +14811,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.162540435791</v>
+        <v>32.1625442504883</v>
       </c>
       <c r="H498" t="n">
         <v>32373</v>
@@ -14840,7 +14840,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H499" t="n">
         <v>11923</v>
@@ -14869,7 +14869,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634883880615</v>
+        <v>30.1634864807129</v>
       </c>
       <c r="H500" t="n">
         <v>80023</v>
@@ -14898,7 +14898,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H501" t="n">
         <v>30662</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177398681641</v>
+        <v>32.9177322387695</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15159,7 +15159,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071517944336</v>
+        <v>31.8071556091309</v>
       </c>
       <c r="H510" t="n">
         <v>24075</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627258300781</v>
+        <v>31.7627277374268</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15246,7 +15246,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510101318359</v>
+        <v>33.0510063171387</v>
       </c>
       <c r="H513" t="n">
         <v>30830</v>
@@ -15275,7 +15275,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508209228516</v>
+        <v>33.4508171081543</v>
       </c>
       <c r="H514" t="n">
         <v>66935</v>
@@ -15391,7 +15391,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288955688477</v>
       </c>
       <c r="H518" t="n">
         <v>13845</v>
@@ -15420,7 +15420,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290809631348</v>
+        <v>32.429084777832</v>
       </c>
       <c r="H519" t="n">
         <v>27308</v>
@@ -15449,7 +15449,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.317554473877</v>
+        <v>33.3175506591797</v>
       </c>
       <c r="H520" t="n">
         <v>18235</v>
@@ -15507,7 +15507,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954322814941</v>
+        <v>33.0954284667969</v>
       </c>
       <c r="H522" t="n">
         <v>24452</v>
@@ -15536,7 +15536,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729393005371</v>
+        <v>33.6729316711426</v>
       </c>
       <c r="H523" t="n">
         <v>18883</v>
@@ -15565,7 +15565,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.294864654541</v>
+        <v>34.2948608398438</v>
       </c>
       <c r="H524" t="n">
         <v>40082</v>
@@ -15710,7 +15710,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960018157959</v>
+        <v>31.8959999084473</v>
       </c>
       <c r="H529" t="n">
         <v>38776</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15971,7 +15971,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727500915527</v>
+        <v>34.0727424621582</v>
       </c>
       <c r="H538" t="n">
         <v>33816</v>
@@ -16000,7 +16000,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H539" t="n">
         <v>56910</v>
@@ -16058,7 +16058,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H541" t="n">
         <v>30426</v>
@@ -16116,7 +16116,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290809631348</v>
+        <v>32.429084777832</v>
       </c>
       <c r="H543" t="n">
         <v>43887</v>
@@ -16232,7 +16232,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H547" t="n">
         <v>60536</v>
@@ -16261,7 +16261,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H548" t="n">
         <v>151703</v>
@@ -16290,7 +16290,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279418945312</v>
+        <v>34.8279457092285</v>
       </c>
       <c r="H549" t="n">
         <v>115069</v>
@@ -16348,7 +16348,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H551" t="n">
         <v>43962</v>
@@ -16377,7 +16377,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275634765625</v>
+        <v>35.6275672912598</v>
       </c>
       <c r="H552" t="n">
         <v>107403</v>
@@ -16406,7 +16406,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H553" t="n">
         <v>48943</v>
@@ -16493,7 +16493,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.294864654541</v>
+        <v>34.2948608398438</v>
       </c>
       <c r="H556" t="n">
         <v>29679</v>
@@ -16551,7 +16551,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H558" t="n">
         <v>31513</v>
@@ -16609,7 +16609,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721748352051</v>
+        <v>35.2721786499023</v>
       </c>
       <c r="H560" t="n">
         <v>92873</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.405445098877</v>
+        <v>35.4054489135742</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16696,7 +16696,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714256286621</v>
+        <v>36.8714179992676</v>
       </c>
       <c r="H563" t="n">
         <v>79980</v>
@@ -16841,7 +16841,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530933380127</v>
+        <v>28.6530914306641</v>
       </c>
       <c r="H568" t="n">
         <v>187078</v>
@@ -16870,7 +16870,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655696868896</v>
+        <v>25.7655715942383</v>
       </c>
       <c r="H569" t="n">
         <v>154319</v>
@@ -16899,7 +16899,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.788257598877</v>
+        <v>24.7882556915283</v>
       </c>
       <c r="H570" t="n">
         <v>115179</v>
@@ -16928,7 +16928,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.3430767059326</v>
+        <v>26.343074798584</v>
       </c>
       <c r="H571" t="n">
         <v>102740</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184967041016</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17102,7 +17102,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519523620605</v>
       </c>
       <c r="H577" t="n">
         <v>60129</v>
@@ -17131,7 +17131,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H578" t="n">
         <v>447251</v>
@@ -17160,7 +17160,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H579" t="n">
         <v>47898</v>
@@ -17218,7 +17218,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H581" t="n">
         <v>35526</v>
@@ -17276,7 +17276,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H583" t="n">
         <v>48569</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17334,7 +17334,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H585" t="n">
         <v>89419</v>
@@ -17392,7 +17392,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H587" t="n">
         <v>35265</v>
@@ -17479,7 +17479,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069625854492</v>
+        <v>32.2069664001465</v>
       </c>
       <c r="H590" t="n">
         <v>44682</v>
@@ -17537,7 +17537,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744510650635</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H592" t="n">
         <v>28557</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17711,7 +17711,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519523620605</v>
       </c>
       <c r="H598" t="n">
         <v>20035</v>
@@ -17769,7 +17769,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H600" t="n">
         <v>24723</v>
@@ -17798,7 +17798,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294593811035</v>
       </c>
       <c r="H601" t="n">
         <v>16163</v>
@@ -17827,7 +17827,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H602" t="n">
         <v>46419</v>
@@ -17856,7 +17856,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863636016846</v>
       </c>
       <c r="H603" t="n">
         <v>26401</v>
@@ -17885,7 +17885,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G604" t="n">
-        <v>28.9640522003174</v>
+        <v>28.964054107666</v>
       </c>
       <c r="H604" t="n">
         <v>20198</v>
@@ -17914,7 +17914,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859832763672</v>
+        <v>29.5859813690186</v>
       </c>
       <c r="H605" t="n">
         <v>31886</v>
@@ -17943,7 +17943,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H606" t="n">
         <v>22611</v>
@@ -18204,7 +18204,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828468322754</v>
+        <v>32.3828506469727</v>
       </c>
       <c r="H615" t="n">
         <v>35851</v>
@@ -18291,7 +18291,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658050537109</v>
+        <v>33.9658088684082</v>
       </c>
       <c r="H618" t="n">
         <v>36011</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.890344619751</v>
+        <v>30.8903465270996</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18465,7 +18465,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>30.1667022705078</v>
+        <v>30.1667041778564</v>
       </c>
       <c r="H624" t="n">
         <v>21890</v>
@@ -18494,7 +18494,7 @@
         <v>34.5</v>
       </c>
       <c r="G625" t="n">
-        <v>31.2069358825684</v>
+        <v>31.2069339752197</v>
       </c>
       <c r="H625" t="n">
         <v>24917</v>
@@ -18552,7 +18552,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898941040039</v>
+        <v>32.7898979187012</v>
       </c>
       <c r="H627" t="n">
         <v>41583</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.890344619751</v>
+        <v>30.8903465270996</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18610,7 +18610,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189804077148</v>
+        <v>30.6189765930176</v>
       </c>
       <c r="H629" t="n">
         <v>25073</v>
@@ -18755,7 +18755,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260257720947</v>
+        <v>31.0260238647461</v>
       </c>
       <c r="H634" t="n">
         <v>36768</v>
@@ -18784,7 +18784,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.1667022705078</v>
+        <v>30.1667041778564</v>
       </c>
       <c r="H635" t="n">
         <v>21215</v>
@@ -18813,7 +18813,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H636" t="n">
         <v>49552</v>
@@ -18958,7 +18958,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>28.8551082611084</v>
+        <v>28.8551063537598</v>
       </c>
       <c r="H641" t="n">
         <v>47653</v>
@@ -19016,7 +19016,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H643" t="n">
         <v>23506</v>
@@ -19190,7 +19190,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H649" t="n">
         <v>12887</v>
@@ -19306,7 +19306,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339683532715</v>
+        <v>27.6339664459229</v>
       </c>
       <c r="H653" t="n">
         <v>22878</v>
@@ -19480,7 +19480,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H659" t="n">
         <v>11969</v>
@@ -19596,7 +19596,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214771270752</v>
+        <v>30.1214752197266</v>
       </c>
       <c r="H663" t="n">
         <v>13226</v>
@@ -19625,7 +19625,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H664" t="n">
         <v>12292</v>
@@ -19683,7 +19683,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260257720947</v>
+        <v>31.0260238647461</v>
       </c>
       <c r="H666" t="n">
         <v>41810</v>
@@ -19770,7 +19770,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H669" t="n">
         <v>27479</v>
@@ -19857,7 +19857,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H672" t="n">
         <v>11102</v>
@@ -19886,7 +19886,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H673" t="n">
         <v>12485</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.935567855835</v>
+        <v>30.9355697631836</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19973,7 +19973,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023891448975</v>
+        <v>30.3023872375488</v>
       </c>
       <c r="H676" t="n">
         <v>13444</v>
@@ -20002,7 +20002,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832954406738</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H677" t="n">
         <v>25987</v>
@@ -20089,7 +20089,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H680" t="n">
         <v>18879</v>
@@ -20379,7 +20379,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H690" t="n">
         <v>13325</v>
@@ -20437,7 +20437,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H692" t="n">
         <v>20442</v>
@@ -20466,7 +20466,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123798370361</v>
+        <v>28.3123779296875</v>
       </c>
       <c r="H693" t="n">
         <v>18525</v>
@@ -20640,7 +20640,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H699" t="n">
         <v>56297</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.719425201416</v>
+        <v>28.7194271087646</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20901,7 +20901,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G708" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H708" t="n">
         <v>15124</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314697265625</v>
+        <v>28.1314678192139</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21046,7 +21046,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H713" t="n">
         <v>37089</v>
@@ -21249,7 +21249,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H720" t="n">
         <v>19906</v>
@@ -21307,7 +21307,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H722" t="n">
         <v>27650</v>
@@ -21336,7 +21336,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H723" t="n">
         <v>10352</v>
@@ -21365,7 +21365,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H724" t="n">
         <v>28121</v>
@@ -21423,7 +21423,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>29.9857959747314</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H726" t="n">
         <v>26161</v>
@@ -21481,7 +21481,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G728" t="n">
-        <v>29.0812473297119</v>
+        <v>29.0812454223633</v>
       </c>
       <c r="H728" t="n">
         <v>20050</v>
@@ -21713,7 +21713,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H736" t="n">
         <v>39696</v>
@@ -21742,7 +21742,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H737" t="n">
         <v>13524</v>
@@ -21858,7 +21858,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H741" t="n">
         <v>14572</v>
@@ -21887,7 +21887,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285263061523</v>
       </c>
       <c r="H742" t="n">
         <v>22513</v>
@@ -21974,7 +21974,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401165008545</v>
+        <v>31.8401203155518</v>
       </c>
       <c r="H745" t="n">
         <v>20993</v>
@@ -22090,7 +22090,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>30.1667022705078</v>
+        <v>30.1667041778564</v>
       </c>
       <c r="H749" t="n">
         <v>16880</v>
@@ -22119,7 +22119,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832954406738</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H750" t="n">
         <v>5976</v>
@@ -22612,7 +22612,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969413757324</v>
+        <v>33.1969451904297</v>
       </c>
       <c r="H767" t="n">
         <v>47582</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.252161026001</v>
+        <v>31.2521648406982</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637626647949</v>
+        <v>32.5637588500977</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -23047,7 +23047,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.875358581543</v>
+        <v>33.8753547668457</v>
       </c>
       <c r="H782" t="n">
         <v>27238</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23221,7 +23221,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.875358581543</v>
+        <v>33.8753547668457</v>
       </c>
       <c r="H788" t="n">
         <v>10901</v>
@@ -23395,7 +23395,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658050537109</v>
+        <v>33.9658088684082</v>
       </c>
       <c r="H794" t="n">
         <v>32389</v>
@@ -23424,7 +23424,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H795" t="n">
         <v>28476</v>
@@ -23453,7 +23453,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H796" t="n">
         <v>22692</v>
@@ -23482,7 +23482,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035400390625</v>
+        <v>35.5035438537598</v>
       </c>
       <c r="H797" t="n">
         <v>15860</v>
@@ -23540,7 +23540,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392288208008</v>
       </c>
       <c r="H799" t="n">
         <v>12129</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578643798828</v>
+        <v>37.3578681945801</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23801,7 +23801,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.2271766662598</v>
+        <v>36.227180480957</v>
       </c>
       <c r="H808" t="n">
         <v>31459</v>
@@ -23830,7 +23830,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.0914993286133</v>
+        <v>36.0915031433105</v>
       </c>
       <c r="H809" t="n">
         <v>50811</v>
@@ -23859,7 +23859,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.0914993286133</v>
+        <v>36.0915031433105</v>
       </c>
       <c r="H810" t="n">
         <v>26507</v>
@@ -23917,7 +23917,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G812" t="n">
-        <v>36.7699127197266</v>
+        <v>36.7699089050293</v>
       </c>
       <c r="H812" t="n">
         <v>15630</v>
@@ -23946,7 +23946,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.5437774658203</v>
+        <v>36.543773651123</v>
       </c>
       <c r="H813" t="n">
         <v>27397</v>
@@ -24149,7 +24149,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433288574219</v>
+        <v>38.4433250427246</v>
       </c>
       <c r="H820" t="n">
         <v>48120</v>
@@ -24178,7 +24178,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312805175781</v>
       </c>
       <c r="H821" t="n">
         <v>71113</v>
@@ -24207,7 +24207,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3981018066406</v>
+        <v>38.3980979919434</v>
       </c>
       <c r="H822" t="n">
         <v>31744</v>
@@ -24381,7 +24381,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312805175781</v>
       </c>
       <c r="H828" t="n">
         <v>29768</v>
@@ -24410,7 +24410,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H829" t="n">
         <v>35652</v>
@@ -24468,7 +24468,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910545349121</v>
+        <v>37.9910507202148</v>
       </c>
       <c r="H831" t="n">
         <v>31412</v>
@@ -24526,7 +24526,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649154663086</v>
+        <v>37.7649192810059</v>
       </c>
       <c r="H833" t="n">
         <v>30771</v>
@@ -24584,7 +24584,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H835" t="n">
         <v>34627</v>
@@ -24642,7 +24642,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.1819534301758</v>
+        <v>36.1819496154785</v>
       </c>
       <c r="H837" t="n">
         <v>119181</v>
@@ -24700,7 +24700,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367301940918</v>
+        <v>36.1367263793945</v>
       </c>
       <c r="H839" t="n">
         <v>32321</v>
@@ -24758,7 +24758,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392250061035</v>
+        <v>35.6392288208008</v>
       </c>
       <c r="H841" t="n">
         <v>39832</v>
@@ -24845,7 +24845,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.1819534301758</v>
+        <v>36.1819496154785</v>
       </c>
       <c r="H844" t="n">
         <v>20530</v>
@@ -24903,7 +24903,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.1819534301758</v>
+        <v>36.1819496154785</v>
       </c>
       <c r="H846" t="n">
         <v>26328</v>
@@ -24961,7 +24961,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.910587310791</v>
+        <v>35.9105911254883</v>
       </c>
       <c r="H848" t="n">
         <v>26054</v>
@@ -24990,7 +24990,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387802124023</v>
+        <v>37.5387763977051</v>
       </c>
       <c r="H849" t="n">
         <v>30157</v>
@@ -25135,7 +25135,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744613647461</v>
+        <v>37.6744575500488</v>
       </c>
       <c r="H854" t="n">
         <v>14320</v>
@@ -25309,7 +25309,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.0462684631348</v>
+        <v>36.046272277832</v>
       </c>
       <c r="H860" t="n">
         <v>13910</v>
@@ -25367,7 +25367,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>36.7699127197266</v>
+        <v>36.7699089050293</v>
       </c>
       <c r="H862" t="n">
         <v>14424</v>
@@ -25396,7 +25396,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H863" t="n">
         <v>17246</v>
@@ -25425,7 +25425,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H864" t="n">
         <v>25714</v>
@@ -25512,7 +25512,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H867" t="n">
         <v>6491</v>
@@ -25744,7 +25744,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>36.4113121032715</v>
+        <v>36.4113159179688</v>
       </c>
       <c r="H875" t="n">
         <v>10487</v>
@@ -25831,7 +25831,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354751586914</v>
+        <v>36.1354713439941</v>
       </c>
       <c r="H878" t="n">
         <v>14544</v>
@@ -25860,7 +25860,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>35.5378112792969</v>
+        <v>35.5378150939941</v>
       </c>
       <c r="H879" t="n">
         <v>20797</v>
@@ -25976,7 +25976,7 @@
         <v>38</v>
       </c>
       <c r="G883" t="n">
-        <v>34.9401512145996</v>
+        <v>34.9401550292969</v>
       </c>
       <c r="H883" t="n">
         <v>16359</v>
@@ -26034,7 +26034,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.618335723877</v>
+        <v>34.6183319091797</v>
       </c>
       <c r="H885" t="n">
         <v>19645</v>
@@ -26179,7 +26179,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H890" t="n">
         <v>21938</v>
@@ -26208,7 +26208,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>34.664306640625</v>
+        <v>34.6643104553223</v>
       </c>
       <c r="H891" t="n">
         <v>21890</v>
@@ -26324,7 +26324,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>35.5378112792969</v>
+        <v>35.5378150939941</v>
       </c>
       <c r="H895" t="n">
         <v>24511</v>
@@ -26353,7 +26353,7 @@
         <v>38.25</v>
       </c>
       <c r="G896" t="n">
-        <v>35.1700210571289</v>
+        <v>35.1700172424316</v>
       </c>
       <c r="H896" t="n">
         <v>56083</v>
@@ -26585,7 +26585,7 @@
         <v>38</v>
       </c>
       <c r="G904" t="n">
-        <v>34.9401512145996</v>
+        <v>34.9401550292969</v>
       </c>
       <c r="H904" t="n">
         <v>19538</v>
@@ -26701,7 +26701,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G908" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H908" t="n">
         <v>19888</v>
@@ -26875,7 +26875,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G914" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H914" t="n">
         <v>24076</v>
@@ -26991,7 +26991,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H918" t="n">
         <v>15454</v>
@@ -27020,7 +27020,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310699462891</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H919" t="n">
         <v>14186</v>
@@ -27194,7 +27194,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H925" t="n">
         <v>24388</v>
@@ -27281,7 +27281,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H928" t="n">
         <v>18700</v>
@@ -27368,7 +27368,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>34.664306640625</v>
+        <v>34.6643104553223</v>
       </c>
       <c r="H931" t="n">
         <v>102214</v>
@@ -27455,7 +27455,7 @@
         <v>37.5</v>
       </c>
       <c r="G934" t="n">
-        <v>34.480411529541</v>
+        <v>34.4804153442383</v>
       </c>
       <c r="H934" t="n">
         <v>36101</v>
@@ -27542,7 +27542,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G937" t="n">
-        <v>35.0780754089355</v>
+        <v>35.0780715942383</v>
       </c>
       <c r="H937" t="n">
         <v>13021</v>
@@ -27571,7 +27571,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>35.2619705200195</v>
+        <v>35.2619667053223</v>
       </c>
       <c r="H938" t="n">
         <v>29216</v>
@@ -27600,7 +27600,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.296516418457</v>
+        <v>34.2965126037598</v>
       </c>
       <c r="H939" t="n">
         <v>16255</v>
@@ -27977,7 +27977,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H952" t="n">
         <v>8028</v>
@@ -28006,7 +28006,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H953" t="n">
         <v>30708</v>
@@ -28093,7 +28093,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448348999023</v>
+        <v>33.7448310852051</v>
       </c>
       <c r="H956" t="n">
         <v>7086</v>
@@ -28151,7 +28151,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H958" t="n">
         <v>18202</v>
@@ -28267,7 +28267,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H962" t="n">
         <v>19440</v>
@@ -28296,7 +28296,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.503532409668</v>
+        <v>32.5035362243652</v>
       </c>
       <c r="H963" t="n">
         <v>11379</v>
@@ -28354,7 +28354,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H965" t="n">
         <v>16412</v>
@@ -28412,7 +28412,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H967" t="n">
         <v>23454</v>
@@ -28470,7 +28470,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H969" t="n">
         <v>26969</v>
@@ -28557,7 +28557,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G972" t="n">
-        <v>33.0092468261719</v>
+        <v>33.0092506408691</v>
       </c>
       <c r="H972" t="n">
         <v>17502</v>
@@ -28673,7 +28673,7 @@
         <v>35.75</v>
       </c>
       <c r="G976" t="n">
-        <v>32.8713302612305</v>
+        <v>32.8713264465332</v>
       </c>
       <c r="H976" t="n">
         <v>23421</v>
@@ -28731,7 +28731,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6069068908691</v>
+        <v>33.6069107055664</v>
       </c>
       <c r="H978" t="n">
         <v>13732</v>
@@ -28789,7 +28789,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310699462891</v>
+        <v>33.3310661315918</v>
       </c>
       <c r="H980" t="n">
         <v>18596</v>
@@ -28818,7 +28818,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H981" t="n">
         <v>23720</v>
@@ -28934,7 +28934,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H985" t="n">
         <v>10944</v>
@@ -29108,7 +29108,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783424377441</v>
+        <v>31.0783443450928</v>
       </c>
       <c r="H991" t="n">
         <v>22083</v>
@@ -29253,7 +29253,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H996" t="n">
         <v>15814</v>
@@ -29456,7 +29456,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>36.4113121032715</v>
+        <v>36.4113159179688</v>
       </c>
       <c r="H1003" t="n">
         <v>52594</v>
@@ -29485,7 +29485,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>35.3079414367676</v>
+        <v>35.3079452514648</v>
       </c>
       <c r="H1004" t="n">
         <v>19185</v>
@@ -29514,7 +29514,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>35.8136558532715</v>
+        <v>35.8136596679688</v>
       </c>
       <c r="H1005" t="n">
         <v>29077</v>
@@ -29630,7 +29630,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1009" t="n">
         <v>15324</v>
@@ -29659,7 +29659,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1010" t="n">
         <v>9446</v>
@@ -29717,7 +29717,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1012" t="n">
         <v>19550</v>
@@ -29746,7 +29746,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>35.8136558532715</v>
+        <v>35.8136596679688</v>
       </c>
       <c r="H1013" t="n">
         <v>21171</v>
@@ -29862,7 +29862,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1017" t="n">
-        <v>36.8710517883301</v>
+        <v>36.8710556030273</v>
       </c>
       <c r="H1017" t="n">
         <v>16992</v>
@@ -30065,7 +30065,7 @@
         <v>42</v>
       </c>
       <c r="G1024" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1024" t="n">
         <v>27579</v>
@@ -30152,7 +30152,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1027" t="n">
         <v>33681</v>
@@ -30268,7 +30268,7 @@
         <v>42.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1031" t="n">
         <v>32251</v>
@@ -30326,7 +30326,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1033" t="n">
         <v>17293</v>
@@ -30355,7 +30355,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>38.2502708435059</v>
+        <v>38.2502746582031</v>
       </c>
       <c r="H1034" t="n">
         <v>34988</v>
@@ -30442,7 +30442,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985816955566</v>
+        <v>37.6985855102539</v>
       </c>
       <c r="H1037" t="n">
         <v>16755</v>
@@ -30471,7 +30471,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1038" t="n">
         <v>24399</v>
@@ -30500,7 +30500,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1039" t="n">
         <v>35974</v>
@@ -30529,7 +30529,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1040" t="n">
         <v>10126</v>
@@ -30645,7 +30645,7 @@
         <v>42.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1044" t="n">
         <v>25555</v>
@@ -30703,7 +30703,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1046" t="n">
         <v>27206</v>
@@ -30732,7 +30732,7 @@
         <v>42.5</v>
       </c>
       <c r="G1047" t="n">
-        <v>39.0778007507324</v>
+        <v>39.0778045654297</v>
       </c>
       <c r="H1047" t="n">
         <v>18406</v>
@@ -30790,7 +30790,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1049" t="n">
         <v>25230</v>
@@ -30848,7 +30848,7 @@
         <v>44</v>
       </c>
       <c r="G1051" t="n">
-        <v>40.4570159912109</v>
+        <v>40.4570198059082</v>
       </c>
       <c r="H1051" t="n">
         <v>26021</v>
@@ -30877,7 +30877,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1052" t="n">
-        <v>41.3305206298828</v>
+        <v>41.3305244445801</v>
       </c>
       <c r="H1052" t="n">
         <v>34152</v>
@@ -31022,7 +31022,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1057" t="n">
         <v>25708</v>
@@ -31051,7 +31051,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1058" t="n">
         <v>26015</v>
@@ -31225,7 +31225,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>41.3305206298828</v>
+        <v>41.3305244445801</v>
       </c>
       <c r="H1064" t="n">
         <v>70471</v>
@@ -31254,7 +31254,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442893981934</v>
+        <v>41.7442855834961</v>
       </c>
       <c r="H1065" t="n">
         <v>58297</v>
@@ -31283,7 +31283,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>40.5489616394043</v>
+        <v>40.5489654541016</v>
       </c>
       <c r="H1066" t="n">
         <v>41750</v>
@@ -31428,7 +31428,7 @@
         <v>42</v>
       </c>
       <c r="G1071" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1071" t="n">
         <v>21365</v>
@@ -31457,7 +31457,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1072" t="n">
         <v>20307</v>
@@ -31689,7 +31689,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985816955566</v>
+        <v>37.6985855102539</v>
       </c>
       <c r="H1080" t="n">
         <v>21026</v>
@@ -31718,7 +31718,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H1081" t="n">
         <v>37081</v>
@@ -31747,7 +31747,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009216308594</v>
+        <v>37.1009178161621</v>
       </c>
       <c r="H1082" t="n">
         <v>33479</v>
@@ -31834,7 +31834,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422164916992</v>
+        <v>38.3422203063965</v>
       </c>
       <c r="H1085" t="n">
         <v>44926</v>
@@ -31892,7 +31892,7 @@
         <v>42</v>
       </c>
       <c r="G1087" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1087" t="n">
         <v>47019</v>
@@ -32095,7 +32095,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824844360352</v>
+        <v>37.8824806213379</v>
       </c>
       <c r="H1094" t="n">
         <v>23661</v>
@@ -32124,7 +32124,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1095" t="n">
         <v>27027</v>
@@ -32153,7 +32153,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>38.7559852600098</v>
+        <v>38.7559814453125</v>
       </c>
       <c r="H1096" t="n">
         <v>30370</v>
@@ -32182,7 +32182,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1097" t="n">
-        <v>37.744556427002</v>
+        <v>37.7445602416992</v>
       </c>
       <c r="H1097" t="n">
         <v>46557</v>
@@ -32211,7 +32211,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1098" t="n">
         <v>26751</v>
@@ -32240,7 +32240,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1099" t="n">
         <v>14005</v>
@@ -32501,7 +32501,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1108" t="n">
-        <v>36.4113121032715</v>
+        <v>36.4113159179688</v>
       </c>
       <c r="H1108" t="n">
         <v>21226</v>
@@ -32559,7 +32559,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1110" t="n">
-        <v>35.7217102050781</v>
+        <v>35.7217063903809</v>
       </c>
       <c r="H1110" t="n">
         <v>18379</v>
@@ -32588,7 +32588,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.7217102050781</v>
+        <v>35.7217063903809</v>
       </c>
       <c r="H1111" t="n">
         <v>13856</v>
@@ -32733,7 +32733,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1116" t="n">
         <v>18589</v>
@@ -32849,7 +32849,7 @@
         <v>42</v>
       </c>
       <c r="G1120" t="n">
-        <v>38.6180610656738</v>
+        <v>38.6180648803711</v>
       </c>
       <c r="H1120" t="n">
         <v>22119</v>
@@ -32907,7 +32907,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858589172363</v>
+        <v>38.9858551025391</v>
       </c>
       <c r="H1122" t="n">
         <v>13057</v>
@@ -32936,7 +32936,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>39.4915657043457</v>
+        <v>39.491569519043</v>
       </c>
       <c r="H1123" t="n">
         <v>13686</v>
@@ -33110,7 +33110,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422164916992</v>
+        <v>38.3422203063965</v>
       </c>
       <c r="H1129" t="n">
         <v>76007</v>
@@ -33197,7 +33197,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727020263672</v>
+        <v>39.4727058410645</v>
       </c>
       <c r="H1132" t="n">
         <v>28234</v>
@@ -33226,7 +33226,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900787353516</v>
+        <v>39.1900825500488</v>
       </c>
       <c r="H1133" t="n">
         <v>17044</v>
@@ -33371,7 +33371,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1138" t="n">
         <v>14887</v>
@@ -33429,7 +33429,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082214355469</v>
+        <v>39.7082176208496</v>
       </c>
       <c r="H1140" t="n">
         <v>25485</v>
@@ -33458,7 +33458,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842864990234</v>
+        <v>39.2842903137207</v>
       </c>
       <c r="H1141" t="n">
         <v>10680</v>
@@ -33487,7 +33487,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379409790039</v>
+        <v>40.0379447937012</v>
       </c>
       <c r="H1142" t="n">
         <v>21497</v>
@@ -33516,7 +33516,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1143" t="n">
         <v>17609</v>
@@ -33545,7 +33545,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452499389648</v>
+        <v>41.5452537536621</v>
       </c>
       <c r="H1144" t="n">
         <v>77350</v>
@@ -33661,7 +33661,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437408447266</v>
+        <v>39.9437370300293</v>
       </c>
       <c r="H1148" t="n">
         <v>26093</v>
@@ -33864,7 +33864,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132553100586</v>
+        <v>38.8132514953613</v>
       </c>
       <c r="H1155" t="n">
         <v>17325</v>
@@ -34154,7 +34154,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1165" t="n">
         <v>25025</v>
@@ -34212,7 +34212,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1167" t="n">
         <v>17311</v>
@@ -34241,7 +34241,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1168" t="n">
         <v>18709</v>
@@ -34270,7 +34270,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522880554199</v>
+        <v>36.5522842407227</v>
       </c>
       <c r="H1169" t="n">
         <v>7654</v>
@@ -34299,7 +34299,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1170" t="n">
         <v>11922</v>
@@ -34357,7 +34357,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993919372559</v>
+        <v>36.5993881225586</v>
       </c>
       <c r="H1172" t="n">
         <v>22854</v>
@@ -34444,7 +34444,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1175" t="n">
         <v>14281</v>
@@ -34589,7 +34589,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1180" t="n">
         <v>12217</v>
@@ -34647,7 +34647,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1182" t="n">
         <v>17442</v>
@@ -34763,7 +34763,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1186" t="n">
         <v>16678</v>
@@ -34850,7 +34850,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376625061035</v>
+        <v>33.5376663208008</v>
       </c>
       <c r="H1189" t="n">
         <v>13671</v>
@@ -34908,7 +34908,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202857971191</v>
+        <v>33.8202896118164</v>
       </c>
       <c r="H1191" t="n">
         <v>14410</v>
@@ -34937,7 +34937,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1192" t="n">
         <v>21211</v>
@@ -35053,7 +35053,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275947570801</v>
+        <v>35.3275985717773</v>
       </c>
       <c r="H1196" t="n">
         <v>18810</v>
@@ -35198,7 +35198,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1201" t="n">
         <v>10943</v>
@@ -35227,7 +35227,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1202" t="n">
         <v>13284</v>
@@ -35372,7 +35372,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1207" t="n">
         <v>86976</v>
@@ -35401,7 +35401,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1208" t="n">
         <v>107480</v>
@@ -35459,7 +35459,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238048553467</v>
+        <v>31.3238010406494</v>
       </c>
       <c r="H1210" t="n">
         <v>97335</v>
@@ -35517,7 +35517,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890419006348</v>
+        <v>31.8890399932861</v>
       </c>
       <c r="H1212" t="n">
         <v>19682</v>
@@ -35575,7 +35575,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1214" t="n">
         <v>32700</v>
@@ -35604,7 +35604,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1215" t="n">
         <v>71954</v>
@@ -35633,7 +35633,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419380187988</v>
+        <v>31.8419399261475</v>
       </c>
       <c r="H1216" t="n">
         <v>29272</v>
@@ -35662,7 +35662,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1217" t="n">
         <v>40121</v>
@@ -35691,7 +35691,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1218" t="n">
         <v>88062</v>
@@ -35720,7 +35720,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1219" t="n">
         <v>20873</v>
@@ -35807,7 +35807,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804908752441</v>
+        <v>35.2804946899414</v>
       </c>
       <c r="H1222" t="n">
         <v>55066</v>
@@ -35836,7 +35836,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391830444336</v>
+        <v>35.1391792297363</v>
       </c>
       <c r="H1223" t="n">
         <v>48119</v>
@@ -35952,7 +35952,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558052062988</v>
+        <v>34.0558013916016</v>
       </c>
       <c r="H1227" t="n">
         <v>33020</v>
@@ -36068,7 +36068,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1231" t="n">
         <v>27966</v>
@@ -36126,7 +36126,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160102844238</v>
+        <v>35.5160140991211</v>
       </c>
       <c r="H1233" t="n">
         <v>18372</v>
@@ -36155,7 +36155,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1234" t="n">
         <v>21216</v>
@@ -36271,7 +36271,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.023323059082</v>
+        <v>37.0233192443848</v>
       </c>
       <c r="H1238" t="n">
         <v>31944</v>
@@ -36329,7 +36329,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1240" t="n">
         <v>21979</v>
@@ -36358,7 +36358,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739440917969</v>
+        <v>34.5739402770996</v>
       </c>
       <c r="H1241" t="n">
         <v>36159</v>
@@ -36532,7 +36532,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955963134766</v>
+        <v>32.5955924987793</v>
       </c>
       <c r="H1247" t="n">
         <v>20275</v>
@@ -36619,7 +36619,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1250" t="n">
         <v>26995</v>
@@ -36735,7 +36735,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1254" t="n">
         <v>86029</v>
@@ -36938,7 +36938,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1261" t="n">
         <v>62483</v>
@@ -37083,7 +37083,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099376678467</v>
+        <v>29.1099395751953</v>
       </c>
       <c r="H1266" t="n">
         <v>42903</v>
@@ -37257,7 +37257,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1272" t="n">
         <v>69703</v>
@@ -37286,7 +37286,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1273" t="n">
         <v>51566</v>
@@ -37344,7 +37344,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1275" t="n">
         <v>39875</v>
@@ -37373,7 +37373,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1276" t="n">
         <v>33069</v>
@@ -37605,7 +37605,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164901733398</v>
+        <v>29.8164920806885</v>
       </c>
       <c r="H1284" t="n">
         <v>24216</v>
@@ -37663,7 +37663,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643524169922</v>
+        <v>30.6643543243408</v>
       </c>
       <c r="H1286" t="n">
         <v>27493</v>
@@ -37692,7 +37692,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1287" t="n">
         <v>27163</v>
@@ -37808,7 +37808,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1291" t="n">
         <v>50126</v>
@@ -37837,7 +37837,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1292" t="n">
         <v>15339</v>
@@ -37953,7 +37953,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1296" t="n">
         <v>31760</v>
@@ -38127,7 +38127,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832515716553</v>
+        <v>31.9832496643066</v>
       </c>
       <c r="H1302" t="n">
         <v>58973</v>
@@ -38156,7 +38156,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1303" t="n">
         <v>39498</v>
@@ -38330,7 +38330,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.349250793457</v>
+        <v>33.3492546081543</v>
       </c>
       <c r="H1309" t="n">
         <v>34631</v>
@@ -38417,7 +38417,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1312" t="n">
         <v>27726</v>
@@ -38533,7 +38533,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1316" t="n">
         <v>82490</v>
@@ -38562,7 +38562,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1317" t="n">
         <v>126426</v>
@@ -38707,7 +38707,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1322" t="n">
         <v>44000</v>
@@ -38765,7 +38765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1324" t="n">
         <v>42930</v>
@@ -38823,7 +38823,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1326" t="n">
         <v>38026</v>
@@ -38852,7 +38852,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1327" t="n">
         <v>61320</v>
@@ -38939,7 +38939,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041473388672</v>
+        <v>29.2041454315186</v>
       </c>
       <c r="H1330" t="n">
         <v>38634</v>
@@ -39113,7 +39113,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207656860352</v>
+        <v>28.1207675933838</v>
       </c>
       <c r="H1336" t="n">
         <v>109851</v>
@@ -39229,7 +39229,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1340" t="n">
         <v>55268</v>
@@ -39258,7 +39258,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1341" t="n">
         <v>36968</v>
@@ -39374,7 +39374,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844917297363</v>
+        <v>27.0844898223877</v>
       </c>
       <c r="H1345" t="n">
         <v>66714</v>
@@ -39432,7 +39432,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1347" t="n">
         <v>104150</v>
@@ -39519,7 +39519,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902820587158</v>
+        <v>26.9902839660645</v>
       </c>
       <c r="H1350" t="n">
         <v>33485</v>
@@ -39548,7 +39548,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779392242432</v>
+        <v>26.3779373168945</v>
       </c>
       <c r="H1351" t="n">
         <v>128641</v>
@@ -39606,7 +39606,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1353" t="n">
         <v>181757</v>
@@ -39635,7 +39635,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1354" t="n">
         <v>138211</v>
@@ -39664,7 +39664,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829730987549</v>
+        <v>25.4829711914062</v>
       </c>
       <c r="H1355" t="n">
         <v>105911</v>
@@ -39838,7 +39838,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011100769043</v>
+        <v>26.0011119842529</v>
       </c>
       <c r="H1361" t="n">
         <v>64528</v>
@@ -39867,7 +39867,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.3887672424316</v>
+        <v>25.388765335083</v>
       </c>
       <c r="H1362" t="n">
         <v>44652</v>
@@ -39896,7 +39896,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003536224365</v>
+        <v>25.2003517150879</v>
       </c>
       <c r="H1363" t="n">
         <v>43761</v>
@@ -39925,7 +39925,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.189525604248</v>
+        <v>26.1895236968994</v>
       </c>
       <c r="H1364" t="n">
         <v>45391</v>
@@ -39954,7 +39954,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076625823975</v>
+        <v>26.7076644897461</v>
       </c>
       <c r="H1365" t="n">
         <v>53357</v>
@@ -40157,7 +40157,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1372" t="n">
         <v>44289</v>
@@ -40215,7 +40215,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.696834564209</v>
+        <v>27.6968364715576</v>
       </c>
       <c r="H1374" t="n">
         <v>43847</v>
@@ -50936,7 +50936,7 @@
         <v>34</v>
       </c>
       <c r="D1744" t="n">
-        <v>34.939998626709</v>
+        <v>35.0400009155273</v>
       </c>
       <c r="E1744" t="n">
         <v>34</v>
@@ -50948,9 +50948,38 @@
         <v>35.0400009155273</v>
       </c>
       <c r="H1744" t="n">
-        <v>24241</v>
+        <v>25008</v>
       </c>
       <c r="I1744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1745" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>34.9000015258789</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>34.9000015258789</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>34.3199996948242</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>34.2599983215332</v>
+      </c>
+      <c r="G1745" t="n">
+        <v>34.2599983215332</v>
+      </c>
+      <c r="H1745" t="n">
+        <v>17366</v>
+      </c>
+      <c r="I1745" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -514,7 +514,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479238510132</v>
+        <v>13.7479257583618</v>
       </c>
       <c r="H5" t="n">
         <v>18109</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934656143188</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -717,7 +717,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896392822266</v>
+        <v>13.9896383285522</v>
       </c>
       <c r="H12" t="n">
         <v>10618</v>
@@ -804,7 +804,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915510177612</v>
+        <v>13.8915529251099</v>
       </c>
       <c r="H15" t="n">
         <v>15065</v>
@@ -833,7 +833,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073152542114</v>
+        <v>13.9073162078857</v>
       </c>
       <c r="H16" t="n">
         <v>30923</v>
@@ -862,7 +862,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.8722848892212</v>
+        <v>13.8722858428955</v>
       </c>
       <c r="H17" t="n">
         <v>116007</v>
@@ -891,7 +891,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G18" t="n">
-        <v>13.942346572876</v>
+        <v>13.9423456192017</v>
       </c>
       <c r="H18" t="n">
         <v>74522</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071271896362</v>
+        <v>15.1071262359619</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1181,7 +1181,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916883468628</v>
+        <v>14.8916864395142</v>
       </c>
       <c r="H28" t="n">
         <v>63118</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757604598999</v>
+        <v>14.9757614135742</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1239,7 +1239,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730644226074</v>
+        <v>14.4730653762817</v>
       </c>
       <c r="H30" t="n">
         <v>42455</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881845474243</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1442,7 +1442,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.355712890625</v>
+        <v>14.3557119369507</v>
       </c>
       <c r="H37" t="n">
         <v>37432</v>
@@ -1471,7 +1471,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628784179688</v>
+        <v>14.2628803253174</v>
       </c>
       <c r="H38" t="n">
         <v>11160</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609676361084</v>
+        <v>14.3609666824341</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1558,7 +1558,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>14.6604824066162</v>
+        <v>14.6604833602905</v>
       </c>
       <c r="H41" t="n">
         <v>29941</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006067276001</v>
+        <v>14.8006048202515</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1616,7 +1616,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443956375122</v>
+        <v>14.8443946838379</v>
       </c>
       <c r="H43" t="n">
         <v>115888</v>
@@ -1674,7 +1674,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655744552612</v>
+        <v>14.7655763626099</v>
       </c>
       <c r="H45" t="n">
         <v>31415</v>
@@ -1703,7 +1703,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6236991882324</v>
+        <v>14.6237001419067</v>
       </c>
       <c r="H46" t="n">
         <v>33733</v>
@@ -1761,7 +1761,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633392333984</v>
+        <v>15.0633401870728</v>
       </c>
       <c r="H48" t="n">
         <v>87381</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369047164917</v>
+        <v>15.1369037628174</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1819,7 +1819,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.126259803772</v>
+        <v>14.1262578964233</v>
       </c>
       <c r="H50" t="n">
         <v>74499</v>
@@ -1848,7 +1848,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.26988697052</v>
+        <v>14.2698879241943</v>
       </c>
       <c r="H51" t="n">
         <v>29049</v>
@@ -1906,7 +1906,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089044570923</v>
+        <v>14.0089063644409</v>
       </c>
       <c r="H53" t="n">
         <v>23213</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -1964,7 +1964,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H55" t="n">
         <v>37252</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111669540405</v>
+        <v>12.6111679077148</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320241928101</v>
+        <v>12.7320251464844</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2167,7 +2167,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602369308472</v>
+        <v>11.5602378845215</v>
       </c>
       <c r="H62" t="n">
         <v>43479</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0714197158813</v>
+        <v>10.071418762207</v>
       </c>
       <c r="H63" t="n">
         <v>21708</v>
@@ -2225,7 +2225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>11.0347738265991</v>
+        <v>11.0347728729248</v>
       </c>
       <c r="H64" t="n">
         <v>37959</v>
@@ -2254,7 +2254,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868530273438</v>
+        <v>9.80868625640869</v>
       </c>
       <c r="H65" t="n">
         <v>49411</v>
@@ -2312,7 +2312,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837688446045</v>
+        <v>9.45837497711182</v>
       </c>
       <c r="H67" t="n">
         <v>48156</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806465148926</v>
+        <v>9.10806560516357</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2370,7 +2370,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96619033813477</v>
+        <v>8.96619129180908</v>
       </c>
       <c r="H69" t="n">
         <v>122433</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494094848633</v>
+        <v>8.54494285583496</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2515,7 +2515,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6701774597168</v>
+        <v>8.67017650604248</v>
       </c>
       <c r="H74" t="n">
         <v>15416</v>
@@ -2544,7 +2544,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032096862793</v>
+        <v>8.69032192230225</v>
       </c>
       <c r="H75" t="n">
         <v>14690</v>
@@ -2573,7 +2573,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415332794189</v>
+        <v>8.92415237426758</v>
       </c>
       <c r="H76" t="n">
         <v>26972</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04501056671143</v>
+        <v>9.04500865936279</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2689,7 +2689,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921152114868</v>
       </c>
       <c r="H80" t="n">
         <v>20417</v>
@@ -2718,7 +2718,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.596884727478</v>
+        <v>10.5968837738037</v>
       </c>
       <c r="H81" t="n">
         <v>17348</v>
@@ -2747,7 +2747,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070697784424</v>
+        <v>10.8070707321167</v>
       </c>
       <c r="H82" t="n">
         <v>3945</v>
@@ -2892,7 +2892,7 @@
         <v>12.8079996109009</v>
       </c>
       <c r="G87" t="n">
-        <v>11.2169322967529</v>
+        <v>11.2169332504272</v>
       </c>
       <c r="H87" t="n">
         <v>10905</v>
@@ -2921,7 +2921,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>11.7353935241699</v>
+        <v>11.7353925704956</v>
       </c>
       <c r="H88" t="n">
         <v>24596</v>
@@ -2950,7 +2950,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898508071899</v>
+        <v>11.6898517608643</v>
       </c>
       <c r="H89" t="n">
         <v>19363</v>
@@ -2979,7 +2979,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068817138672</v>
+        <v>12.0068826675415</v>
       </c>
       <c r="H90" t="n">
         <v>11410</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229703903198</v>
+        <v>11.8229694366455</v>
       </c>
       <c r="H91" t="n">
         <v>16703</v>
@@ -3037,7 +3037,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325357437134</v>
+        <v>11.3325366973877</v>
       </c>
       <c r="H92" t="n">
         <v>25713</v>
@@ -3066,7 +3066,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0347738265991</v>
+        <v>11.0347728729248</v>
       </c>
       <c r="H93" t="n">
         <v>52489</v>
@@ -3124,7 +3124,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471950531006</v>
+        <v>10.9471940994263</v>
       </c>
       <c r="H95" t="n">
         <v>49105</v>
@@ -3182,7 +3182,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655170440674</v>
+        <v>10.465518951416</v>
       </c>
       <c r="H97" t="n">
         <v>30855</v>
@@ -3240,7 +3240,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691825866699</v>
+        <v>10.3691835403442</v>
       </c>
       <c r="H99" t="n">
         <v>11865</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465744018555</v>
+        <v>10.2465734481812</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3356,7 +3356,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616907119751</v>
+        <v>10.6616916656494</v>
       </c>
       <c r="H103" t="n">
         <v>12365</v>
@@ -3414,7 +3414,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.3814430236816</v>
+        <v>10.3814420700073</v>
       </c>
       <c r="H105" t="n">
         <v>19187</v>
@@ -3501,7 +3501,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220252990723</v>
+        <v>11.3220262527466</v>
       </c>
       <c r="H108" t="n">
         <v>36330</v>
@@ -3559,7 +3559,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726600646973</v>
+        <v>11.4726591110229</v>
       </c>
       <c r="H110" t="n">
         <v>21522</v>
@@ -3675,7 +3675,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834657669067</v>
+        <v>12.3834676742554</v>
       </c>
       <c r="H114" t="n">
         <v>29369</v>
@@ -3762,7 +3762,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258272171021</v>
+        <v>12.2258262634277</v>
       </c>
       <c r="H117" t="n">
         <v>24996</v>
@@ -3791,7 +3791,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922233581543</v>
+        <v>12.3922243118286</v>
       </c>
       <c r="H118" t="n">
         <v>16297</v>
@@ -3820,7 +3820,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205724716187</v>
+        <v>12.220573425293</v>
       </c>
       <c r="H119" t="n">
         <v>70567</v>
@@ -3878,7 +3878,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.7600498199463</v>
+        <v>12.760048866272</v>
       </c>
       <c r="H121" t="n">
         <v>53970</v>
@@ -3907,7 +3907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H122" t="n">
         <v>27467</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901498794556</v>
+        <v>12.5901489257812</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4052,7 +4052,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H127" t="n">
         <v>96046</v>
@@ -4081,7 +4081,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H128" t="n">
         <v>20883</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.211950302124</v>
+        <v>13.2119512557983</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4139,7 +4139,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976144790649</v>
+        <v>13.3976135253906</v>
       </c>
       <c r="H130" t="n">
         <v>7245</v>
@@ -4226,7 +4226,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.5272302627563</v>
+        <v>13.527229309082</v>
       </c>
       <c r="H133" t="n">
         <v>18810</v>
@@ -4255,7 +4255,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H134" t="n">
         <v>10358</v>
@@ -4342,7 +4342,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H137" t="n">
         <v>5525</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681613922119</v>
+        <v>13.1681604385376</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H140" t="n">
         <v>6887</v>
@@ -4487,7 +4487,7 @@
         <v>15.3579998016357</v>
       </c>
       <c r="G142" t="n">
-        <v>13.4501600265503</v>
+        <v>13.4501609802246</v>
       </c>
       <c r="H142" t="n">
         <v>4891</v>
@@ -4545,7 +4545,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928449630737</v>
+        <v>13.0928440093994</v>
       </c>
       <c r="H144" t="n">
         <v>3240</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504854202271</v>
+        <v>13.2504835128784</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4661,7 +4661,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821746826172</v>
+        <v>13.1821737289429</v>
       </c>
       <c r="H148" t="n">
         <v>863</v>
@@ -4719,7 +4719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H150" t="n">
         <v>1530</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620979309082</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4806,7 +4806,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324850082397</v>
+        <v>13.5324831008911</v>
       </c>
       <c r="H153" t="n">
         <v>9502</v>
@@ -4864,7 +4864,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.4694271087646</v>
+        <v>13.469428062439</v>
       </c>
       <c r="H155" t="n">
         <v>2209</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277135848999</v>
+        <v>13.2277145385742</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348810195923</v>
+        <v>13.1348819732666</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -4980,7 +4980,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823335647583</v>
+        <v>13.0823345184326</v>
       </c>
       <c r="H159" t="n">
         <v>22453</v>
@@ -5038,7 +5038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H161" t="n">
         <v>8576</v>
@@ -5067,7 +5067,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309202194214</v>
+        <v>12.3309192657471</v>
       </c>
       <c r="H162" t="n">
         <v>17829</v>
@@ -5096,7 +5096,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673799514771</v>
+        <v>12.5673789978027</v>
       </c>
       <c r="H163" t="n">
         <v>11473</v>
@@ -5154,7 +5154,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094169616699</v>
+        <v>12.6094150543213</v>
       </c>
       <c r="H165" t="n">
         <v>15675</v>
@@ -5212,7 +5212,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H167" t="n">
         <v>9897</v>
@@ -5241,7 +5241,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097385406494</v>
+        <v>12.409740447998</v>
       </c>
       <c r="H168" t="n">
         <v>11733</v>
@@ -5270,7 +5270,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="n">
-        <v>13.1366338729858</v>
+        <v>13.1366329193115</v>
       </c>
       <c r="H169" t="n">
         <v>3414</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620979309082</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5502,7 +5502,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H177" t="n">
         <v>16366</v>
@@ -5531,7 +5531,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H178" t="n">
         <v>14964</v>
@@ -5676,7 +5676,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G183" t="n">
-        <v>13.7847061157227</v>
+        <v>13.784707069397</v>
       </c>
       <c r="H183" t="n">
         <v>22904</v>
@@ -5908,7 +5908,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G191" t="n">
-        <v>13.8722848892212</v>
+        <v>13.8722858428955</v>
       </c>
       <c r="H191" t="n">
         <v>17918</v>
@@ -6111,7 +6111,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1366338729858</v>
+        <v>13.1366329193115</v>
       </c>
       <c r="H198" t="n">
         <v>5996</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614772796631</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H199" t="n">
         <v>7759</v>
@@ -6169,7 +6169,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767562866211</v>
+        <v>13.2767572402954</v>
       </c>
       <c r="H200" t="n">
         <v>6789</v>
@@ -6198,7 +6198,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321605682373</v>
+        <v>13.732159614563</v>
       </c>
       <c r="H201" t="n">
         <v>43057</v>
@@ -6343,7 +6343,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.4678134918213</v>
+        <v>14.4678115844727</v>
       </c>
       <c r="H206" t="n">
         <v>39648</v>
@@ -6372,7 +6372,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H207" t="n">
         <v>18020</v>
@@ -6401,7 +6401,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H208" t="n">
         <v>11562</v>
@@ -6459,7 +6459,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H210" t="n">
         <v>16575</v>
@@ -6488,7 +6488,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.7305450439453</v>
+        <v>14.7305431365967</v>
       </c>
       <c r="H211" t="n">
         <v>9090</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H212" t="n">
         <v>5728</v>
@@ -6575,7 +6575,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955137252808</v>
+        <v>14.6955146789551</v>
       </c>
       <c r="H214" t="n">
         <v>13259</v>
@@ -6691,7 +6691,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>14.0474405288696</v>
+        <v>14.0474395751953</v>
       </c>
       <c r="H218" t="n">
         <v>5034</v>
@@ -6749,7 +6749,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H220" t="n">
         <v>11900</v>
@@ -6836,7 +6836,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H223" t="n">
         <v>17777</v>
@@ -6865,7 +6865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H224" t="n">
         <v>45360</v>
@@ -6894,7 +6894,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.259241104126</v>
+        <v>13.2592420578003</v>
       </c>
       <c r="H225" t="n">
         <v>9073</v>
@@ -6923,7 +6923,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H226" t="n">
         <v>5423</v>
@@ -6952,7 +6952,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1016035079956</v>
+        <v>13.101601600647</v>
       </c>
       <c r="H227" t="n">
         <v>2440</v>
@@ -6981,7 +6981,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321605682373</v>
+        <v>13.732159614563</v>
       </c>
       <c r="H228" t="n">
         <v>2543</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219736099243</v>
+        <v>13.52197265625</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620979309082</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7097,7 +7097,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G232" t="n">
-        <v>13.7847061157227</v>
+        <v>13.784707069397</v>
       </c>
       <c r="H232" t="n">
         <v>19127</v>
@@ -7126,7 +7126,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H233" t="n">
         <v>26206</v>
@@ -7242,7 +7242,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H237" t="n">
         <v>17203</v>
@@ -7271,7 +7271,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H238" t="n">
         <v>12067</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7445,7 +7445,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H244" t="n">
         <v>25909</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219736099243</v>
+        <v>13.52197265625</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7532,7 +7532,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H247" t="n">
         <v>18668</v>
@@ -7561,7 +7561,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H248" t="n">
         <v>7591</v>
@@ -7590,7 +7590,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H249" t="n">
         <v>4482</v>
@@ -7619,7 +7619,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H250" t="n">
         <v>41070</v>
@@ -7648,7 +7648,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H251" t="n">
         <v>2749</v>
@@ -7706,7 +7706,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993663787842</v>
       </c>
       <c r="H253" t="n">
         <v>8244</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7822,7 +7822,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H257" t="n">
         <v>7773</v>
@@ -7880,7 +7880,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.574520111084</v>
+        <v>13.5745210647583</v>
       </c>
       <c r="H259" t="n">
         <v>10259</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219736099243</v>
+        <v>13.52197265625</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7967,7 +7967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197364807129</v>
+        <v>13.8197374343872</v>
       </c>
       <c r="H262" t="n">
         <v>19414</v>
@@ -7996,7 +7996,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773769378662</v>
+        <v>13.9773788452148</v>
       </c>
       <c r="H263" t="n">
         <v>14625</v>
@@ -8025,7 +8025,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>14.0474405288696</v>
+        <v>14.0474395751953</v>
       </c>
       <c r="H264" t="n">
         <v>10439</v>
@@ -8054,7 +8054,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.1525325775146</v>
+        <v>14.1525316238403</v>
       </c>
       <c r="H265" t="n">
         <v>11125</v>
@@ -8112,7 +8112,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H267" t="n">
         <v>21797</v>
@@ -8141,7 +8141,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H268" t="n">
         <v>16682</v>
@@ -8199,7 +8199,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.2576265335083</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H270" t="n">
         <v>5152</v>
@@ -8228,7 +8228,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028429031372</v>
+        <v>14.5028419494629</v>
       </c>
       <c r="H271" t="n">
         <v>6060</v>
@@ -8257,7 +8257,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028429031372</v>
+        <v>14.5028419494629</v>
       </c>
       <c r="H272" t="n">
         <v>8570</v>
@@ -8286,7 +8286,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079359054565</v>
+        <v>14.6079368591309</v>
       </c>
       <c r="H273" t="n">
         <v>7891</v>
@@ -8402,7 +8402,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.2576265335083</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H277" t="n">
         <v>6898</v>
@@ -8431,7 +8431,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G278" t="n">
-        <v>14.5729036331177</v>
+        <v>14.572904586792</v>
       </c>
       <c r="H278" t="n">
         <v>26113</v>
@@ -8460,7 +8460,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034635543823</v>
+        <v>15.2034645080566</v>
       </c>
       <c r="H279" t="n">
         <v>80397</v>
@@ -8518,7 +8518,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114152908325</v>
+        <v>15.7114133834839</v>
       </c>
       <c r="H281" t="n">
         <v>48160</v>
@@ -8576,7 +8576,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888051986694</v>
+        <v>15.5888032913208</v>
       </c>
       <c r="H283" t="n">
         <v>32761</v>
@@ -8634,7 +8634,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814779281616</v>
+        <v>15.7814750671387</v>
       </c>
       <c r="H285" t="n">
         <v>16215</v>
@@ -8692,7 +8692,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317863464355</v>
+        <v>16.1317844390869</v>
       </c>
       <c r="H287" t="n">
         <v>34304</v>
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397361755371</v>
+        <v>16.6397342681885</v>
       </c>
       <c r="H288" t="n">
         <v>19711</v>
@@ -8750,7 +8750,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>16.4295501708984</v>
+        <v>16.4295482635498</v>
       </c>
       <c r="H289" t="n">
         <v>27587</v>
@@ -8779,7 +8779,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973728179932</v>
+        <v>16.7973747253418</v>
       </c>
       <c r="H290" t="n">
         <v>32844</v>
@@ -8837,7 +8837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403549194336</v>
+        <v>17.340353012085</v>
       </c>
       <c r="H292" t="n">
         <v>108964</v>
@@ -8866,7 +8866,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753871917725</v>
+        <v>17.3753890991211</v>
       </c>
       <c r="H293" t="n">
         <v>29298</v>
@@ -8895,7 +8895,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5593013763428</v>
+        <v>17.5592994689941</v>
       </c>
       <c r="H294" t="n">
         <v>17437</v>
@@ -8924,7 +8924,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220329284668</v>
+        <v>17.8220310211182</v>
       </c>
       <c r="H295" t="n">
         <v>52008</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.2527809143066</v>
+        <v>17.252779006958</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9098,7 +9098,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>16.7273120880127</v>
+        <v>16.7273139953613</v>
       </c>
       <c r="H301" t="n">
         <v>28487</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979953765869</v>
+        <v>17.4979934692383</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9156,7 +9156,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H303" t="n">
         <v>51778</v>
@@ -9214,7 +9214,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>18.1285552978516</v>
+        <v>18.1285533905029</v>
       </c>
       <c r="H305" t="n">
         <v>35889</v>
@@ -9272,7 +9272,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>18.7853870391846</v>
+        <v>18.7853832244873</v>
       </c>
       <c r="H307" t="n">
         <v>24097</v>
@@ -9301,7 +9301,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108501434326</v>
+        <v>19.310848236084</v>
       </c>
       <c r="H308" t="n">
         <v>58530</v>
@@ -9330,7 +9330,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H309" t="n">
         <v>14880</v>
@@ -9359,7 +9359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H310" t="n">
         <v>34531</v>
@@ -9417,7 +9417,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415981292725</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H312" t="n">
         <v>23897</v>
@@ -9446,7 +9446,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356964111328</v>
+        <v>19.1356945037842</v>
       </c>
       <c r="H313" t="n">
         <v>16234</v>
@@ -9533,7 +9533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H316" t="n">
         <v>27872</v>
@@ -9591,7 +9591,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>18.7853870391846</v>
+        <v>18.7853832244873</v>
       </c>
       <c r="H318" t="n">
         <v>14808</v>
@@ -9649,7 +9649,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173706054688</v>
+        <v>19.6173725128174</v>
       </c>
       <c r="H320" t="n">
         <v>55008</v>
@@ -9678,7 +9678,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7925281524658</v>
+        <v>19.7925262451172</v>
       </c>
       <c r="H321" t="n">
         <v>38533</v>
@@ -9707,7 +9707,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422187805176</v>
+        <v>19.4422168731689</v>
       </c>
       <c r="H322" t="n">
         <v>48797</v>
@@ -9794,7 +9794,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611652374268</v>
+        <v>19.6611614227295</v>
       </c>
       <c r="H325" t="n">
         <v>22459</v>
@@ -9823,7 +9823,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H326" t="n">
         <v>15812</v>
@@ -9852,7 +9852,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735836029053</v>
       </c>
       <c r="H327" t="n">
         <v>7040</v>
@@ -9939,7 +9939,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167537689209</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H330" t="n">
         <v>9202</v>
@@ -10084,7 +10084,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.7853870391846</v>
+        <v>18.7853832244873</v>
       </c>
       <c r="H335" t="n">
         <v>17649</v>
@@ -10142,7 +10142,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415981292725</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H337" t="n">
         <v>8572</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546390533447</v>
+        <v>19.3546409606934</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10200,7 +10200,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167537689209</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H339" t="n">
         <v>11503</v>
@@ -10258,7 +10258,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>18.9605407714844</v>
+        <v>18.9605388641357</v>
       </c>
       <c r="H341" t="n">
         <v>7028</v>
@@ -10287,7 +10287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H342" t="n">
         <v>48534</v>
@@ -10316,7 +10316,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H343" t="n">
         <v>22326</v>
@@ -10345,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.391284942627</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H344" t="n">
         <v>18146</v>
@@ -10374,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.391284942627</v>
+        <v>18.3912868499756</v>
       </c>
       <c r="H345" t="n">
         <v>7042</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799438476562</v>
+        <v>18.8799419403076</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10519,7 +10519,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903388977051</v>
+        <v>20.3903408050537</v>
       </c>
       <c r="H350" t="n">
         <v>39422</v>
@@ -10548,7 +10548,7 @@
         <v>23</v>
       </c>
       <c r="G351" t="n">
-        <v>20.4347648620605</v>
+        <v>20.4347629547119</v>
       </c>
       <c r="H351" t="n">
         <v>25210</v>
@@ -10577,7 +10577,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>20.1237964630127</v>
+        <v>20.1237983703613</v>
       </c>
       <c r="H352" t="n">
         <v>39061</v>
@@ -10606,7 +10606,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572616577148</v>
+        <v>19.8572597503662</v>
       </c>
       <c r="H353" t="n">
         <v>50006</v>
@@ -10635,7 +10635,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793762207031</v>
+        <v>20.0793743133545</v>
       </c>
       <c r="H354" t="n">
         <v>30645</v>
@@ -10664,7 +10664,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905281066895</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H355" t="n">
         <v>20044</v>
@@ -10722,7 +10722,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684135437012</v>
+        <v>19.7684116363525</v>
       </c>
       <c r="H357" t="n">
         <v>47937</v>
@@ -10751,7 +10751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461097717285</v>
+        <v>19.9461059570312</v>
       </c>
       <c r="H358" t="n">
         <v>49210</v>
@@ -10780,7 +10780,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.835521697998</v>
+        <v>18.8355197906494</v>
       </c>
       <c r="H359" t="n">
         <v>57619</v>
@@ -10809,7 +10809,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G360" t="n">
-        <v>18.7466773986816</v>
+        <v>18.7466735839844</v>
       </c>
       <c r="H360" t="n">
         <v>21783</v>
@@ -10838,7 +10838,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>18.7910957336426</v>
+        <v>18.7910976409912</v>
       </c>
       <c r="H361" t="n">
         <v>19501</v>
@@ -10896,7 +10896,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>19.4574489593506</v>
+        <v>19.457447052002</v>
       </c>
       <c r="H363" t="n">
         <v>18679</v>
@@ -10925,7 +10925,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G364" t="n">
-        <v>20.1237964630127</v>
+        <v>20.1237983703613</v>
       </c>
       <c r="H364" t="n">
         <v>53805</v>
@@ -10983,7 +10983,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905281066895</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H366" t="n">
         <v>12885</v>
@@ -11215,7 +11215,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>23.2334365844727</v>
+        <v>23.233434677124</v>
       </c>
       <c r="H374" t="n">
         <v>53913</v>
@@ -11273,7 +11273,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890125274658</v>
+        <v>23.1890163421631</v>
       </c>
       <c r="H376" t="n">
         <v>28296</v>
@@ -11331,7 +11331,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G378" t="n">
-        <v>22.833625793457</v>
+        <v>22.8336277008057</v>
       </c>
       <c r="H378" t="n">
         <v>26713</v>
@@ -11360,7 +11360,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H379" t="n">
         <v>1533317</v>
@@ -11418,7 +11418,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H381" t="n">
         <v>46241</v>
@@ -11476,7 +11476,7 @@
         <v>24.25</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5453491210938</v>
+        <v>21.5453472137451</v>
       </c>
       <c r="H383" t="n">
         <v>33134</v>
@@ -11621,7 +11621,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566902160645</v>
+        <v>21.0566940307617</v>
       </c>
       <c r="H388" t="n">
         <v>20039</v>
@@ -11650,7 +11650,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>20.701301574707</v>
+        <v>20.7013034820557</v>
       </c>
       <c r="H389" t="n">
         <v>22114</v>
@@ -11679,7 +11679,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>20.701301574707</v>
+        <v>20.7013034820557</v>
       </c>
       <c r="H390" t="n">
         <v>27192</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11766,7 +11766,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H393" t="n">
         <v>23385</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11824,7 +11824,7 @@
         <v>23.5</v>
       </c>
       <c r="G395" t="n">
-        <v>20.878999710083</v>
+        <v>20.8789978027344</v>
       </c>
       <c r="H395" t="n">
         <v>27666</v>
@@ -11853,7 +11853,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H396" t="n">
         <v>21826</v>
@@ -12027,7 +12027,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.6786193847656</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H402" t="n">
         <v>58589</v>
@@ -12056,7 +12056,7 @@
         <v>24.25</v>
       </c>
       <c r="G403" t="n">
-        <v>21.5453491210938</v>
+        <v>21.5453472137451</v>
       </c>
       <c r="H403" t="n">
         <v>29308</v>
@@ -12143,7 +12143,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H406" t="n">
         <v>42941</v>
@@ -12172,7 +12172,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459167480469</v>
+        <v>20.3459148406982</v>
       </c>
       <c r="H407" t="n">
         <v>12913</v>
@@ -12201,7 +12201,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.612455368042</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H408" t="n">
         <v>17907</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115112304688</v>
+        <v>22.6115074157715</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12491,7 +12491,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561206817627</v>
+        <v>22.2561225891113</v>
       </c>
       <c r="H418" t="n">
         <v>18147</v>
@@ -12578,7 +12578,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224739074707</v>
+        <v>22.9224720001221</v>
       </c>
       <c r="H421" t="n">
         <v>20723</v>
@@ -12607,7 +12607,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113220214844</v>
+        <v>23.0113201141357</v>
       </c>
       <c r="H422" t="n">
         <v>22051</v>
@@ -12636,7 +12636,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551746368408</v>
+        <v>24.2551765441895</v>
       </c>
       <c r="H423" t="n">
         <v>80709</v>
@@ -12665,7 +12665,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>24.1663303375244</v>
+        <v>24.1663284301758</v>
       </c>
       <c r="H424" t="n">
         <v>33528</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5443992614746</v>
+        <v>23.5444011688232</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12752,7 +12752,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886360168457</v>
+        <v>23.9886341094971</v>
       </c>
       <c r="H427" t="n">
         <v>21987</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661373138428</v>
+        <v>24.5661392211914</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -12955,7 +12955,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438354492188</v>
+        <v>24.7438316345215</v>
       </c>
       <c r="H434" t="n">
         <v>22801</v>
@@ -12984,7 +12984,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>24.8326816558838</v>
+        <v>24.8326797485352</v>
       </c>
       <c r="H435" t="n">
         <v>15025</v>
@@ -13013,7 +13013,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324905395508</v>
+        <v>25.2324886322021</v>
       </c>
       <c r="H436" t="n">
         <v>14765</v>
@@ -13042,7 +13042,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103740692139</v>
+        <v>25.0103721618652</v>
       </c>
       <c r="H437" t="n">
         <v>16754</v>
@@ -13071,7 +13071,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H438" t="n">
         <v>49309</v>
@@ -13100,7 +13100,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H439" t="n">
         <v>22024</v>
@@ -13129,7 +13129,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H440" t="n">
         <v>28408</v>
@@ -13187,7 +13187,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H442" t="n">
         <v>23385</v>
@@ -13216,7 +13216,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205780029297</v>
+        <v>26.9205799102783</v>
       </c>
       <c r="H443" t="n">
         <v>23035</v>
@@ -13245,7 +13245,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536628723145</v>
+        <v>27.4536609649658</v>
       </c>
       <c r="H444" t="n">
         <v>42660</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425052642822</v>
+        <v>27.5425071716309</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13332,7 +13332,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300308227539</v>
+        <v>30.4300270080566</v>
       </c>
       <c r="H447" t="n">
         <v>138213</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967548370361</v>
+        <v>30.2967567443848</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13390,7 +13390,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.696569442749</v>
+        <v>30.6965675354004</v>
       </c>
       <c r="H449" t="n">
         <v>65084</v>
@@ -13448,7 +13448,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417503356934</v>
+        <v>29.1417484283447</v>
       </c>
       <c r="H451" t="n">
         <v>55282</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527130126953</v>
+        <v>29.4527149200439</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13506,7 +13506,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748294830322</v>
+        <v>29.6748332977295</v>
       </c>
       <c r="H453" t="n">
         <v>18449</v>
@@ -13535,7 +13535,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300308227539</v>
+        <v>30.4300270080566</v>
       </c>
       <c r="H454" t="n">
         <v>27063</v>
@@ -13564,7 +13564,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744491577148</v>
+        <v>30.4744510650635</v>
       </c>
       <c r="H455" t="n">
         <v>27798</v>
@@ -13709,7 +13709,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423179626465</v>
+        <v>27.9423160552979</v>
       </c>
       <c r="H460" t="n">
         <v>17404</v>
@@ -13767,7 +13767,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H462" t="n">
         <v>26586</v>
@@ -13796,7 +13796,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H463" t="n">
         <v>39977</v>
@@ -13825,7 +13825,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.2305965423584</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H464" t="n">
         <v>33973</v>
@@ -13854,7 +13854,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H465" t="n">
         <v>29892</v>
@@ -13912,7 +13912,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857959747314</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H467" t="n">
         <v>54363</v>
@@ -13970,7 +13970,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409934997559</v>
+        <v>30.7409915924072</v>
       </c>
       <c r="H469" t="n">
         <v>41790</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296485900879</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627277374268</v>
+        <v>31.7627296447754</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14086,7 +14086,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H473" t="n">
         <v>41695</v>
@@ -14173,7 +14173,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G476" t="n">
-        <v>33.8506278991699</v>
+        <v>33.8506240844727</v>
       </c>
       <c r="H476" t="n">
         <v>38154</v>
@@ -14347,7 +14347,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.717357635498</v>
+        <v>33.7173614501953</v>
       </c>
       <c r="H482" t="n">
         <v>45662</v>
@@ -14405,7 +14405,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942932128906</v>
+        <v>35.4942970275879</v>
       </c>
       <c r="H484" t="n">
         <v>95655</v>
@@ -14463,7 +14463,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617874145508</v>
+        <v>33.7617797851562</v>
       </c>
       <c r="H486" t="n">
         <v>58518</v>
@@ -14521,7 +14521,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398582458496</v>
+        <v>33.1398544311523</v>
       </c>
       <c r="H488" t="n">
         <v>34481</v>
@@ -14637,7 +14637,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288955688477</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H492" t="n">
         <v>26262</v>
@@ -14666,7 +14666,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844734191895</v>
+        <v>32.7844657897949</v>
       </c>
       <c r="H493" t="n">
         <v>16789</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14869,7 +14869,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634864807129</v>
+        <v>30.1634883880615</v>
       </c>
       <c r="H500" t="n">
         <v>80023</v>
@@ -14898,7 +14898,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H501" t="n">
         <v>30662</v>
@@ -14927,7 +14927,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404239654541</v>
+        <v>31.9404277801514</v>
       </c>
       <c r="H502" t="n">
         <v>44140</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296485900879</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177322387695</v>
+        <v>32.9177360534668</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627277374268</v>
+        <v>31.7627296447754</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15304,7 +15304,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.4734992980957</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H515" t="n">
         <v>28750</v>
@@ -15333,7 +15333,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.4734992980957</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H516" t="n">
         <v>39270</v>
@@ -15391,7 +15391,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288955688477</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H518" t="n">
         <v>13845</v>
@@ -15420,7 +15420,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.429084777832</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H519" t="n">
         <v>27308</v>
@@ -15449,7 +15449,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.3175506591797</v>
+        <v>33.3175468444824</v>
       </c>
       <c r="H520" t="n">
         <v>18235</v>
@@ -15536,7 +15536,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729316711426</v>
+        <v>33.6729393005371</v>
       </c>
       <c r="H523" t="n">
         <v>18883</v>
@@ -15565,7 +15565,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H524" t="n">
         <v>40082</v>
@@ -15623,7 +15623,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283241271973</v>
+        <v>34.0283203125</v>
       </c>
       <c r="H526" t="n">
         <v>15120</v>
@@ -15710,7 +15710,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8959999084473</v>
+        <v>31.8960018157959</v>
       </c>
       <c r="H529" t="n">
         <v>38776</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15768,7 +15768,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840911865234</v>
+        <v>33.5840873718262</v>
       </c>
       <c r="H531" t="n">
         <v>37158</v>
@@ -15797,7 +15797,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G532" t="n">
-        <v>33.1842803955078</v>
+        <v>33.1842765808105</v>
       </c>
       <c r="H532" t="n">
         <v>28931</v>
@@ -15826,7 +15826,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H533" t="n">
         <v>33489</v>
@@ -15855,7 +15855,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H534" t="n">
         <v>20804</v>
@@ -15942,7 +15942,7 @@
         <v>40.5</v>
       </c>
       <c r="G537" t="n">
-        <v>35.9829521179199</v>
+        <v>35.9829483032227</v>
       </c>
       <c r="H537" t="n">
         <v>52532</v>
@@ -15971,7 +15971,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727424621582</v>
+        <v>34.0727500915527</v>
       </c>
       <c r="H538" t="n">
         <v>33816</v>
@@ -16000,7 +16000,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H539" t="n">
         <v>56910</v>
@@ -16058,7 +16058,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H541" t="n">
         <v>30426</v>
@@ -16116,7 +16116,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.429084777832</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H543" t="n">
         <v>43887</v>
@@ -16145,7 +16145,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H544" t="n">
         <v>89245</v>
@@ -16232,7 +16232,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H547" t="n">
         <v>60536</v>
@@ -16261,7 +16261,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H548" t="n">
         <v>151703</v>
@@ -16319,7 +16319,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H550" t="n">
         <v>59281</v>
@@ -16348,7 +16348,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H551" t="n">
         <v>43962</v>
@@ -16377,7 +16377,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275672912598</v>
+        <v>35.6275634765625</v>
       </c>
       <c r="H552" t="n">
         <v>107403</v>
@@ -16406,7 +16406,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H553" t="n">
         <v>48943</v>
@@ -16493,7 +16493,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H556" t="n">
         <v>29679</v>
@@ -16580,7 +16580,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394760131836</v>
+        <v>33.9394798278809</v>
       </c>
       <c r="H559" t="n">
         <v>87892</v>
@@ -16609,7 +16609,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721786499023</v>
+        <v>35.2721748352051</v>
       </c>
       <c r="H560" t="n">
         <v>92873</v>
@@ -16638,7 +16638,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>36.7381477355957</v>
+        <v>36.738151550293</v>
       </c>
       <c r="H561" t="n">
         <v>96737</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.4054489135742</v>
+        <v>35.405445098877</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16696,7 +16696,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714179992676</v>
+        <v>36.8714218139648</v>
       </c>
       <c r="H563" t="n">
         <v>79980</v>
@@ -16841,7 +16841,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530914306641</v>
+        <v>28.6530933380127</v>
       </c>
       <c r="H568" t="n">
         <v>187078</v>
@@ -16899,7 +16899,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882556915283</v>
+        <v>24.788257598877</v>
       </c>
       <c r="H570" t="n">
         <v>115179</v>
@@ -16957,7 +16957,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873096466064</v>
+        <v>26.7873077392578</v>
       </c>
       <c r="H572" t="n">
         <v>79386</v>
@@ -16986,7 +16986,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.2305965423584</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H573" t="n">
         <v>133949</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190624237061</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184967041016</v>
+        <v>31.3184947967529</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17102,7 +17102,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519523620605</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H577" t="n">
         <v>60129</v>
@@ -17131,7 +17131,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H578" t="n">
         <v>447251</v>
@@ -17160,7 +17160,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H579" t="n">
         <v>47898</v>
@@ -17189,7 +17189,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623550415039</v>
+        <v>32.5623512268066</v>
       </c>
       <c r="H580" t="n">
         <v>40631</v>
@@ -17218,7 +17218,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H581" t="n">
         <v>35526</v>
@@ -17276,7 +17276,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408042907715</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H583" t="n">
         <v>48569</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186840057373</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17334,7 +17334,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H585" t="n">
         <v>89419</v>
@@ -17363,7 +17363,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>33.8506278991699</v>
+        <v>33.8506240844727</v>
       </c>
       <c r="H586" t="n">
         <v>57760</v>
@@ -17392,7 +17392,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H587" t="n">
         <v>35265</v>
@@ -17537,7 +17537,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744491577148</v>
+        <v>30.4744510650635</v>
       </c>
       <c r="H592" t="n">
         <v>28557</v>
@@ -17566,7 +17566,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521415710449</v>
       </c>
       <c r="H593" t="n">
         <v>18121</v>
@@ -17624,7 +17624,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521415710449</v>
       </c>
       <c r="H595" t="n">
         <v>37402</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186840057373</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17711,7 +17711,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519523620605</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H598" t="n">
         <v>20035</v>
@@ -17740,7 +17740,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740726470947</v>
+        <v>31.274076461792</v>
       </c>
       <c r="H599" t="n">
         <v>22406</v>
@@ -17769,7 +17769,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H600" t="n">
         <v>24723</v>
@@ -17798,7 +17798,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294593811035</v>
+        <v>31.6294574737549</v>
       </c>
       <c r="H601" t="n">
         <v>16163</v>
@@ -17827,7 +17827,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408042907715</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H602" t="n">
         <v>46419</v>
@@ -17856,7 +17856,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863636016846</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H603" t="n">
         <v>26401</v>
@@ -17914,7 +17914,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859813690186</v>
+        <v>29.5859832763672</v>
       </c>
       <c r="H605" t="n">
         <v>31886</v>
@@ -17943,7 +17943,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857959747314</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H606" t="n">
         <v>22611</v>
@@ -18030,7 +18030,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H609" t="n">
         <v>29532</v>
@@ -18088,7 +18088,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H611" t="n">
         <v>81317</v>
@@ -18175,7 +18175,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H614" t="n">
         <v>41499</v>
@@ -18233,7 +18233,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H616" t="n">
         <v>45928</v>
@@ -18291,7 +18291,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H618" t="n">
         <v>36011</v>
@@ -18349,7 +18349,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9758014678955</v>
+        <v>31.9757976531982</v>
       </c>
       <c r="H620" t="n">
         <v>19405</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18465,7 +18465,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>30.1667041778564</v>
+        <v>30.1667022705078</v>
       </c>
       <c r="H624" t="n">
         <v>21890</v>
@@ -18494,7 +18494,7 @@
         <v>34.5</v>
       </c>
       <c r="G625" t="n">
-        <v>31.2069339752197</v>
+        <v>31.2069358825684</v>
       </c>
       <c r="H625" t="n">
         <v>24917</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18726,7 +18726,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737476348877</v>
       </c>
       <c r="H633" t="n">
         <v>27780</v>
@@ -18755,7 +18755,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260238647461</v>
+        <v>31.0260219573975</v>
       </c>
       <c r="H634" t="n">
         <v>36768</v>
@@ -18784,7 +18784,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G635" t="n">
-        <v>30.1667041778564</v>
+        <v>30.1667022705078</v>
       </c>
       <c r="H635" t="n">
         <v>21215</v>
@@ -18813,7 +18813,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H636" t="n">
         <v>49552</v>
@@ -18871,7 +18871,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H638" t="n">
         <v>56267</v>
@@ -18929,7 +18929,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766986846924</v>
+        <v>28.1766967773438</v>
       </c>
       <c r="H640" t="n">
         <v>27100</v>
@@ -19132,7 +19132,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H647" t="n">
         <v>19011</v>
@@ -19190,7 +19190,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H649" t="n">
         <v>12887</v>
@@ -19277,7 +19277,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>28.5837440490723</v>
+        <v>28.5837459564209</v>
       </c>
       <c r="H652" t="n">
         <v>15473</v>
@@ -19306,7 +19306,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339664459229</v>
+        <v>27.6339683532715</v>
       </c>
       <c r="H653" t="n">
         <v>22878</v>
@@ -19335,7 +19335,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H654" t="n">
         <v>70905</v>
@@ -19451,7 +19451,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H658" t="n">
         <v>15664</v>
@@ -19480,7 +19480,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H659" t="n">
         <v>11969</v>
@@ -19567,7 +19567,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787506103516</v>
+        <v>29.5787487030029</v>
       </c>
       <c r="H662" t="n">
         <v>11492</v>
@@ -19625,7 +19625,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H664" t="n">
         <v>12292</v>
@@ -19654,7 +19654,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H665" t="n">
         <v>5963</v>
@@ -19683,7 +19683,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260238647461</v>
+        <v>31.0260219573975</v>
       </c>
       <c r="H666" t="n">
         <v>41810</v>
@@ -19770,7 +19770,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H669" t="n">
         <v>27479</v>
@@ -19857,7 +19857,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H672" t="n">
         <v>11102</v>
@@ -19886,7 +19886,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H673" t="n">
         <v>12485</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355697631836</v>
+        <v>30.9355716705322</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19973,7 +19973,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023872375488</v>
+        <v>30.3023853302002</v>
       </c>
       <c r="H676" t="n">
         <v>13444</v>
@@ -20002,7 +20002,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832973480225</v>
+        <v>30.4832992553711</v>
       </c>
       <c r="H677" t="n">
         <v>25987</v>
@@ -20031,7 +20031,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787506103516</v>
+        <v>29.5787487030029</v>
       </c>
       <c r="H678" t="n">
         <v>13528</v>
@@ -20060,7 +20060,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G679" t="n">
-        <v>29.714427947998</v>
+        <v>29.7144298553467</v>
       </c>
       <c r="H679" t="n">
         <v>10560</v>
@@ -20089,7 +20089,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H680" t="n">
         <v>18879</v>
@@ -20118,7 +20118,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H681" t="n">
         <v>24865</v>
@@ -20147,7 +20147,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048877716064</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H682" t="n">
         <v>13128</v>
@@ -20321,7 +20321,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H688" t="n">
         <v>9866</v>
@@ -20350,7 +20350,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H689" t="n">
         <v>6251</v>
@@ -20379,7 +20379,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H690" t="n">
         <v>13325</v>
@@ -20437,7 +20437,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H692" t="n">
         <v>20442</v>
@@ -20466,7 +20466,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123779296875</v>
+        <v>28.3123798370361</v>
       </c>
       <c r="H693" t="n">
         <v>18525</v>
@@ -20495,7 +20495,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505615234375</v>
+        <v>27.9505596160889</v>
       </c>
       <c r="H694" t="n">
         <v>28033</v>
@@ -20582,7 +20582,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>28.3576068878174</v>
+        <v>28.357608795166</v>
       </c>
       <c r="H697" t="n">
         <v>14113</v>
@@ -20611,7 +20611,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H698" t="n">
         <v>35920</v>
@@ -20640,7 +20640,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H699" t="n">
         <v>56297</v>
@@ -20669,7 +20669,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762500762939</v>
+        <v>30.0762519836426</v>
       </c>
       <c r="H700" t="n">
         <v>23460</v>
@@ -20727,7 +20727,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G702" t="n">
-        <v>29.714427947998</v>
+        <v>29.7144298553467</v>
       </c>
       <c r="H702" t="n">
         <v>60927</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.7194271087646</v>
+        <v>28.719425201416</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20872,7 +20872,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H707" t="n">
         <v>13065</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314678192139</v>
+        <v>28.1314716339111</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21046,7 +21046,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H713" t="n">
         <v>37089</v>
@@ -21104,7 +21104,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048877716064</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H715" t="n">
         <v>26731</v>
@@ -21133,7 +21133,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H716" t="n">
         <v>30596</v>
@@ -21162,7 +21162,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H717" t="n">
         <v>59213</v>
@@ -21191,7 +21191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073825836182</v>
       </c>
       <c r="H718" t="n">
         <v>15926</v>
@@ -21249,7 +21249,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H720" t="n">
         <v>19906</v>
@@ -21307,7 +21307,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H722" t="n">
         <v>27650</v>
@@ -21336,7 +21336,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H723" t="n">
         <v>10352</v>
@@ -21365,7 +21365,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H724" t="n">
         <v>28121</v>
@@ -21394,7 +21394,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H725" t="n">
         <v>27078</v>
@@ -21423,7 +21423,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857978820801</v>
       </c>
       <c r="H726" t="n">
         <v>26161</v>
@@ -21452,7 +21452,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H727" t="n">
         <v>23140</v>
@@ -21510,7 +21510,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>28.5837440490723</v>
+        <v>28.5837459564209</v>
       </c>
       <c r="H729" t="n">
         <v>13692</v>
@@ -21539,7 +21539,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932880401611</v>
+        <v>28.4932899475098</v>
       </c>
       <c r="H730" t="n">
         <v>19631</v>
@@ -21713,7 +21713,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H736" t="n">
         <v>39696</v>
@@ -21742,7 +21742,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H737" t="n">
         <v>13524</v>
@@ -21771,7 +21771,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H738" t="n">
         <v>31102</v>
@@ -21800,7 +21800,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882907867432</v>
+        <v>29.4882926940918</v>
       </c>
       <c r="H739" t="n">
         <v>12783</v>
@@ -21829,7 +21829,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405670166016</v>
       </c>
       <c r="H740" t="n">
         <v>25796</v>
@@ -21858,7 +21858,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H741" t="n">
         <v>14572</v>
@@ -21887,7 +21887,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285263061523</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H742" t="n">
         <v>22513</v>
@@ -21916,7 +21916,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H743" t="n">
         <v>39509</v>
@@ -21945,7 +21945,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H744" t="n">
         <v>24053</v>
@@ -22061,7 +22061,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119312286377</v>
+        <v>30.2119331359863</v>
       </c>
       <c r="H748" t="n">
         <v>18927</v>
@@ -22090,7 +22090,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G749" t="n">
-        <v>30.1667041778564</v>
+        <v>30.1667022705078</v>
       </c>
       <c r="H749" t="n">
         <v>16880</v>
@@ -22119,7 +22119,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832973480225</v>
+        <v>30.4832992553711</v>
       </c>
       <c r="H750" t="n">
         <v>5976</v>
@@ -22148,7 +22148,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737476348877</v>
       </c>
       <c r="H751" t="n">
         <v>7222</v>
@@ -22206,7 +22206,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H753" t="n">
         <v>33549</v>
@@ -22235,7 +22235,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235290527344</v>
+        <v>31.5235252380371</v>
       </c>
       <c r="H754" t="n">
         <v>23044</v>
@@ -22264,7 +22264,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H755" t="n">
         <v>11292</v>
@@ -22293,7 +22293,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H756" t="n">
         <v>12661</v>
@@ -22409,7 +22409,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H760" t="n">
         <v>38359</v>
@@ -22438,7 +22438,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H761" t="n">
         <v>16883</v>
@@ -22467,7 +22467,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>31.3878421783447</v>
+        <v>31.387845993042</v>
       </c>
       <c r="H762" t="n">
         <v>46057</v>
@@ -22525,7 +22525,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.885347366333</v>
+        <v>31.8853511810303</v>
       </c>
       <c r="H764" t="n">
         <v>11653</v>
@@ -22612,7 +22612,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969451904297</v>
+        <v>33.1969413757324</v>
       </c>
       <c r="H767" t="n">
         <v>47582</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22728,7 +22728,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330768585205</v>
       </c>
       <c r="H771" t="n">
         <v>8172</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521648406982</v>
+        <v>31.252161026001</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637588500977</v>
+        <v>32.5637626647949</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -22873,7 +22873,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H776" t="n">
         <v>6543</v>
@@ -22902,7 +22902,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H777" t="n">
         <v>22186</v>
@@ -22931,7 +22931,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.9205856323242</v>
+        <v>33.920581817627</v>
       </c>
       <c r="H778" t="n">
         <v>24835</v>
@@ -22960,7 +22960,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230842590332</v>
+        <v>33.4230804443359</v>
       </c>
       <c r="H779" t="n">
         <v>8669</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23395,7 +23395,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H794" t="n">
         <v>32389</v>
@@ -23424,7 +23424,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H795" t="n">
         <v>28476</v>
@@ -23453,7 +23453,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H796" t="n">
         <v>22692</v>
@@ -23511,7 +23511,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558143615723</v>
+        <v>35.9558181762695</v>
       </c>
       <c r="H798" t="n">
         <v>25747</v>
@@ -23540,7 +23540,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G799" t="n">
-        <v>35.6392288208008</v>
+        <v>35.6392250061035</v>
       </c>
       <c r="H799" t="n">
         <v>12129</v>
@@ -23598,7 +23598,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>36.4533195495605</v>
+        <v>36.4533233642578</v>
       </c>
       <c r="H801" t="n">
         <v>40738</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578681945801</v>
+        <v>37.3578643798828</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23743,7 +23743,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.4080924987793</v>
+        <v>36.4080963134766</v>
       </c>
       <c r="H806" t="n">
         <v>19091</v>
@@ -23830,7 +23830,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>36.0915031433105</v>
+        <v>36.0914993286133</v>
       </c>
       <c r="H809" t="n">
         <v>50811</v>
@@ -23859,7 +23859,7 @@
         <v>39.9000015258789</v>
       </c>
       <c r="G810" t="n">
-        <v>36.0915031433105</v>
+        <v>36.0914993286133</v>
       </c>
       <c r="H810" t="n">
         <v>26507</v>
@@ -23888,7 +23888,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G811" t="n">
-        <v>36.4533195495605</v>
+        <v>36.4533233642578</v>
       </c>
       <c r="H811" t="n">
         <v>24654</v>
@@ -23975,7 +23975,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>36.3628616333008</v>
+        <v>36.362865447998</v>
       </c>
       <c r="H814" t="n">
         <v>19882</v>
@@ -24004,7 +24004,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H815" t="n">
         <v>35580</v>
@@ -24033,7 +24033,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.7246856689453</v>
+        <v>36.724681854248</v>
       </c>
       <c r="H816" t="n">
         <v>28980</v>
@@ -24178,7 +24178,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H821" t="n">
         <v>71113</v>
@@ -24236,7 +24236,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8956031799316</v>
+        <v>38.8955993652344</v>
       </c>
       <c r="H823" t="n">
         <v>45948</v>
@@ -24381,7 +24381,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H828" t="n">
         <v>29768</v>
@@ -24410,7 +24410,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H829" t="n">
         <v>35652</v>
@@ -24497,7 +24497,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H832" t="n">
         <v>71309</v>
@@ -24526,7 +24526,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649192810059</v>
+        <v>37.7649154663086</v>
       </c>
       <c r="H833" t="n">
         <v>30771</v>
@@ -24584,7 +24584,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H835" t="n">
         <v>34627</v>
@@ -24642,7 +24642,7 @@
         <v>40</v>
       </c>
       <c r="G837" t="n">
-        <v>36.1819496154785</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H837" t="n">
         <v>119181</v>
@@ -24671,7 +24671,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H838" t="n">
         <v>42162</v>
@@ -24700,7 +24700,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367263793945</v>
+        <v>36.1367301940918</v>
       </c>
       <c r="H839" t="n">
         <v>32321</v>
@@ -24758,7 +24758,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>35.6392288208008</v>
+        <v>35.6392250061035</v>
       </c>
       <c r="H841" t="n">
         <v>39832</v>
@@ -24845,7 +24845,7 @@
         <v>40</v>
       </c>
       <c r="G844" t="n">
-        <v>36.1819496154785</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H844" t="n">
         <v>20530</v>
@@ -24874,7 +24874,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.4080924987793</v>
+        <v>36.4080963134766</v>
       </c>
       <c r="H845" t="n">
         <v>19073</v>
@@ -24903,7 +24903,7 @@
         <v>40</v>
       </c>
       <c r="G846" t="n">
-        <v>36.1819496154785</v>
+        <v>36.1819534301758</v>
       </c>
       <c r="H846" t="n">
         <v>26328</v>
@@ -24932,7 +24932,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342277526855</v>
+        <v>36.6342239379883</v>
       </c>
       <c r="H847" t="n">
         <v>16900</v>
@@ -25019,7 +25019,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.7246856689453</v>
+        <v>36.724681854248</v>
       </c>
       <c r="H850" t="n">
         <v>32977</v>
@@ -25135,7 +25135,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744575500488</v>
+        <v>37.6744613647461</v>
       </c>
       <c r="H854" t="n">
         <v>14320</v>
@@ -25222,7 +25222,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>36.3628616333008</v>
+        <v>36.362865447998</v>
       </c>
       <c r="H857" t="n">
         <v>13892</v>
@@ -25280,7 +25280,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342277526855</v>
+        <v>36.6342239379883</v>
       </c>
       <c r="H859" t="n">
         <v>12270</v>
@@ -25338,7 +25338,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.4080924987793</v>
+        <v>36.4080963134766</v>
       </c>
       <c r="H861" t="n">
         <v>8194</v>
@@ -25396,7 +25396,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G863" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H863" t="n">
         <v>17246</v>
@@ -25425,7 +25425,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G864" t="n">
-        <v>36.8710556030273</v>
+        <v>36.8710517883301</v>
       </c>
       <c r="H864" t="n">
         <v>25714</v>
@@ -25512,7 +25512,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G867" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H867" t="n">
         <v>6491</v>
@@ -25744,7 +25744,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H875" t="n">
         <v>10487</v>
@@ -25831,7 +25831,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354713439941</v>
+        <v>36.1354751586914</v>
       </c>
       <c r="H878" t="n">
         <v>14544</v>
@@ -25860,7 +25860,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G879" t="n">
-        <v>35.5378150939941</v>
+        <v>35.5378112792969</v>
       </c>
       <c r="H879" t="n">
         <v>20797</v>
@@ -25976,7 +25976,7 @@
         <v>38</v>
       </c>
       <c r="G883" t="n">
-        <v>34.9401550292969</v>
+        <v>34.9401512145996</v>
       </c>
       <c r="H883" t="n">
         <v>16359</v>
@@ -26034,7 +26034,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>34.6183319091797</v>
+        <v>34.618335723877</v>
       </c>
       <c r="H885" t="n">
         <v>19645</v>
@@ -26179,7 +26179,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H890" t="n">
         <v>21938</v>
@@ -26208,7 +26208,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>34.6643104553223</v>
+        <v>34.664306640625</v>
       </c>
       <c r="H891" t="n">
         <v>21890</v>
@@ -26324,7 +26324,7 @@
         <v>38.6500015258789</v>
       </c>
       <c r="G895" t="n">
-        <v>35.5378150939941</v>
+        <v>35.5378112792969</v>
       </c>
       <c r="H895" t="n">
         <v>24511</v>
@@ -26353,7 +26353,7 @@
         <v>38.25</v>
       </c>
       <c r="G896" t="n">
-        <v>35.1700172424316</v>
+        <v>35.1700210571289</v>
       </c>
       <c r="H896" t="n">
         <v>56083</v>
@@ -26585,7 +26585,7 @@
         <v>38</v>
       </c>
       <c r="G904" t="n">
-        <v>34.9401550292969</v>
+        <v>34.9401512145996</v>
       </c>
       <c r="H904" t="n">
         <v>19538</v>
@@ -26701,7 +26701,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G908" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H908" t="n">
         <v>19888</v>
@@ -26875,7 +26875,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G914" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H914" t="n">
         <v>24076</v>
@@ -26991,7 +26991,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G918" t="n">
-        <v>33.0092506408691</v>
+        <v>33.0092468261719</v>
       </c>
       <c r="H918" t="n">
         <v>15454</v>
@@ -27020,7 +27020,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310699462891</v>
       </c>
       <c r="H919" t="n">
         <v>14186</v>
@@ -27194,7 +27194,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H925" t="n">
         <v>24388</v>
@@ -27281,7 +27281,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H928" t="n">
         <v>18700</v>
@@ -27368,7 +27368,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>34.6643104553223</v>
+        <v>34.664306640625</v>
       </c>
       <c r="H931" t="n">
         <v>102214</v>
@@ -27455,7 +27455,7 @@
         <v>37.5</v>
       </c>
       <c r="G934" t="n">
-        <v>34.4804153442383</v>
+        <v>34.480411529541</v>
       </c>
       <c r="H934" t="n">
         <v>36101</v>
@@ -27542,7 +27542,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G937" t="n">
-        <v>35.0780715942383</v>
+        <v>35.0780754089355</v>
       </c>
       <c r="H937" t="n">
         <v>13021</v>
@@ -27571,7 +27571,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>35.2619667053223</v>
+        <v>35.2619705200195</v>
       </c>
       <c r="H938" t="n">
         <v>29216</v>
@@ -27600,7 +27600,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965126037598</v>
+        <v>34.296516418457</v>
       </c>
       <c r="H939" t="n">
         <v>16255</v>
@@ -27977,7 +27977,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H952" t="n">
         <v>8028</v>
@@ -28006,7 +28006,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>33.0092506408691</v>
+        <v>33.0092468261719</v>
       </c>
       <c r="H953" t="n">
         <v>30708</v>
@@ -28093,7 +28093,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448310852051</v>
+        <v>33.7448348999023</v>
       </c>
       <c r="H956" t="n">
         <v>7086</v>
@@ -28151,7 +28151,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H958" t="n">
         <v>18202</v>
@@ -28267,7 +28267,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H962" t="n">
         <v>19440</v>
@@ -28296,7 +28296,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.5035362243652</v>
+        <v>32.503532409668</v>
       </c>
       <c r="H963" t="n">
         <v>11379</v>
@@ -28354,7 +28354,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H965" t="n">
         <v>16412</v>
@@ -28412,7 +28412,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H967" t="n">
         <v>23454</v>
@@ -28470,7 +28470,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H969" t="n">
         <v>26969</v>
@@ -28557,7 +28557,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G972" t="n">
-        <v>33.0092506408691</v>
+        <v>33.0092468261719</v>
       </c>
       <c r="H972" t="n">
         <v>17502</v>
@@ -28673,7 +28673,7 @@
         <v>35.75</v>
       </c>
       <c r="G976" t="n">
-        <v>32.8713264465332</v>
+        <v>32.8713302612305</v>
       </c>
       <c r="H976" t="n">
         <v>23421</v>
@@ -28731,7 +28731,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G978" t="n">
-        <v>33.6069107055664</v>
+        <v>33.6069068908691</v>
       </c>
       <c r="H978" t="n">
         <v>13732</v>
@@ -28789,7 +28789,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310661315918</v>
+        <v>33.3310699462891</v>
       </c>
       <c r="H980" t="n">
         <v>18596</v>
@@ -28818,7 +28818,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H981" t="n">
         <v>23720</v>
@@ -28934,7 +28934,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H985" t="n">
         <v>10944</v>
@@ -29108,7 +29108,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783443450928</v>
+        <v>31.0783424377441</v>
       </c>
       <c r="H991" t="n">
         <v>22083</v>
@@ -29253,7 +29253,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H996" t="n">
         <v>15814</v>
@@ -29456,7 +29456,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H1003" t="n">
         <v>52594</v>
@@ -29485,7 +29485,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1004" t="n">
-        <v>35.3079452514648</v>
+        <v>35.3079414367676</v>
       </c>
       <c r="H1004" t="n">
         <v>19185</v>
@@ -29514,7 +29514,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1005" t="n">
-        <v>35.8136596679688</v>
+        <v>35.8136558532715</v>
       </c>
       <c r="H1005" t="n">
         <v>29077</v>
@@ -29630,7 +29630,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1009" t="n">
         <v>15324</v>
@@ -29659,7 +29659,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1010" t="n">
         <v>9446</v>
@@ -29717,7 +29717,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1012" t="n">
         <v>19550</v>
@@ -29746,7 +29746,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>35.8136596679688</v>
+        <v>35.8136558532715</v>
       </c>
       <c r="H1013" t="n">
         <v>21171</v>
@@ -29862,7 +29862,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1017" t="n">
-        <v>36.8710556030273</v>
+        <v>36.8710517883301</v>
       </c>
       <c r="H1017" t="n">
         <v>16992</v>
@@ -30065,7 +30065,7 @@
         <v>42</v>
       </c>
       <c r="G1024" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1024" t="n">
         <v>27579</v>
@@ -30152,7 +30152,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1027" t="n">
         <v>33681</v>
@@ -30268,7 +30268,7 @@
         <v>42.5</v>
       </c>
       <c r="G1031" t="n">
-        <v>39.0778045654297</v>
+        <v>39.0778007507324</v>
       </c>
       <c r="H1031" t="n">
         <v>32251</v>
@@ -30326,7 +30326,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1033" t="n">
         <v>17293</v>
@@ -30355,7 +30355,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1034" t="n">
-        <v>38.2502746582031</v>
+        <v>38.2502708435059</v>
       </c>
       <c r="H1034" t="n">
         <v>34988</v>
@@ -30442,7 +30442,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1037" t="n">
         <v>16755</v>
@@ -30471,7 +30471,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1038" t="n">
         <v>24399</v>
@@ -30500,7 +30500,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1039" t="n">
         <v>35974</v>
@@ -30529,7 +30529,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1040" t="n">
         <v>10126</v>
@@ -30645,7 +30645,7 @@
         <v>42.5</v>
       </c>
       <c r="G1044" t="n">
-        <v>39.0778045654297</v>
+        <v>39.0778007507324</v>
       </c>
       <c r="H1044" t="n">
         <v>25555</v>
@@ -30703,7 +30703,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1046" t="n">
         <v>27206</v>
@@ -30732,7 +30732,7 @@
         <v>42.5</v>
       </c>
       <c r="G1047" t="n">
-        <v>39.0778045654297</v>
+        <v>39.0778007507324</v>
       </c>
       <c r="H1047" t="n">
         <v>18406</v>
@@ -30790,7 +30790,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>39.491569519043</v>
+        <v>39.4915657043457</v>
       </c>
       <c r="H1049" t="n">
         <v>25230</v>
@@ -30848,7 +30848,7 @@
         <v>44</v>
       </c>
       <c r="G1051" t="n">
-        <v>40.4570198059082</v>
+        <v>40.4570159912109</v>
       </c>
       <c r="H1051" t="n">
         <v>26021</v>
@@ -30877,7 +30877,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1052" t="n">
-        <v>41.3305244445801</v>
+        <v>41.3305206298828</v>
       </c>
       <c r="H1052" t="n">
         <v>34152</v>
@@ -31022,7 +31022,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>39.491569519043</v>
+        <v>39.4915657043457</v>
       </c>
       <c r="H1057" t="n">
         <v>25708</v>
@@ -31051,7 +31051,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1058" t="n">
         <v>26015</v>
@@ -31225,7 +31225,7 @@
         <v>44.9500007629395</v>
       </c>
       <c r="G1064" t="n">
-        <v>41.3305244445801</v>
+        <v>41.3305206298828</v>
       </c>
       <c r="H1064" t="n">
         <v>70471</v>
@@ -31254,7 +31254,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442855834961</v>
+        <v>41.7442893981934</v>
       </c>
       <c r="H1065" t="n">
         <v>58297</v>
@@ -31283,7 +31283,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>40.5489654541016</v>
+        <v>40.5489616394043</v>
       </c>
       <c r="H1066" t="n">
         <v>41750</v>
@@ -31428,7 +31428,7 @@
         <v>42</v>
       </c>
       <c r="G1071" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1071" t="n">
         <v>21365</v>
@@ -31457,7 +31457,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1072" t="n">
         <v>20307</v>
@@ -31689,7 +31689,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1080" t="n">
         <v>21026</v>
@@ -31718,7 +31718,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1081" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1081" t="n">
         <v>37081</v>
@@ -31747,7 +31747,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G1082" t="n">
-        <v>37.1009178161621</v>
+        <v>37.1009216308594</v>
       </c>
       <c r="H1082" t="n">
         <v>33479</v>
@@ -31834,7 +31834,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422164916992</v>
       </c>
       <c r="H1085" t="n">
         <v>44926</v>
@@ -31892,7 +31892,7 @@
         <v>42</v>
       </c>
       <c r="G1087" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1087" t="n">
         <v>47019</v>
@@ -32095,7 +32095,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824806213379</v>
+        <v>37.8824844360352</v>
       </c>
       <c r="H1094" t="n">
         <v>23661</v>
@@ -32124,7 +32124,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1095" t="n">
         <v>27027</v>
@@ -32153,7 +32153,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>38.7559814453125</v>
+        <v>38.7559852600098</v>
       </c>
       <c r="H1096" t="n">
         <v>30370</v>
@@ -32182,7 +32182,7 @@
         <v>41.0499992370605</v>
       </c>
       <c r="G1097" t="n">
-        <v>37.7445602416992</v>
+        <v>37.744556427002</v>
       </c>
       <c r="H1097" t="n">
         <v>46557</v>
@@ -32211,7 +32211,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1098" t="n">
         <v>26751</v>
@@ -32240,7 +32240,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1099" t="n">
         <v>14005</v>
@@ -32501,7 +32501,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1108" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H1108" t="n">
         <v>21226</v>
@@ -32559,7 +32559,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1110" t="n">
-        <v>35.7217063903809</v>
+        <v>35.7217102050781</v>
       </c>
       <c r="H1110" t="n">
         <v>18379</v>
@@ -32588,7 +32588,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.7217063903809</v>
+        <v>35.7217102050781</v>
       </c>
       <c r="H1111" t="n">
         <v>13856</v>
@@ -32733,7 +32733,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1116" t="n">
         <v>18589</v>
@@ -32849,7 +32849,7 @@
         <v>42</v>
       </c>
       <c r="G1120" t="n">
-        <v>38.6180648803711</v>
+        <v>38.6180610656738</v>
       </c>
       <c r="H1120" t="n">
         <v>22119</v>
@@ -32907,7 +32907,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858551025391</v>
+        <v>38.9858589172363</v>
       </c>
       <c r="H1122" t="n">
         <v>13057</v>
@@ -32936,7 +32936,7 @@
         <v>42.9500007629395</v>
       </c>
       <c r="G1123" t="n">
-        <v>39.491569519043</v>
+        <v>39.4915657043457</v>
       </c>
       <c r="H1123" t="n">
         <v>13686</v>
@@ -33110,7 +33110,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422164916992</v>
       </c>
       <c r="H1129" t="n">
         <v>76007</v>
@@ -33197,7 +33197,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727058410645</v>
+        <v>39.4727020263672</v>
       </c>
       <c r="H1132" t="n">
         <v>28234</v>
@@ -33226,7 +33226,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900825500488</v>
+        <v>39.1900787353516</v>
       </c>
       <c r="H1133" t="n">
         <v>17044</v>
@@ -33371,7 +33371,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1138" t="n">
         <v>14887</v>
@@ -33429,7 +33429,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082176208496</v>
+        <v>39.7082214355469</v>
       </c>
       <c r="H1140" t="n">
         <v>25485</v>
@@ -33458,7 +33458,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842903137207</v>
+        <v>39.2842864990234</v>
       </c>
       <c r="H1141" t="n">
         <v>10680</v>
@@ -33487,7 +33487,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379447937012</v>
+        <v>40.0379409790039</v>
       </c>
       <c r="H1142" t="n">
         <v>21497</v>
@@ -33516,7 +33516,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1143" t="n">
         <v>17609</v>
@@ -33545,7 +33545,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452537536621</v>
+        <v>41.5452499389648</v>
       </c>
       <c r="H1144" t="n">
         <v>77350</v>
@@ -33661,7 +33661,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437370300293</v>
+        <v>39.9437408447266</v>
       </c>
       <c r="H1148" t="n">
         <v>26093</v>
@@ -33864,7 +33864,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132514953613</v>
+        <v>38.8132553100586</v>
       </c>
       <c r="H1155" t="n">
         <v>17325</v>
@@ -34154,7 +34154,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1165" t="n">
         <v>25025</v>
@@ -34212,7 +34212,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1167" t="n">
         <v>17311</v>
@@ -34241,7 +34241,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1168" t="n">
         <v>18709</v>
@@ -34270,7 +34270,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522842407227</v>
+        <v>36.5522880554199</v>
       </c>
       <c r="H1169" t="n">
         <v>7654</v>
@@ -34299,7 +34299,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1170" t="n">
         <v>11922</v>
@@ -34357,7 +34357,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993881225586</v>
+        <v>36.5993919372559</v>
       </c>
       <c r="H1172" t="n">
         <v>22854</v>
@@ -34444,7 +34444,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1175" t="n">
         <v>14281</v>
@@ -34589,7 +34589,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1180" t="n">
         <v>12217</v>
@@ -34647,7 +34647,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1182" t="n">
         <v>17442</v>
@@ -34763,7 +34763,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1186" t="n">
         <v>16678</v>
@@ -34850,7 +34850,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376663208008</v>
+        <v>33.5376625061035</v>
       </c>
       <c r="H1189" t="n">
         <v>13671</v>
@@ -34908,7 +34908,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202896118164</v>
+        <v>33.8202857971191</v>
       </c>
       <c r="H1191" t="n">
         <v>14410</v>
@@ -34937,7 +34937,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1192" t="n">
         <v>21211</v>
@@ -35053,7 +35053,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275985717773</v>
+        <v>35.3275947570801</v>
       </c>
       <c r="H1196" t="n">
         <v>18810</v>
@@ -35198,7 +35198,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1201" t="n">
         <v>10943</v>
@@ -35227,7 +35227,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1202" t="n">
         <v>13284</v>
@@ -35372,7 +35372,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1207" t="n">
         <v>86976</v>
@@ -35401,7 +35401,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1208" t="n">
         <v>107480</v>
@@ -35459,7 +35459,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238010406494</v>
+        <v>31.3238048553467</v>
       </c>
       <c r="H1210" t="n">
         <v>97335</v>
@@ -35517,7 +35517,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890399932861</v>
+        <v>31.8890419006348</v>
       </c>
       <c r="H1212" t="n">
         <v>19682</v>
@@ -35575,7 +35575,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1214" t="n">
         <v>32700</v>
@@ -35604,7 +35604,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1215" t="n">
         <v>71954</v>
@@ -35633,7 +35633,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419399261475</v>
+        <v>31.8419380187988</v>
       </c>
       <c r="H1216" t="n">
         <v>29272</v>
@@ -35662,7 +35662,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1217" t="n">
         <v>40121</v>
@@ -35691,7 +35691,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1218" t="n">
         <v>88062</v>
@@ -35720,7 +35720,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1219" t="n">
         <v>20873</v>
@@ -35807,7 +35807,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804946899414</v>
+        <v>35.2804908752441</v>
       </c>
       <c r="H1222" t="n">
         <v>55066</v>
@@ -35836,7 +35836,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391792297363</v>
+        <v>35.1391830444336</v>
       </c>
       <c r="H1223" t="n">
         <v>48119</v>
@@ -35952,7 +35952,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558013916016</v>
+        <v>34.0558052062988</v>
       </c>
       <c r="H1227" t="n">
         <v>33020</v>
@@ -36068,7 +36068,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1231" t="n">
         <v>27966</v>
@@ -36126,7 +36126,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160140991211</v>
+        <v>35.5160102844238</v>
       </c>
       <c r="H1233" t="n">
         <v>18372</v>
@@ -36155,7 +36155,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1234" t="n">
         <v>21216</v>
@@ -36271,7 +36271,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.0233192443848</v>
+        <v>37.023323059082</v>
       </c>
       <c r="H1238" t="n">
         <v>31944</v>
@@ -36329,7 +36329,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1240" t="n">
         <v>21979</v>
@@ -36358,7 +36358,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739402770996</v>
+        <v>34.5739440917969</v>
       </c>
       <c r="H1241" t="n">
         <v>36159</v>
@@ -36532,7 +36532,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955924987793</v>
+        <v>32.5955963134766</v>
       </c>
       <c r="H1247" t="n">
         <v>20275</v>
@@ -36619,7 +36619,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1250" t="n">
         <v>26995</v>
@@ -36735,7 +36735,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1254" t="n">
         <v>86029</v>
@@ -36938,7 +36938,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1261" t="n">
         <v>62483</v>
@@ -37083,7 +37083,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099395751953</v>
+        <v>29.1099376678467</v>
       </c>
       <c r="H1266" t="n">
         <v>42903</v>
@@ -37257,7 +37257,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1272" t="n">
         <v>69703</v>
@@ -37286,7 +37286,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1273" t="n">
         <v>51566</v>
@@ -37344,7 +37344,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1275" t="n">
         <v>39875</v>
@@ -37373,7 +37373,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1276" t="n">
         <v>33069</v>
@@ -37605,7 +37605,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164920806885</v>
+        <v>29.8164901733398</v>
       </c>
       <c r="H1284" t="n">
         <v>24216</v>
@@ -37663,7 +37663,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643543243408</v>
+        <v>30.6643524169922</v>
       </c>
       <c r="H1286" t="n">
         <v>27493</v>
@@ -37692,7 +37692,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1287" t="n">
         <v>27163</v>
@@ -37808,7 +37808,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1291" t="n">
         <v>50126</v>
@@ -37837,7 +37837,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1292" t="n">
         <v>15339</v>
@@ -37953,7 +37953,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1296" t="n">
         <v>31760</v>
@@ -38127,7 +38127,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832496643066</v>
+        <v>31.9832515716553</v>
       </c>
       <c r="H1302" t="n">
         <v>58973</v>
@@ -38156,7 +38156,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1303" t="n">
         <v>39498</v>
@@ -38330,7 +38330,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.3492546081543</v>
+        <v>33.349250793457</v>
       </c>
       <c r="H1309" t="n">
         <v>34631</v>
@@ -38417,7 +38417,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1312" t="n">
         <v>27726</v>
@@ -38533,7 +38533,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1316" t="n">
         <v>82490</v>
@@ -38562,7 +38562,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1317" t="n">
         <v>126426</v>
@@ -38707,7 +38707,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1322" t="n">
         <v>44000</v>
@@ -38765,7 +38765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1324" t="n">
         <v>42930</v>
@@ -38823,7 +38823,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1326" t="n">
         <v>38026</v>
@@ -38852,7 +38852,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1327" t="n">
         <v>61320</v>
@@ -38939,7 +38939,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041454315186</v>
+        <v>29.2041473388672</v>
       </c>
       <c r="H1330" t="n">
         <v>38634</v>
@@ -39113,7 +39113,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207675933838</v>
+        <v>28.1207656860352</v>
       </c>
       <c r="H1336" t="n">
         <v>109851</v>
@@ -39229,7 +39229,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1340" t="n">
         <v>55268</v>
@@ -39258,7 +39258,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1341" t="n">
         <v>36968</v>
@@ -39374,7 +39374,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844898223877</v>
+        <v>27.0844917297363</v>
       </c>
       <c r="H1345" t="n">
         <v>66714</v>
@@ -39432,7 +39432,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1347" t="n">
         <v>104150</v>
@@ -39519,7 +39519,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902839660645</v>
+        <v>26.9902820587158</v>
       </c>
       <c r="H1350" t="n">
         <v>33485</v>
@@ -39548,7 +39548,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779373168945</v>
+        <v>26.3779392242432</v>
       </c>
       <c r="H1351" t="n">
         <v>128641</v>
@@ -39606,7 +39606,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1353" t="n">
         <v>181757</v>
@@ -39635,7 +39635,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1354" t="n">
         <v>138211</v>
@@ -39664,7 +39664,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829711914062</v>
+        <v>25.4829730987549</v>
       </c>
       <c r="H1355" t="n">
         <v>105911</v>
@@ -39838,7 +39838,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011119842529</v>
+        <v>26.0011100769043</v>
       </c>
       <c r="H1361" t="n">
         <v>64528</v>
@@ -39867,7 +39867,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.388765335083</v>
+        <v>25.3887672424316</v>
       </c>
       <c r="H1362" t="n">
         <v>44652</v>
@@ -39896,7 +39896,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003517150879</v>
+        <v>25.2003536224365</v>
       </c>
       <c r="H1363" t="n">
         <v>43761</v>
@@ -39925,7 +39925,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.1895236968994</v>
+        <v>26.189525604248</v>
       </c>
       <c r="H1364" t="n">
         <v>45391</v>
@@ -39954,7 +39954,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076644897461</v>
+        <v>26.7076625823975</v>
       </c>
       <c r="H1365" t="n">
         <v>53357</v>
@@ -40157,7 +40157,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1372" t="n">
         <v>44289</v>
@@ -40215,7 +40215,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.6968364715576</v>
+        <v>27.696834564209</v>
       </c>
       <c r="H1374" t="n">
         <v>43847</v>
@@ -50968,7 +50968,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="E1745" t="n">
-        <v>34.3199996948242</v>
+        <v>34.2599983215332</v>
       </c>
       <c r="F1745" t="n">
         <v>34.2599983215332</v>
@@ -50980,6 +50980,35 @@
         <v>17366</v>
       </c>
       <c r="I1745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1746" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1746" t="n">
+        <v>34.5200004577637</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>34.5200004577637</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>33.7999992370605</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>34.2999992370605</v>
+      </c>
+      <c r="G1746" t="n">
+        <v>34.2999992370605</v>
+      </c>
+      <c r="H1746" t="n">
+        <v>15728</v>
+      </c>
+      <c r="I1746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.416880607605</v>
+        <v>13.4168815612793</v>
       </c>
       <c r="H3" t="n">
         <v>251735</v>
@@ -485,7 +485,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818502426147</v>
+        <v>13.3818511962891</v>
       </c>
       <c r="H4" t="n">
         <v>54824</v>
@@ -543,7 +543,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.0018997192383</v>
+        <v>14.001898765564</v>
       </c>
       <c r="H6" t="n">
         <v>24177</v>
@@ -572,7 +572,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810434341431</v>
+        <v>13.8810424804688</v>
       </c>
       <c r="H7" t="n">
         <v>41257</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934656143188</v>
+        <v>13.7934646606445</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -688,7 +688,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390054702759</v>
+        <v>13.8390064239502</v>
       </c>
       <c r="H11" t="n">
         <v>10789</v>
@@ -746,7 +746,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370918273926</v>
+        <v>13.9370908737183</v>
       </c>
       <c r="H13" t="n">
         <v>8422</v>
@@ -775,7 +775,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598608016968</v>
+        <v>13.9598627090454</v>
       </c>
       <c r="H14" t="n">
         <v>75034</v>
@@ -833,7 +833,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073162078857</v>
+        <v>13.9073143005371</v>
       </c>
       <c r="H16" t="n">
         <v>30923</v>
@@ -862,7 +862,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>13.8722858428955</v>
+        <v>13.8722848892212</v>
       </c>
       <c r="H17" t="n">
         <v>116007</v>
@@ -891,7 +891,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G18" t="n">
-        <v>13.9423456192017</v>
+        <v>13.942346572876</v>
       </c>
       <c r="H18" t="n">
         <v>74522</v>
@@ -920,7 +920,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H19" t="n">
         <v>69364</v>
@@ -978,7 +978,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963205337524</v>
+        <v>14.1963195800781</v>
       </c>
       <c r="H21" t="n">
         <v>76030</v>
@@ -1007,7 +1007,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130279541016</v>
+        <v>14.7130270004272</v>
       </c>
       <c r="H22" t="n">
         <v>147663</v>
@@ -1036,7 +1036,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692409515381</v>
+        <v>14.6692390441895</v>
       </c>
       <c r="H23" t="n">
         <v>297347</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071262359619</v>
+        <v>15.1071281433105</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1094,7 +1094,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260717391968</v>
+        <v>15.3260736465454</v>
       </c>
       <c r="H25" t="n">
         <v>73618</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881826400757</v>
+        <v>14.88818359375</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1152,7 +1152,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463083267212</v>
+        <v>14.7463073730469</v>
       </c>
       <c r="H27" t="n">
         <v>68742</v>
@@ -1181,7 +1181,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916864395142</v>
+        <v>14.8916873931885</v>
       </c>
       <c r="H28" t="n">
         <v>63118</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757614135742</v>
+        <v>14.9757604598999</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1268,7 +1268,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G31" t="n">
-        <v>14.5203580856323</v>
+        <v>14.5203590393066</v>
       </c>
       <c r="H31" t="n">
         <v>43925</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881826400757</v>
+        <v>14.88818359375</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881826400757</v>
+        <v>14.88818359375</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1384,7 +1384,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.644718170166</v>
+        <v>14.6447191238403</v>
       </c>
       <c r="H35" t="n">
         <v>11249</v>
@@ -1442,7 +1442,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.3557119369507</v>
+        <v>14.355712890625</v>
       </c>
       <c r="H37" t="n">
         <v>37432</v>
@@ -1500,7 +1500,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H39" t="n">
         <v>17569</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609666824341</v>
+        <v>14.3609676361084</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006048202515</v>
+        <v>14.8006057739258</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1616,7 +1616,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443946838379</v>
+        <v>14.8443956375122</v>
       </c>
       <c r="H43" t="n">
         <v>115888</v>
@@ -1645,7 +1645,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692409515381</v>
+        <v>14.6692390441895</v>
       </c>
       <c r="H44" t="n">
         <v>35731</v>
@@ -1703,7 +1703,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237001419067</v>
+        <v>14.6236991882324</v>
       </c>
       <c r="H46" t="n">
         <v>33733</v>
@@ -1732,7 +1732,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708292007446</v>
+        <v>14.7708301544189</v>
       </c>
       <c r="H47" t="n">
         <v>59163</v>
@@ -1761,7 +1761,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633401870728</v>
+        <v>15.0633392333984</v>
       </c>
       <c r="H48" t="n">
         <v>87381</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369037628174</v>
+        <v>15.136905670166</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1819,7 +1819,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1262578964233</v>
+        <v>14.1262588500977</v>
       </c>
       <c r="H50" t="n">
         <v>74499</v>
@@ -1906,7 +1906,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089063644409</v>
+        <v>14.0089073181152</v>
       </c>
       <c r="H53" t="n">
         <v>23213</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111679077148</v>
+        <v>12.6111669540405</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2109,7 +2109,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781866073608</v>
+        <v>13.4781856536865</v>
       </c>
       <c r="H60" t="n">
         <v>34756</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320251464844</v>
+        <v>12.7320261001587</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2167,7 +2167,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602378845215</v>
+        <v>11.5602369308472</v>
       </c>
       <c r="H62" t="n">
         <v>43479</v>
@@ -2283,7 +2283,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>9.63353061676025</v>
+        <v>9.63353157043457</v>
       </c>
       <c r="H66" t="n">
         <v>74779</v>
@@ -2312,7 +2312,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837497711182</v>
+        <v>9.45837593078613</v>
       </c>
       <c r="H67" t="n">
         <v>48156</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806560516357</v>
+        <v>9.10806655883789</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2370,7 +2370,7 @@
         <v>10.2379999160767</v>
       </c>
       <c r="G69" t="n">
-        <v>8.96619129180908</v>
+        <v>8.96619033813477</v>
       </c>
       <c r="H69" t="n">
         <v>122433</v>
@@ -2428,7 +2428,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651287078857</v>
+        <v>8.76651477813721</v>
       </c>
       <c r="H71" t="n">
         <v>44594</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494285583496</v>
+        <v>8.54494190216064</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2544,7 +2544,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032192230225</v>
+        <v>8.69032096862793</v>
       </c>
       <c r="H75" t="n">
         <v>14690</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500865936279</v>
+        <v>9.04500961303711</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2631,7 +2631,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.35328197479248</v>
+        <v>9.3532829284668</v>
       </c>
       <c r="H78" t="n">
         <v>29100</v>
@@ -2660,7 +2660,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G79" t="n">
-        <v>9.82620239257812</v>
+        <v>9.82620143890381</v>
       </c>
       <c r="H79" t="n">
         <v>19607</v>
@@ -2689,7 +2689,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921152114868</v>
+        <v>10.2921142578125</v>
       </c>
       <c r="H80" t="n">
         <v>20417</v>
@@ -2747,7 +2747,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070707321167</v>
+        <v>10.8070697784424</v>
       </c>
       <c r="H82" t="n">
         <v>3945</v>
@@ -2892,7 +2892,7 @@
         <v>12.8079996109009</v>
       </c>
       <c r="G87" t="n">
-        <v>11.2169332504272</v>
+        <v>11.2169322967529</v>
       </c>
       <c r="H87" t="n">
         <v>10905</v>
@@ -2950,7 +2950,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898517608643</v>
+        <v>11.6898508071899</v>
       </c>
       <c r="H89" t="n">
         <v>19363</v>
@@ -2979,7 +2979,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068826675415</v>
+        <v>12.0068817138672</v>
       </c>
       <c r="H90" t="n">
         <v>11410</v>
@@ -3095,7 +3095,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331817626953</v>
+        <v>10.9331827163696</v>
       </c>
       <c r="H94" t="n">
         <v>46331</v>
@@ -3153,7 +3153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143999099731</v>
+        <v>10.6144008636475</v>
       </c>
       <c r="H96" t="n">
         <v>30171</v>
@@ -3182,7 +3182,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.465518951416</v>
+        <v>10.4655179977417</v>
       </c>
       <c r="H97" t="n">
         <v>30855</v>
@@ -3240,7 +3240,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691835403442</v>
+        <v>10.3691825866699</v>
       </c>
       <c r="H99" t="n">
         <v>11865</v>
@@ -3327,7 +3327,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075550079346</v>
+        <v>10.5075559616089</v>
       </c>
       <c r="H102" t="n">
         <v>41323</v>
@@ -3356,7 +3356,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616916656494</v>
+        <v>10.6616926193237</v>
       </c>
       <c r="H103" t="n">
         <v>12365</v>
@@ -3414,7 +3414,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.3814420700073</v>
+        <v>10.381443977356</v>
       </c>
       <c r="H105" t="n">
         <v>19187</v>
@@ -3443,7 +3443,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093069076538</v>
+        <v>10.5093059539795</v>
       </c>
       <c r="H106" t="n">
         <v>15170</v>
@@ -3472,7 +3472,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G107" t="n">
-        <v>11.3412933349609</v>
+        <v>11.3412923812866</v>
       </c>
       <c r="H107" t="n">
         <v>39114</v>
@@ -3559,7 +3559,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726591110229</v>
+        <v>11.4726600646973</v>
       </c>
       <c r="H110" t="n">
         <v>21522</v>
@@ -3588,7 +3588,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565723419189</v>
+        <v>11.6565713882446</v>
       </c>
       <c r="H111" t="n">
         <v>27521</v>
@@ -3675,7 +3675,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834676742554</v>
+        <v>12.3834657669067</v>
       </c>
       <c r="H114" t="n">
         <v>29369</v>
@@ -3704,7 +3704,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727954864502</v>
+        <v>12.4727945327759</v>
       </c>
       <c r="H115" t="n">
         <v>41546</v>
@@ -3733,7 +3733,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506715774536</v>
+        <v>12.0506706237793</v>
       </c>
       <c r="H116" t="n">
         <v>330572</v>
@@ -3762,7 +3762,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258262634277</v>
+        <v>12.2258272171021</v>
       </c>
       <c r="H117" t="n">
         <v>24996</v>
@@ -3820,7 +3820,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.220573425293</v>
+        <v>12.2205715179443</v>
       </c>
       <c r="H119" t="n">
         <v>70567</v>
@@ -3965,7 +3965,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930067062378</v>
+        <v>12.9930057525635</v>
       </c>
       <c r="H124" t="n">
         <v>20213</v>
@@ -3994,7 +3994,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.786322593689</v>
+        <v>12.7863235473633</v>
       </c>
       <c r="H125" t="n">
         <v>14042</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901489257812</v>
+        <v>12.5901498794556</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119512557983</v>
+        <v>13.211950302124</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4139,7 +4139,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976135253906</v>
+        <v>13.3976154327393</v>
       </c>
       <c r="H130" t="n">
         <v>7245</v>
@@ -4168,7 +4168,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361476898193</v>
+        <v>13.4361486434937</v>
       </c>
       <c r="H131" t="n">
         <v>17251</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681604385376</v>
+        <v>13.1681613922119</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4400,7 +4400,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805835723877</v>
+        <v>13.0805826187134</v>
       </c>
       <c r="H139" t="n">
         <v>13088</v>
@@ -4574,7 +4574,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490550994873</v>
+        <v>13.0490560531616</v>
       </c>
       <c r="H145" t="n">
         <v>1877</v>
@@ -4603,7 +4603,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772415161133</v>
+        <v>12.9772424697876</v>
       </c>
       <c r="H146" t="n">
         <v>4221</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504835128784</v>
+        <v>13.2504844665527</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4661,7 +4661,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821737289429</v>
+        <v>13.1821727752686</v>
       </c>
       <c r="H148" t="n">
         <v>863</v>
@@ -4806,7 +4806,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324831008911</v>
+        <v>13.5324821472168</v>
       </c>
       <c r="H153" t="n">
         <v>9502</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277145385742</v>
+        <v>13.2277135848999</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4922,7 +4922,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555774688721</v>
+        <v>13.3555765151978</v>
       </c>
       <c r="H157" t="n">
         <v>9479</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348819732666</v>
+        <v>13.1348810195923</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -4980,7 +4980,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823345184326</v>
+        <v>13.0823354721069</v>
       </c>
       <c r="H159" t="n">
         <v>22453</v>
@@ -5038,7 +5038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H161" t="n">
         <v>8576</v>
@@ -5154,7 +5154,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094150543213</v>
+        <v>12.6094169616699</v>
       </c>
       <c r="H165" t="n">
         <v>15675</v>
@@ -5212,7 +5212,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H167" t="n">
         <v>9897</v>
@@ -5241,7 +5241,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.409740447998</v>
+        <v>12.4097394943237</v>
       </c>
       <c r="H168" t="n">
         <v>11733</v>
@@ -5299,7 +5299,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909313201904</v>
+        <v>13.1909322738647</v>
       </c>
       <c r="H170" t="n">
         <v>36613</v>
@@ -5357,7 +5357,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132169723511</v>
+        <v>13.5132160186768</v>
       </c>
       <c r="H172" t="n">
         <v>10655</v>
@@ -5560,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H179" t="n">
         <v>13803</v>
@@ -5589,7 +5589,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H180" t="n">
         <v>13692</v>
@@ -5618,7 +5618,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493532180786</v>
+        <v>13.9493541717529</v>
       </c>
       <c r="H181" t="n">
         <v>30984</v>
@@ -5647,7 +5647,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H182" t="n">
         <v>15865</v>
@@ -5676,7 +5676,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G183" t="n">
-        <v>13.784707069397</v>
+        <v>13.7847061157227</v>
       </c>
       <c r="H183" t="n">
         <v>22904</v>
@@ -5705,7 +5705,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H184" t="n">
         <v>25117</v>
@@ -5763,7 +5763,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H186" t="n">
         <v>9698</v>
@@ -5792,7 +5792,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H187" t="n">
         <v>24640</v>
@@ -5821,7 +5821,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H188" t="n">
         <v>35173</v>
@@ -5850,7 +5850,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H189" t="n">
         <v>28944</v>
@@ -5908,7 +5908,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G191" t="n">
-        <v>13.8722858428955</v>
+        <v>13.8722848892212</v>
       </c>
       <c r="H191" t="n">
         <v>17918</v>
@@ -5995,7 +5995,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971292495728</v>
       </c>
       <c r="H194" t="n">
         <v>8929</v>
@@ -6169,7 +6169,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767572402954</v>
+        <v>13.2767581939697</v>
       </c>
       <c r="H200" t="n">
         <v>6789</v>
@@ -6198,7 +6198,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.732159614563</v>
+        <v>13.7321615219116</v>
       </c>
       <c r="H201" t="n">
         <v>43057</v>
@@ -6227,7 +6227,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124082565308</v>
+        <v>14.0124092102051</v>
       </c>
       <c r="H202" t="n">
         <v>32085</v>
@@ -6256,7 +6256,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.3101720809937</v>
+        <v>14.3101739883423</v>
       </c>
       <c r="H203" t="n">
         <v>21909</v>
@@ -6372,7 +6372,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H207" t="n">
         <v>18020</v>
@@ -6401,7 +6401,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H208" t="n">
         <v>11562</v>
@@ -6459,7 +6459,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502983093262</v>
       </c>
       <c r="H210" t="n">
         <v>16575</v>
@@ -6488,7 +6488,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.7305431365967</v>
+        <v>14.730544090271</v>
       </c>
       <c r="H211" t="n">
         <v>9090</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502983093262</v>
       </c>
       <c r="H212" t="n">
         <v>5728</v>
@@ -6546,7 +6546,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H213" t="n">
         <v>3813</v>
@@ -6575,7 +6575,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955146789551</v>
+        <v>14.6955156326294</v>
       </c>
       <c r="H214" t="n">
         <v>13259</v>
@@ -6604,7 +6604,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H215" t="n">
         <v>13883</v>
@@ -6894,7 +6894,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592420578003</v>
+        <v>13.2592430114746</v>
       </c>
       <c r="H225" t="n">
         <v>9073</v>
@@ -6981,7 +6981,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.732159614563</v>
+        <v>13.7321615219116</v>
       </c>
       <c r="H228" t="n">
         <v>2543</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.52197265625</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7097,7 +7097,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G232" t="n">
-        <v>13.784707069397</v>
+        <v>13.7847061157227</v>
       </c>
       <c r="H232" t="n">
         <v>19127</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.52197265625</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022232055664</v>
+        <v>13.8022222518921</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.52197265625</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7938,7 +7938,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971302032471</v>
+        <v>13.6971292495728</v>
       </c>
       <c r="H261" t="n">
         <v>11448</v>
@@ -7967,7 +7967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197374343872</v>
+        <v>13.8197383880615</v>
       </c>
       <c r="H262" t="n">
         <v>19414</v>
@@ -8083,7 +8083,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.3101720809937</v>
+        <v>14.3101739883423</v>
       </c>
       <c r="H266" t="n">
         <v>8011</v>
@@ -8112,7 +8112,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502973556519</v>
+        <v>14.4502983093262</v>
       </c>
       <c r="H267" t="n">
         <v>21797</v>
@@ -8141,7 +8141,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751407623291</v>
+        <v>14.2751398086548</v>
       </c>
       <c r="H268" t="n">
         <v>16682</v>
@@ -8170,7 +8170,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H269" t="n">
         <v>28438</v>
@@ -8199,7 +8199,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576246261597</v>
       </c>
       <c r="H270" t="n">
         <v>5152</v>
@@ -8228,7 +8228,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028409957886</v>
       </c>
       <c r="H271" t="n">
         <v>6060</v>
@@ -8257,7 +8257,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028409957886</v>
       </c>
       <c r="H272" t="n">
         <v>8570</v>
@@ -8286,7 +8286,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079368591309</v>
+        <v>14.6079359054565</v>
       </c>
       <c r="H273" t="n">
         <v>7891</v>
@@ -8315,7 +8315,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G274" t="n">
-        <v>14.3977508544922</v>
+        <v>14.3977499008179</v>
       </c>
       <c r="H274" t="n">
         <v>5498</v>
@@ -8373,7 +8373,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276891708374</v>
+        <v>14.3276901245117</v>
       </c>
       <c r="H276" t="n">
         <v>6927</v>
@@ -8402,7 +8402,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576246261597</v>
       </c>
       <c r="H277" t="n">
         <v>6898</v>
@@ -8460,7 +8460,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034645080566</v>
+        <v>15.203462600708</v>
       </c>
       <c r="H279" t="n">
         <v>80397</v>
@@ -8489,7 +8489,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311647415161</v>
+        <v>15.4311637878418</v>
       </c>
       <c r="H280" t="n">
         <v>50717</v>
@@ -8605,7 +8605,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165054321289</v>
+        <v>15.8165035247803</v>
       </c>
       <c r="H284" t="n">
         <v>60606</v>
@@ -8692,7 +8692,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317844390869</v>
+        <v>16.1317863464355</v>
       </c>
       <c r="H287" t="n">
         <v>34304</v>
@@ -8750,7 +8750,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>16.4295482635498</v>
+        <v>16.4295501708984</v>
       </c>
       <c r="H289" t="n">
         <v>27587</v>
@@ -8779,7 +8779,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973747253418</v>
+        <v>16.7973766326904</v>
       </c>
       <c r="H290" t="n">
         <v>32844</v>
@@ -8866,7 +8866,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3753890991211</v>
+        <v>17.3753871917725</v>
       </c>
       <c r="H293" t="n">
         <v>29298</v>
@@ -8924,7 +8924,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220310211182</v>
+        <v>17.8220329284668</v>
       </c>
       <c r="H295" t="n">
         <v>52008</v>
@@ -8953,7 +8953,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906642913818</v>
+        <v>17.6906661987305</v>
       </c>
       <c r="H296" t="n">
         <v>36908</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.252779006958</v>
+        <v>17.2527770996094</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9011,7 +9011,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468772888184</v>
+        <v>17.6468753814697</v>
       </c>
       <c r="H298" t="n">
         <v>49334</v>
@@ -9040,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.5155086517334</v>
+        <v>17.5155124664307</v>
       </c>
       <c r="H299" t="n">
         <v>21074</v>
@@ -9069,7 +9069,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G300" t="n">
-        <v>17.3228416442871</v>
+        <v>17.3228397369385</v>
       </c>
       <c r="H300" t="n">
         <v>7964</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979934692383</v>
+        <v>17.4979972839355</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9156,7 +9156,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H303" t="n">
         <v>51778</v>
@@ -9272,7 +9272,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>18.7853832244873</v>
+        <v>18.7853851318359</v>
       </c>
       <c r="H307" t="n">
         <v>24097</v>
@@ -9301,7 +9301,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.310848236084</v>
+        <v>19.3108520507812</v>
       </c>
       <c r="H308" t="n">
         <v>58530</v>
@@ -9388,7 +9388,7 @@
         <v>21.5</v>
       </c>
       <c r="G311" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H311" t="n">
         <v>24053</v>
@@ -9446,7 +9446,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356945037842</v>
+        <v>19.1356964111328</v>
       </c>
       <c r="H313" t="n">
         <v>16234</v>
@@ -9475,7 +9475,7 @@
         <v>21.5</v>
       </c>
       <c r="G314" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H314" t="n">
         <v>16356</v>
@@ -9562,7 +9562,7 @@
         <v>21.5</v>
       </c>
       <c r="G317" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H317" t="n">
         <v>18086</v>
@@ -9591,7 +9591,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>18.7853832244873</v>
+        <v>18.7853851318359</v>
       </c>
       <c r="H318" t="n">
         <v>14808</v>
@@ -9620,7 +9620,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="n">
-        <v>19.2670612335205</v>
+        <v>19.2670631408691</v>
       </c>
       <c r="H319" t="n">
         <v>26626</v>
@@ -9736,7 +9736,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794834136963</v>
+        <v>19.1794853210449</v>
       </c>
       <c r="H323" t="n">
         <v>9282</v>
@@ -9765,7 +9765,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7487392425537</v>
+        <v>19.7487373352051</v>
       </c>
       <c r="H324" t="n">
         <v>38949</v>
@@ -9794,7 +9794,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611614227295</v>
+        <v>19.6611633300781</v>
       </c>
       <c r="H325" t="n">
         <v>22459</v>
@@ -9910,7 +9910,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729629516602</v>
+        <v>18.8729610443115</v>
       </c>
       <c r="H329" t="n">
         <v>14665</v>
@@ -9939,7 +9939,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167499542236</v>
+        <v>18.9167518615723</v>
       </c>
       <c r="H330" t="n">
         <v>9202</v>
@@ -10084,7 +10084,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.7853832244873</v>
+        <v>18.7853851318359</v>
       </c>
       <c r="H335" t="n">
         <v>17649</v>
@@ -10113,7 +10113,7 @@
         <v>21.5</v>
       </c>
       <c r="G336" t="n">
-        <v>18.8291759490967</v>
+        <v>18.8291721343994</v>
       </c>
       <c r="H336" t="n">
         <v>16890</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546409606934</v>
+        <v>19.3546390533447</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10200,7 +10200,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167499542236</v>
+        <v>18.9167518615723</v>
       </c>
       <c r="H339" t="n">
         <v>11503</v>
@@ -10229,7 +10229,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794834136963</v>
+        <v>19.1794853210449</v>
       </c>
       <c r="H340" t="n">
         <v>8629</v>
@@ -10258,7 +10258,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G341" t="n">
-        <v>18.9605388641357</v>
+        <v>18.9605407714844</v>
       </c>
       <c r="H341" t="n">
         <v>7028</v>
@@ -10287,7 +10287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H342" t="n">
         <v>48534</v>
@@ -10316,7 +10316,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409774780273</v>
+        <v>18.0409755706787</v>
       </c>
       <c r="H343" t="n">
         <v>22326</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799419403076</v>
+        <v>18.8799457550049</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10432,7 +10432,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797546386719</v>
+        <v>19.2797565460205</v>
       </c>
       <c r="H347" t="n">
         <v>18924</v>
@@ -10490,7 +10490,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.2126445770264</v>
+        <v>20.212646484375</v>
       </c>
       <c r="H349" t="n">
         <v>34567</v>
@@ -10635,7 +10635,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793743133545</v>
+        <v>20.0793762207031</v>
       </c>
       <c r="H354" t="n">
         <v>30645</v>
@@ -10664,7 +10664,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905300140381</v>
+        <v>19.9905319213867</v>
       </c>
       <c r="H355" t="n">
         <v>20044</v>
@@ -10780,7 +10780,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.8355197906494</v>
+        <v>18.835521697998</v>
       </c>
       <c r="H359" t="n">
         <v>57619</v>
@@ -10896,7 +10896,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G363" t="n">
-        <v>19.457447052002</v>
+        <v>19.4574489593506</v>
       </c>
       <c r="H363" t="n">
         <v>18679</v>
@@ -10954,7 +10954,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5236110687256</v>
+        <v>20.523609161377</v>
       </c>
       <c r="H365" t="n">
         <v>43029</v>
@@ -10983,7 +10983,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905300140381</v>
+        <v>19.9905319213867</v>
       </c>
       <c r="H366" t="n">
         <v>12885</v>
@@ -11070,7 +11070,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455364227295</v>
+        <v>21.1455383300781</v>
       </c>
       <c r="H369" t="n">
         <v>96384</v>
@@ -11099,7 +11099,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G370" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H370" t="n">
         <v>39616</v>
@@ -11215,7 +11215,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>23.233434677124</v>
+        <v>23.2334365844727</v>
       </c>
       <c r="H374" t="n">
         <v>53913</v>
@@ -11273,7 +11273,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>23.1890163421631</v>
+        <v>23.1890144348145</v>
       </c>
       <c r="H376" t="n">
         <v>28296</v>
@@ -11302,7 +11302,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.1445903778076</v>
+        <v>23.144588470459</v>
       </c>
       <c r="H377" t="n">
         <v>33185</v>
@@ -11505,7 +11505,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.589771270752</v>
+        <v>21.5897693634033</v>
       </c>
       <c r="H384" t="n">
         <v>31931</v>
@@ -11563,7 +11563,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H386" t="n">
         <v>27193</v>
@@ -11592,7 +11592,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011142730713</v>
+        <v>21.1011161804199</v>
       </c>
       <c r="H387" t="n">
         <v>8616</v>
@@ -11621,7 +11621,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566940307617</v>
+        <v>21.0566921234131</v>
       </c>
       <c r="H388" t="n">
         <v>20039</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11882,7 +11882,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680332183838</v>
+        <v>20.5680313110352</v>
       </c>
       <c r="H397" t="n">
         <v>6449</v>
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H399" t="n">
         <v>85005</v>
@@ -11969,7 +11969,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H400" t="n">
         <v>41832</v>
@@ -11998,7 +11998,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.589771270752</v>
+        <v>21.5897693634033</v>
       </c>
       <c r="H401" t="n">
         <v>37886</v>
@@ -12114,7 +12114,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G405" t="n">
-        <v>21.27880859375</v>
+        <v>21.2788105010986</v>
       </c>
       <c r="H405" t="n">
         <v>18949</v>
@@ -12172,7 +12172,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459148406982</v>
+        <v>20.3459167480469</v>
       </c>
       <c r="H407" t="n">
         <v>12913</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12317,7 +12317,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H412" t="n">
         <v>32846</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115074157715</v>
+        <v>22.6115093231201</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12520,7 +12520,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5226631164551</v>
+        <v>22.5226650238037</v>
       </c>
       <c r="H419" t="n">
         <v>40477</v>
@@ -12607,7 +12607,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113201141357</v>
+        <v>23.0113182067871</v>
       </c>
       <c r="H422" t="n">
         <v>22051</v>
@@ -12636,7 +12636,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551765441895</v>
+        <v>24.2551746368408</v>
       </c>
       <c r="H423" t="n">
         <v>80709</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444011688232</v>
+        <v>23.5444030761719</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12781,7 +12781,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772891998291</v>
+        <v>24.4772930145264</v>
       </c>
       <c r="H428" t="n">
         <v>27149</v>
@@ -12955,7 +12955,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>24.7438316345215</v>
+        <v>24.7438335418701</v>
       </c>
       <c r="H434" t="n">
         <v>22801</v>
@@ -13013,7 +13013,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324886322021</v>
+        <v>25.2324905395508</v>
       </c>
       <c r="H436" t="n">
         <v>14765</v>
@@ -13042,7 +13042,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103721618652</v>
+        <v>25.0103740692139</v>
       </c>
       <c r="H437" t="n">
         <v>16754</v>
@@ -13245,7 +13245,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536609649658</v>
+        <v>27.4536590576172</v>
       </c>
       <c r="H444" t="n">
         <v>42660</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425071716309</v>
+        <v>27.5425090789795</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13332,7 +13332,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300270080566</v>
+        <v>30.430025100708</v>
       </c>
       <c r="H447" t="n">
         <v>138213</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967567443848</v>
+        <v>30.2967548370361</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13390,7 +13390,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.6965675354004</v>
+        <v>30.6965656280518</v>
       </c>
       <c r="H449" t="n">
         <v>65084</v>
@@ -13419,7 +13419,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636775970459</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H450" t="n">
         <v>69374</v>
@@ -13448,7 +13448,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417484283447</v>
+        <v>29.1417503356934</v>
       </c>
       <c r="H451" t="n">
         <v>55282</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527149200439</v>
+        <v>29.4527187347412</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13535,7 +13535,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300270080566</v>
+        <v>30.430025100708</v>
       </c>
       <c r="H454" t="n">
         <v>27063</v>
@@ -13622,7 +13622,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646236419678</v>
+        <v>27.7646217346191</v>
       </c>
       <c r="H457" t="n">
         <v>101299</v>
@@ -13709,7 +13709,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423160552979</v>
+        <v>27.9423179626465</v>
       </c>
       <c r="H460" t="n">
         <v>17404</v>
@@ -13767,7 +13767,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867420196533</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H462" t="n">
         <v>26586</v>
@@ -13796,7 +13796,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867420196533</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H463" t="n">
         <v>39977</v>
@@ -13825,7 +13825,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.230598449707</v>
+        <v>29.2306003570557</v>
       </c>
       <c r="H464" t="n">
         <v>33973</v>
@@ -13854,7 +13854,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H465" t="n">
         <v>29892</v>
@@ -13883,7 +13883,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.164436340332</v>
+        <v>28.1644344329834</v>
       </c>
       <c r="H466" t="n">
         <v>19936</v>
@@ -13912,7 +13912,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857902526855</v>
       </c>
       <c r="H467" t="n">
         <v>54363</v>
@@ -13941,7 +13941,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525218963623</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H468" t="n">
         <v>33525</v>
@@ -13970,7 +13970,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409915924072</v>
+        <v>30.7409896850586</v>
       </c>
       <c r="H469" t="n">
         <v>41790</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14028,7 +14028,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406131744385</v>
+        <v>31.5406112670898</v>
       </c>
       <c r="H471" t="n">
         <v>48516</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627296447754</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14086,7 +14086,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H473" t="n">
         <v>41695</v>
@@ -14115,7 +14115,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H474" t="n">
         <v>26719</v>
@@ -14173,7 +14173,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G476" t="n">
-        <v>33.8506240844727</v>
+        <v>33.8506278991699</v>
       </c>
       <c r="H476" t="n">
         <v>38154</v>
@@ -14289,7 +14289,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G480" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H480" t="n">
         <v>25306</v>
@@ -14318,7 +14318,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956176757812</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H481" t="n">
         <v>18772</v>
@@ -14376,7 +14376,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731246948242</v>
+        <v>33.273120880127</v>
       </c>
       <c r="H483" t="n">
         <v>61904</v>
@@ -14405,7 +14405,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942970275879</v>
+        <v>35.4942932128906</v>
       </c>
       <c r="H484" t="n">
         <v>95655</v>
@@ -14434,7 +14434,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H485" t="n">
         <v>147072</v>
@@ -14463,7 +14463,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617797851562</v>
+        <v>33.7617835998535</v>
       </c>
       <c r="H486" t="n">
         <v>58518</v>
@@ -14492,7 +14492,7 @@
         <v>37.75</v>
       </c>
       <c r="G487" t="n">
-        <v>33.5396690368652</v>
+        <v>33.539665222168</v>
       </c>
       <c r="H487" t="n">
         <v>40045</v>
@@ -14550,7 +14550,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065879821777</v>
+        <v>33.0065841674805</v>
       </c>
       <c r="H489" t="n">
         <v>27315</v>
@@ -14608,7 +14608,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731246948242</v>
+        <v>33.273120880127</v>
       </c>
       <c r="H491" t="n">
         <v>10757</v>
@@ -14666,7 +14666,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844657897949</v>
+        <v>32.7844696044922</v>
       </c>
       <c r="H493" t="n">
         <v>16789</v>
@@ -14695,7 +14695,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H494" t="n">
         <v>20925</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179290771484</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14811,7 +14811,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H498" t="n">
         <v>32373</v>
@@ -14869,7 +14869,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634883880615</v>
+        <v>30.1634864807129</v>
       </c>
       <c r="H500" t="n">
         <v>80023</v>
@@ -14927,7 +14927,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404277801514</v>
+        <v>31.9404258728027</v>
       </c>
       <c r="H502" t="n">
         <v>44140</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15072,7 +15072,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956176757812</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H507" t="n">
         <v>36805</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177360534668</v>
+        <v>32.9177398681641</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15159,7 +15159,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071556091309</v>
+        <v>31.8071517944336</v>
       </c>
       <c r="H510" t="n">
         <v>24075</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627296447754</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15304,7 +15304,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.473503112793</v>
+        <v>32.4734992980957</v>
       </c>
       <c r="H515" t="n">
         <v>28750</v>
@@ -15333,7 +15333,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.473503112793</v>
+        <v>32.4734992980957</v>
       </c>
       <c r="H516" t="n">
         <v>39270</v>
@@ -15420,7 +15420,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290809631348</v>
+        <v>32.4290771484375</v>
       </c>
       <c r="H519" t="n">
         <v>27308</v>
@@ -15449,7 +15449,7 @@
         <v>37.5</v>
       </c>
       <c r="G520" t="n">
-        <v>33.3175468444824</v>
+        <v>33.3175506591797</v>
       </c>
       <c r="H520" t="n">
         <v>18235</v>
@@ -15507,7 +15507,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H522" t="n">
         <v>24452</v>
@@ -15536,7 +15536,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729393005371</v>
+        <v>33.6729354858398</v>
       </c>
       <c r="H523" t="n">
         <v>18883</v>
@@ -15623,7 +15623,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>34.0283203125</v>
+        <v>34.0283241271973</v>
       </c>
       <c r="H526" t="n">
         <v>15120</v>
@@ -15652,7 +15652,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H527" t="n">
         <v>15724</v>
@@ -15710,7 +15710,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960018157959</v>
+        <v>31.8960056304932</v>
       </c>
       <c r="H529" t="n">
         <v>38776</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179252624512</v>
+        <v>32.5179290771484</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15942,7 +15942,7 @@
         <v>40.5</v>
       </c>
       <c r="G537" t="n">
-        <v>35.9829483032227</v>
+        <v>35.9829521179199</v>
       </c>
       <c r="H537" t="n">
         <v>52532</v>
@@ -15971,7 +15971,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727500915527</v>
+        <v>34.0727424621582</v>
       </c>
       <c r="H538" t="n">
         <v>33816</v>
@@ -16029,7 +16029,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>31.4517669677734</v>
+        <v>31.4517650604248</v>
       </c>
       <c r="H540" t="n">
         <v>30779</v>
@@ -16058,7 +16058,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H541" t="n">
         <v>30426</v>
@@ -16116,7 +16116,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290809631348</v>
+        <v>32.4290771484375</v>
       </c>
       <c r="H543" t="n">
         <v>43887</v>
@@ -16174,7 +16174,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H545" t="n">
         <v>71422</v>
@@ -16203,7 +16203,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956176757812</v>
+        <v>32.6956214904785</v>
       </c>
       <c r="H546" t="n">
         <v>50699</v>
@@ -16232,7 +16232,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H547" t="n">
         <v>60536</v>
@@ -16551,7 +16551,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731246948242</v>
+        <v>33.273120880127</v>
       </c>
       <c r="H558" t="n">
         <v>31513</v>
@@ -16609,7 +16609,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721748352051</v>
+        <v>35.2721786499023</v>
       </c>
       <c r="H560" t="n">
         <v>92873</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.405445098877</v>
+        <v>35.4054489135742</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16725,7 +16725,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>34.3837089538574</v>
+        <v>34.3837127685547</v>
       </c>
       <c r="H564" t="n">
         <v>118997</v>
@@ -16841,7 +16841,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530933380127</v>
+        <v>28.6530914306641</v>
       </c>
       <c r="H568" t="n">
         <v>187078</v>
@@ -16899,7 +16899,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.788257598877</v>
+        <v>24.7882556915283</v>
       </c>
       <c r="H570" t="n">
         <v>115179</v>
@@ -16928,7 +16928,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.343074798584</v>
+        <v>26.3430728912354</v>
       </c>
       <c r="H571" t="n">
         <v>102740</v>
@@ -16957,7 +16957,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873077392578</v>
+        <v>26.7873096466064</v>
       </c>
       <c r="H572" t="n">
         <v>79386</v>
@@ -16986,7 +16986,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.230598449707</v>
+        <v>29.2306003570557</v>
       </c>
       <c r="H573" t="n">
         <v>133949</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190624237061</v>
+        <v>30.1190643310547</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17044,7 +17044,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525218963623</v>
+        <v>29.8525199890137</v>
       </c>
       <c r="H575" t="n">
         <v>71925</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184986114502</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17102,7 +17102,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519542694092</v>
       </c>
       <c r="H577" t="n">
         <v>60129</v>
@@ -17247,7 +17247,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298358917236</v>
+        <v>30.8298397064209</v>
       </c>
       <c r="H582" t="n">
         <v>35488</v>
@@ -17276,7 +17276,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H583" t="n">
         <v>48569</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186840057373</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17363,7 +17363,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G586" t="n">
-        <v>33.8506240844727</v>
+        <v>33.8506278991699</v>
       </c>
       <c r="H586" t="n">
         <v>57760</v>
@@ -17392,7 +17392,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.6511993408203</v>
+        <v>32.651195526123</v>
       </c>
       <c r="H587" t="n">
         <v>35265</v>
@@ -17421,7 +17421,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>32.1181182861328</v>
+        <v>32.1181221008301</v>
       </c>
       <c r="H588" t="n">
         <v>33386</v>
@@ -17450,7 +17450,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G589" t="n">
-        <v>32.2513847351074</v>
+        <v>32.2513885498047</v>
       </c>
       <c r="H589" t="n">
         <v>67180</v>
@@ -17508,7 +17508,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>31.4517669677734</v>
+        <v>31.4517650604248</v>
       </c>
       <c r="H591" t="n">
         <v>44060</v>
@@ -17566,7 +17566,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521415710449</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H593" t="n">
         <v>18121</v>
@@ -17595,7 +17595,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636775970459</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H594" t="n">
         <v>35604</v>
@@ -17624,7 +17624,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521415710449</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H595" t="n">
         <v>37402</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186840057373</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17682,7 +17682,7 @@
         <v>35</v>
       </c>
       <c r="G597" t="n">
-        <v>31.096378326416</v>
+        <v>31.0963821411133</v>
       </c>
       <c r="H597" t="n">
         <v>23818</v>
@@ -17711,7 +17711,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519542694092</v>
       </c>
       <c r="H598" t="n">
         <v>20035</v>
@@ -17740,7 +17740,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.274076461792</v>
+        <v>31.2740783691406</v>
       </c>
       <c r="H599" t="n">
         <v>22406</v>
@@ -17769,7 +17769,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H600" t="n">
         <v>24723</v>
@@ -17827,7 +17827,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H602" t="n">
         <v>46419</v>
@@ -17856,7 +17856,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863616943359</v>
       </c>
       <c r="H603" t="n">
         <v>26401</v>
@@ -17914,7 +17914,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859832763672</v>
+        <v>29.5859851837158</v>
       </c>
       <c r="H605" t="n">
         <v>31886</v>
@@ -17943,7 +17943,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857902526855</v>
       </c>
       <c r="H606" t="n">
         <v>22611</v>
@@ -17972,7 +17972,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289691925049</v>
       </c>
       <c r="H607" t="n">
         <v>27177</v>
@@ -18030,7 +18030,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H609" t="n">
         <v>29532</v>
@@ -18088,7 +18088,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H611" t="n">
         <v>81317</v>
@@ -18117,7 +18117,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H612" t="n">
         <v>85415</v>
@@ -18204,7 +18204,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>32.3828506469727</v>
+        <v>32.3828468322754</v>
       </c>
       <c r="H615" t="n">
         <v>35851</v>
@@ -18233,7 +18233,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H616" t="n">
         <v>45928</v>
@@ -18262,7 +18262,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110359191895</v>
+        <v>34.0110321044922</v>
       </c>
       <c r="H617" t="n">
         <v>48629</v>
@@ -18349,7 +18349,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9757976531982</v>
+        <v>31.9758033752441</v>
       </c>
       <c r="H620" t="n">
         <v>19405</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.890344619751</v>
+        <v>30.8903427124023</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18552,7 +18552,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898979187012</v>
+        <v>32.7898941040039</v>
       </c>
       <c r="H627" t="n">
         <v>41583</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.890344619751</v>
+        <v>30.8903427124023</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18610,7 +18610,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189765930176</v>
+        <v>30.6189785003662</v>
       </c>
       <c r="H629" t="n">
         <v>25073</v>
@@ -18639,7 +18639,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G630" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164798736572</v>
       </c>
       <c r="H630" t="n">
         <v>9830</v>
@@ -18697,7 +18697,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426208496094</v>
+        <v>31.3426189422607</v>
       </c>
       <c r="H632" t="n">
         <v>44384</v>
@@ -18726,7 +18726,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5737476348877</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H633" t="n">
         <v>27780</v>
@@ -18755,7 +18755,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260219573975</v>
+        <v>31.0260276794434</v>
       </c>
       <c r="H634" t="n">
         <v>36768</v>
@@ -18813,7 +18813,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H636" t="n">
         <v>49552</v>
@@ -18842,7 +18842,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289691925049</v>
       </c>
       <c r="H637" t="n">
         <v>26649</v>
@@ -18987,7 +18987,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289691925049</v>
       </c>
       <c r="H642" t="n">
         <v>7805</v>
@@ -19045,7 +19045,7 @@
         <v>32</v>
       </c>
       <c r="G644" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H644" t="n">
         <v>31552</v>
@@ -19132,7 +19132,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H647" t="n">
         <v>19011</v>
@@ -19161,7 +19161,7 @@
         <v>32</v>
       </c>
       <c r="G648" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H648" t="n">
         <v>10722</v>
@@ -19190,7 +19190,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H649" t="n">
         <v>12887</v>
@@ -19248,7 +19248,7 @@
         <v>32</v>
       </c>
       <c r="G651" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H651" t="n">
         <v>18834</v>
@@ -19306,7 +19306,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339683532715</v>
+        <v>27.6339664459229</v>
       </c>
       <c r="H653" t="n">
         <v>22878</v>
@@ -19335,7 +19335,7 @@
         <v>31.5</v>
       </c>
       <c r="G654" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H654" t="n">
         <v>70905</v>
@@ -19393,7 +19393,7 @@
         <v>33</v>
       </c>
       <c r="G656" t="n">
-        <v>29.8501129150391</v>
+        <v>29.8501148223877</v>
       </c>
       <c r="H656" t="n">
         <v>35738</v>
@@ -19422,7 +19422,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>29.6692028045654</v>
+        <v>29.6692008972168</v>
       </c>
       <c r="H657" t="n">
         <v>10389</v>
@@ -19451,7 +19451,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H658" t="n">
         <v>15664</v>
@@ -19480,7 +19480,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H659" t="n">
         <v>11969</v>
@@ -19509,7 +19509,7 @@
         <v>33</v>
       </c>
       <c r="G660" t="n">
-        <v>29.8501129150391</v>
+        <v>29.8501148223877</v>
       </c>
       <c r="H660" t="n">
         <v>20537</v>
@@ -19538,7 +19538,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H661" t="n">
         <v>16406</v>
@@ -19596,7 +19596,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214752197266</v>
+        <v>30.1214771270752</v>
       </c>
       <c r="H663" t="n">
         <v>13226</v>
@@ -19625,7 +19625,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H664" t="n">
         <v>12292</v>
@@ -19654,7 +19654,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H665" t="n">
         <v>5963</v>
@@ -19683,7 +19683,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260219573975</v>
+        <v>31.0260276794434</v>
       </c>
       <c r="H666" t="n">
         <v>41810</v>
@@ -19770,7 +19770,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H669" t="n">
         <v>27479</v>
@@ -19799,7 +19799,7 @@
         <v>33</v>
       </c>
       <c r="G670" t="n">
-        <v>29.8501129150391</v>
+        <v>29.8501148223877</v>
       </c>
       <c r="H670" t="n">
         <v>16306</v>
@@ -19886,7 +19886,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H673" t="n">
         <v>12485</v>
@@ -19973,7 +19973,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023853302002</v>
+        <v>30.3023872375488</v>
       </c>
       <c r="H676" t="n">
         <v>13444</v>
@@ -20002,7 +20002,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832992553711</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H677" t="n">
         <v>25987</v>
@@ -20060,7 +20060,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G679" t="n">
-        <v>29.7144298553467</v>
+        <v>29.714427947998</v>
       </c>
       <c r="H679" t="n">
         <v>10560</v>
@@ -20089,7 +20089,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H680" t="n">
         <v>18879</v>
@@ -20118,7 +20118,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H681" t="n">
         <v>24865</v>
@@ -20176,7 +20176,7 @@
         <v>32.25</v>
       </c>
       <c r="G683" t="n">
-        <v>29.1716995239258</v>
+        <v>29.1717014312744</v>
       </c>
       <c r="H683" t="n">
         <v>7419</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H687" t="n">
         <v>31220</v>
@@ -20321,7 +20321,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H688" t="n">
         <v>9866</v>
@@ -20350,7 +20350,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H689" t="n">
         <v>6251</v>
@@ -20379,7 +20379,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H690" t="n">
         <v>13325</v>
@@ -20408,7 +20408,7 @@
         <v>32</v>
       </c>
       <c r="G691" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H691" t="n">
         <v>11145</v>
@@ -20437,7 +20437,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H692" t="n">
         <v>20442</v>
@@ -20466,7 +20466,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123798370361</v>
+        <v>28.3123779296875</v>
       </c>
       <c r="H693" t="n">
         <v>18525</v>
@@ -20582,7 +20582,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>28.357608795166</v>
+        <v>28.3576068878174</v>
       </c>
       <c r="H697" t="n">
         <v>14113</v>
@@ -20611,7 +20611,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G698" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H698" t="n">
         <v>35920</v>
@@ -20669,7 +20669,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762519836426</v>
+        <v>30.0762500762939</v>
       </c>
       <c r="H700" t="n">
         <v>23460</v>
@@ -20698,7 +20698,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567115783691</v>
+        <v>32.1567077636719</v>
       </c>
       <c r="H701" t="n">
         <v>56088</v>
@@ -20727,7 +20727,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G702" t="n">
-        <v>29.7144298553467</v>
+        <v>29.714427947998</v>
       </c>
       <c r="H702" t="n">
         <v>60927</v>
@@ -20756,7 +20756,7 @@
         <v>33</v>
       </c>
       <c r="G703" t="n">
-        <v>29.8501129150391</v>
+        <v>29.8501148223877</v>
       </c>
       <c r="H703" t="n">
         <v>24157</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.719425201416</v>
+        <v>28.7194271087646</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20872,7 +20872,7 @@
         <v>31.5</v>
       </c>
       <c r="G707" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H707" t="n">
         <v>13065</v>
@@ -20930,7 +20930,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957885742188</v>
+        <v>27.9957866668701</v>
       </c>
       <c r="H709" t="n">
         <v>20930</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314716339111</v>
+        <v>28.1314697265625</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21017,7 +21017,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289710998535</v>
+        <v>28.6289691925049</v>
       </c>
       <c r="H712" t="n">
         <v>33341</v>
@@ -21046,7 +21046,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H713" t="n">
         <v>37089</v>
@@ -21075,7 +21075,7 @@
         <v>32.25</v>
       </c>
       <c r="G714" t="n">
-        <v>29.1716995239258</v>
+        <v>29.1717014312744</v>
       </c>
       <c r="H714" t="n">
         <v>28119</v>
@@ -21133,7 +21133,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H716" t="n">
         <v>30596</v>
@@ -21162,7 +21162,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119331359863</v>
+        <v>30.211935043335</v>
       </c>
       <c r="H717" t="n">
         <v>59213</v>
@@ -21191,7 +21191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073825836182</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H718" t="n">
         <v>15926</v>
@@ -21220,7 +21220,7 @@
         <v>32</v>
       </c>
       <c r="G719" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H719" t="n">
         <v>25143</v>
@@ -21249,7 +21249,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H720" t="n">
         <v>19906</v>
@@ -21278,7 +21278,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430656433105</v>
+        <v>29.4430637359619</v>
       </c>
       <c r="H721" t="n">
         <v>14502</v>
@@ -21307,7 +21307,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098812103271</v>
+        <v>28.8098831176758</v>
       </c>
       <c r="H722" t="n">
         <v>27650</v>
@@ -21336,7 +21336,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H723" t="n">
         <v>10352</v>
@@ -21365,7 +21365,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H724" t="n">
         <v>28121</v>
@@ -21394,7 +21394,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H725" t="n">
         <v>27078</v>
@@ -21423,7 +21423,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>29.9857978820801</v>
+        <v>29.9857940673828</v>
       </c>
       <c r="H726" t="n">
         <v>26161</v>
@@ -21452,7 +21452,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H727" t="n">
         <v>23140</v>
@@ -21539,7 +21539,7 @@
         <v>31.5</v>
       </c>
       <c r="G730" t="n">
-        <v>28.4932899475098</v>
+        <v>28.4932880401611</v>
       </c>
       <c r="H730" t="n">
         <v>19631</v>
@@ -21655,7 +21655,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H734" t="n">
         <v>19361</v>
@@ -21684,7 +21684,7 @@
         <v>32</v>
       </c>
       <c r="G735" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H735" t="n">
         <v>17587</v>
@@ -21713,7 +21713,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H736" t="n">
         <v>39696</v>
@@ -21742,7 +21742,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H737" t="n">
         <v>13524</v>
@@ -21771,7 +21771,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H738" t="n">
         <v>31102</v>
@@ -21800,7 +21800,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G739" t="n">
-        <v>29.4882926940918</v>
+        <v>29.4882907867432</v>
       </c>
       <c r="H739" t="n">
         <v>12783</v>
@@ -21829,7 +21829,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405670166016</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H740" t="n">
         <v>25796</v>
@@ -21858,7 +21858,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476123809814</v>
+        <v>30.3476142883301</v>
       </c>
       <c r="H741" t="n">
         <v>14572</v>
@@ -21945,7 +21945,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H744" t="n">
         <v>24053</v>
@@ -22003,7 +22003,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210304260254</v>
+        <v>32.0210342407227</v>
       </c>
       <c r="H746" t="n">
         <v>23768</v>
@@ -22032,7 +22032,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998867034912</v>
+        <v>30.7998905181885</v>
       </c>
       <c r="H747" t="n">
         <v>9633</v>
@@ -22061,7 +22061,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119331359863</v>
+        <v>30.211935043335</v>
       </c>
       <c r="H748" t="n">
         <v>18927</v>
@@ -22119,7 +22119,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832992553711</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H750" t="n">
         <v>5976</v>
@@ -22148,7 +22148,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.5737476348877</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H751" t="n">
         <v>7222</v>
@@ -22264,7 +22264,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H755" t="n">
         <v>11292</v>
@@ -22322,7 +22322,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164798736572</v>
       </c>
       <c r="H757" t="n">
         <v>15048</v>
@@ -22380,7 +22380,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>32.4733047485352</v>
+        <v>32.4733085632324</v>
       </c>
       <c r="H759" t="n">
         <v>32628</v>
@@ -22409,7 +22409,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H760" t="n">
         <v>38359</v>
@@ -22438,7 +22438,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H761" t="n">
         <v>16883</v>
@@ -22525,7 +22525,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853511810303</v>
+        <v>31.885347366333</v>
       </c>
       <c r="H764" t="n">
         <v>11653</v>
@@ -22612,7 +22612,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969413757324</v>
+        <v>33.1969451904297</v>
       </c>
       <c r="H767" t="n">
         <v>47582</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22670,7 +22670,7 @@
         <v>35.5</v>
       </c>
       <c r="G769" t="n">
-        <v>32.1114845275879</v>
+        <v>32.1114807128906</v>
       </c>
       <c r="H769" t="n">
         <v>44649</v>
@@ -22728,7 +22728,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330768585205</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H771" t="n">
         <v>8172</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.252161026001</v>
+        <v>31.2521667480469</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637626647949</v>
+        <v>32.5637550354004</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -22873,7 +22873,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H776" t="n">
         <v>6543</v>
@@ -22902,7 +22902,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H777" t="n">
         <v>22186</v>
@@ -22931,7 +22931,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.920581817627</v>
+        <v>33.9205856323242</v>
       </c>
       <c r="H778" t="n">
         <v>24835</v>
@@ -22960,7 +22960,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>33.4230804443359</v>
+        <v>33.4230842590332</v>
       </c>
       <c r="H779" t="n">
         <v>8669</v>
@@ -22989,7 +22989,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064834594727</v>
+        <v>33.1064872741699</v>
       </c>
       <c r="H780" t="n">
         <v>8743</v>
@@ -23018,7 +23018,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919479370117</v>
+        <v>34.1919441223145</v>
       </c>
       <c r="H781" t="n">
         <v>27307</v>
@@ -23047,7 +23047,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.8753547668457</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H782" t="n">
         <v>27238</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23134,7 +23134,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919479370117</v>
+        <v>34.1919441223145</v>
       </c>
       <c r="H785" t="n">
         <v>16126</v>
@@ -23163,7 +23163,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110359191895</v>
+        <v>34.0110321044922</v>
       </c>
       <c r="H786" t="n">
         <v>10605</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23221,7 +23221,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.8753547668457</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H788" t="n">
         <v>10901</v>
@@ -23366,7 +23366,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>34.101490020752</v>
+        <v>34.1014938354492</v>
       </c>
       <c r="H793" t="n">
         <v>25794</v>
@@ -23424,7 +23424,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H795" t="n">
         <v>28476</v>
@@ -23453,7 +23453,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H796" t="n">
         <v>22692</v>
@@ -23482,7 +23482,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035438537598</v>
+        <v>35.5035400390625</v>
       </c>
       <c r="H797" t="n">
         <v>15860</v>
@@ -23569,7 +23569,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H800" t="n">
         <v>24431</v>
@@ -23598,7 +23598,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>36.4533233642578</v>
+        <v>36.4533195495605</v>
       </c>
       <c r="H801" t="n">
         <v>40738</v>
@@ -23743,7 +23743,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.4080963134766</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H806" t="n">
         <v>19091</v>
@@ -23772,7 +23772,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H807" t="n">
         <v>30091</v>
@@ -23888,7 +23888,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G811" t="n">
-        <v>36.4533233642578</v>
+        <v>36.4533195495605</v>
       </c>
       <c r="H811" t="n">
         <v>24654</v>
@@ -23917,7 +23917,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G812" t="n">
-        <v>36.7699089050293</v>
+        <v>36.7699127197266</v>
       </c>
       <c r="H812" t="n">
         <v>15630</v>
@@ -24033,7 +24033,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.724681854248</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H816" t="n">
         <v>28980</v>
@@ -24062,7 +24062,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.9055938720703</v>
+        <v>36.905590057373</v>
       </c>
       <c r="H817" t="n">
         <v>29508</v>
@@ -24120,7 +24120,7 @@
         <v>41.25</v>
       </c>
       <c r="G819" t="n">
-        <v>37.3126411437988</v>
+        <v>37.3126373291016</v>
       </c>
       <c r="H819" t="n">
         <v>39954</v>
@@ -24207,7 +24207,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3980979919434</v>
+        <v>38.3981018066406</v>
       </c>
       <c r="H822" t="n">
         <v>31744</v>
@@ -24236,7 +24236,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8955993652344</v>
+        <v>38.8956031799316</v>
       </c>
       <c r="H823" t="n">
         <v>45948</v>
@@ -24294,7 +24294,7 @@
         <v>43.5499992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>39.3931045532227</v>
+        <v>39.3931007385254</v>
       </c>
       <c r="H825" t="n">
         <v>40999</v>
@@ -24323,7 +24323,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860572814941</v>
+        <v>38.9860534667969</v>
       </c>
       <c r="H826" t="n">
         <v>26184</v>
@@ -24526,7 +24526,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649154663086</v>
+        <v>37.7649116516113</v>
       </c>
       <c r="H833" t="n">
         <v>30771</v>
@@ -24555,7 +24555,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9005966186523</v>
+        <v>37.9006004333496</v>
       </c>
       <c r="H834" t="n">
         <v>57165</v>
@@ -24700,7 +24700,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367301940918</v>
+        <v>36.1367263793945</v>
       </c>
       <c r="H839" t="n">
         <v>32321</v>
@@ -24729,7 +24729,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.8653678894043</v>
+        <v>35.8653602600098</v>
       </c>
       <c r="H840" t="n">
         <v>24851</v>
@@ -24787,7 +24787,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G842" t="n">
-        <v>36.2724113464355</v>
+        <v>36.2724075317383</v>
       </c>
       <c r="H842" t="n">
         <v>29267</v>
@@ -24816,7 +24816,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.8653678894043</v>
+        <v>35.8653602600098</v>
       </c>
       <c r="H843" t="n">
         <v>30983</v>
@@ -24874,7 +24874,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.4080963134766</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H845" t="n">
         <v>19073</v>
@@ -24932,7 +24932,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342239379883</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H847" t="n">
         <v>16900</v>
@@ -24961,7 +24961,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.9105911254883</v>
+        <v>35.910587310791</v>
       </c>
       <c r="H848" t="n">
         <v>26054</v>
@@ -25019,7 +25019,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.724681854248</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H850" t="n">
         <v>32977</v>
@@ -25077,7 +25077,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101387023926</v>
+        <v>37.8101425170898</v>
       </c>
       <c r="H852" t="n">
         <v>12442</v>
@@ -25280,7 +25280,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342239379883</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H859" t="n">
         <v>12270</v>
@@ -25338,7 +25338,7 @@
         <v>40.25</v>
       </c>
       <c r="G861" t="n">
-        <v>36.4080963134766</v>
+        <v>36.4080924987793</v>
       </c>
       <c r="H861" t="n">
         <v>8194</v>
@@ -25367,7 +25367,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G862" t="n">
-        <v>36.7699089050293</v>
+        <v>36.7699127197266</v>
       </c>
       <c r="H862" t="n">
         <v>14424</v>
@@ -25541,7 +25541,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H868" t="n">
         <v>14461</v>
@@ -25744,7 +25744,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>36.4113121032715</v>
+        <v>36.4113159179688</v>
       </c>
       <c r="H875" t="n">
         <v>10487</v>
@@ -25773,7 +25773,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H876" t="n">
         <v>14179</v>
@@ -25802,7 +25802,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>36.7331314086914</v>
+        <v>36.7331352233887</v>
       </c>
       <c r="H877" t="n">
         <v>15633</v>
@@ -26005,7 +26005,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>34.1585998535156</v>
+        <v>34.1585960388184</v>
       </c>
       <c r="H884" t="n">
         <v>74828</v>
@@ -26063,7 +26063,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.2159957885742</v>
+        <v>35.215991973877</v>
       </c>
       <c r="H886" t="n">
         <v>9003</v>
@@ -26121,7 +26121,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>34.1585998535156</v>
+        <v>34.1585960388184</v>
       </c>
       <c r="H888" t="n">
         <v>18290</v>
@@ -26179,7 +26179,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H890" t="n">
         <v>21938</v>
@@ -26208,7 +26208,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>34.664306640625</v>
+        <v>34.6643104553223</v>
       </c>
       <c r="H891" t="n">
         <v>21890</v>
@@ -26469,7 +26469,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H900" t="n">
         <v>16294</v>
@@ -26498,7 +26498,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H901" t="n">
         <v>13534</v>
@@ -26556,7 +26556,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G903" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H903" t="n">
         <v>13508</v>
@@ -26701,7 +26701,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G908" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H908" t="n">
         <v>19888</v>
@@ -26788,7 +26788,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H911" t="n">
         <v>9666</v>
@@ -26817,7 +26817,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H912" t="n">
         <v>17366</v>
@@ -26875,7 +26875,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G914" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H914" t="n">
         <v>24076</v>
@@ -26904,7 +26904,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>33.9747009277344</v>
+        <v>33.9747047424316</v>
       </c>
       <c r="H915" t="n">
         <v>25831</v>
@@ -27020,7 +27020,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310699462891</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H919" t="n">
         <v>14186</v>
@@ -27078,7 +27078,7 @@
         <v>35</v>
       </c>
       <c r="G921" t="n">
-        <v>32.1817169189453</v>
+        <v>32.1817207336426</v>
       </c>
       <c r="H921" t="n">
         <v>25157</v>
@@ -27107,7 +27107,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>32.089771270752</v>
+        <v>32.0897750854492</v>
       </c>
       <c r="H922" t="n">
         <v>9260</v>
@@ -27136,7 +27136,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>31.9978218078613</v>
+        <v>31.9978256225586</v>
       </c>
       <c r="H923" t="n">
         <v>23180</v>
@@ -27223,7 +27223,7 @@
         <v>35</v>
       </c>
       <c r="G926" t="n">
-        <v>32.1817169189453</v>
+        <v>32.1817207336426</v>
       </c>
       <c r="H926" t="n">
         <v>18401</v>
@@ -27252,7 +27252,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575653076172</v>
+        <v>32.4575576782227</v>
       </c>
       <c r="H927" t="n">
         <v>15137</v>
@@ -27339,7 +27339,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689865112305</v>
+        <v>33.4689903259277</v>
       </c>
       <c r="H930" t="n">
         <v>54293</v>
@@ -27368,7 +27368,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>34.664306640625</v>
+        <v>34.6643104553223</v>
       </c>
       <c r="H931" t="n">
         <v>102214</v>
@@ -27977,7 +27977,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H952" t="n">
         <v>8028</v>
@@ -28093,7 +28093,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448348999023</v>
+        <v>33.7448272705078</v>
       </c>
       <c r="H956" t="n">
         <v>7086</v>
@@ -28238,7 +28238,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>32.5954818725586</v>
+        <v>32.5954856872559</v>
       </c>
       <c r="H961" t="n">
         <v>21271</v>
@@ -28267,7 +28267,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H962" t="n">
         <v>19440</v>
@@ -28296,7 +28296,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.503532409668</v>
+        <v>32.5035362243652</v>
       </c>
       <c r="H963" t="n">
         <v>11379</v>
@@ -28383,7 +28383,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380821228027</v>
+        <v>31.5380840301514</v>
       </c>
       <c r="H966" t="n">
         <v>27835</v>
@@ -28412,7 +28412,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656158447266</v>
+        <v>32.3656120300293</v>
       </c>
       <c r="H967" t="n">
         <v>23454</v>
@@ -28586,7 +28586,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>32.5954818725586</v>
+        <v>32.5954856872559</v>
       </c>
       <c r="H973" t="n">
         <v>25464</v>
@@ -28673,7 +28673,7 @@
         <v>35.75</v>
       </c>
       <c r="G976" t="n">
-        <v>32.8713302612305</v>
+        <v>32.8713264465332</v>
       </c>
       <c r="H976" t="n">
         <v>23421</v>
@@ -28789,7 +28789,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310699462891</v>
+        <v>33.3310623168945</v>
       </c>
       <c r="H980" t="n">
         <v>18596</v>
@@ -29021,7 +29021,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>30.7565288543701</v>
+        <v>30.7565269470215</v>
       </c>
       <c r="H988" t="n">
         <v>19829</v>
@@ -29050,7 +29050,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347095489502</v>
+        <v>30.4347076416016</v>
       </c>
       <c r="H989" t="n">
         <v>20300</v>
@@ -29079,7 +29079,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541889190674</v>
+        <v>31.3541870117188</v>
       </c>
       <c r="H990" t="n">
         <v>16205</v>
@@ -29137,7 +29137,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G992" t="n">
-        <v>30.8944492340088</v>
+        <v>30.8944473266602</v>
       </c>
       <c r="H992" t="n">
         <v>20906</v>
@@ -29253,7 +29253,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>33.8827476501465</v>
+        <v>33.8827514648438</v>
       </c>
       <c r="H996" t="n">
         <v>15814</v>
@@ -29282,7 +29282,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>34.1585998535156</v>
+        <v>34.1585960388184</v>
       </c>
       <c r="H997" t="n">
         <v>21195</v>
@@ -29398,7 +29398,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1001" t="n">
         <v>38594</v>
@@ -29456,7 +29456,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>36.4113121032715</v>
+        <v>36.4113159179688</v>
       </c>
       <c r="H1003" t="n">
         <v>52594</v>
@@ -29630,7 +29630,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1009" t="n">
         <v>15324</v>
@@ -29659,7 +29659,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1010" t="n">
         <v>9446</v>
@@ -29717,7 +29717,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539161682129</v>
+        <v>35.3539199829102</v>
       </c>
       <c r="H1012" t="n">
         <v>19550</v>
@@ -29775,7 +29775,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H1014" t="n">
         <v>42877</v>
@@ -29891,7 +29891,7 @@
         <v>40.75</v>
       </c>
       <c r="G1018" t="n">
-        <v>37.4687194824219</v>
+        <v>37.4687156677246</v>
       </c>
       <c r="H1018" t="n">
         <v>22790</v>
@@ -30123,7 +30123,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>39.2157211303711</v>
+        <v>39.2157249450684</v>
       </c>
       <c r="H1026" t="n">
         <v>24452</v>
@@ -30239,7 +30239,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>39.353645324707</v>
+        <v>39.3536415100098</v>
       </c>
       <c r="H1030" t="n">
         <v>43234</v>
@@ -30326,7 +30326,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1033" t="n">
         <v>17293</v>
@@ -30442,7 +30442,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985816955566</v>
+        <v>37.6985855102539</v>
       </c>
       <c r="H1037" t="n">
         <v>16755</v>
@@ -30471,7 +30471,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1038" t="n">
         <v>24399</v>
@@ -30500,7 +30500,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1039" t="n">
         <v>35974</v>
@@ -30529,7 +30529,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1040" t="n">
         <v>10126</v>
@@ -30558,7 +30558,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>38.2042961120605</v>
+        <v>38.2042922973633</v>
       </c>
       <c r="H1041" t="n">
         <v>13783</v>
@@ -30587,7 +30587,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>39.2157211303711</v>
+        <v>39.2157249450684</v>
       </c>
       <c r="H1042" t="n">
         <v>29619</v>
@@ -30616,7 +30616,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>38.8939056396484</v>
+        <v>38.8939018249512</v>
       </c>
       <c r="H1043" t="n">
         <v>12351</v>
@@ -30819,7 +30819,7 @@
         <v>43.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>39.7674102783203</v>
+        <v>39.767406463623</v>
       </c>
       <c r="H1050" t="n">
         <v>27149</v>
@@ -30906,7 +30906,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>40.2731246948242</v>
+        <v>40.273120880127</v>
       </c>
       <c r="H1053" t="n">
         <v>15184</v>
@@ -30935,7 +30935,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>40.6409149169922</v>
+        <v>40.6409111022949</v>
       </c>
       <c r="H1054" t="n">
         <v>19707</v>
@@ -31051,7 +31051,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1058" t="n">
         <v>26015</v>
@@ -31109,7 +31109,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>38.8939056396484</v>
+        <v>38.8939018249512</v>
       </c>
       <c r="H1060" t="n">
         <v>30816</v>
@@ -31138,7 +31138,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>40.4110412597656</v>
+        <v>40.4110450744629</v>
       </c>
       <c r="H1061" t="n">
         <v>51174</v>
@@ -31167,7 +31167,7 @@
         <v>43.25</v>
       </c>
       <c r="G1062" t="n">
-        <v>39.7674102783203</v>
+        <v>39.767406463623</v>
       </c>
       <c r="H1062" t="n">
         <v>107008</v>
@@ -31254,7 +31254,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442893981934</v>
+        <v>41.7442855834961</v>
       </c>
       <c r="H1065" t="n">
         <v>58297</v>
@@ -31283,7 +31283,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>40.5489616394043</v>
+        <v>40.5489654541016</v>
       </c>
       <c r="H1066" t="n">
         <v>41750</v>
@@ -31457,7 +31457,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1072" t="n">
         <v>20307</v>
@@ -31544,7 +31544,7 @@
         <v>41.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>37.9284515380859</v>
+        <v>37.9284553527832</v>
       </c>
       <c r="H1075" t="n">
         <v>19218</v>
@@ -31689,7 +31689,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985816955566</v>
+        <v>37.6985855102539</v>
       </c>
       <c r="H1080" t="n">
         <v>21026</v>
@@ -31834,7 +31834,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422164916992</v>
+        <v>38.3422203063965</v>
       </c>
       <c r="H1085" t="n">
         <v>44926</v>
@@ -32037,7 +32037,7 @@
         <v>40.75</v>
       </c>
       <c r="G1092" t="n">
-        <v>37.4687194824219</v>
+        <v>37.4687156677246</v>
       </c>
       <c r="H1092" t="n">
         <v>28651</v>
@@ -32095,7 +32095,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824844360352</v>
+        <v>37.8824768066406</v>
       </c>
       <c r="H1094" t="n">
         <v>23661</v>
@@ -32124,7 +32124,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1095" t="n">
         <v>27027</v>
@@ -32211,7 +32211,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398803710938</v>
+        <v>38.9398765563965</v>
       </c>
       <c r="H1098" t="n">
         <v>26751</v>
@@ -32240,7 +32240,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019561767578</v>
+        <v>38.8019599914551</v>
       </c>
       <c r="H1099" t="n">
         <v>14005</v>
@@ -32414,7 +32414,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.59521484375</v>
+        <v>36.5952072143555</v>
       </c>
       <c r="H1105" t="n">
         <v>26729</v>
@@ -32501,7 +32501,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1108" t="n">
-        <v>36.4113121032715</v>
+        <v>36.4113159179688</v>
       </c>
       <c r="H1108" t="n">
         <v>21226</v>
@@ -32530,7 +32530,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733917236328</v>
+        <v>36.2733955383301</v>
       </c>
       <c r="H1109" t="n">
         <v>25222</v>
@@ -32559,7 +32559,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1110" t="n">
-        <v>35.7217102050781</v>
+        <v>35.7217063903809</v>
       </c>
       <c r="H1110" t="n">
         <v>18379</v>
@@ -32588,7 +32588,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.7217102050781</v>
+        <v>35.7217063903809</v>
       </c>
       <c r="H1111" t="n">
         <v>13856</v>
@@ -32733,7 +32733,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720863342285</v>
+        <v>38.5720901489258</v>
       </c>
       <c r="H1116" t="n">
         <v>18589</v>
@@ -32791,7 +32791,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>38.2042961120605</v>
+        <v>38.2042922973633</v>
       </c>
       <c r="H1118" t="n">
         <v>11676</v>
@@ -32907,7 +32907,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858589172363</v>
+        <v>38.9858551025391</v>
       </c>
       <c r="H1122" t="n">
         <v>13057</v>
@@ -32965,7 +32965,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>39.9053344726562</v>
+        <v>39.905330657959</v>
       </c>
       <c r="H1124" t="n">
         <v>29851</v>
@@ -32994,7 +32994,7 @@
         <v>44.4500007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>40.8707809448242</v>
+        <v>40.8707847595215</v>
       </c>
       <c r="H1125" t="n">
         <v>59380</v>
@@ -33023,7 +33023,7 @@
         <v>45.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>42.0661010742188</v>
+        <v>42.066104888916</v>
       </c>
       <c r="H1126" t="n">
         <v>38246</v>
@@ -33110,7 +33110,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422164916992</v>
+        <v>38.3422203063965</v>
       </c>
       <c r="H1129" t="n">
         <v>76007</v>
@@ -51009,6 +51009,35 @@
         <v>15728</v>
       </c>
       <c r="I1746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1747" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>34.2999992370605</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>35.5400009155273</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>34.2999992370605</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>35.1199989318848</v>
+      </c>
+      <c r="G1747" t="n">
+        <v>35.1199989318848</v>
+      </c>
+      <c r="H1747" t="n">
+        <v>23447</v>
+      </c>
+      <c r="I1747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025457382202</v>
+        <v>13.6025466918945</v>
       </c>
       <c r="H2" t="n">
         <v>487001</v>
@@ -456,7 +456,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4168815612793</v>
+        <v>13.416880607605</v>
       </c>
       <c r="H3" t="n">
         <v>251735</v>
@@ -514,7 +514,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479257583618</v>
+        <v>13.7479248046875</v>
       </c>
       <c r="H5" t="n">
         <v>18109</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934637069702</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -688,7 +688,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390064239502</v>
+        <v>13.8390054702759</v>
       </c>
       <c r="H11" t="n">
         <v>10789</v>
@@ -717,7 +717,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896383285522</v>
+        <v>13.9896392822266</v>
       </c>
       <c r="H12" t="n">
         <v>10618</v>
@@ -746,7 +746,7 @@
         <v>15.9139995574951</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9370908737183</v>
+        <v>13.9370918273926</v>
       </c>
       <c r="H13" t="n">
         <v>8422</v>
@@ -833,7 +833,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073143005371</v>
+        <v>13.9073162078857</v>
       </c>
       <c r="H16" t="n">
         <v>30923</v>
@@ -891,7 +891,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G18" t="n">
-        <v>13.942346572876</v>
+        <v>13.9423456192017</v>
       </c>
       <c r="H18" t="n">
         <v>74522</v>
@@ -920,7 +920,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H19" t="n">
         <v>69364</v>
@@ -978,7 +978,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963195800781</v>
+        <v>14.1963214874268</v>
       </c>
       <c r="H21" t="n">
         <v>76030</v>
@@ -1036,7 +1036,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692390441895</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H23" t="n">
         <v>297347</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071281433105</v>
+        <v>15.1071271896362</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1094,7 +1094,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260736465454</v>
+        <v>15.3260726928711</v>
       </c>
       <c r="H25" t="n">
         <v>73618</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.88818359375</v>
+        <v>14.8881816864014</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1152,7 +1152,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463073730469</v>
+        <v>14.7463083267212</v>
       </c>
       <c r="H27" t="n">
         <v>68742</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757604598999</v>
+        <v>14.9757623672485</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1268,7 +1268,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G31" t="n">
-        <v>14.5203590393066</v>
+        <v>14.520357131958</v>
       </c>
       <c r="H31" t="n">
         <v>43925</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.88818359375</v>
+        <v>14.8881816864014</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.88818359375</v>
+        <v>14.8881816864014</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1500,7 +1500,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H39" t="n">
         <v>17569</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609676361084</v>
+        <v>14.3609666824341</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1558,7 +1558,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>14.6604833602905</v>
+        <v>14.6604824066162</v>
       </c>
       <c r="H41" t="n">
         <v>29941</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006057739258</v>
+        <v>14.8006048202515</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1645,7 +1645,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692390441895</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H44" t="n">
         <v>35731</v>
@@ -1674,7 +1674,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655763626099</v>
+        <v>14.7655754089355</v>
       </c>
       <c r="H45" t="n">
         <v>31415</v>
@@ -1703,7 +1703,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6236991882324</v>
+        <v>14.6237001419067</v>
       </c>
       <c r="H46" t="n">
         <v>33733</v>
@@ -1732,7 +1732,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708301544189</v>
+        <v>14.7708282470703</v>
       </c>
       <c r="H47" t="n">
         <v>59163</v>
@@ -1761,7 +1761,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633392333984</v>
+        <v>15.0633401870728</v>
       </c>
       <c r="H48" t="n">
         <v>87381</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.136905670166</v>
+        <v>15.1369037628174</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1848,7 +1848,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.2698879241943</v>
+        <v>14.26988697052</v>
       </c>
       <c r="H51" t="n">
         <v>29049</v>
@@ -1906,7 +1906,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089073181152</v>
+        <v>14.0089063644409</v>
       </c>
       <c r="H53" t="n">
         <v>23213</v>
@@ -1964,7 +1964,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H55" t="n">
         <v>37252</v>
@@ -1993,7 +1993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H56" t="n">
         <v>23379</v>
@@ -2022,7 +2022,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987457275391</v>
+        <v>12.6987447738647</v>
       </c>
       <c r="H57" t="n">
         <v>15626</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111669540405</v>
+        <v>12.6111660003662</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320261001587</v>
+        <v>12.7320251464844</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2167,7 +2167,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602369308472</v>
+        <v>11.5602378845215</v>
       </c>
       <c r="H62" t="n">
         <v>43479</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.071418762207</v>
+        <v>10.0714197158813</v>
       </c>
       <c r="H63" t="n">
         <v>21708</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806655883789</v>
+        <v>9.10806465148926</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2428,7 +2428,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651477813721</v>
+        <v>8.76651287078857</v>
       </c>
       <c r="H71" t="n">
         <v>44594</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494190216064</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2689,7 +2689,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921142578125</v>
+        <v>10.2921133041382</v>
       </c>
       <c r="H80" t="n">
         <v>20417</v>
@@ -2747,7 +2747,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070697784424</v>
+        <v>10.8070707321167</v>
       </c>
       <c r="H82" t="n">
         <v>3945</v>
@@ -2776,7 +2776,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156656265259</v>
+        <v>10.9156665802002</v>
       </c>
       <c r="H83" t="n">
         <v>6741</v>
@@ -2950,7 +2950,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898508071899</v>
+        <v>11.6898517608643</v>
       </c>
       <c r="H89" t="n">
         <v>19363</v>
@@ -2979,7 +2979,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068817138672</v>
+        <v>12.0068826675415</v>
       </c>
       <c r="H90" t="n">
         <v>11410</v>
@@ -3037,7 +3037,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G92" t="n">
-        <v>11.3325366973877</v>
+        <v>11.3325357437134</v>
       </c>
       <c r="H92" t="n">
         <v>25713</v>
@@ -3095,7 +3095,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331827163696</v>
+        <v>10.9331817626953</v>
       </c>
       <c r="H94" t="n">
         <v>46331</v>
@@ -3124,7 +3124,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471940994263</v>
+        <v>10.9471950531006</v>
       </c>
       <c r="H95" t="n">
         <v>49105</v>
@@ -3153,7 +3153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6144008636475</v>
+        <v>10.6143989562988</v>
       </c>
       <c r="H96" t="n">
         <v>30171</v>
@@ -3182,7 +3182,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655179977417</v>
+        <v>10.465518951416</v>
       </c>
       <c r="H97" t="n">
         <v>30855</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465734481812</v>
+        <v>10.2465744018555</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3414,7 +3414,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.381443977356</v>
+        <v>10.3814430236816</v>
       </c>
       <c r="H105" t="n">
         <v>19187</v>
@@ -3443,7 +3443,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093059539795</v>
+        <v>10.5093069076538</v>
       </c>
       <c r="H106" t="n">
         <v>15170</v>
@@ -3501,7 +3501,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220262527466</v>
+        <v>11.3220272064209</v>
       </c>
       <c r="H108" t="n">
         <v>36330</v>
@@ -3530,7 +3530,7 @@
         <v>13.0120000839233</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3955917358398</v>
+        <v>11.3955907821655</v>
       </c>
       <c r="H109" t="n">
         <v>18584</v>
@@ -3559,7 +3559,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726600646973</v>
+        <v>11.4726610183716</v>
       </c>
       <c r="H110" t="n">
         <v>21522</v>
@@ -3588,7 +3588,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>11.6565713882446</v>
+        <v>11.6565723419189</v>
       </c>
       <c r="H111" t="n">
         <v>27521</v>
@@ -3646,7 +3646,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119756698608</v>
+        <v>12.1119766235352</v>
       </c>
       <c r="H113" t="n">
         <v>32594</v>
@@ -3704,7 +3704,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727945327759</v>
+        <v>12.4727954864502</v>
       </c>
       <c r="H115" t="n">
         <v>41546</v>
@@ -3733,7 +3733,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506706237793</v>
+        <v>12.0506725311279</v>
       </c>
       <c r="H116" t="n">
         <v>330572</v>
@@ -3762,7 +3762,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258272171021</v>
+        <v>12.2258262634277</v>
       </c>
       <c r="H117" t="n">
         <v>24996</v>
@@ -3791,7 +3791,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922243118286</v>
+        <v>12.3922233581543</v>
       </c>
       <c r="H118" t="n">
         <v>16297</v>
@@ -3820,7 +3820,7 @@
         <v>13.9540004730225</v>
       </c>
       <c r="G119" t="n">
-        <v>12.2205715179443</v>
+        <v>12.2205724716187</v>
       </c>
       <c r="H119" t="n">
         <v>70567</v>
@@ -3878,7 +3878,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.760048866272</v>
+        <v>12.7600498199463</v>
       </c>
       <c r="H121" t="n">
         <v>53970</v>
@@ -3936,7 +3936,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.3100366592407</v>
+        <v>13.3100357055664</v>
       </c>
       <c r="H123" t="n">
         <v>25697</v>
@@ -3965,7 +3965,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930057525635</v>
+        <v>12.9930067062378</v>
       </c>
       <c r="H124" t="n">
         <v>20213</v>
@@ -4052,7 +4052,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H127" t="n">
         <v>96046</v>
@@ -4081,7 +4081,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H128" t="n">
         <v>20883</v>
@@ -4139,7 +4139,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976154327393</v>
+        <v>13.3976135253906</v>
       </c>
       <c r="H130" t="n">
         <v>7245</v>
@@ -4168,7 +4168,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361486434937</v>
+        <v>13.4361476898193</v>
       </c>
       <c r="H131" t="n">
         <v>17251</v>
@@ -4197,7 +4197,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>13.3030309677124</v>
+        <v>13.3030300140381</v>
       </c>
       <c r="H132" t="n">
         <v>11780</v>
@@ -4226,7 +4226,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.527229309082</v>
+        <v>13.5272283554077</v>
       </c>
       <c r="H133" t="n">
         <v>18810</v>
@@ -4255,7 +4255,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H134" t="n">
         <v>10358</v>
@@ -4284,7 +4284,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>13.2679996490479</v>
+        <v>13.2679986953735</v>
       </c>
       <c r="H135" t="n">
         <v>4036</v>
@@ -4313,7 +4313,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H136" t="n">
         <v>7773</v>
@@ -4342,7 +4342,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H137" t="n">
         <v>5525</v>
@@ -4400,7 +4400,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805826187134</v>
+        <v>13.0805835723877</v>
       </c>
       <c r="H139" t="n">
         <v>13088</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H140" t="n">
         <v>6887</v>
@@ -4458,7 +4458,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606704711914</v>
+        <v>13.4606695175171</v>
       </c>
       <c r="H141" t="n">
         <v>4654</v>
@@ -4516,7 +4516,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979370117188</v>
+        <v>13.1979360580444</v>
       </c>
       <c r="H143" t="n">
         <v>3314</v>
@@ -4574,7 +4574,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490560531616</v>
+        <v>13.0490550994873</v>
       </c>
       <c r="H145" t="n">
         <v>1877</v>
@@ -4603,7 +4603,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772424697876</v>
+        <v>12.9772415161133</v>
       </c>
       <c r="H146" t="n">
         <v>4221</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504844665527</v>
+        <v>13.2504835128784</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4661,7 +4661,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821727752686</v>
+        <v>13.1821737289429</v>
       </c>
       <c r="H148" t="n">
         <v>863</v>
@@ -4690,7 +4690,7 @@
         <v>15.0019998550415</v>
       </c>
       <c r="G149" t="n">
-        <v>13.1383848190308</v>
+        <v>13.1383838653564</v>
       </c>
       <c r="H149" t="n">
         <v>7310</v>
@@ -4719,7 +4719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H150" t="n">
         <v>1530</v>
@@ -4748,7 +4748,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606704711914</v>
+        <v>13.4606695175171</v>
       </c>
       <c r="H151" t="n">
         <v>14307</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6621007919312</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4806,7 +4806,7 @@
         <v>15.4519996643066</v>
       </c>
       <c r="G153" t="n">
-        <v>13.5324821472168</v>
+        <v>13.5324831008911</v>
       </c>
       <c r="H153" t="n">
         <v>9502</v>
@@ -4864,7 +4864,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.469428062439</v>
+        <v>13.4694290161133</v>
       </c>
       <c r="H155" t="n">
         <v>2209</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277135848999</v>
+        <v>13.2277145385742</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4922,7 +4922,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555765151978</v>
+        <v>13.3555774688721</v>
       </c>
       <c r="H157" t="n">
         <v>9479</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348810195923</v>
+        <v>13.1348829269409</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -4980,7 +4980,7 @@
         <v>14.9379997253418</v>
       </c>
       <c r="G159" t="n">
-        <v>13.0823354721069</v>
+        <v>13.0823345184326</v>
       </c>
       <c r="H159" t="n">
         <v>22453</v>
@@ -5009,7 +5009,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987457275391</v>
+        <v>12.6987447738647</v>
       </c>
       <c r="H160" t="n">
         <v>8710</v>
@@ -5038,7 +5038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H161" t="n">
         <v>8576</v>
@@ -5125,7 +5125,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393533706665</v>
+        <v>12.5393543243408</v>
       </c>
       <c r="H164" t="n">
         <v>30378</v>
@@ -5154,7 +5154,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094169616699</v>
+        <v>12.6094160079956</v>
       </c>
       <c r="H165" t="n">
         <v>15675</v>
@@ -5212,7 +5212,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H167" t="n">
         <v>9897</v>
@@ -5241,7 +5241,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097394943237</v>
+        <v>12.409740447998</v>
       </c>
       <c r="H168" t="n">
         <v>11733</v>
@@ -5299,7 +5299,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909322738647</v>
+        <v>13.1909313201904</v>
       </c>
       <c r="H170" t="n">
         <v>36613</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H171" t="n">
         <v>7984</v>
@@ -5357,7 +5357,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132160186768</v>
+        <v>13.5132179260254</v>
       </c>
       <c r="H172" t="n">
         <v>10655</v>
@@ -5415,7 +5415,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G174" t="n">
-        <v>13.653341293335</v>
+        <v>13.6533403396606</v>
       </c>
       <c r="H174" t="n">
         <v>7527</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6621007919312</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5473,7 +5473,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>13.2679996490479</v>
+        <v>13.2679986953735</v>
       </c>
       <c r="H176" t="n">
         <v>5800</v>
@@ -5502,7 +5502,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H177" t="n">
         <v>16366</v>
@@ -5531,7 +5531,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H178" t="n">
         <v>14964</v>
@@ -5560,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="G179" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H179" t="n">
         <v>13803</v>
@@ -5589,7 +5589,7 @@
         <v>16</v>
       </c>
       <c r="G180" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H180" t="n">
         <v>13692</v>
@@ -5618,7 +5618,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493541717529</v>
+        <v>13.9493532180786</v>
       </c>
       <c r="H181" t="n">
         <v>30984</v>
@@ -5647,7 +5647,7 @@
         <v>16</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H182" t="n">
         <v>15865</v>
@@ -5676,7 +5676,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G183" t="n">
-        <v>13.7847061157227</v>
+        <v>13.784707069397</v>
       </c>
       <c r="H183" t="n">
         <v>22904</v>
@@ -5705,7 +5705,7 @@
         <v>16</v>
       </c>
       <c r="G184" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H184" t="n">
         <v>25117</v>
@@ -5763,7 +5763,7 @@
         <v>16</v>
       </c>
       <c r="G186" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H186" t="n">
         <v>9698</v>
@@ -5792,7 +5792,7 @@
         <v>16</v>
       </c>
       <c r="G187" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H187" t="n">
         <v>24640</v>
@@ -5821,7 +5821,7 @@
         <v>16</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H188" t="n">
         <v>35173</v>
@@ -5850,7 +5850,7 @@
         <v>16</v>
       </c>
       <c r="G189" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H189" t="n">
         <v>28944</v>
@@ -5995,7 +5995,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G194" t="n">
-        <v>13.6971292495728</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H194" t="n">
         <v>8929</v>
@@ -6169,7 +6169,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767581939697</v>
+        <v>13.2767562866211</v>
       </c>
       <c r="H200" t="n">
         <v>6789</v>
@@ -6227,7 +6227,7 @@
         <v>16</v>
       </c>
       <c r="G202" t="n">
-        <v>14.0124092102051</v>
+        <v>14.0124082565308</v>
       </c>
       <c r="H202" t="n">
         <v>32085</v>
@@ -6256,7 +6256,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.3101739883423</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H203" t="n">
         <v>21909</v>
@@ -6372,7 +6372,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H207" t="n">
         <v>18020</v>
@@ -6401,7 +6401,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G208" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H208" t="n">
         <v>11562</v>
@@ -6459,7 +6459,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502983093262</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H210" t="n">
         <v>16575</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502983093262</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H212" t="n">
         <v>5728</v>
@@ -6546,7 +6546,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H213" t="n">
         <v>3813</v>
@@ -6575,7 +6575,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955156326294</v>
+        <v>14.6955137252808</v>
       </c>
       <c r="H214" t="n">
         <v>13259</v>
@@ -6604,7 +6604,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H215" t="n">
         <v>13883</v>
@@ -6633,7 +6633,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452024459839</v>
+        <v>14.3452014923096</v>
       </c>
       <c r="H216" t="n">
         <v>9351</v>
@@ -6691,7 +6691,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>14.0474395751953</v>
+        <v>14.0474405288696</v>
       </c>
       <c r="H218" t="n">
         <v>5034</v>
@@ -6749,7 +6749,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H220" t="n">
         <v>11900</v>
@@ -6807,7 +6807,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H222" t="n">
         <v>6474</v>
@@ -6836,7 +6836,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H223" t="n">
         <v>17777</v>
@@ -6865,7 +6865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.3117876052856</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H224" t="n">
         <v>45360</v>
@@ -6894,7 +6894,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592430114746</v>
+        <v>13.2592420578003</v>
       </c>
       <c r="H225" t="n">
         <v>9073</v>
@@ -6923,7 +6923,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.3117876052856</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H226" t="n">
         <v>5423</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7039,7 +7039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H230" t="n">
         <v>2511</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6621007919312</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7097,7 +7097,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G232" t="n">
-        <v>13.7847061157227</v>
+        <v>13.784707069397</v>
       </c>
       <c r="H232" t="n">
         <v>19127</v>
@@ -7126,7 +7126,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H233" t="n">
         <v>26206</v>
@@ -7155,7 +7155,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H234" t="n">
         <v>16461</v>
@@ -7184,7 +7184,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H235" t="n">
         <v>16963</v>
@@ -7213,7 +7213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H236" t="n">
         <v>8277</v>
@@ -7242,7 +7242,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H237" t="n">
         <v>17203</v>
@@ -7271,7 +7271,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H238" t="n">
         <v>12067</v>
@@ -7329,7 +7329,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H240" t="n">
         <v>23600</v>
@@ -7358,7 +7358,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H241" t="n">
         <v>4135</v>
@@ -7387,7 +7387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H242" t="n">
         <v>10822</v>
@@ -7445,7 +7445,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H244" t="n">
         <v>25909</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7503,7 +7503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H246" t="n">
         <v>7116</v>
@@ -7532,7 +7532,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H247" t="n">
         <v>18668</v>
@@ -7561,7 +7561,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H248" t="n">
         <v>7591</v>
@@ -7590,7 +7590,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H249" t="n">
         <v>4482</v>
@@ -7619,7 +7619,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H250" t="n">
         <v>41070</v>
@@ -7648,7 +7648,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H251" t="n">
         <v>2749</v>
@@ -7677,7 +7677,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H252" t="n">
         <v>3351</v>
@@ -7706,7 +7706,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993663787842</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H253" t="n">
         <v>8244</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022222518921</v>
+        <v>13.8022232055664</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7764,7 +7764,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869432449341</v>
+        <v>13.4869441986084</v>
       </c>
       <c r="H255" t="n">
         <v>3852</v>
@@ -7822,7 +7822,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H257" t="n">
         <v>7773</v>
@@ -7880,7 +7880,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.5745210647583</v>
+        <v>13.5745220184326</v>
       </c>
       <c r="H259" t="n">
         <v>10259</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7938,7 +7938,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G261" t="n">
-        <v>13.6971292495728</v>
+        <v>13.6971302032471</v>
       </c>
       <c r="H261" t="n">
         <v>11448</v>
@@ -7996,7 +7996,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773788452148</v>
+        <v>13.9773778915405</v>
       </c>
       <c r="H263" t="n">
         <v>14625</v>
@@ -8025,7 +8025,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>14.0474395751953</v>
+        <v>14.0474405288696</v>
       </c>
       <c r="H264" t="n">
         <v>10439</v>
@@ -8054,7 +8054,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G265" t="n">
-        <v>14.1525316238403</v>
+        <v>14.1525325775146</v>
       </c>
       <c r="H265" t="n">
         <v>11125</v>
@@ -8083,7 +8083,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.3101739883423</v>
+        <v>14.3101720809937</v>
       </c>
       <c r="H266" t="n">
         <v>8011</v>
@@ -8112,7 +8112,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502983093262</v>
+        <v>14.4502964019775</v>
       </c>
       <c r="H267" t="n">
         <v>21797</v>
@@ -8141,7 +8141,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>14.2751398086548</v>
+        <v>14.2751407623291</v>
       </c>
       <c r="H268" t="n">
         <v>16682</v>
@@ -8170,7 +8170,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627195358276</v>
+        <v>14.3627185821533</v>
       </c>
       <c r="H269" t="n">
         <v>28438</v>
@@ -8199,7 +8199,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.2576246261597</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H270" t="n">
         <v>5152</v>
@@ -8315,7 +8315,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G274" t="n">
-        <v>14.3977499008179</v>
+        <v>14.3977508544922</v>
       </c>
       <c r="H274" t="n">
         <v>5498</v>
@@ -8373,7 +8373,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276901245117</v>
+        <v>14.3276891708374</v>
       </c>
       <c r="H276" t="n">
         <v>6927</v>
@@ -8402,7 +8402,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.2576246261597</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H277" t="n">
         <v>6898</v>
@@ -8460,7 +8460,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.203462600708</v>
+        <v>15.2034645080566</v>
       </c>
       <c r="H279" t="n">
         <v>80397</v>
@@ -8489,7 +8489,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311637878418</v>
+        <v>15.4311656951904</v>
       </c>
       <c r="H280" t="n">
         <v>50717</v>
@@ -8547,7 +8547,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989921569824</v>
+        <v>15.7989912033081</v>
       </c>
       <c r="H282" t="n">
         <v>60104</v>
@@ -8576,7 +8576,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888032913208</v>
+        <v>15.5888023376465</v>
       </c>
       <c r="H283" t="n">
         <v>32761</v>
@@ -8605,7 +8605,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165035247803</v>
+        <v>15.8165044784546</v>
       </c>
       <c r="H284" t="n">
         <v>60606</v>
@@ -8634,7 +8634,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814750671387</v>
+        <v>15.7814769744873</v>
       </c>
       <c r="H285" t="n">
         <v>16215</v>
@@ -8692,7 +8692,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317863464355</v>
+        <v>16.1317844390869</v>
       </c>
       <c r="H287" t="n">
         <v>34304</v>
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397342681885</v>
+        <v>16.6397361755371</v>
       </c>
       <c r="H288" t="n">
         <v>19711</v>
@@ -8779,7 +8779,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G290" t="n">
-        <v>16.7973766326904</v>
+        <v>16.7973747253418</v>
       </c>
       <c r="H290" t="n">
         <v>32844</v>
@@ -8895,7 +8895,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592994689941</v>
+        <v>17.5592975616455</v>
       </c>
       <c r="H294" t="n">
         <v>17437</v>
@@ -8924,7 +8924,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220329284668</v>
+        <v>17.8220310211182</v>
       </c>
       <c r="H295" t="n">
         <v>52008</v>
@@ -8953,7 +8953,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906661987305</v>
+        <v>17.6906681060791</v>
       </c>
       <c r="H296" t="n">
         <v>36908</v>
@@ -9011,7 +9011,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468753814697</v>
+        <v>17.6468772888184</v>
       </c>
       <c r="H298" t="n">
         <v>49334</v>
@@ -9040,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.5155124664307</v>
+        <v>17.515510559082</v>
       </c>
       <c r="H299" t="n">
         <v>21074</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979972839355</v>
+        <v>17.4979953765869</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9243,7 +9243,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0919055938721</v>
+        <v>19.0919075012207</v>
       </c>
       <c r="H306" t="n">
         <v>77246</v>
@@ -9301,7 +9301,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108520507812</v>
+        <v>19.3108501434326</v>
       </c>
       <c r="H308" t="n">
         <v>58530</v>
@@ -9330,7 +9330,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H309" t="n">
         <v>14880</v>
@@ -9359,7 +9359,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H310" t="n">
         <v>34531</v>
@@ -9388,7 +9388,7 @@
         <v>21.5</v>
       </c>
       <c r="G311" t="n">
-        <v>18.8291721343994</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H311" t="n">
         <v>24053</v>
@@ -9417,7 +9417,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415962219238</v>
       </c>
       <c r="H312" t="n">
         <v>23897</v>
@@ -9475,7 +9475,7 @@
         <v>21.5</v>
       </c>
       <c r="G314" t="n">
-        <v>18.8291721343994</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H314" t="n">
         <v>16356</v>
@@ -9504,7 +9504,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0919055938721</v>
+        <v>19.0919075012207</v>
       </c>
       <c r="H315" t="n">
         <v>9511</v>
@@ -9533,7 +9533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H316" t="n">
         <v>27872</v>
@@ -9562,7 +9562,7 @@
         <v>21.5</v>
       </c>
       <c r="G317" t="n">
-        <v>18.8291721343994</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H317" t="n">
         <v>18086</v>
@@ -9707,7 +9707,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.4422168731689</v>
+        <v>19.4422187805176</v>
       </c>
       <c r="H322" t="n">
         <v>48797</v>
@@ -9765,7 +9765,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7487373352051</v>
+        <v>19.7487392425537</v>
       </c>
       <c r="H324" t="n">
         <v>38949</v>
@@ -9794,7 +9794,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611633300781</v>
+        <v>19.6611652374268</v>
       </c>
       <c r="H325" t="n">
         <v>22459</v>
@@ -9823,7 +9823,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H326" t="n">
         <v>15812</v>
@@ -9852,7 +9852,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735836029053</v>
+        <v>19.5735855102539</v>
       </c>
       <c r="H327" t="n">
         <v>7040</v>
@@ -9968,7 +9968,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H331" t="n">
         <v>11487</v>
@@ -9997,7 +9997,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>19.0919055938721</v>
+        <v>19.0919075012207</v>
       </c>
       <c r="H332" t="n">
         <v>8982</v>
@@ -10055,7 +10055,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.04811668396</v>
+        <v>19.0481185913086</v>
       </c>
       <c r="H334" t="n">
         <v>5987</v>
@@ -10113,7 +10113,7 @@
         <v>21.5</v>
       </c>
       <c r="G336" t="n">
-        <v>18.8291721343994</v>
+        <v>18.829174041748</v>
       </c>
       <c r="H336" t="n">
         <v>16890</v>
@@ -10142,7 +10142,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415962219238</v>
       </c>
       <c r="H337" t="n">
         <v>8572</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546390533447</v>
+        <v>19.3546409606934</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799457550049</v>
+        <v>18.8799438476562</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10461,7 +10461,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.7239894866943</v>
+        <v>19.723991394043</v>
       </c>
       <c r="H348" t="n">
         <v>25636</v>
@@ -10519,7 +10519,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903408050537</v>
+        <v>20.3903388977051</v>
       </c>
       <c r="H350" t="n">
         <v>39422</v>
@@ -10606,7 +10606,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572597503662</v>
+        <v>19.8572616577148</v>
       </c>
       <c r="H353" t="n">
         <v>50006</v>
@@ -10635,7 +10635,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793762207031</v>
+        <v>20.0793743133545</v>
       </c>
       <c r="H354" t="n">
         <v>30645</v>
@@ -10664,7 +10664,7 @@
         <v>22.5</v>
       </c>
       <c r="G355" t="n">
-        <v>19.9905319213867</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H355" t="n">
         <v>20044</v>
@@ -10722,7 +10722,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684116363525</v>
+        <v>19.7684135437012</v>
       </c>
       <c r="H357" t="n">
         <v>47937</v>
@@ -10751,7 +10751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461059570312</v>
+        <v>19.9461078643799</v>
       </c>
       <c r="H358" t="n">
         <v>49210</v>
@@ -10780,7 +10780,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G359" t="n">
-        <v>18.835521697998</v>
+        <v>18.8355197906494</v>
       </c>
       <c r="H359" t="n">
         <v>57619</v>
@@ -10983,7 +10983,7 @@
         <v>22.5</v>
       </c>
       <c r="G366" t="n">
-        <v>19.9905319213867</v>
+        <v>19.9905300140381</v>
       </c>
       <c r="H366" t="n">
         <v>12885</v>
@@ -11012,7 +11012,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570686340332</v>
+        <v>20.2570667266846</v>
       </c>
       <c r="H367" t="n">
         <v>19035</v>
@@ -11041,7 +11041,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570686340332</v>
+        <v>20.2570667266846</v>
       </c>
       <c r="H368" t="n">
         <v>25835</v>
@@ -11186,7 +11186,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>23.2778606414795</v>
+        <v>23.2778625488281</v>
       </c>
       <c r="H373" t="n">
         <v>72531</v>
@@ -11215,7 +11215,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>23.2334365844727</v>
+        <v>23.233434677124</v>
       </c>
       <c r="H374" t="n">
         <v>53913</v>
@@ -11244,7 +11244,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>23.2778606414795</v>
+        <v>23.2778625488281</v>
       </c>
       <c r="H375" t="n">
         <v>34567</v>
@@ -11360,7 +11360,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786155700684</v>
       </c>
       <c r="H379" t="n">
         <v>1533317</v>
@@ -11418,7 +11418,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786155700684</v>
       </c>
       <c r="H381" t="n">
         <v>46241</v>
@@ -11534,7 +11534,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5009250640869</v>
+        <v>21.5009269714355</v>
       </c>
       <c r="H385" t="n">
         <v>66958</v>
@@ -11563,7 +11563,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H386" t="n">
         <v>27193</v>
@@ -11592,7 +11592,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011161804199</v>
+        <v>21.1011142730713</v>
       </c>
       <c r="H387" t="n">
         <v>8616</v>
@@ -11621,7 +11621,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566921234131</v>
+        <v>21.0566940307617</v>
       </c>
       <c r="H388" t="n">
         <v>20039</v>
@@ -11708,7 +11708,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901496887207</v>
+        <v>20.7901515960693</v>
       </c>
       <c r="H391" t="n">
         <v>21903</v>
@@ -11766,7 +11766,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H393" t="n">
         <v>23385</v>
@@ -11853,7 +11853,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H396" t="n">
         <v>21826</v>
@@ -11882,7 +11882,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680313110352</v>
+        <v>20.5680332183838</v>
       </c>
       <c r="H397" t="n">
         <v>6449</v>
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H399" t="n">
         <v>85005</v>
@@ -12027,7 +12027,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786155700684</v>
       </c>
       <c r="H402" t="n">
         <v>58589</v>
@@ -12143,7 +12143,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H406" t="n">
         <v>42941</v>
@@ -12172,7 +12172,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459167480469</v>
+        <v>20.3459148406982</v>
       </c>
       <c r="H407" t="n">
         <v>12913</v>
@@ -12201,7 +12201,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.6124572753906</v>
+        <v>20.6124591827393</v>
       </c>
       <c r="H408" t="n">
         <v>17907</v>
@@ -12317,7 +12317,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232307434082</v>
+        <v>21.3232326507568</v>
       </c>
       <c r="H412" t="n">
         <v>32846</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115093231201</v>
+        <v>22.6115112304688</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12491,7 +12491,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561225891113</v>
+        <v>22.2561206817627</v>
       </c>
       <c r="H418" t="n">
         <v>18147</v>
@@ -12578,7 +12578,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224720001221</v>
+        <v>22.9224739074707</v>
       </c>
       <c r="H421" t="n">
         <v>20723</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444030761719</v>
+        <v>23.5444011688232</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12839,7 +12839,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774822235107</v>
+        <v>24.0774803161621</v>
       </c>
       <c r="H430" t="n">
         <v>23999</v>
@@ -12868,7 +12868,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215259552002</v>
+        <v>24.9215240478516</v>
       </c>
       <c r="H431" t="n">
         <v>25118</v>
@@ -12897,7 +12897,7 @@
         <v>27.5</v>
       </c>
       <c r="G432" t="n">
-        <v>24.4328689575195</v>
+        <v>24.4328708648682</v>
       </c>
       <c r="H432" t="n">
         <v>17561</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661392211914</v>
+        <v>24.5661373138428</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -13013,7 +13013,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324905395508</v>
+        <v>25.2324886322021</v>
       </c>
       <c r="H436" t="n">
         <v>14765</v>
@@ -13042,7 +13042,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103740692139</v>
+        <v>25.0103721618652</v>
       </c>
       <c r="H437" t="n">
         <v>16754</v>
@@ -13071,7 +13071,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H438" t="n">
         <v>49309</v>
@@ -13100,7 +13100,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3875007629395</v>
+        <v>26.3874988555908</v>
       </c>
       <c r="H439" t="n">
         <v>22024</v>
@@ -13129,7 +13129,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H440" t="n">
         <v>28408</v>
@@ -13187,7 +13187,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317337036133</v>
+        <v>26.8317317962646</v>
       </c>
       <c r="H442" t="n">
         <v>23385</v>
@@ -13216,7 +13216,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205799102783</v>
+        <v>26.9205780029297</v>
       </c>
       <c r="H443" t="n">
         <v>23035</v>
@@ -13245,7 +13245,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536590576172</v>
+        <v>27.4536609649658</v>
       </c>
       <c r="H444" t="n">
         <v>42660</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425090789795</v>
+        <v>27.5425071716309</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13303,7 +13303,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975154876709</v>
+        <v>28.6975173950195</v>
       </c>
       <c r="H446" t="n">
         <v>109999</v>
@@ -13332,7 +13332,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.430025100708</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H447" t="n">
         <v>138213</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967548370361</v>
+        <v>30.2967567443848</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13390,7 +13390,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>30.6965656280518</v>
+        <v>30.6965675354004</v>
       </c>
       <c r="H449" t="n">
         <v>65084</v>
@@ -13419,7 +13419,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636737823486</v>
+        <v>29.7636756896973</v>
       </c>
       <c r="H450" t="n">
         <v>69374</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527187347412</v>
+        <v>29.4527149200439</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13535,7 +13535,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.430025100708</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H454" t="n">
         <v>27063</v>
@@ -13564,7 +13564,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744510650635</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H455" t="n">
         <v>27798</v>
@@ -13622,7 +13622,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646217346191</v>
+        <v>27.7646236419678</v>
       </c>
       <c r="H457" t="n">
         <v>101299</v>
@@ -13825,7 +13825,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.2306003570557</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H464" t="n">
         <v>33973</v>
@@ -13854,7 +13854,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863616943359</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H465" t="n">
         <v>29892</v>
@@ -13912,7 +13912,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857902526855</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H467" t="n">
         <v>54363</v>
@@ -13970,7 +13970,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G469" t="n">
-        <v>30.7409896850586</v>
+        <v>30.7409915924072</v>
       </c>
       <c r="H469" t="n">
         <v>41790</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296485900879</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.762731552124</v>
+        <v>31.7627296447754</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14115,7 +14115,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.162540435791</v>
+        <v>32.1625442504883</v>
       </c>
       <c r="H474" t="n">
         <v>26719</v>
@@ -14202,7 +14202,7 @@
         <v>37</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8733139038086</v>
+        <v>32.8733100891113</v>
       </c>
       <c r="H477" t="n">
         <v>43808</v>
@@ -14318,7 +14318,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H481" t="n">
         <v>18772</v>
@@ -14376,7 +14376,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.273120880127</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H483" t="n">
         <v>61904</v>
@@ -14434,7 +14434,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H485" t="n">
         <v>147072</v>
@@ -14550,7 +14550,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065841674805</v>
+        <v>33.0065879821777</v>
       </c>
       <c r="H489" t="n">
         <v>27315</v>
@@ -14579,7 +14579,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619728088379</v>
+        <v>33.3619689941406</v>
       </c>
       <c r="H490" t="n">
         <v>30081</v>
@@ -14608,7 +14608,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.273120880127</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H491" t="n">
         <v>10757</v>
@@ -14637,7 +14637,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288879394531</v>
       </c>
       <c r="H492" t="n">
         <v>26262</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179290771484</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14811,7 +14811,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.162540435791</v>
+        <v>32.1625442504883</v>
       </c>
       <c r="H498" t="n">
         <v>32373</v>
@@ -14869,7 +14869,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634864807129</v>
+        <v>30.1634883880615</v>
       </c>
       <c r="H500" t="n">
         <v>80023</v>
@@ -14927,7 +14927,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404258728027</v>
+        <v>31.9404239654541</v>
       </c>
       <c r="H502" t="n">
         <v>44140</v>
@@ -14985,7 +14985,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852245330811</v>
+        <v>31.1852226257324</v>
       </c>
       <c r="H504" t="n">
         <v>25156</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296485900879</v>
+        <v>31.2296524047852</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15043,7 +15043,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852245330811</v>
+        <v>31.1852226257324</v>
       </c>
       <c r="H506" t="n">
         <v>14367</v>
@@ -15072,7 +15072,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G507" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H507" t="n">
         <v>36805</v>
@@ -15101,7 +15101,7 @@
         <v>37</v>
       </c>
       <c r="G508" t="n">
-        <v>32.8733139038086</v>
+        <v>32.8733100891113</v>
       </c>
       <c r="H508" t="n">
         <v>20299</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177398681641</v>
+        <v>32.9177360534668</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.762731552124</v>
+        <v>31.7627296447754</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15246,7 +15246,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510063171387</v>
+        <v>33.0510139465332</v>
       </c>
       <c r="H513" t="n">
         <v>30830</v>
@@ -15275,7 +15275,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508171081543</v>
+        <v>33.4508209228516</v>
       </c>
       <c r="H514" t="n">
         <v>66935</v>
@@ -15304,7 +15304,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.4734992980957</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H515" t="n">
         <v>28750</v>
@@ -15333,7 +15333,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.4734992980957</v>
+        <v>32.473503112793</v>
       </c>
       <c r="H516" t="n">
         <v>39270</v>
@@ -15391,7 +15391,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288917541504</v>
+        <v>32.8288879394531</v>
       </c>
       <c r="H518" t="n">
         <v>13845</v>
@@ -15420,7 +15420,7 @@
         <v>36.5</v>
       </c>
       <c r="G519" t="n">
-        <v>32.4290771484375</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H519" t="n">
         <v>27308</v>
@@ -15478,7 +15478,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619728088379</v>
+        <v>33.3619689941406</v>
       </c>
       <c r="H521" t="n">
         <v>16885</v>
@@ -15565,7 +15565,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.294864654541</v>
+        <v>34.2948608398438</v>
       </c>
       <c r="H524" t="n">
         <v>40082</v>
@@ -15594,7 +15594,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H525" t="n">
         <v>30151</v>
@@ -15652,7 +15652,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H527" t="n">
         <v>15724</v>
@@ -15681,7 +15681,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H528" t="n">
         <v>23614</v>
@@ -15710,7 +15710,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>31.8960056304932</v>
+        <v>31.8960018157959</v>
       </c>
       <c r="H529" t="n">
         <v>38776</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179290771484</v>
+        <v>32.5179214477539</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15768,7 +15768,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840873718262</v>
+        <v>33.5840911865234</v>
       </c>
       <c r="H531" t="n">
         <v>37158</v>
@@ -15884,7 +15884,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G535" t="n">
-        <v>33.228702545166</v>
+        <v>33.2287063598633</v>
       </c>
       <c r="H535" t="n">
         <v>20158</v>
@@ -15971,7 +15971,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727424621582</v>
+        <v>34.0727500915527</v>
       </c>
       <c r="H538" t="n">
         <v>33816</v>
@@ -16029,7 +16029,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>31.4517650604248</v>
+        <v>31.4517669677734</v>
       </c>
       <c r="H540" t="n">
         <v>30779</v>
@@ -16116,7 +16116,7 @@
         <v>36.5</v>
       </c>
       <c r="G543" t="n">
-        <v>32.4290771484375</v>
+        <v>32.4290809631348</v>
       </c>
       <c r="H543" t="n">
         <v>43887</v>
@@ -16174,7 +16174,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063911437988</v>
+        <v>33.4063949584961</v>
       </c>
       <c r="H545" t="n">
         <v>71422</v>
@@ -16203,7 +16203,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>32.6956214904785</v>
+        <v>32.6956176757812</v>
       </c>
       <c r="H546" t="n">
         <v>50699</v>
@@ -16261,7 +16261,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H548" t="n">
         <v>151703</v>
@@ -16348,7 +16348,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H551" t="n">
         <v>43962</v>
@@ -16406,7 +16406,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H553" t="n">
         <v>48943</v>
@@ -16435,7 +16435,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H554" t="n">
         <v>69956</v>
@@ -16464,7 +16464,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H555" t="n">
         <v>49369</v>
@@ -16493,7 +16493,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.294864654541</v>
+        <v>34.2948608398438</v>
       </c>
       <c r="H556" t="n">
         <v>29679</v>
@@ -16551,7 +16551,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.273120880127</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H558" t="n">
         <v>31513</v>
@@ -16638,7 +16638,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>36.738151550293</v>
+        <v>36.7381553649902</v>
       </c>
       <c r="H561" t="n">
         <v>96737</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.4054489135742</v>
+        <v>35.405445098877</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16754,7 +16754,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H565" t="n">
         <v>57075</v>
@@ -16957,7 +16957,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873096466064</v>
+        <v>26.7873077392578</v>
       </c>
       <c r="H572" t="n">
         <v>79386</v>
@@ -16986,7 +16986,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.2306003570557</v>
+        <v>29.230598449707</v>
       </c>
       <c r="H573" t="n">
         <v>133949</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190643310547</v>
+        <v>30.1190662384033</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184986114502</v>
+        <v>31.3184947967529</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17102,7 +17102,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519542694092</v>
+        <v>31.0519599914551</v>
       </c>
       <c r="H577" t="n">
         <v>60129</v>
@@ -17276,7 +17276,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408042907715</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H583" t="n">
         <v>48569</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17334,7 +17334,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H585" t="n">
         <v>89419</v>
@@ -17508,7 +17508,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>31.4517650604248</v>
+        <v>31.4517669677734</v>
       </c>
       <c r="H591" t="n">
         <v>44060</v>
@@ -17537,7 +17537,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744510650635</v>
+        <v>30.4744491577148</v>
       </c>
       <c r="H592" t="n">
         <v>28557</v>
@@ -17595,7 +17595,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636737823486</v>
+        <v>29.7636756896973</v>
       </c>
       <c r="H594" t="n">
         <v>35604</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186878204346</v>
+        <v>30.9186859130859</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17711,7 +17711,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519542694092</v>
+        <v>31.0519599914551</v>
       </c>
       <c r="H598" t="n">
         <v>20035</v>
@@ -17740,7 +17740,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740783691406</v>
+        <v>31.2740745544434</v>
       </c>
       <c r="H599" t="n">
         <v>22406</v>
@@ -17827,7 +17827,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408042907715</v>
+        <v>31.1408023834229</v>
       </c>
       <c r="H602" t="n">
         <v>46419</v>
@@ -17856,7 +17856,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863616943359</v>
+        <v>28.7863655090332</v>
       </c>
       <c r="H603" t="n">
         <v>26401</v>
@@ -17914,7 +17914,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>29.5859851837158</v>
+        <v>29.5859832763672</v>
       </c>
       <c r="H605" t="n">
         <v>31886</v>
@@ -17943,7 +17943,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857902526855</v>
+        <v>29.9857921600342</v>
       </c>
       <c r="H606" t="n">
         <v>22611</v>
@@ -17972,7 +17972,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H607" t="n">
         <v>27177</v>
@@ -18001,7 +18001,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621536254883</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H608" t="n">
         <v>42611</v>
@@ -18030,7 +18030,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H609" t="n">
         <v>29532</v>
@@ -18059,7 +18059,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621536254883</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H610" t="n">
         <v>31377</v>
@@ -18088,7 +18088,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405632019043</v>
       </c>
       <c r="H611" t="n">
         <v>81317</v>
@@ -18117,7 +18117,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H612" t="n">
         <v>85415</v>
@@ -18146,7 +18146,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H613" t="n">
         <v>43669</v>
@@ -18262,7 +18262,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H617" t="n">
         <v>48629</v>
@@ -18291,7 +18291,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658050537109</v>
+        <v>33.9658088684082</v>
       </c>
       <c r="H618" t="n">
         <v>36011</v>
@@ -18349,7 +18349,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9758033752441</v>
+        <v>31.9758014678955</v>
       </c>
       <c r="H620" t="n">
         <v>19405</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903427124023</v>
+        <v>30.8903465270996</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18407,7 +18407,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094326019287</v>
+        <v>30.709436416626</v>
       </c>
       <c r="H622" t="n">
         <v>13020</v>
@@ -18436,7 +18436,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>30.0310249328613</v>
+        <v>30.0310230255127</v>
       </c>
       <c r="H623" t="n">
         <v>15007</v>
@@ -18523,7 +18523,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617069244385</v>
+        <v>31.1617088317871</v>
       </c>
       <c r="H626" t="n">
         <v>16502</v>
@@ -18552,7 +18552,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898941040039</v>
+        <v>32.7898979187012</v>
       </c>
       <c r="H627" t="n">
         <v>41583</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903427124023</v>
+        <v>30.8903465270996</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18639,7 +18639,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G630" t="n">
-        <v>31.1164798736572</v>
+        <v>31.1164817810059</v>
       </c>
       <c r="H630" t="n">
         <v>9830</v>
@@ -18668,7 +18668,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>30.0310249328613</v>
+        <v>30.0310230255127</v>
       </c>
       <c r="H631" t="n">
         <v>20315</v>
@@ -18726,7 +18726,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5737533569336</v>
+        <v>30.573751449585</v>
       </c>
       <c r="H633" t="n">
         <v>27780</v>
@@ -18842,7 +18842,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H637" t="n">
         <v>26649</v>
@@ -18900,7 +18900,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H639" t="n">
         <v>19934</v>
@@ -18958,7 +18958,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>28.8551063537598</v>
+        <v>28.8551082611084</v>
       </c>
       <c r="H641" t="n">
         <v>47653</v>
@@ -18987,7 +18987,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G642" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H642" t="n">
         <v>7805</v>
@@ -19016,7 +19016,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G643" t="n">
-        <v>29.0812454223633</v>
+        <v>29.0812473297119</v>
       </c>
       <c r="H643" t="n">
         <v>23506</v>
@@ -19045,7 +19045,7 @@
         <v>32</v>
       </c>
       <c r="G644" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H644" t="n">
         <v>31552</v>
@@ -19074,7 +19074,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601055145264</v>
+        <v>27.8601016998291</v>
       </c>
       <c r="H645" t="n">
         <v>17310</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H646" t="n">
         <v>21557</v>
@@ -19132,7 +19132,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H647" t="n">
         <v>19011</v>
@@ -19161,7 +19161,7 @@
         <v>32</v>
       </c>
       <c r="G648" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H648" t="n">
         <v>10722</v>
@@ -19248,7 +19248,7 @@
         <v>32</v>
       </c>
       <c r="G651" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H651" t="n">
         <v>18834</v>
@@ -19277,7 +19277,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>28.5837459564209</v>
+        <v>28.5837440490723</v>
       </c>
       <c r="H652" t="n">
         <v>15473</v>
@@ -19364,7 +19364,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>28.0862426757812</v>
+        <v>28.0862407684326</v>
       </c>
       <c r="H655" t="n">
         <v>36534</v>
@@ -19393,7 +19393,7 @@
         <v>33</v>
       </c>
       <c r="G656" t="n">
-        <v>29.8501148223877</v>
+        <v>29.8501110076904</v>
       </c>
       <c r="H656" t="n">
         <v>35738</v>
@@ -19422,7 +19422,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>29.6692008972168</v>
+        <v>29.6692028045654</v>
       </c>
       <c r="H657" t="n">
         <v>10389</v>
@@ -19451,7 +19451,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H658" t="n">
         <v>15664</v>
@@ -19509,7 +19509,7 @@
         <v>33</v>
       </c>
       <c r="G660" t="n">
-        <v>29.8501148223877</v>
+        <v>29.8501110076904</v>
       </c>
       <c r="H660" t="n">
         <v>20537</v>
@@ -19538,7 +19538,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H661" t="n">
         <v>16406</v>
@@ -19596,7 +19596,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214771270752</v>
+        <v>30.1214752197266</v>
       </c>
       <c r="H663" t="n">
         <v>13226</v>
@@ -19654,7 +19654,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405632019043</v>
       </c>
       <c r="H665" t="n">
         <v>5963</v>
@@ -19712,7 +19712,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0310249328613</v>
+        <v>30.0310230255127</v>
       </c>
       <c r="H667" t="n">
         <v>20516</v>
@@ -19799,7 +19799,7 @@
         <v>33</v>
       </c>
       <c r="G670" t="n">
-        <v>29.8501148223877</v>
+        <v>29.8501110076904</v>
       </c>
       <c r="H670" t="n">
         <v>16306</v>
@@ -19857,7 +19857,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285205841064</v>
       </c>
       <c r="H672" t="n">
         <v>11102</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355716705322</v>
+        <v>30.9355697631836</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19944,7 +19944,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9808006286621</v>
+        <v>30.9807968139648</v>
       </c>
       <c r="H675" t="n">
         <v>14000</v>
@@ -20002,7 +20002,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832954406738</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H677" t="n">
         <v>25987</v>
@@ -20147,7 +20147,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048858642578</v>
+        <v>29.8048820495605</v>
       </c>
       <c r="H682" t="n">
         <v>13128</v>
@@ -20205,7 +20205,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H684" t="n">
         <v>27461</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H687" t="n">
         <v>31220</v>
@@ -20321,7 +20321,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H688" t="n">
         <v>9866</v>
@@ -20350,7 +20350,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H689" t="n">
         <v>6251</v>
@@ -20408,7 +20408,7 @@
         <v>32</v>
       </c>
       <c r="G691" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H691" t="n">
         <v>11145</v>
@@ -20495,7 +20495,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505596160889</v>
+        <v>27.9505577087402</v>
       </c>
       <c r="H694" t="n">
         <v>28033</v>
@@ -20524,7 +20524,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H695" t="n">
         <v>25276</v>
@@ -20640,7 +20640,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285205841064</v>
       </c>
       <c r="H699" t="n">
         <v>56297</v>
@@ -20669,7 +20669,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762500762939</v>
+        <v>30.0762481689453</v>
       </c>
       <c r="H700" t="n">
         <v>23460</v>
@@ -20698,7 +20698,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567077636719</v>
+        <v>32.1567115783691</v>
       </c>
       <c r="H701" t="n">
         <v>56088</v>
@@ -20756,7 +20756,7 @@
         <v>33</v>
       </c>
       <c r="G703" t="n">
-        <v>29.8501148223877</v>
+        <v>29.8501110076904</v>
       </c>
       <c r="H703" t="n">
         <v>24157</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.7194271087646</v>
+        <v>28.719425201416</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20814,7 +20814,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>28.0862426757812</v>
+        <v>28.0862407684326</v>
       </c>
       <c r="H705" t="n">
         <v>27391</v>
@@ -20901,7 +20901,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G708" t="n">
-        <v>29.0812454223633</v>
+        <v>29.0812473297119</v>
       </c>
       <c r="H708" t="n">
         <v>15124</v>
@@ -20959,7 +20959,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364669799805</v>
+        <v>27.1364650726318</v>
       </c>
       <c r="H710" t="n">
         <v>48790</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314697265625</v>
+        <v>28.1314716339111</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21017,7 +21017,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>28.6289691925049</v>
+        <v>28.6289710998535</v>
       </c>
       <c r="H712" t="n">
         <v>33341</v>
@@ -21104,7 +21104,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048858642578</v>
+        <v>29.8048820495605</v>
       </c>
       <c r="H715" t="n">
         <v>26731</v>
@@ -21133,7 +21133,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H716" t="n">
         <v>30596</v>
@@ -21162,7 +21162,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.211935043335</v>
+        <v>30.2119293212891</v>
       </c>
       <c r="H717" t="n">
         <v>59213</v>
@@ -21191,7 +21191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073844909668</v>
+        <v>29.3073863983154</v>
       </c>
       <c r="H718" t="n">
         <v>15926</v>
@@ -21220,7 +21220,7 @@
         <v>32</v>
       </c>
       <c r="G719" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H719" t="n">
         <v>25143</v>
@@ -21278,7 +21278,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430637359619</v>
+        <v>29.4430656433105</v>
       </c>
       <c r="H721" t="n">
         <v>14502</v>
@@ -21336,7 +21336,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H723" t="n">
         <v>10352</v>
@@ -21365,7 +21365,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H724" t="n">
         <v>28121</v>
@@ -21394,7 +21394,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H725" t="n">
         <v>27078</v>
@@ -21423,7 +21423,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G726" t="n">
-        <v>29.9857940673828</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H726" t="n">
         <v>26161</v>
@@ -21452,7 +21452,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H727" t="n">
         <v>23140</v>
@@ -21481,7 +21481,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G728" t="n">
-        <v>29.0812454223633</v>
+        <v>29.0812473297119</v>
       </c>
       <c r="H728" t="n">
         <v>20050</v>
@@ -21510,7 +21510,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>28.5837459564209</v>
+        <v>28.5837440490723</v>
       </c>
       <c r="H729" t="n">
         <v>13692</v>
@@ -21568,7 +21568,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646522521973</v>
+        <v>28.7646541595459</v>
       </c>
       <c r="H731" t="n">
         <v>24208</v>
@@ -21597,7 +21597,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H732" t="n">
         <v>39155</v>
@@ -21626,7 +21626,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621536254883</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H733" t="n">
         <v>36285</v>
@@ -21655,7 +21655,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.216926574707</v>
+        <v>29.2169284820557</v>
       </c>
       <c r="H734" t="n">
         <v>19361</v>
@@ -21684,7 +21684,7 @@
         <v>32</v>
       </c>
       <c r="G735" t="n">
-        <v>28.9455642700195</v>
+        <v>28.9455623626709</v>
       </c>
       <c r="H735" t="n">
         <v>17587</v>
@@ -21713,7 +21713,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.3526096343994</v>
+        <v>29.352611541748</v>
       </c>
       <c r="H736" t="n">
         <v>39696</v>
@@ -21771,7 +21771,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H738" t="n">
         <v>31102</v>
@@ -21829,7 +21829,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405651092529</v>
+        <v>29.9405632019043</v>
       </c>
       <c r="H740" t="n">
         <v>25796</v>
@@ -21887,7 +21887,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285243988037</v>
+        <v>30.5285205841064</v>
       </c>
       <c r="H742" t="n">
         <v>22513</v>
@@ -21945,7 +21945,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H744" t="n">
         <v>24053</v>
@@ -21974,7 +21974,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401203155518</v>
+        <v>31.8401222229004</v>
       </c>
       <c r="H745" t="n">
         <v>20993</v>
@@ -22032,7 +22032,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998905181885</v>
+        <v>30.7998867034912</v>
       </c>
       <c r="H747" t="n">
         <v>9633</v>
@@ -22061,7 +22061,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.211935043335</v>
+        <v>30.2119293212891</v>
       </c>
       <c r="H748" t="n">
         <v>18927</v>
@@ -22119,7 +22119,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832954406738</v>
+        <v>30.4832973480225</v>
       </c>
       <c r="H750" t="n">
         <v>5976</v>
@@ -22148,7 +22148,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.5737533569336</v>
+        <v>30.573751449585</v>
       </c>
       <c r="H751" t="n">
         <v>7222</v>
@@ -22177,7 +22177,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094326019287</v>
+        <v>30.709436416626</v>
       </c>
       <c r="H752" t="n">
         <v>15924</v>
@@ -22235,7 +22235,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235252380371</v>
+        <v>31.5235271453857</v>
       </c>
       <c r="H754" t="n">
         <v>23044</v>
@@ -22264,7 +22264,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H755" t="n">
         <v>11292</v>
@@ -22322,7 +22322,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>31.1164798736572</v>
+        <v>31.1164817810059</v>
       </c>
       <c r="H757" t="n">
         <v>15048</v>
@@ -22380,7 +22380,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G759" t="n">
-        <v>32.4733085632324</v>
+        <v>32.4733047485352</v>
       </c>
       <c r="H759" t="n">
         <v>32628</v>
@@ -22409,7 +22409,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H760" t="n">
         <v>38359</v>
@@ -22438,7 +22438,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H761" t="n">
         <v>16883</v>
@@ -22496,7 +22496,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G763" t="n">
-        <v>32.2019386291504</v>
+        <v>32.2019348144531</v>
       </c>
       <c r="H763" t="n">
         <v>35066</v>
@@ -22525,7 +22525,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.885347366333</v>
+        <v>31.8853492736816</v>
       </c>
       <c r="H764" t="n">
         <v>11653</v>
@@ -22583,7 +22583,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G766" t="n">
-        <v>32.2019386291504</v>
+        <v>32.2019348144531</v>
       </c>
       <c r="H766" t="n">
         <v>18901</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803558349609</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22670,7 +22670,7 @@
         <v>35.5</v>
       </c>
       <c r="G769" t="n">
-        <v>32.1114807128906</v>
+        <v>32.1114883422852</v>
       </c>
       <c r="H769" t="n">
         <v>44649</v>
@@ -22728,7 +22728,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330711364746</v>
+        <v>31.4330730438232</v>
       </c>
       <c r="H771" t="n">
         <v>8172</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.2521667480469</v>
+        <v>31.252161026001</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803482055664</v>
+        <v>32.8803558349609</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637550354004</v>
+        <v>32.5637626647949</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -22873,7 +22873,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089820861816</v>
+        <v>32.6089859008789</v>
       </c>
       <c r="H776" t="n">
         <v>6543</v>
@@ -22931,7 +22931,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.9205856323242</v>
+        <v>33.9205780029297</v>
       </c>
       <c r="H778" t="n">
         <v>24835</v>
@@ -23047,7 +23047,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.875358581543</v>
+        <v>33.8753509521484</v>
       </c>
       <c r="H782" t="n">
         <v>27238</v>
@@ -23163,7 +23163,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110321044922</v>
+        <v>34.0110359191895</v>
       </c>
       <c r="H786" t="n">
         <v>10605</v>
@@ -23221,7 +23221,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.875358581543</v>
+        <v>33.8753509521484</v>
       </c>
       <c r="H788" t="n">
         <v>10901</v>
@@ -23250,7 +23250,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>34.5085411071777</v>
+        <v>34.5085372924805</v>
       </c>
       <c r="H789" t="n">
         <v>22080</v>
@@ -23279,7 +23279,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442222595215</v>
+        <v>34.6442184448242</v>
       </c>
       <c r="H790" t="n">
         <v>23430</v>
@@ -23366,7 +23366,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>34.1014938354492</v>
+        <v>34.101490020752</v>
       </c>
       <c r="H793" t="n">
         <v>25794</v>
@@ -23395,7 +23395,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658050537109</v>
+        <v>33.9658088684082</v>
       </c>
       <c r="H794" t="n">
         <v>32389</v>
@@ -23482,7 +23482,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035400390625</v>
+        <v>35.5035438537598</v>
       </c>
       <c r="H797" t="n">
         <v>15860</v>
@@ -23511,7 +23511,7 @@
         <v>39.75</v>
       </c>
       <c r="G798" t="n">
-        <v>35.9558181762695</v>
+        <v>35.9558143615723</v>
       </c>
       <c r="H798" t="n">
         <v>25747</v>
@@ -23569,7 +23569,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H800" t="n">
         <v>24431</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578643798828</v>
+        <v>37.3578720092773</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23772,7 +23772,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749099731445</v>
+        <v>35.7749061584473</v>
       </c>
       <c r="H807" t="n">
         <v>30091</v>
@@ -23946,7 +23946,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.543773651123</v>
+        <v>36.5437774658203</v>
       </c>
       <c r="H813" t="n">
         <v>27397</v>
@@ -24004,7 +24004,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H815" t="n">
         <v>35580</v>
@@ -24033,7 +24033,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.7246856689453</v>
+        <v>36.7246780395508</v>
       </c>
       <c r="H816" t="n">
         <v>28980</v>
@@ -24062,7 +24062,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>36.905590057373</v>
+        <v>36.9055938720703</v>
       </c>
       <c r="H817" t="n">
         <v>29508</v>
@@ -24120,7 +24120,7 @@
         <v>41.25</v>
       </c>
       <c r="G819" t="n">
-        <v>37.3126373291016</v>
+        <v>37.3126411437988</v>
       </c>
       <c r="H819" t="n">
         <v>39954</v>
@@ -24149,7 +24149,7 @@
         <v>42.5</v>
       </c>
       <c r="G820" t="n">
-        <v>38.4433250427246</v>
+        <v>38.4433288574219</v>
       </c>
       <c r="H820" t="n">
         <v>48120</v>
@@ -24178,7 +24178,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312805175781</v>
       </c>
       <c r="H821" t="n">
         <v>71113</v>
@@ -24207,7 +24207,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3981018066406</v>
+        <v>38.3980979919434</v>
       </c>
       <c r="H822" t="n">
         <v>31744</v>
@@ -24236,7 +24236,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8956031799316</v>
+        <v>38.8955993652344</v>
       </c>
       <c r="H823" t="n">
         <v>45948</v>
@@ -24381,7 +24381,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312843322754</v>
+        <v>39.0312805175781</v>
       </c>
       <c r="H828" t="n">
         <v>29768</v>
@@ -24410,7 +24410,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H829" t="n">
         <v>35652</v>
@@ -24468,7 +24468,7 @@
         <v>42</v>
       </c>
       <c r="G831" t="n">
-        <v>37.9910507202148</v>
+        <v>37.9910545349121</v>
       </c>
       <c r="H831" t="n">
         <v>31412</v>
@@ -24497,7 +24497,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H832" t="n">
         <v>71309</v>
@@ -24526,7 +24526,7 @@
         <v>41.75</v>
       </c>
       <c r="G833" t="n">
-        <v>37.7649116516113</v>
+        <v>37.7649154663086</v>
       </c>
       <c r="H833" t="n">
         <v>30771</v>
@@ -24584,7 +24584,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624168395996</v>
+        <v>38.2624130249023</v>
       </c>
       <c r="H835" t="n">
         <v>34627</v>
@@ -24613,7 +24613,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>38.4885520935059</v>
+        <v>38.4885559082031</v>
       </c>
       <c r="H836" t="n">
         <v>39749</v>
@@ -24671,7 +24671,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>37.0412750244141</v>
+        <v>37.0412788391113</v>
       </c>
       <c r="H838" t="n">
         <v>42162</v>
@@ -24729,7 +24729,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.8653602600098</v>
+        <v>35.865364074707</v>
       </c>
       <c r="H840" t="n">
         <v>24851</v>
@@ -24816,7 +24816,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.8653602600098</v>
+        <v>35.865364074707</v>
       </c>
       <c r="H843" t="n">
         <v>30983</v>
@@ -24932,7 +24932,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342277526855</v>
+        <v>36.6342315673828</v>
       </c>
       <c r="H847" t="n">
         <v>16900</v>
@@ -24961,7 +24961,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.910587310791</v>
+        <v>35.9105911254883</v>
       </c>
       <c r="H848" t="n">
         <v>26054</v>
@@ -25019,7 +25019,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.7246856689453</v>
+        <v>36.7246780395508</v>
       </c>
       <c r="H850" t="n">
         <v>32977</v>
@@ -25135,7 +25135,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744613647461</v>
+        <v>37.6744651794434</v>
       </c>
       <c r="H854" t="n">
         <v>14320</v>
@@ -25193,7 +25193,7 @@
         <v>40.75</v>
       </c>
       <c r="G856" t="n">
-        <v>36.8603668212891</v>
+        <v>36.8603630065918</v>
       </c>
       <c r="H856" t="n">
         <v>25546</v>
@@ -25280,7 +25280,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342277526855</v>
+        <v>36.6342315673828</v>
       </c>
       <c r="H859" t="n">
         <v>12270</v>
@@ -25309,7 +25309,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>36.046272277832</v>
+        <v>36.0462684631348</v>
       </c>
       <c r="H860" t="n">
         <v>13910</v>
@@ -25802,7 +25802,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>36.7331352233887</v>
+        <v>36.7331314086914</v>
       </c>
       <c r="H877" t="n">
         <v>15633</v>
@@ -25831,7 +25831,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354751586914</v>
+        <v>36.1354713439941</v>
       </c>
       <c r="H878" t="n">
         <v>14544</v>
@@ -26469,7 +26469,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G900" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H900" t="n">
         <v>16294</v>
@@ -26498,7 +26498,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G901" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H901" t="n">
         <v>13534</v>
@@ -26556,7 +26556,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G903" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H903" t="n">
         <v>13508</v>
@@ -26904,7 +26904,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>33.9747047424316</v>
+        <v>33.9747009277344</v>
       </c>
       <c r="H915" t="n">
         <v>25831</v>
@@ -27049,7 +27049,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H920" t="n">
         <v>12456</v>
@@ -27078,7 +27078,7 @@
         <v>35</v>
       </c>
       <c r="G921" t="n">
-        <v>32.1817207336426</v>
+        <v>32.1817169189453</v>
       </c>
       <c r="H921" t="n">
         <v>25157</v>
@@ -27107,7 +27107,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G922" t="n">
-        <v>32.0897750854492</v>
+        <v>32.089771270752</v>
       </c>
       <c r="H922" t="n">
         <v>9260</v>
@@ -27136,7 +27136,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>31.9978256225586</v>
+        <v>31.9978218078613</v>
       </c>
       <c r="H923" t="n">
         <v>23180</v>
@@ -27194,7 +27194,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H925" t="n">
         <v>24388</v>
@@ -27223,7 +27223,7 @@
         <v>35</v>
       </c>
       <c r="G926" t="n">
-        <v>32.1817207336426</v>
+        <v>32.1817169189453</v>
       </c>
       <c r="H926" t="n">
         <v>18401</v>
@@ -27252,7 +27252,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575576782227</v>
+        <v>32.4575614929199</v>
       </c>
       <c r="H927" t="n">
         <v>15137</v>
@@ -27281,7 +27281,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H928" t="n">
         <v>18700</v>
@@ -27426,7 +27426,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424873352051</v>
+        <v>34.3424911499023</v>
       </c>
       <c r="H933" t="n">
         <v>31757</v>
@@ -27600,7 +27600,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.296516418457</v>
+        <v>34.2965126037598</v>
       </c>
       <c r="H939" t="n">
         <v>16255</v>
@@ -28035,7 +28035,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H954" t="n">
         <v>10979</v>
@@ -28093,7 +28093,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448272705078</v>
+        <v>33.7448310852051</v>
       </c>
       <c r="H956" t="n">
         <v>7086</v>
@@ -28151,7 +28151,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H958" t="n">
         <v>18202</v>
@@ -28209,7 +28209,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>32.9632720947266</v>
+        <v>32.9632759094238</v>
       </c>
       <c r="H960" t="n">
         <v>35963</v>
@@ -28238,7 +28238,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>32.5954856872559</v>
+        <v>32.5954818725586</v>
       </c>
       <c r="H961" t="n">
         <v>21271</v>
@@ -28267,7 +28267,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G962" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H962" t="n">
         <v>19440</v>
@@ -28296,7 +28296,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G963" t="n">
-        <v>32.5035362243652</v>
+        <v>32.503532409668</v>
       </c>
       <c r="H963" t="n">
         <v>11379</v>
@@ -28325,7 +28325,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G964" t="n">
-        <v>32.2736625671387</v>
+        <v>32.2736663818359</v>
       </c>
       <c r="H964" t="n">
         <v>19495</v>
@@ -28354,7 +28354,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115905761719</v>
+        <v>32.4115867614746</v>
       </c>
       <c r="H965" t="n">
         <v>16412</v>
@@ -28412,7 +28412,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G967" t="n">
-        <v>32.3656120300293</v>
+        <v>32.3656158447266</v>
       </c>
       <c r="H967" t="n">
         <v>23454</v>
@@ -28470,7 +28470,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H969" t="n">
         <v>26969</v>
@@ -28528,7 +28528,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>33.0552215576172</v>
+        <v>33.0552253723145</v>
       </c>
       <c r="H971" t="n">
         <v>12593</v>
@@ -28586,7 +28586,7 @@
         <v>35.4500007629395</v>
       </c>
       <c r="G973" t="n">
-        <v>32.5954856872559</v>
+        <v>32.5954818725586</v>
       </c>
       <c r="H973" t="n">
         <v>25464</v>
@@ -28644,7 +28644,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H975" t="n">
         <v>22418</v>
@@ -28818,7 +28818,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495109558105</v>
+        <v>32.5495147705078</v>
       </c>
       <c r="H981" t="n">
         <v>23720</v>
@@ -28847,7 +28847,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9173011779785</v>
+        <v>32.9172973632812</v>
       </c>
       <c r="H982" t="n">
         <v>17608</v>
@@ -28876,7 +28876,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9173011779785</v>
+        <v>32.9172973632812</v>
       </c>
       <c r="H983" t="n">
         <v>19478</v>
@@ -28934,7 +28934,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391204833984</v>
+        <v>33.2391166687012</v>
       </c>
       <c r="H985" t="n">
         <v>10944</v>
@@ -28963,7 +28963,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253555297852</v>
+        <v>32.8253517150879</v>
       </c>
       <c r="H986" t="n">
         <v>11601</v>
@@ -29079,7 +29079,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541870117188</v>
+        <v>31.3541851043701</v>
       </c>
       <c r="H990" t="n">
         <v>16205</v>
@@ -29108,7 +29108,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783424377441</v>
+        <v>31.0783443450928</v>
       </c>
       <c r="H991" t="n">
         <v>22083</v>
@@ -29195,7 +29195,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G994" t="n">
-        <v>32.9632720947266</v>
+        <v>32.9632759094238</v>
       </c>
       <c r="H994" t="n">
         <v>25799</v>
@@ -30123,7 +30123,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1026" t="n">
-        <v>39.2157249450684</v>
+        <v>39.2157211303711</v>
       </c>
       <c r="H1026" t="n">
         <v>24452</v>
@@ -30152,7 +30152,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1027" t="n">
         <v>33681</v>
@@ -30181,7 +30181,7 @@
         <v>42.75</v>
       </c>
       <c r="G1028" t="n">
-        <v>39.3076705932617</v>
+        <v>39.3076667785645</v>
       </c>
       <c r="H1028" t="n">
         <v>26762</v>
@@ -30239,7 +30239,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1030" t="n">
-        <v>39.3536415100098</v>
+        <v>39.353645324707</v>
       </c>
       <c r="H1030" t="n">
         <v>43234</v>
@@ -30297,7 +30297,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616958618164</v>
+        <v>39.2616996765137</v>
       </c>
       <c r="H1032" t="n">
         <v>26646</v>
@@ -30326,7 +30326,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1033" t="n">
         <v>17293</v>
@@ -30384,7 +30384,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1035" t="n">
-        <v>38.0204010009766</v>
+        <v>38.0203971862793</v>
       </c>
       <c r="H1035" t="n">
         <v>30679</v>
@@ -30413,7 +30413,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>37.9744262695312</v>
+        <v>37.9744300842285</v>
       </c>
       <c r="H1036" t="n">
         <v>34011</v>
@@ -30500,7 +30500,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1039" t="n">
         <v>35974</v>
@@ -30558,7 +30558,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>38.2042922973633</v>
+        <v>38.2042961120605</v>
       </c>
       <c r="H1041" t="n">
         <v>13783</v>
@@ -30587,7 +30587,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>39.2157249450684</v>
+        <v>39.2157211303711</v>
       </c>
       <c r="H1042" t="n">
         <v>29619</v>
@@ -30674,7 +30674,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996200561523</v>
+        <v>39.3996162414551</v>
       </c>
       <c r="H1045" t="n">
         <v>13666</v>
@@ -30703,7 +30703,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.6754608154297</v>
+        <v>39.675464630127</v>
       </c>
       <c r="H1046" t="n">
         <v>27206</v>
@@ -30761,7 +30761,7 @@
         <v>42.75</v>
       </c>
       <c r="G1048" t="n">
-        <v>39.3076705932617</v>
+        <v>39.3076667785645</v>
       </c>
       <c r="H1048" t="n">
         <v>28234</v>
@@ -30819,7 +30819,7 @@
         <v>43.25</v>
       </c>
       <c r="G1050" t="n">
-        <v>39.767406463623</v>
+        <v>39.7674102783203</v>
       </c>
       <c r="H1050" t="n">
         <v>27149</v>
@@ -30906,7 +30906,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G1053" t="n">
-        <v>40.273120880127</v>
+        <v>40.2731246948242</v>
       </c>
       <c r="H1053" t="n">
         <v>15184</v>
@@ -30935,7 +30935,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>40.6409111022949</v>
+        <v>40.6409149169922</v>
       </c>
       <c r="H1054" t="n">
         <v>19707</v>
@@ -31051,7 +31051,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1058" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1058" t="n">
         <v>26015</v>
@@ -31167,7 +31167,7 @@
         <v>43.25</v>
       </c>
       <c r="G1062" t="n">
-        <v>39.767406463623</v>
+        <v>39.7674102783203</v>
       </c>
       <c r="H1062" t="n">
         <v>107008</v>
@@ -31196,7 +31196,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627265930176</v>
+        <v>40.9627304077148</v>
       </c>
       <c r="H1063" t="n">
         <v>114652</v>
@@ -31254,7 +31254,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1065" t="n">
-        <v>41.7442855834961</v>
+        <v>41.7442893981934</v>
       </c>
       <c r="H1065" t="n">
         <v>58297</v>
@@ -31312,7 +31312,7 @@
         <v>42.75</v>
       </c>
       <c r="G1067" t="n">
-        <v>39.3076705932617</v>
+        <v>39.3076667785645</v>
       </c>
       <c r="H1067" t="n">
         <v>57559</v>
@@ -31341,7 +31341,7 @@
         <v>42.25</v>
       </c>
       <c r="G1068" t="n">
-        <v>38.8479309082031</v>
+        <v>38.8479347229004</v>
       </c>
       <c r="H1068" t="n">
         <v>39015</v>
@@ -31370,7 +31370,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>38.2962455749512</v>
+        <v>38.2962493896484</v>
       </c>
       <c r="H1069" t="n">
         <v>40978</v>
@@ -31399,7 +31399,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>37.9744262695312</v>
+        <v>37.9744300842285</v>
       </c>
       <c r="H1070" t="n">
         <v>24074</v>
@@ -31457,7 +31457,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1072" t="n">
         <v>20307</v>
@@ -31515,7 +31515,7 @@
         <v>42.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>38.8479309082031</v>
+        <v>38.8479347229004</v>
       </c>
       <c r="H1074" t="n">
         <v>19772</v>
@@ -31544,7 +31544,7 @@
         <v>41.25</v>
       </c>
       <c r="G1075" t="n">
-        <v>37.9284553527832</v>
+        <v>37.9284515380859</v>
       </c>
       <c r="H1075" t="n">
         <v>19218</v>
@@ -31573,7 +31573,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>37.9744262695312</v>
+        <v>37.9744300842285</v>
       </c>
       <c r="H1076" t="n">
         <v>35632</v>
@@ -31602,7 +31602,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1077" t="n">
         <v>48482</v>
@@ -31631,7 +31631,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1078" t="n">
         <v>21323</v>
@@ -31805,7 +31805,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365097045898</v>
+        <v>37.8365058898926</v>
       </c>
       <c r="H1084" t="n">
         <v>33932</v>
@@ -32066,7 +32066,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9744262695312</v>
+        <v>37.9744300842285</v>
       </c>
       <c r="H1093" t="n">
         <v>21149</v>
@@ -32095,7 +32095,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824768066406</v>
+        <v>37.8824806213379</v>
       </c>
       <c r="H1094" t="n">
         <v>23661</v>
@@ -32124,7 +32124,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1095" t="n">
         <v>27027</v>
@@ -32211,7 +32211,7 @@
         <v>42.3499984741211</v>
       </c>
       <c r="G1098" t="n">
-        <v>38.9398765563965</v>
+        <v>38.9398803710938</v>
       </c>
       <c r="H1098" t="n">
         <v>26751</v>
@@ -32240,7 +32240,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1099" t="n">
-        <v>38.8019599914551</v>
+        <v>38.8019561767578</v>
       </c>
       <c r="H1099" t="n">
         <v>14005</v>
@@ -32269,7 +32269,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1100" t="n">
-        <v>38.2962455749512</v>
+        <v>38.2962493896484</v>
       </c>
       <c r="H1100" t="n">
         <v>26546</v>
@@ -32298,7 +32298,7 @@
         <v>42.25</v>
       </c>
       <c r="G1101" t="n">
-        <v>38.8479309082031</v>
+        <v>38.8479347229004</v>
       </c>
       <c r="H1101" t="n">
         <v>11787</v>
@@ -32327,7 +32327,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1102" t="n">
-        <v>38.2962455749512</v>
+        <v>38.2962493896484</v>
       </c>
       <c r="H1102" t="n">
         <v>17758</v>
@@ -32617,7 +32617,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227447509766</v>
+        <v>37.4227409362793</v>
       </c>
       <c r="H1112" t="n">
         <v>49066</v>
@@ -32675,7 +32675,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227447509766</v>
+        <v>37.4227409362793</v>
       </c>
       <c r="H1114" t="n">
         <v>12691</v>
@@ -32704,7 +32704,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.560661315918</v>
+        <v>37.5606651306152</v>
       </c>
       <c r="H1115" t="n">
         <v>9595</v>
@@ -32762,7 +32762,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365097045898</v>
+        <v>37.8365058898926</v>
       </c>
       <c r="H1117" t="n">
         <v>12581</v>
@@ -32791,7 +32791,7 @@
         <v>41.5499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>38.2042922973633</v>
+        <v>38.2042961120605</v>
       </c>
       <c r="H1118" t="n">
         <v>11676</v>
@@ -33081,7 +33081,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616958618164</v>
+        <v>39.2616996765137</v>
       </c>
       <c r="H1128" t="n">
         <v>49587</v>
@@ -33197,7 +33197,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727020263672</v>
+        <v>39.4727058410645</v>
       </c>
       <c r="H1132" t="n">
         <v>28234</v>
@@ -33226,7 +33226,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900787353516</v>
+        <v>39.1900825500488</v>
       </c>
       <c r="H1133" t="n">
         <v>17044</v>
@@ -33371,7 +33371,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1138" t="n">
         <v>14887</v>
@@ -33429,7 +33429,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082214355469</v>
+        <v>39.7082176208496</v>
       </c>
       <c r="H1140" t="n">
         <v>25485</v>
@@ -33458,7 +33458,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842864990234</v>
+        <v>39.2842903137207</v>
       </c>
       <c r="H1141" t="n">
         <v>10680</v>
@@ -33487,7 +33487,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379409790039</v>
+        <v>40.0379447937012</v>
       </c>
       <c r="H1142" t="n">
         <v>21497</v>
@@ -33516,7 +33516,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553215026855</v>
+        <v>39.7553253173828</v>
       </c>
       <c r="H1143" t="n">
         <v>17609</v>
@@ -33545,7 +33545,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452499389648</v>
+        <v>41.5452537536621</v>
       </c>
       <c r="H1144" t="n">
         <v>77350</v>
@@ -33661,7 +33661,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437408447266</v>
+        <v>39.9437370300293</v>
       </c>
       <c r="H1148" t="n">
         <v>26093</v>
@@ -33864,7 +33864,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132553100586</v>
+        <v>38.8132514953613</v>
       </c>
       <c r="H1155" t="n">
         <v>17325</v>
@@ -34154,7 +34154,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1165" t="n">
         <v>25025</v>
@@ -34212,7 +34212,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1167" t="n">
         <v>17311</v>
@@ -34241,7 +34241,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935958862305</v>
+        <v>36.6935997009277</v>
       </c>
       <c r="H1168" t="n">
         <v>18709</v>
@@ -34270,7 +34270,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522880554199</v>
+        <v>36.5522842407227</v>
       </c>
       <c r="H1169" t="n">
         <v>7654</v>
@@ -34299,7 +34299,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1170" t="n">
         <v>11922</v>
@@ -34357,7 +34357,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993919372559</v>
+        <v>36.5993881225586</v>
       </c>
       <c r="H1172" t="n">
         <v>22854</v>
@@ -34444,7 +34444,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.8349075317383</v>
+        <v>36.834903717041</v>
       </c>
       <c r="H1175" t="n">
         <v>14281</v>
@@ -34589,7 +34589,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1180" t="n">
         <v>12217</v>
@@ -34647,7 +34647,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1182" t="n">
         <v>17442</v>
@@ -34763,7 +34763,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1186" t="n">
         <v>16678</v>
@@ -34850,7 +34850,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376625061035</v>
+        <v>33.5376663208008</v>
       </c>
       <c r="H1189" t="n">
         <v>13671</v>
@@ -34908,7 +34908,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202857971191</v>
+        <v>33.8202896118164</v>
       </c>
       <c r="H1191" t="n">
         <v>14410</v>
@@ -34937,7 +34937,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1192" t="n">
         <v>21211</v>
@@ -35053,7 +35053,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275947570801</v>
+        <v>35.3275985717773</v>
       </c>
       <c r="H1196" t="n">
         <v>18810</v>
@@ -35198,7 +35198,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689102172852</v>
+        <v>35.4689064025879</v>
       </c>
       <c r="H1201" t="n">
         <v>10943</v>
@@ -35227,7 +35227,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1202" t="n">
         <v>13284</v>
@@ -35372,7 +35372,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1207" t="n">
         <v>86976</v>
@@ -35401,7 +35401,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1208" t="n">
         <v>107480</v>
@@ -35459,7 +35459,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238048553467</v>
+        <v>31.3238010406494</v>
       </c>
       <c r="H1210" t="n">
         <v>97335</v>
@@ -35517,7 +35517,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890419006348</v>
+        <v>31.8890399932861</v>
       </c>
       <c r="H1212" t="n">
         <v>19682</v>
@@ -35575,7 +35575,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1214" t="n">
         <v>32700</v>
@@ -35604,7 +35604,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477359771729</v>
+        <v>31.7477340698242</v>
       </c>
       <c r="H1215" t="n">
         <v>71954</v>
@@ -35633,7 +35633,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419380187988</v>
+        <v>31.8419399261475</v>
       </c>
       <c r="H1216" t="n">
         <v>29272</v>
@@ -35662,7 +35662,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1217" t="n">
         <v>40121</v>
@@ -35691,7 +35691,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1218" t="n">
         <v>88062</v>
@@ -35720,7 +35720,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608390808105</v>
+        <v>33.1608352661133</v>
       </c>
       <c r="H1219" t="n">
         <v>20873</v>
@@ -35807,7 +35807,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804908752441</v>
+        <v>35.2804946899414</v>
       </c>
       <c r="H1222" t="n">
         <v>55066</v>
@@ -35836,7 +35836,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391830444336</v>
+        <v>35.1391792297363</v>
       </c>
       <c r="H1223" t="n">
         <v>48119</v>
@@ -35952,7 +35952,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558052062988</v>
+        <v>34.0558013916016</v>
       </c>
       <c r="H1227" t="n">
         <v>33020</v>
@@ -36068,7 +36068,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1231" t="n">
         <v>27966</v>
@@ -36126,7 +36126,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160102844238</v>
+        <v>35.5160140991211</v>
       </c>
       <c r="H1233" t="n">
         <v>18372</v>
@@ -36155,7 +36155,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986297607422</v>
+        <v>35.7986335754395</v>
       </c>
       <c r="H1234" t="n">
         <v>21216</v>
@@ -36271,7 +36271,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.023323059082</v>
+        <v>37.0233192443848</v>
       </c>
       <c r="H1238" t="n">
         <v>31944</v>
@@ -36329,7 +36329,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754570007324</v>
+        <v>36.1754608154297</v>
       </c>
       <c r="H1240" t="n">
         <v>21979</v>
@@ -36358,7 +36358,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739440917969</v>
+        <v>34.5739402770996</v>
       </c>
       <c r="H1241" t="n">
         <v>36159</v>
@@ -36532,7 +36532,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955963134766</v>
+        <v>32.5955924987793</v>
       </c>
       <c r="H1247" t="n">
         <v>20275</v>
@@ -36619,7 +36619,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071807861328</v>
+        <v>32.4071846008301</v>
       </c>
       <c r="H1250" t="n">
         <v>26995</v>
@@ -36735,7 +36735,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1254" t="n">
         <v>86029</v>
@@ -36938,7 +36938,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1261" t="n">
         <v>62483</v>
@@ -37083,7 +37083,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099376678467</v>
+        <v>29.1099395751953</v>
       </c>
       <c r="H1266" t="n">
         <v>42903</v>
@@ -37257,7 +37257,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1272" t="n">
         <v>69703</v>
@@ -37286,7 +37286,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338726043701</v>
+        <v>29.5338706970215</v>
       </c>
       <c r="H1273" t="n">
         <v>51566</v>
@@ -37344,7 +37344,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1275" t="n">
         <v>39875</v>
@@ -37373,7 +37373,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1276" t="n">
         <v>33069</v>
@@ -37605,7 +37605,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164901733398</v>
+        <v>29.8164920806885</v>
       </c>
       <c r="H1284" t="n">
         <v>24216</v>
@@ -37663,7 +37663,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643524169922</v>
+        <v>30.6643543243408</v>
       </c>
       <c r="H1286" t="n">
         <v>27493</v>
@@ -37692,7 +37692,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1287" t="n">
         <v>27163</v>
@@ -37808,7 +37808,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940776824951</v>
+        <v>30.9940795898438</v>
       </c>
       <c r="H1291" t="n">
         <v>50126</v>
@@ -37837,7 +37837,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1292" t="n">
         <v>15339</v>
@@ -37953,7 +37953,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288368225098</v>
+        <v>30.4288349151611</v>
       </c>
       <c r="H1296" t="n">
         <v>31760</v>
@@ -38127,7 +38127,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832515716553</v>
+        <v>31.9832496643066</v>
       </c>
       <c r="H1302" t="n">
         <v>58973</v>
@@ -38156,7 +38156,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774574279785</v>
+        <v>32.0774536132812</v>
       </c>
       <c r="H1303" t="n">
         <v>39498</v>
@@ -38330,7 +38330,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.349250793457</v>
+        <v>33.3492546081543</v>
       </c>
       <c r="H1309" t="n">
         <v>34631</v>
@@ -38417,7 +38417,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079429626465</v>
+        <v>33.2079391479492</v>
       </c>
       <c r="H1312" t="n">
         <v>27726</v>
@@ -38533,7 +38533,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.044979095459</v>
+        <v>35.0449752807617</v>
       </c>
       <c r="H1316" t="n">
         <v>82490</v>
@@ -38562,7 +38562,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500129699707</v>
+        <v>34.1500091552734</v>
       </c>
       <c r="H1317" t="n">
         <v>126426</v>
@@ -38707,7 +38707,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056640625</v>
+        <v>30.8056659698486</v>
       </c>
       <c r="H1322" t="n">
         <v>44000</v>
@@ -38765,7 +38765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1324" t="n">
         <v>42930</v>
@@ -38823,7 +38823,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.3709030151367</v>
+        <v>31.370906829834</v>
       </c>
       <c r="H1326" t="n">
         <v>38026</v>
@@ -38852,7 +38852,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172504425049</v>
+        <v>30.6172485351562</v>
       </c>
       <c r="H1327" t="n">
         <v>61320</v>
@@ -38939,7 +38939,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041473388672</v>
+        <v>29.2041454315186</v>
       </c>
       <c r="H1330" t="n">
         <v>38634</v>
@@ -39113,7 +39113,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207656860352</v>
+        <v>28.1207675933838</v>
       </c>
       <c r="H1336" t="n">
         <v>109851</v>
@@ -39229,7 +39229,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1340" t="n">
         <v>55268</v>
@@ -39258,7 +39258,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1341" t="n">
         <v>36968</v>
@@ -39374,7 +39374,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844917297363</v>
+        <v>27.0844898223877</v>
       </c>
       <c r="H1345" t="n">
         <v>66714</v>
@@ -39432,7 +39432,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200092315674</v>
+        <v>27.3200073242188</v>
       </c>
       <c r="H1347" t="n">
         <v>104150</v>
@@ -39519,7 +39519,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902820587158</v>
+        <v>26.9902839660645</v>
       </c>
       <c r="H1350" t="n">
         <v>33485</v>
@@ -39548,7 +39548,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779392242432</v>
+        <v>26.3779373168945</v>
       </c>
       <c r="H1351" t="n">
         <v>128641</v>
@@ -39606,7 +39606,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1353" t="n">
         <v>181757</v>
@@ -39635,7 +39635,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648361206055</v>
+        <v>24.9648342132568</v>
       </c>
       <c r="H1354" t="n">
         <v>138211</v>
@@ -39664,7 +39664,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829730987549</v>
+        <v>25.4829711914062</v>
       </c>
       <c r="H1355" t="n">
         <v>105911</v>
@@ -39838,7 +39838,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011100769043</v>
+        <v>26.0011119842529</v>
       </c>
       <c r="H1361" t="n">
         <v>64528</v>
@@ -39867,7 +39867,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.3887672424316</v>
+        <v>25.388765335083</v>
       </c>
       <c r="H1362" t="n">
         <v>44652</v>
@@ -39896,7 +39896,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003536224365</v>
+        <v>25.2003517150879</v>
       </c>
       <c r="H1363" t="n">
         <v>43761</v>
@@ -39925,7 +39925,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.189525604248</v>
+        <v>26.1895236968994</v>
       </c>
       <c r="H1364" t="n">
         <v>45391</v>
@@ -39954,7 +39954,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076625823975</v>
+        <v>26.7076644897461</v>
       </c>
       <c r="H1365" t="n">
         <v>53357</v>
@@ -40157,7 +40157,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084228515625</v>
+        <v>27.5084209442139</v>
       </c>
       <c r="H1372" t="n">
         <v>44289</v>
@@ -40215,7 +40215,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.696834564209</v>
+        <v>27.6968364715576</v>
       </c>
       <c r="H1374" t="n">
         <v>43847</v>
@@ -51038,6 +51038,35 @@
         <v>23447</v>
       </c>
       <c r="I1747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1748" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>35.2000007629395</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>35.8400001525879</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>34.7599983215332</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>35.8400001525879</v>
+      </c>
+      <c r="G1748" t="n">
+        <v>35.8400001525879</v>
+      </c>
+      <c r="H1748" t="n">
+        <v>19781</v>
+      </c>
+      <c r="I1748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025466918945</v>
+        <v>13.6025457382202</v>
       </c>
       <c r="H2" t="n">
         <v>487001</v>
@@ -485,7 +485,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818511962891</v>
+        <v>13.3818502426147</v>
       </c>
       <c r="H4" t="n">
         <v>54824</v>
@@ -543,7 +543,7 @@
         <v>15.9879999160767</v>
       </c>
       <c r="G6" t="n">
-        <v>14.001898765564</v>
+        <v>14.0018997192383</v>
       </c>
       <c r="H6" t="n">
         <v>24177</v>
@@ -572,7 +572,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8810424804688</v>
+        <v>13.8810434341431</v>
       </c>
       <c r="H7" t="n">
         <v>41257</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934637069702</v>
+        <v>13.7934646606445</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -717,7 +717,7 @@
         <v>15.9739999771118</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9896392822266</v>
+        <v>13.9896383285522</v>
       </c>
       <c r="H12" t="n">
         <v>10618</v>
@@ -775,7 +775,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9598627090454</v>
+        <v>13.9598617553711</v>
       </c>
       <c r="H14" t="n">
         <v>75034</v>
@@ -949,7 +949,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9948930740356</v>
+        <v>13.9948921203613</v>
       </c>
       <c r="H20" t="n">
         <v>34939</v>
@@ -978,7 +978,7 @@
         <v>16.2099990844727</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1963214874268</v>
+        <v>14.1963205337524</v>
       </c>
       <c r="H21" t="n">
         <v>76030</v>
@@ -1007,7 +1007,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130270004272</v>
+        <v>14.7130279541016</v>
       </c>
       <c r="H22" t="n">
         <v>147663</v>
@@ -1036,7 +1036,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692399978638</v>
+        <v>14.6692380905151</v>
       </c>
       <c r="H23" t="n">
         <v>297347</v>
@@ -1094,7 +1094,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260726928711</v>
+        <v>15.3260717391968</v>
       </c>
       <c r="H25" t="n">
         <v>73618</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881816864014</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1152,7 +1152,7 @@
         <v>16.8379993438721</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7463083267212</v>
+        <v>14.7463073730469</v>
       </c>
       <c r="H27" t="n">
         <v>68742</v>
@@ -1181,7 +1181,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916873931885</v>
+        <v>14.8916883468628</v>
       </c>
       <c r="H28" t="n">
         <v>63118</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757623672485</v>
+        <v>14.9757614135742</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1268,7 +1268,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G31" t="n">
-        <v>14.520357131958</v>
+        <v>14.5203590393066</v>
       </c>
       <c r="H31" t="n">
         <v>43925</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881816864014</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881816864014</v>
+        <v>14.8881826400757</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1355,7 +1355,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378751754761</v>
+        <v>14.5378761291504</v>
       </c>
       <c r="H34" t="n">
         <v>28201</v>
@@ -1442,7 +1442,7 @@
         <v>16.3920001983643</v>
       </c>
       <c r="G37" t="n">
-        <v>14.355712890625</v>
+        <v>14.3557119369507</v>
       </c>
       <c r="H37" t="n">
         <v>37432</v>
@@ -1471,7 +1471,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628803253174</v>
+        <v>14.2628812789917</v>
       </c>
       <c r="H38" t="n">
         <v>11160</v>
@@ -1500,7 +1500,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H39" t="n">
         <v>17569</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006048202515</v>
+        <v>14.8006038665771</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1616,7 +1616,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443956375122</v>
+        <v>14.8443946838379</v>
       </c>
       <c r="H43" t="n">
         <v>115888</v>
@@ -1645,7 +1645,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692399978638</v>
+        <v>14.6692380905151</v>
       </c>
       <c r="H44" t="n">
         <v>35731</v>
@@ -1674,7 +1674,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7655754089355</v>
+        <v>14.7655763626099</v>
       </c>
       <c r="H45" t="n">
         <v>31415</v>
@@ -1732,7 +1732,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708282470703</v>
+        <v>14.7708301544189</v>
       </c>
       <c r="H47" t="n">
         <v>59163</v>
@@ -1761,7 +1761,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633401870728</v>
+        <v>15.0633392333984</v>
       </c>
       <c r="H48" t="n">
         <v>87381</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.1369037628174</v>
+        <v>15.136905670166</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1819,7 +1819,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1262588500977</v>
+        <v>14.126259803772</v>
       </c>
       <c r="H50" t="n">
         <v>74499</v>
@@ -1848,7 +1848,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.26988697052</v>
+        <v>14.2698879241943</v>
       </c>
       <c r="H51" t="n">
         <v>29049</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -1964,7 +1964,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H55" t="n">
         <v>37252</v>
@@ -1993,7 +1993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H56" t="n">
         <v>23379</v>
@@ -2022,7 +2022,7 @@
         <v>14.5</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H57" t="n">
         <v>15626</v>
@@ -2080,7 +2080,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>12.6111660003662</v>
+        <v>12.6111669540405</v>
       </c>
       <c r="H59" t="n">
         <v>41726</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.0714197158813</v>
+        <v>10.071418762207</v>
       </c>
       <c r="H63" t="n">
         <v>21708</v>
@@ -2225,7 +2225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>11.0347728729248</v>
+        <v>11.0347719192505</v>
       </c>
       <c r="H64" t="n">
         <v>37959</v>
@@ -2283,7 +2283,7 @@
         <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>9.63353157043457</v>
+        <v>9.63353061676025</v>
       </c>
       <c r="H66" t="n">
         <v>74779</v>
@@ -2312,7 +2312,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>9.45837593078613</v>
+        <v>9.45837497711182</v>
       </c>
       <c r="H67" t="n">
         <v>48156</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806465148926</v>
+        <v>9.10806560516357</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2428,7 +2428,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651287078857</v>
+        <v>8.76651477813721</v>
       </c>
       <c r="H71" t="n">
         <v>44594</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494094848633</v>
+        <v>8.54494190216064</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2515,7 +2515,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.67017650604248</v>
+        <v>8.6701774597168</v>
       </c>
       <c r="H74" t="n">
         <v>15416</v>
@@ -2573,7 +2573,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415237426758</v>
+        <v>8.92415142059326</v>
       </c>
       <c r="H76" t="n">
         <v>26972</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04500961303711</v>
+        <v>9.04501056671143</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2631,7 +2631,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G78" t="n">
-        <v>9.3532829284668</v>
+        <v>9.35328388214111</v>
       </c>
       <c r="H78" t="n">
         <v>29100</v>
@@ -2689,7 +2689,7 @@
         <v>11.7519998550415</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2921133041382</v>
+        <v>10.2921152114868</v>
       </c>
       <c r="H80" t="n">
         <v>20417</v>
@@ -2718,7 +2718,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G81" t="n">
-        <v>10.5968837738037</v>
+        <v>10.596884727478</v>
       </c>
       <c r="H81" t="n">
         <v>17348</v>
@@ -2776,7 +2776,7 @@
         <v>12.46399974823</v>
       </c>
       <c r="G83" t="n">
-        <v>10.9156665802002</v>
+        <v>10.9156656265259</v>
       </c>
       <c r="H83" t="n">
         <v>6741</v>
@@ -2950,7 +2950,7 @@
         <v>13.3479995727539</v>
       </c>
       <c r="G89" t="n">
-        <v>11.6898517608643</v>
+        <v>11.6898508071899</v>
       </c>
       <c r="H89" t="n">
         <v>19363</v>
@@ -2979,7 +2979,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G90" t="n">
-        <v>12.0068826675415</v>
+        <v>12.0068817138672</v>
       </c>
       <c r="H90" t="n">
         <v>11410</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229694366455</v>
+        <v>11.8229684829712</v>
       </c>
       <c r="H91" t="n">
         <v>16703</v>
@@ -3066,7 +3066,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0347728729248</v>
+        <v>11.0347719192505</v>
       </c>
       <c r="H93" t="n">
         <v>52489</v>
@@ -3124,7 +3124,7 @@
         <v>12.5</v>
       </c>
       <c r="G95" t="n">
-        <v>10.9471950531006</v>
+        <v>10.9471940994263</v>
       </c>
       <c r="H95" t="n">
         <v>49105</v>
@@ -3153,7 +3153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143989562988</v>
+        <v>10.6143999099731</v>
       </c>
       <c r="H96" t="n">
         <v>30171</v>
@@ -3182,7 +3182,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.465518951416</v>
+        <v>10.4655179977417</v>
       </c>
       <c r="H97" t="n">
         <v>30855</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.3078784942627</v>
+        <v>10.307879447937</v>
       </c>
       <c r="H100" t="n">
         <v>7478</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465744018555</v>
+        <v>10.2465734481812</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3327,7 +3327,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075559616089</v>
+        <v>10.5075550079346</v>
       </c>
       <c r="H102" t="n">
         <v>41323</v>
@@ -3356,7 +3356,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616926193237</v>
+        <v>10.6616916656494</v>
       </c>
       <c r="H103" t="n">
         <v>12365</v>
@@ -3443,7 +3443,7 @@
         <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>10.5093069076538</v>
+        <v>10.5093059539795</v>
       </c>
       <c r="H106" t="n">
         <v>15170</v>
@@ -3501,7 +3501,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220272064209</v>
+        <v>11.3220262527466</v>
       </c>
       <c r="H108" t="n">
         <v>36330</v>
@@ -3559,7 +3559,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726610183716</v>
+        <v>11.4726600646973</v>
       </c>
       <c r="H110" t="n">
         <v>21522</v>
@@ -3617,7 +3617,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667583465576</v>
+        <v>11.8667593002319</v>
       </c>
       <c r="H112" t="n">
         <v>27613</v>
@@ -3646,7 +3646,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119766235352</v>
+        <v>12.1119756698608</v>
       </c>
       <c r="H113" t="n">
         <v>32594</v>
@@ -3675,7 +3675,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834657669067</v>
+        <v>12.3834667205811</v>
       </c>
       <c r="H114" t="n">
         <v>29369</v>
@@ -3704,7 +3704,7 @@
         <v>14.2419996261597</v>
       </c>
       <c r="G115" t="n">
-        <v>12.4727954864502</v>
+        <v>12.4727945327759</v>
       </c>
       <c r="H115" t="n">
         <v>41546</v>
@@ -3733,7 +3733,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G116" t="n">
-        <v>12.0506725311279</v>
+        <v>12.0506706237793</v>
       </c>
       <c r="H116" t="n">
         <v>330572</v>
@@ -3791,7 +3791,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922233581543</v>
+        <v>12.3922252655029</v>
       </c>
       <c r="H118" t="n">
         <v>16297</v>
@@ -3878,7 +3878,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.7600498199463</v>
+        <v>12.760048866272</v>
       </c>
       <c r="H121" t="n">
         <v>53970</v>
@@ -3907,7 +3907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614782333374</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H122" t="n">
         <v>27467</v>
@@ -3936,7 +3936,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.3100357055664</v>
+        <v>13.3100366592407</v>
       </c>
       <c r="H123" t="n">
         <v>25697</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901498794556</v>
+        <v>12.5901489257812</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4081,7 +4081,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H128" t="n">
         <v>20883</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.211950302124</v>
+        <v>13.2119512557983</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4139,7 +4139,7 @@
         <v>15.2980003356934</v>
       </c>
       <c r="G130" t="n">
-        <v>13.3976135253906</v>
+        <v>13.3976144790649</v>
       </c>
       <c r="H130" t="n">
         <v>7245</v>
@@ -4168,7 +4168,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361476898193</v>
+        <v>13.4361486434937</v>
       </c>
       <c r="H131" t="n">
         <v>17251</v>
@@ -4197,7 +4197,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>13.3030300140381</v>
+        <v>13.3030309677124</v>
       </c>
       <c r="H132" t="n">
         <v>11780</v>
@@ -4226,7 +4226,7 @@
         <v>15.4460000991821</v>
       </c>
       <c r="G133" t="n">
-        <v>13.5272283554077</v>
+        <v>13.527229309082</v>
       </c>
       <c r="H133" t="n">
         <v>18810</v>
@@ -4284,7 +4284,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>13.2679986953735</v>
+        <v>13.2679996490479</v>
       </c>
       <c r="H135" t="n">
         <v>4036</v>
@@ -4313,7 +4313,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H136" t="n">
         <v>7773</v>
@@ -4342,7 +4342,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H137" t="n">
         <v>5525</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681613922119</v>
+        <v>13.1681604385376</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4400,7 +4400,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805835723877</v>
+        <v>13.0805826187134</v>
       </c>
       <c r="H139" t="n">
         <v>13088</v>
@@ -4458,7 +4458,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G141" t="n">
-        <v>13.4606695175171</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H141" t="n">
         <v>4654</v>
@@ -4516,7 +4516,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>13.1979360580444</v>
+        <v>13.1979370117188</v>
       </c>
       <c r="H143" t="n">
         <v>3314</v>
@@ -4545,7 +4545,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928440093994</v>
+        <v>13.0928430557251</v>
       </c>
       <c r="H144" t="n">
         <v>3240</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504835128784</v>
+        <v>13.2504844665527</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4661,7 +4661,7 @@
         <v>15.0520000457764</v>
       </c>
       <c r="G148" t="n">
-        <v>13.1821737289429</v>
+        <v>13.1821727752686</v>
       </c>
       <c r="H148" t="n">
         <v>863</v>
@@ -4690,7 +4690,7 @@
         <v>15.0019998550415</v>
       </c>
       <c r="G149" t="n">
-        <v>13.1383838653564</v>
+        <v>13.1383848190308</v>
       </c>
       <c r="H149" t="n">
         <v>7310</v>
@@ -4719,7 +4719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H150" t="n">
         <v>1530</v>
@@ -4748,7 +4748,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G151" t="n">
-        <v>13.4606695175171</v>
+        <v>13.4606704711914</v>
       </c>
       <c r="H151" t="n">
         <v>14307</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6621007919312</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4864,7 +4864,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G155" t="n">
-        <v>13.4694290161133</v>
+        <v>13.469428062439</v>
       </c>
       <c r="H155" t="n">
         <v>2209</v>
@@ -4922,7 +4922,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555774688721</v>
+        <v>13.3555765151978</v>
       </c>
       <c r="H157" t="n">
         <v>9479</v>
@@ -4951,7 +4951,7 @@
         <v>14.9980001449585</v>
       </c>
       <c r="G158" t="n">
-        <v>13.1348829269409</v>
+        <v>13.1348819732666</v>
       </c>
       <c r="H158" t="n">
         <v>7412</v>
@@ -5009,7 +5009,7 @@
         <v>14.5</v>
       </c>
       <c r="G160" t="n">
-        <v>12.6987447738647</v>
+        <v>12.6987457275391</v>
       </c>
       <c r="H160" t="n">
         <v>8710</v>
@@ -5038,7 +5038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H161" t="n">
         <v>8576</v>
@@ -5067,7 +5067,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309192657471</v>
+        <v>12.3309183120728</v>
       </c>
       <c r="H162" t="n">
         <v>17829</v>
@@ -5125,7 +5125,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393543243408</v>
+        <v>12.5393533706665</v>
       </c>
       <c r="H164" t="n">
         <v>30378</v>
@@ -5183,7 +5183,7 @@
         <v>14.1940002441406</v>
       </c>
       <c r="G166" t="n">
-        <v>12.430757522583</v>
+        <v>12.4307584762573</v>
       </c>
       <c r="H166" t="n">
         <v>16661</v>
@@ -5212,7 +5212,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484354019165</v>
+        <v>12.3484363555908</v>
       </c>
       <c r="H167" t="n">
         <v>9897</v>
@@ -5241,7 +5241,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.409740447998</v>
+        <v>12.4097385406494</v>
       </c>
       <c r="H168" t="n">
         <v>11733</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H171" t="n">
         <v>7984</v>
@@ -5357,7 +5357,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G172" t="n">
-        <v>13.5132179260254</v>
+        <v>13.5132169723511</v>
       </c>
       <c r="H172" t="n">
         <v>10655</v>
@@ -5386,7 +5386,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.686619758606</v>
+        <v>13.6866207122803</v>
       </c>
       <c r="H173" t="n">
         <v>4657</v>
@@ -5415,7 +5415,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G174" t="n">
-        <v>13.6533403396606</v>
+        <v>13.653341293335</v>
       </c>
       <c r="H174" t="n">
         <v>7527</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6621007919312</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5473,7 +5473,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>13.2679986953735</v>
+        <v>13.2679996490479</v>
       </c>
       <c r="H176" t="n">
         <v>5800</v>
@@ -5502,7 +5502,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H177" t="n">
         <v>16366</v>
@@ -5531,7 +5531,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H178" t="n">
         <v>14964</v>
@@ -5618,7 +5618,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493532180786</v>
+        <v>13.9493541717529</v>
       </c>
       <c r="H181" t="n">
         <v>30984</v>
@@ -5937,7 +5937,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445827484131</v>
+        <v>13.6445837020874</v>
       </c>
       <c r="H192" t="n">
         <v>31164</v>
@@ -6053,7 +6053,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>13.5920372009277</v>
+        <v>13.5920362472534</v>
       </c>
       <c r="H196" t="n">
         <v>10776</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614782333374</v>
+        <v>12.9614791870117</v>
       </c>
       <c r="H199" t="n">
         <v>7759</v>
@@ -6169,7 +6169,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G200" t="n">
-        <v>13.2767562866211</v>
+        <v>13.2767572402954</v>
       </c>
       <c r="H200" t="n">
         <v>6789</v>
@@ -6198,7 +6198,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H201" t="n">
         <v>43057</v>
@@ -6256,7 +6256,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G203" t="n">
-        <v>14.3101720809937</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H203" t="n">
         <v>21909</v>
@@ -6285,7 +6285,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H204" t="n">
         <v>59951</v>
@@ -6314,7 +6314,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G205" t="n">
-        <v>14.8531522750854</v>
+        <v>14.8531532287598</v>
       </c>
       <c r="H205" t="n">
         <v>52305</v>
@@ -6459,7 +6459,7 @@
         <v>16.5</v>
       </c>
       <c r="G210" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H210" t="n">
         <v>16575</v>
@@ -6517,7 +6517,7 @@
         <v>16.5</v>
       </c>
       <c r="G212" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H212" t="n">
         <v>5728</v>
@@ -6546,7 +6546,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H213" t="n">
         <v>3813</v>
@@ -6575,7 +6575,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955137252808</v>
+        <v>14.6955146789551</v>
       </c>
       <c r="H214" t="n">
         <v>13259</v>
@@ -6604,7 +6604,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H215" t="n">
         <v>13883</v>
@@ -6633,7 +6633,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452014923096</v>
+        <v>14.3452024459839</v>
       </c>
       <c r="H216" t="n">
         <v>9351</v>
@@ -6807,7 +6807,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H222" t="n">
         <v>6474</v>
@@ -6836,7 +6836,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044584274292</v>
+        <v>13.5044593811035</v>
       </c>
       <c r="H223" t="n">
         <v>17777</v>
@@ -6865,7 +6865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H224" t="n">
         <v>45360</v>
@@ -6923,7 +6923,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.31178855896</v>
+        <v>13.3117876052856</v>
       </c>
       <c r="H226" t="n">
         <v>5423</v>
@@ -6952,7 +6952,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.101601600647</v>
+        <v>13.1016025543213</v>
       </c>
       <c r="H227" t="n">
         <v>2440</v>
@@ -6981,7 +6981,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G228" t="n">
-        <v>13.7321615219116</v>
+        <v>13.7321605682373</v>
       </c>
       <c r="H228" t="n">
         <v>2543</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7039,7 +7039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H230" t="n">
         <v>2511</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6621007919312</v>
+        <v>13.6620998382568</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7155,7 +7155,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H234" t="n">
         <v>16461</v>
@@ -7184,7 +7184,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G235" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H235" t="n">
         <v>16963</v>
@@ -7213,7 +7213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H236" t="n">
         <v>8277</v>
@@ -7329,7 +7329,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H240" t="n">
         <v>23600</v>
@@ -7358,7 +7358,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H241" t="n">
         <v>4135</v>
@@ -7387,7 +7387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H242" t="n">
         <v>10822</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7503,7 +7503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H246" t="n">
         <v>7116</v>
@@ -7619,7 +7619,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H250" t="n">
         <v>41070</v>
@@ -7677,7 +7677,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G252" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H252" t="n">
         <v>3351</v>
@@ -7706,7 +7706,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993673324585</v>
+        <v>13.3993654251099</v>
       </c>
       <c r="H253" t="n">
         <v>8244</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022232055664</v>
+        <v>13.8022222518921</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7764,7 +7764,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G255" t="n">
-        <v>13.4869441986084</v>
+        <v>13.4869432449341</v>
       </c>
       <c r="H255" t="n">
         <v>3852</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.627067565918</v>
+        <v>13.6270666122437</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219745635986</v>
+        <v>13.5219736099243</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7967,7 +7967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197383880615</v>
+        <v>13.8197374343872</v>
       </c>
       <c r="H262" t="n">
         <v>19414</v>
@@ -7996,7 +7996,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773778915405</v>
+        <v>13.9773797988892</v>
       </c>
       <c r="H263" t="n">
         <v>14625</v>
@@ -8083,7 +8083,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G266" t="n">
-        <v>14.3101720809937</v>
+        <v>14.310173034668</v>
       </c>
       <c r="H266" t="n">
         <v>8011</v>
@@ -8112,7 +8112,7 @@
         <v>16.5</v>
       </c>
       <c r="G267" t="n">
-        <v>14.4502964019775</v>
+        <v>14.4502973556519</v>
       </c>
       <c r="H267" t="n">
         <v>21797</v>
@@ -8170,7 +8170,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>14.3627185821533</v>
+        <v>14.3627195358276</v>
       </c>
       <c r="H269" t="n">
         <v>28438</v>
@@ -8199,7 +8199,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576246261597</v>
       </c>
       <c r="H270" t="n">
         <v>5152</v>
@@ -8228,7 +8228,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028409957886</v>
+        <v>14.5028419494629</v>
       </c>
       <c r="H271" t="n">
         <v>6060</v>
@@ -8257,7 +8257,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028409957886</v>
+        <v>14.5028419494629</v>
       </c>
       <c r="H272" t="n">
         <v>8570</v>
@@ -8286,7 +8286,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079359054565</v>
+        <v>14.6079368591309</v>
       </c>
       <c r="H273" t="n">
         <v>7891</v>
@@ -8402,7 +8402,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.257625579834</v>
+        <v>14.2576246261597</v>
       </c>
       <c r="H277" t="n">
         <v>6898</v>
@@ -8460,7 +8460,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G279" t="n">
-        <v>15.2034645080566</v>
+        <v>15.2034635543823</v>
       </c>
       <c r="H279" t="n">
         <v>80397</v>
@@ -8489,7 +8489,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G280" t="n">
-        <v>15.4311656951904</v>
+        <v>15.4311647415161</v>
       </c>
       <c r="H280" t="n">
         <v>50717</v>
@@ -8547,7 +8547,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989912033081</v>
+        <v>15.7989921569824</v>
       </c>
       <c r="H282" t="n">
         <v>60104</v>
@@ -8576,7 +8576,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888023376465</v>
+        <v>15.5888042449951</v>
       </c>
       <c r="H283" t="n">
         <v>32761</v>
@@ -8634,7 +8634,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G285" t="n">
-        <v>15.7814769744873</v>
+        <v>15.7814750671387</v>
       </c>
       <c r="H285" t="n">
         <v>16215</v>
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397361755371</v>
+        <v>16.6397342681885</v>
       </c>
       <c r="H288" t="n">
         <v>19711</v>
@@ -8837,7 +8837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.340353012085</v>
+        <v>17.3403549194336</v>
       </c>
       <c r="H292" t="n">
         <v>108964</v>
@@ -8924,7 +8924,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>17.8220310211182</v>
+        <v>17.8220329284668</v>
       </c>
       <c r="H295" t="n">
         <v>52008</v>
@@ -8953,7 +8953,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906681060791</v>
+        <v>17.6906661987305</v>
       </c>
       <c r="H296" t="n">
         <v>36908</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.2527770996094</v>
+        <v>17.252779006958</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9011,7 +9011,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6468772888184</v>
+        <v>17.646879196167</v>
       </c>
       <c r="H298" t="n">
         <v>49334</v>
@@ -9040,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="G299" t="n">
-        <v>17.515510559082</v>
+        <v>17.5155086517334</v>
       </c>
       <c r="H299" t="n">
         <v>21074</v>
@@ -9301,7 +9301,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>19.3108501434326</v>
+        <v>19.310848236084</v>
       </c>
       <c r="H308" t="n">
         <v>58530</v>
@@ -9417,7 +9417,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H312" t="n">
         <v>23897</v>
@@ -9446,7 +9446,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356964111328</v>
+        <v>19.1356983184814</v>
       </c>
       <c r="H313" t="n">
         <v>16234</v>
@@ -9620,7 +9620,7 @@
         <v>22</v>
       </c>
       <c r="G319" t="n">
-        <v>19.2670631408691</v>
+        <v>19.2670612335205</v>
       </c>
       <c r="H319" t="n">
         <v>26626</v>
@@ -9794,7 +9794,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>19.6611652374268</v>
+        <v>19.6611614227295</v>
       </c>
       <c r="H325" t="n">
         <v>22459</v>
@@ -9910,7 +9910,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729610443115</v>
+        <v>18.8729591369629</v>
       </c>
       <c r="H329" t="n">
         <v>14665</v>
@@ -9939,7 +9939,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H330" t="n">
         <v>9202</v>
@@ -10142,7 +10142,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415962219238</v>
+        <v>18.7415943145752</v>
       </c>
       <c r="H337" t="n">
         <v>8572</v>
@@ -10171,7 +10171,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>19.3546409606934</v>
+        <v>19.3546390533447</v>
       </c>
       <c r="H338" t="n">
         <v>9204</v>
@@ -10200,7 +10200,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>18.9167518615723</v>
+        <v>18.9167499542236</v>
       </c>
       <c r="H339" t="n">
         <v>11503</v>
@@ -10345,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912868499756</v>
+        <v>18.3912887573242</v>
       </c>
       <c r="H344" t="n">
         <v>18146</v>
@@ -10374,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912868499756</v>
+        <v>18.3912887573242</v>
       </c>
       <c r="H345" t="n">
         <v>7042</v>
@@ -10432,7 +10432,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>19.2797565460205</v>
+        <v>19.2797546386719</v>
       </c>
       <c r="H347" t="n">
         <v>18924</v>
@@ -10461,7 +10461,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.723991394043</v>
+        <v>19.7239894866943</v>
       </c>
       <c r="H348" t="n">
         <v>25636</v>
@@ -10519,7 +10519,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G350" t="n">
-        <v>20.3903388977051</v>
+        <v>20.3903408050537</v>
       </c>
       <c r="H350" t="n">
         <v>39422</v>
@@ -10722,7 +10722,7 @@
         <v>22.25</v>
       </c>
       <c r="G357" t="n">
-        <v>19.7684135437012</v>
+        <v>19.7684116363525</v>
       </c>
       <c r="H357" t="n">
         <v>47937</v>
@@ -10751,7 +10751,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G358" t="n">
-        <v>19.9461078643799</v>
+        <v>19.9461059570312</v>
       </c>
       <c r="H358" t="n">
         <v>49210</v>
@@ -11012,7 +11012,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H367" t="n">
         <v>19035</v>
@@ -11041,7 +11041,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2570667266846</v>
+        <v>20.2570686340332</v>
       </c>
       <c r="H368" t="n">
         <v>25835</v>
@@ -11070,7 +11070,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455383300781</v>
+        <v>21.1455364227295</v>
       </c>
       <c r="H369" t="n">
         <v>96384</v>
@@ -11186,7 +11186,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>23.2778625488281</v>
+        <v>23.2778606414795</v>
       </c>
       <c r="H373" t="n">
         <v>72531</v>
@@ -11244,7 +11244,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>23.2778625488281</v>
+        <v>23.2778606414795</v>
       </c>
       <c r="H375" t="n">
         <v>34567</v>
@@ -11302,7 +11302,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.144588470459</v>
+        <v>23.1445903778076</v>
       </c>
       <c r="H377" t="n">
         <v>33185</v>
@@ -11360,7 +11360,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.6786155700684</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H379" t="n">
         <v>1533317</v>
@@ -11418,7 +11418,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.6786155700684</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H381" t="n">
         <v>46241</v>
@@ -11534,7 +11534,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5009269714355</v>
+        <v>21.5009250640869</v>
       </c>
       <c r="H385" t="n">
         <v>66958</v>
@@ -11563,7 +11563,7 @@
         <v>24</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H386" t="n">
         <v>27193</v>
@@ -11592,7 +11592,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011142730713</v>
+        <v>21.1011161804199</v>
       </c>
       <c r="H387" t="n">
         <v>8616</v>
@@ -11708,7 +11708,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901515960693</v>
+        <v>20.7901496887207</v>
       </c>
       <c r="H391" t="n">
         <v>21903</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11766,7 +11766,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G393" t="n">
-        <v>20.6124591827393</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H393" t="n">
         <v>23385</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11853,7 +11853,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G396" t="n">
-        <v>20.6124591827393</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H396" t="n">
         <v>21826</v>
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
       <c r="G399" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H399" t="n">
         <v>85005</v>
@@ -12027,7 +12027,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.6786155700684</v>
+        <v>21.678617477417</v>
       </c>
       <c r="H402" t="n">
         <v>58589</v>
@@ -12143,7 +12143,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G406" t="n">
-        <v>20.6124591827393</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H406" t="n">
         <v>42941</v>
@@ -12201,7 +12201,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>20.6124591827393</v>
+        <v>20.6124572753906</v>
       </c>
       <c r="H408" t="n">
         <v>17907</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234199523926</v>
+        <v>20.9234218597412</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12317,7 +12317,7 @@
         <v>24</v>
       </c>
       <c r="G412" t="n">
-        <v>21.3232326507568</v>
+        <v>21.3232307434082</v>
       </c>
       <c r="H412" t="n">
         <v>32846</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115112304688</v>
+        <v>22.6115093231201</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12462,7 +12462,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3893947601318</v>
+        <v>22.3893928527832</v>
       </c>
       <c r="H417" t="n">
         <v>9809</v>
@@ -12491,7 +12491,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>22.2561206817627</v>
+        <v>22.2561225891113</v>
       </c>
       <c r="H418" t="n">
         <v>18147</v>
@@ -12520,7 +12520,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5226650238037</v>
+        <v>22.5226631164551</v>
       </c>
       <c r="H419" t="n">
         <v>40477</v>
@@ -12549,7 +12549,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>22.3893947601318</v>
+        <v>22.3893928527832</v>
       </c>
       <c r="H420" t="n">
         <v>10509</v>
@@ -12578,7 +12578,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224739074707</v>
+        <v>22.9224700927734</v>
       </c>
       <c r="H421" t="n">
         <v>20723</v>
@@ -12607,7 +12607,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>23.0113182067871</v>
+        <v>23.0113201141357</v>
       </c>
       <c r="H422" t="n">
         <v>22051</v>
@@ -12636,7 +12636,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551746368408</v>
+        <v>24.2551765441895</v>
       </c>
       <c r="H423" t="n">
         <v>80709</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444011688232</v>
+        <v>23.5444030761719</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12752,7 +12752,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886341094971</v>
+        <v>23.9886322021484</v>
       </c>
       <c r="H427" t="n">
         <v>21987</v>
@@ -12781,7 +12781,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772930145264</v>
+        <v>24.4772911071777</v>
       </c>
       <c r="H428" t="n">
         <v>27149</v>
@@ -12810,7 +12810,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>24.1219043731689</v>
+        <v>24.1219024658203</v>
       </c>
       <c r="H429" t="n">
         <v>41301</v>
@@ -12839,7 +12839,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>24.0774803161621</v>
+        <v>24.0774822235107</v>
       </c>
       <c r="H430" t="n">
         <v>23999</v>
@@ -12868,7 +12868,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>24.9215240478516</v>
+        <v>24.9215259552002</v>
       </c>
       <c r="H431" t="n">
         <v>25118</v>
@@ -12897,7 +12897,7 @@
         <v>27.5</v>
       </c>
       <c r="G432" t="n">
-        <v>24.4328708648682</v>
+        <v>24.4328689575195</v>
       </c>
       <c r="H432" t="n">
         <v>17561</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661373138428</v>
+        <v>24.5661392211914</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -13042,7 +13042,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>25.0103721618652</v>
+        <v>25.0103740692139</v>
       </c>
       <c r="H437" t="n">
         <v>16754</v>
@@ -13129,7 +13129,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H440" t="n">
         <v>28408</v>
@@ -13187,7 +13187,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G442" t="n">
-        <v>26.8317317962646</v>
+        <v>26.8317337036133</v>
       </c>
       <c r="H442" t="n">
         <v>23385</v>
@@ -13216,7 +13216,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>26.9205780029297</v>
+        <v>26.9205799102783</v>
       </c>
       <c r="H443" t="n">
         <v>23035</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425071716309</v>
+        <v>27.5425090789795</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13303,7 +13303,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G446" t="n">
-        <v>28.6975173950195</v>
+        <v>28.6975154876709</v>
       </c>
       <c r="H446" t="n">
         <v>109999</v>
@@ -13332,7 +13332,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300270080566</v>
       </c>
       <c r="H447" t="n">
         <v>138213</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967567443848</v>
+        <v>30.2967548370361</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13419,7 +13419,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636756896973</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H450" t="n">
         <v>69374</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527149200439</v>
+        <v>29.4527168273926</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13506,7 +13506,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748332977295</v>
+        <v>29.6748352050781</v>
       </c>
       <c r="H453" t="n">
         <v>18449</v>
@@ -13535,7 +13535,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300289154053</v>
+        <v>30.4300270080566</v>
       </c>
       <c r="H454" t="n">
         <v>27063</v>
@@ -13651,7 +13651,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H458" t="n">
         <v>38519</v>
@@ -13680,7 +13680,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311641693115</v>
+        <v>28.0311622619629</v>
       </c>
       <c r="H459" t="n">
         <v>26817</v>
@@ -13738,7 +13738,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.4753971099854</v>
+        <v>28.475399017334</v>
       </c>
       <c r="H461" t="n">
         <v>73902</v>
@@ -13767,7 +13767,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H462" t="n">
         <v>26586</v>
@@ -13796,7 +13796,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867401123047</v>
+        <v>27.9867420196533</v>
       </c>
       <c r="H463" t="n">
         <v>39977</v>
@@ -13854,7 +13854,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863636016846</v>
       </c>
       <c r="H465" t="n">
         <v>29892</v>
@@ -13883,7 +13883,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>28.1644344329834</v>
+        <v>28.164436340332</v>
       </c>
       <c r="H466" t="n">
         <v>19936</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14028,7 +14028,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406112670898</v>
+        <v>31.5406131744385</v>
       </c>
       <c r="H471" t="n">
         <v>48516</v>
@@ -14086,7 +14086,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H473" t="n">
         <v>41695</v>
@@ -14202,7 +14202,7 @@
         <v>37</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8733100891113</v>
+        <v>32.8733139038086</v>
       </c>
       <c r="H477" t="n">
         <v>43808</v>
@@ -14376,7 +14376,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H483" t="n">
         <v>61904</v>
@@ -14405,7 +14405,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>35.4942932128906</v>
+        <v>35.4942970275879</v>
       </c>
       <c r="H484" t="n">
         <v>95655</v>
@@ -14463,7 +14463,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617835998535</v>
+        <v>33.7617797851562</v>
       </c>
       <c r="H486" t="n">
         <v>58518</v>
@@ -14521,7 +14521,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398544311523</v>
+        <v>33.1398506164551</v>
       </c>
       <c r="H488" t="n">
         <v>34481</v>
@@ -14550,7 +14550,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065879821777</v>
+        <v>33.0065841674805</v>
       </c>
       <c r="H489" t="n">
         <v>27315</v>
@@ -14579,7 +14579,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H490" t="n">
         <v>30081</v>
@@ -14608,7 +14608,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H491" t="n">
         <v>10757</v>
@@ -14637,7 +14637,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>32.8288879394531</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H492" t="n">
         <v>26262</v>
@@ -14695,7 +14695,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954322814941</v>
+        <v>33.0954284667969</v>
       </c>
       <c r="H494" t="n">
         <v>20925</v>
@@ -14782,7 +14782,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G497" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H497" t="n">
         <v>23360</v>
@@ -14869,7 +14869,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G500" t="n">
-        <v>30.1634883880615</v>
+        <v>30.1634864807129</v>
       </c>
       <c r="H500" t="n">
         <v>80023</v>
@@ -14985,7 +14985,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G504" t="n">
-        <v>31.1852226257324</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H504" t="n">
         <v>25156</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296524047852</v>
+        <v>31.2296504974365</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15043,7 +15043,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G506" t="n">
-        <v>31.1852226257324</v>
+        <v>31.1852245330811</v>
       </c>
       <c r="H506" t="n">
         <v>14367</v>
@@ -15101,7 +15101,7 @@
         <v>37</v>
       </c>
       <c r="G508" t="n">
-        <v>32.8733100891113</v>
+        <v>32.8733139038086</v>
       </c>
       <c r="H508" t="n">
         <v>20299</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177360534668</v>
+        <v>32.9177398681641</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15159,7 +15159,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071517944336</v>
+        <v>31.8071556091309</v>
       </c>
       <c r="H510" t="n">
         <v>24075</v>
@@ -15246,7 +15246,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510139465332</v>
+        <v>33.0510063171387</v>
       </c>
       <c r="H513" t="n">
         <v>30830</v>
@@ -15275,7 +15275,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508209228516</v>
+        <v>33.4508171081543</v>
       </c>
       <c r="H514" t="n">
         <v>66935</v>
@@ -15391,7 +15391,7 @@
         <v>36.9500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>32.8288879394531</v>
+        <v>32.8288917541504</v>
       </c>
       <c r="H518" t="n">
         <v>13845</v>
@@ -15478,7 +15478,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>33.3619689941406</v>
+        <v>33.3619728088379</v>
       </c>
       <c r="H521" t="n">
         <v>16885</v>
@@ -15507,7 +15507,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954322814941</v>
+        <v>33.0954284667969</v>
       </c>
       <c r="H522" t="n">
         <v>24452</v>
@@ -15536,7 +15536,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729354858398</v>
+        <v>33.6729393005371</v>
       </c>
       <c r="H523" t="n">
         <v>18883</v>
@@ -15565,7 +15565,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G524" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H524" t="n">
         <v>40082</v>
@@ -15594,7 +15594,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H525" t="n">
         <v>30151</v>
@@ -15681,7 +15681,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H528" t="n">
         <v>23614</v>
@@ -15739,7 +15739,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>32.5179214477539</v>
+        <v>32.5179252624512</v>
       </c>
       <c r="H530" t="n">
         <v>12547</v>
@@ -15768,7 +15768,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>33.5840911865234</v>
+        <v>33.5840873718262</v>
       </c>
       <c r="H531" t="n">
         <v>37158</v>
@@ -15855,7 +15855,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H534" t="n">
         <v>20804</v>
@@ -15884,7 +15884,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G535" t="n">
-        <v>33.2287063598633</v>
+        <v>33.228702545166</v>
       </c>
       <c r="H535" t="n">
         <v>20158</v>
@@ -16058,7 +16058,7 @@
         <v>36.75</v>
       </c>
       <c r="G541" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H541" t="n">
         <v>30426</v>
@@ -16232,7 +16232,7 @@
         <v>36.75</v>
       </c>
       <c r="G547" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H547" t="n">
         <v>60536</v>
@@ -16261,7 +16261,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H548" t="n">
         <v>151703</v>
@@ -16319,7 +16319,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060165405273</v>
+        <v>34.2060203552246</v>
       </c>
       <c r="H550" t="n">
         <v>59281</v>
@@ -16348,7 +16348,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H551" t="n">
         <v>43962</v>
@@ -16406,7 +16406,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H553" t="n">
         <v>48943</v>
@@ -16435,7 +16435,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H554" t="n">
         <v>69956</v>
@@ -16464,7 +16464,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H555" t="n">
         <v>49369</v>
@@ -16493,7 +16493,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>34.2948608398438</v>
+        <v>34.294864654541</v>
       </c>
       <c r="H556" t="n">
         <v>29679</v>
@@ -16551,7 +16551,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731285095215</v>
+        <v>33.2731246948242</v>
       </c>
       <c r="H558" t="n">
         <v>31513</v>
@@ -16609,7 +16609,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721786499023</v>
+        <v>35.2721748352051</v>
       </c>
       <c r="H560" t="n">
         <v>92873</v>
@@ -16638,7 +16638,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G561" t="n">
-        <v>36.7381553649902</v>
+        <v>36.7381477355957</v>
       </c>
       <c r="H561" t="n">
         <v>96737</v>
@@ -16754,7 +16754,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950576782227</v>
+        <v>33.8950538635254</v>
       </c>
       <c r="H565" t="n">
         <v>57075</v>
@@ -16841,7 +16841,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530914306641</v>
+        <v>28.6530933380127</v>
       </c>
       <c r="H568" t="n">
         <v>187078</v>
@@ -16928,7 +16928,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.3430728912354</v>
+        <v>26.3430767059326</v>
       </c>
       <c r="H571" t="n">
         <v>102740</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190662384033</v>
+        <v>30.1190624237061</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184947967529</v>
+        <v>31.3184986114502</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17102,7 +17102,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519599914551</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H577" t="n">
         <v>60129</v>
@@ -17189,7 +17189,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G580" t="n">
-        <v>32.5623512268066</v>
+        <v>32.5623550415039</v>
       </c>
       <c r="H580" t="n">
         <v>40631</v>
@@ -17334,7 +17334,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281349182129</v>
+        <v>34.4281387329102</v>
       </c>
       <c r="H585" t="n">
         <v>89419</v>
@@ -17392,7 +17392,7 @@
         <v>36.75</v>
       </c>
       <c r="G587" t="n">
-        <v>32.651195526123</v>
+        <v>32.6511993408203</v>
       </c>
       <c r="H587" t="n">
         <v>35265</v>
@@ -17421,7 +17421,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G588" t="n">
-        <v>32.1181221008301</v>
+        <v>32.1181182861328</v>
       </c>
       <c r="H588" t="n">
         <v>33386</v>
@@ -17566,7 +17566,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521453857422</v>
+        <v>30.6521434783936</v>
       </c>
       <c r="H593" t="n">
         <v>18121</v>
@@ -17595,7 +17595,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636756896973</v>
+        <v>29.7636737823486</v>
       </c>
       <c r="H594" t="n">
         <v>35604</v>
@@ -17624,7 +17624,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521453857422</v>
+        <v>30.6521434783936</v>
       </c>
       <c r="H595" t="n">
         <v>37402</v>
@@ -17682,7 +17682,7 @@
         <v>35</v>
       </c>
       <c r="G597" t="n">
-        <v>31.0963821411133</v>
+        <v>31.096378326416</v>
       </c>
       <c r="H597" t="n">
         <v>23818</v>
@@ -17711,7 +17711,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519599914551</v>
+        <v>31.0519561767578</v>
       </c>
       <c r="H598" t="n">
         <v>20035</v>
@@ -17740,7 +17740,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.2740745544434</v>
+        <v>31.274076461792</v>
       </c>
       <c r="H599" t="n">
         <v>22406</v>
@@ -17769,7 +17769,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629169464111</v>
+        <v>31.3629150390625</v>
       </c>
       <c r="H600" t="n">
         <v>24723</v>
@@ -17856,7 +17856,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G603" t="n">
-        <v>28.7863655090332</v>
+        <v>28.7863636016846</v>
       </c>
       <c r="H603" t="n">
         <v>26401</v>
@@ -18001,7 +18001,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H608" t="n">
         <v>42611</v>
@@ -18030,7 +18030,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H609" t="n">
         <v>29532</v>
@@ -18059,7 +18059,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H610" t="n">
         <v>31377</v>
@@ -18088,7 +18088,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H611" t="n">
         <v>81317</v>
@@ -18146,7 +18146,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H613" t="n">
         <v>43669</v>
@@ -18175,7 +18175,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H614" t="n">
         <v>41499</v>
@@ -18291,7 +18291,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H618" t="n">
         <v>36011</v>
@@ -18378,7 +18378,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G621" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H621" t="n">
         <v>15674</v>
@@ -18407,7 +18407,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.709436416626</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H622" t="n">
         <v>13020</v>
@@ -18436,7 +18436,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>30.0310230255127</v>
+        <v>30.0310249328613</v>
       </c>
       <c r="H623" t="n">
         <v>15007</v>
@@ -18523,7 +18523,7 @@
         <v>34.4500007629395</v>
       </c>
       <c r="G626" t="n">
-        <v>31.1617088317871</v>
+        <v>31.1617069244385</v>
       </c>
       <c r="H626" t="n">
         <v>16502</v>
@@ -18552,7 +18552,7 @@
         <v>36.25</v>
       </c>
       <c r="G627" t="n">
-        <v>32.7898979187012</v>
+        <v>32.7898941040039</v>
       </c>
       <c r="H627" t="n">
         <v>41583</v>
@@ -18581,7 +18581,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G628" t="n">
-        <v>30.8903465270996</v>
+        <v>30.890344619751</v>
       </c>
       <c r="H628" t="n">
         <v>76084</v>
@@ -18610,7 +18610,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189785003662</v>
+        <v>30.6189804077148</v>
       </c>
       <c r="H629" t="n">
         <v>25073</v>
@@ -18668,7 +18668,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>30.0310230255127</v>
+        <v>30.0310249328613</v>
       </c>
       <c r="H631" t="n">
         <v>20315</v>
@@ -18697,7 +18697,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426189422607</v>
+        <v>31.3426208496094</v>
       </c>
       <c r="H632" t="n">
         <v>44384</v>
@@ -18755,7 +18755,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H634" t="n">
         <v>36768</v>
@@ -18813,7 +18813,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H636" t="n">
         <v>49552</v>
@@ -18871,7 +18871,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>28.1766967773438</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H638" t="n">
         <v>56267</v>
@@ -18900,7 +18900,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H639" t="n">
         <v>19934</v>
@@ -18929,7 +18929,7 @@
         <v>31.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>28.1766967773438</v>
+        <v>28.1766986846924</v>
       </c>
       <c r="H640" t="n">
         <v>27100</v>
@@ -19074,7 +19074,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>27.8601016998291</v>
+        <v>27.8601055145264</v>
       </c>
       <c r="H645" t="n">
         <v>17310</v>
@@ -19103,7 +19103,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H646" t="n">
         <v>21557</v>
@@ -19132,7 +19132,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G647" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H647" t="n">
         <v>19011</v>
@@ -19190,7 +19190,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H649" t="n">
         <v>12887</v>
@@ -19306,7 +19306,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>27.6339664459229</v>
+        <v>27.6339683532715</v>
       </c>
       <c r="H653" t="n">
         <v>22878</v>
@@ -19364,7 +19364,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>28.0862407684326</v>
+        <v>28.0862426757812</v>
       </c>
       <c r="H655" t="n">
         <v>36534</v>
@@ -19393,7 +19393,7 @@
         <v>33</v>
       </c>
       <c r="G656" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H656" t="n">
         <v>35738</v>
@@ -19451,7 +19451,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G658" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H658" t="n">
         <v>15664</v>
@@ -19480,7 +19480,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H659" t="n">
         <v>11969</v>
@@ -19509,7 +19509,7 @@
         <v>33</v>
       </c>
       <c r="G660" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H660" t="n">
         <v>20537</v>
@@ -19567,7 +19567,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787506103516</v>
       </c>
       <c r="H662" t="n">
         <v>11492</v>
@@ -19596,7 +19596,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>30.1214752197266</v>
+        <v>30.1214771270752</v>
       </c>
       <c r="H663" t="n">
         <v>13226</v>
@@ -19625,7 +19625,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H664" t="n">
         <v>12292</v>
@@ -19654,7 +19654,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G665" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H665" t="n">
         <v>5963</v>
@@ -19683,7 +19683,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260276794434</v>
+        <v>31.0260257720947</v>
       </c>
       <c r="H666" t="n">
         <v>41810</v>
@@ -19712,7 +19712,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>30.0310230255127</v>
+        <v>30.0310249328613</v>
       </c>
       <c r="H667" t="n">
         <v>20516</v>
@@ -19770,7 +19770,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H669" t="n">
         <v>27479</v>
@@ -19799,7 +19799,7 @@
         <v>33</v>
       </c>
       <c r="G670" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H670" t="n">
         <v>16306</v>
@@ -19857,7 +19857,7 @@
         <v>33.75</v>
       </c>
       <c r="G672" t="n">
-        <v>30.5285205841064</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H672" t="n">
         <v>11102</v>
@@ -19886,7 +19886,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H673" t="n">
         <v>12485</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.9355697631836</v>
+        <v>30.935567855835</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19944,7 +19944,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9807968139648</v>
+        <v>30.9808006286621</v>
       </c>
       <c r="H675" t="n">
         <v>14000</v>
@@ -19973,7 +19973,7 @@
         <v>33.5</v>
       </c>
       <c r="G676" t="n">
-        <v>30.3023872375488</v>
+        <v>30.3023891448975</v>
       </c>
       <c r="H676" t="n">
         <v>13444</v>
@@ -20002,7 +20002,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>30.4832973480225</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H677" t="n">
         <v>25987</v>
@@ -20031,7 +20031,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787487030029</v>
+        <v>29.5787506103516</v>
       </c>
       <c r="H678" t="n">
         <v>13528</v>
@@ -20089,7 +20089,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H680" t="n">
         <v>18879</v>
@@ -20147,7 +20147,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048820495605</v>
+        <v>29.8048877716064</v>
       </c>
       <c r="H682" t="n">
         <v>13128</v>
@@ -20176,7 +20176,7 @@
         <v>32.25</v>
       </c>
       <c r="G683" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H683" t="n">
         <v>7419</v>
@@ -20205,7 +20205,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H684" t="n">
         <v>27461</v>
@@ -20321,7 +20321,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H688" t="n">
         <v>9866</v>
@@ -20350,7 +20350,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G689" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H689" t="n">
         <v>6251</v>
@@ -20379,7 +20379,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H690" t="n">
         <v>13325</v>
@@ -20437,7 +20437,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H692" t="n">
         <v>20442</v>
@@ -20466,7 +20466,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>28.3123779296875</v>
+        <v>28.3123798370361</v>
       </c>
       <c r="H693" t="n">
         <v>18525</v>
@@ -20495,7 +20495,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>27.9505577087402</v>
+        <v>27.9505615234375</v>
       </c>
       <c r="H694" t="n">
         <v>28033</v>
@@ -20524,7 +20524,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G695" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H695" t="n">
         <v>25276</v>
@@ -20640,7 +20640,7 @@
         <v>33.75</v>
       </c>
       <c r="G699" t="n">
-        <v>30.5285205841064</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H699" t="n">
         <v>56297</v>
@@ -20669,7 +20669,7 @@
         <v>33.25</v>
       </c>
       <c r="G700" t="n">
-        <v>30.0762481689453</v>
+        <v>30.0762500762939</v>
       </c>
       <c r="H700" t="n">
         <v>23460</v>
@@ -20756,7 +20756,7 @@
         <v>33</v>
       </c>
       <c r="G703" t="n">
-        <v>29.8501110076904</v>
+        <v>29.8501129150391</v>
       </c>
       <c r="H703" t="n">
         <v>24157</v>
@@ -20814,7 +20814,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>28.0862407684326</v>
+        <v>28.0862426757812</v>
       </c>
       <c r="H705" t="n">
         <v>27391</v>
@@ -20930,7 +20930,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>27.9957866668701</v>
+        <v>27.9957885742188</v>
       </c>
       <c r="H709" t="n">
         <v>20930</v>
@@ -20959,7 +20959,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364650726318</v>
+        <v>27.1364669799805</v>
       </c>
       <c r="H710" t="n">
         <v>48790</v>
@@ -20988,7 +20988,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>28.1314716339111</v>
+        <v>28.1314697265625</v>
       </c>
       <c r="H711" t="n">
         <v>16521</v>
@@ -21046,7 +21046,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H713" t="n">
         <v>37089</v>
@@ -21075,7 +21075,7 @@
         <v>32.25</v>
       </c>
       <c r="G714" t="n">
-        <v>29.1717014312744</v>
+        <v>29.1716995239258</v>
       </c>
       <c r="H714" t="n">
         <v>28119</v>
@@ -21104,7 +21104,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048820495605</v>
+        <v>29.8048877716064</v>
       </c>
       <c r="H715" t="n">
         <v>26731</v>
@@ -21133,7 +21133,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H716" t="n">
         <v>30596</v>
@@ -21162,7 +21162,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G717" t="n">
-        <v>30.2119293212891</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H717" t="n">
         <v>59213</v>
@@ -21191,7 +21191,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G718" t="n">
-        <v>29.3073863983154</v>
+        <v>29.3073844909668</v>
       </c>
       <c r="H718" t="n">
         <v>15926</v>
@@ -21249,7 +21249,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978385925293</v>
+        <v>29.3978366851807</v>
       </c>
       <c r="H720" t="n">
         <v>19906</v>
@@ -21307,7 +21307,7 @@
         <v>31.8500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>28.8098831176758</v>
+        <v>28.8098812103271</v>
       </c>
       <c r="H722" t="n">
         <v>27650</v>
@@ -21394,7 +21394,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H725" t="n">
         <v>27078</v>
@@ -21452,7 +21452,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H727" t="n">
         <v>23140</v>
@@ -21568,7 +21568,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>28.7646541595459</v>
+        <v>28.7646522521973</v>
       </c>
       <c r="H731" t="n">
         <v>24208</v>
@@ -21597,7 +21597,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596588134766</v>
+        <v>29.7596569061279</v>
       </c>
       <c r="H732" t="n">
         <v>39155</v>
@@ -21626,7 +21626,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621555328369</v>
+        <v>29.2621536254883</v>
       </c>
       <c r="H733" t="n">
         <v>36285</v>
@@ -21742,7 +21742,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907894134521</v>
+        <v>28.9907913208008</v>
       </c>
       <c r="H737" t="n">
         <v>13524</v>
@@ -21771,7 +21771,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264743804932</v>
+        <v>29.1264762878418</v>
       </c>
       <c r="H738" t="n">
         <v>31102</v>
@@ -21829,7 +21829,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>29.9405632019043</v>
+        <v>29.9405651092529</v>
       </c>
       <c r="H740" t="n">
         <v>25796</v>
@@ -21858,7 +21858,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G741" t="n">
-        <v>30.3476142883301</v>
+        <v>30.3476123809814</v>
       </c>
       <c r="H741" t="n">
         <v>14572</v>
@@ -21887,7 +21887,7 @@
         <v>33.75</v>
       </c>
       <c r="G742" t="n">
-        <v>30.5285205841064</v>
+        <v>30.5285243988037</v>
       </c>
       <c r="H742" t="n">
         <v>22513</v>
@@ -21916,7 +21916,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G743" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H743" t="n">
         <v>39509</v>
@@ -21974,7 +21974,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401222229004</v>
+        <v>31.8401165008545</v>
       </c>
       <c r="H745" t="n">
         <v>20993</v>
@@ -22003,7 +22003,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G746" t="n">
-        <v>32.0210342407227</v>
+        <v>32.0210304260254</v>
       </c>
       <c r="H746" t="n">
         <v>23768</v>
@@ -22061,7 +22061,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G748" t="n">
-        <v>30.2119293212891</v>
+        <v>30.2119312286377</v>
       </c>
       <c r="H748" t="n">
         <v>18927</v>
@@ -22119,7 +22119,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>30.4832973480225</v>
+        <v>30.4832954406738</v>
       </c>
       <c r="H750" t="n">
         <v>5976</v>
@@ -22177,7 +22177,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.709436416626</v>
+        <v>30.7094326019287</v>
       </c>
       <c r="H752" t="n">
         <v>15924</v>
@@ -22206,7 +22206,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H753" t="n">
         <v>33549</v>
@@ -22235,7 +22235,7 @@
         <v>34.8499984741211</v>
       </c>
       <c r="G754" t="n">
-        <v>31.5235271453857</v>
+        <v>31.5235290527344</v>
       </c>
       <c r="H754" t="n">
         <v>23044</v>
@@ -22293,7 +22293,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G756" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H756" t="n">
         <v>12661</v>
@@ -22409,7 +22409,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G760" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H760" t="n">
         <v>38359</v>
@@ -22467,7 +22467,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>31.387845993042</v>
+        <v>31.3878421783447</v>
       </c>
       <c r="H762" t="n">
         <v>46057</v>
@@ -22496,7 +22496,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G763" t="n">
-        <v>32.2019348144531</v>
+        <v>32.2019386291504</v>
       </c>
       <c r="H763" t="n">
         <v>35066</v>
@@ -22525,7 +22525,7 @@
         <v>35.25</v>
       </c>
       <c r="G764" t="n">
-        <v>31.8853492736816</v>
+        <v>31.885347366333</v>
       </c>
       <c r="H764" t="n">
         <v>11653</v>
@@ -22583,7 +22583,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G766" t="n">
-        <v>32.2019348144531</v>
+        <v>32.2019386291504</v>
       </c>
       <c r="H766" t="n">
         <v>18901</v>
@@ -22612,7 +22612,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969451904297</v>
+        <v>33.1969413757324</v>
       </c>
       <c r="H767" t="n">
         <v>47582</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803558349609</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22670,7 +22670,7 @@
         <v>35.5</v>
       </c>
       <c r="G769" t="n">
-        <v>32.1114883422852</v>
+        <v>32.1114845275879</v>
       </c>
       <c r="H769" t="n">
         <v>44649</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803558349609</v>
+        <v>32.8803520202637</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22873,7 +22873,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G776" t="n">
-        <v>32.6089859008789</v>
+        <v>32.6089820861816</v>
       </c>
       <c r="H776" t="n">
         <v>6543</v>
@@ -22931,7 +22931,7 @@
         <v>37.5</v>
       </c>
       <c r="G778" t="n">
-        <v>33.9205780029297</v>
+        <v>33.9205856323242</v>
       </c>
       <c r="H778" t="n">
         <v>24835</v>
@@ -22989,7 +22989,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>33.1064872741699</v>
+        <v>33.1064834594727</v>
       </c>
       <c r="H780" t="n">
         <v>8743</v>
@@ -23018,7 +23018,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H781" t="n">
         <v>27307</v>
@@ -23047,7 +23047,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>33.8753509521484</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H782" t="n">
         <v>27238</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23134,7 +23134,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919441223145</v>
+        <v>34.1919479370117</v>
       </c>
       <c r="H785" t="n">
         <v>16126</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301277160645</v>
+        <v>33.8301239013672</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23221,7 +23221,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>33.8753509521484</v>
+        <v>33.875358581543</v>
       </c>
       <c r="H788" t="n">
         <v>10901</v>
@@ -23250,7 +23250,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G789" t="n">
-        <v>34.5085372924805</v>
+        <v>34.5085411071777</v>
       </c>
       <c r="H789" t="n">
         <v>22080</v>
@@ -23279,7 +23279,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G790" t="n">
-        <v>34.6442184448242</v>
+        <v>34.6442222595215</v>
       </c>
       <c r="H790" t="n">
         <v>23430</v>
@@ -23395,7 +23395,7 @@
         <v>37.5499992370605</v>
       </c>
       <c r="G794" t="n">
-        <v>33.9658088684082</v>
+        <v>33.9658050537109</v>
       </c>
       <c r="H794" t="n">
         <v>32389</v>
@@ -23424,7 +23424,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H795" t="n">
         <v>28476</v>
@@ -23453,7 +23453,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130897521973</v>
+        <v>35.4130935668945</v>
       </c>
       <c r="H796" t="n">
         <v>22692</v>
@@ -23482,7 +23482,7 @@
         <v>39.25</v>
       </c>
       <c r="G797" t="n">
-        <v>35.5035438537598</v>
+        <v>35.5035400390625</v>
       </c>
       <c r="H797" t="n">
         <v>15860</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578720092773</v>
+        <v>37.3578643798828</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23801,7 +23801,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.227180480957</v>
+        <v>36.2271766662598</v>
       </c>
       <c r="H808" t="n">
         <v>31459</v>
@@ -23975,7 +23975,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G814" t="n">
-        <v>36.362865447998</v>
+        <v>36.3628616333008</v>
       </c>
       <c r="H814" t="n">
         <v>19882</v>
@@ -24033,7 +24033,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G816" t="n">
-        <v>36.7246780395508</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H816" t="n">
         <v>28980</v>
@@ -24178,7 +24178,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G821" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H821" t="n">
         <v>71113</v>
@@ -24207,7 +24207,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3980979919434</v>
+        <v>38.3981018066406</v>
       </c>
       <c r="H822" t="n">
         <v>31744</v>
@@ -24236,7 +24236,7 @@
         <v>43</v>
       </c>
       <c r="G823" t="n">
-        <v>38.8955993652344</v>
+        <v>38.8956031799316</v>
       </c>
       <c r="H823" t="n">
         <v>45948</v>
@@ -24294,7 +24294,7 @@
         <v>43.5499992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>39.3931007385254</v>
+        <v>39.3931045532227</v>
       </c>
       <c r="H825" t="n">
         <v>40999</v>
@@ -24323,7 +24323,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860534667969</v>
+        <v>38.9860572814941</v>
       </c>
       <c r="H826" t="n">
         <v>26184</v>
@@ -24381,7 +24381,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G828" t="n">
-        <v>39.0312805175781</v>
+        <v>39.0312843322754</v>
       </c>
       <c r="H828" t="n">
         <v>29768</v>
@@ -24410,7 +24410,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H829" t="n">
         <v>35652</v>
@@ -24555,7 +24555,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G834" t="n">
-        <v>37.9006004333496</v>
+        <v>37.9005966186523</v>
       </c>
       <c r="H834" t="n">
         <v>57165</v>
@@ -24584,7 +24584,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>38.2624130249023</v>
+        <v>38.2624168395996</v>
       </c>
       <c r="H835" t="n">
         <v>34627</v>
@@ -24613,7 +24613,7 @@
         <v>42.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>38.4885559082031</v>
+        <v>38.4885520935059</v>
       </c>
       <c r="H836" t="n">
         <v>39749</v>
@@ -24700,7 +24700,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367263793945</v>
+        <v>36.1367301940918</v>
       </c>
       <c r="H839" t="n">
         <v>32321</v>
@@ -24729,7 +24729,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.865364074707</v>
+        <v>35.8653678894043</v>
       </c>
       <c r="H840" t="n">
         <v>24851</v>
@@ -24787,7 +24787,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G842" t="n">
-        <v>36.2724075317383</v>
+        <v>36.2724113464355</v>
       </c>
       <c r="H842" t="n">
         <v>29267</v>
@@ -24816,7 +24816,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.865364074707</v>
+        <v>35.8653678894043</v>
       </c>
       <c r="H843" t="n">
         <v>30983</v>
@@ -24932,7 +24932,7 @@
         <v>40.5</v>
       </c>
       <c r="G847" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H847" t="n">
         <v>16900</v>
@@ -24961,7 +24961,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>35.9105911254883</v>
+        <v>35.910587310791</v>
       </c>
       <c r="H848" t="n">
         <v>26054</v>
@@ -24990,7 +24990,7 @@
         <v>41.5</v>
       </c>
       <c r="G849" t="n">
-        <v>37.5387763977051</v>
+        <v>37.5387802124023</v>
       </c>
       <c r="H849" t="n">
         <v>30157</v>
@@ -25019,7 +25019,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G850" t="n">
-        <v>36.7246780395508</v>
+        <v>36.7246856689453</v>
       </c>
       <c r="H850" t="n">
         <v>32977</v>
@@ -25077,7 +25077,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101425170898</v>
+        <v>37.8101387023926</v>
       </c>
       <c r="H852" t="n">
         <v>12442</v>
@@ -25135,7 +25135,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G854" t="n">
-        <v>37.6744651794434</v>
+        <v>37.6744613647461</v>
       </c>
       <c r="H854" t="n">
         <v>14320</v>
@@ -25193,7 +25193,7 @@
         <v>40.75</v>
       </c>
       <c r="G856" t="n">
-        <v>36.8603630065918</v>
+        <v>36.8603668212891</v>
       </c>
       <c r="H856" t="n">
         <v>25546</v>
@@ -25222,7 +25222,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>36.362865447998</v>
+        <v>36.3628616333008</v>
       </c>
       <c r="H857" t="n">
         <v>13892</v>
@@ -25280,7 +25280,7 @@
         <v>40.5</v>
       </c>
       <c r="G859" t="n">
-        <v>36.6342315673828</v>
+        <v>36.6342277526855</v>
       </c>
       <c r="H859" t="n">
         <v>12270</v>
@@ -25541,7 +25541,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>36.5952072143555</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H868" t="n">
         <v>14461</v>
@@ -25744,7 +25744,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H875" t="n">
         <v>10487</v>
@@ -25773,7 +25773,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G876" t="n">
-        <v>36.5952072143555</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H876" t="n">
         <v>14179</v>
@@ -25831,7 +25831,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>36.1354713439941</v>
+        <v>36.1354751586914</v>
       </c>
       <c r="H878" t="n">
         <v>14544</v>
@@ -26005,7 +26005,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G884" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H884" t="n">
         <v>74828</v>
@@ -26063,7 +26063,7 @@
         <v>38.2999992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>35.215991973877</v>
+        <v>35.2159957885742</v>
       </c>
       <c r="H886" t="n">
         <v>9003</v>
@@ -26121,7 +26121,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G888" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H888" t="n">
         <v>18290</v>
@@ -26179,7 +26179,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G890" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H890" t="n">
         <v>21938</v>
@@ -26208,7 +26208,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G891" t="n">
-        <v>34.6643104553223</v>
+        <v>34.664306640625</v>
       </c>
       <c r="H891" t="n">
         <v>21890</v>
@@ -26701,7 +26701,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G908" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H908" t="n">
         <v>19888</v>
@@ -26788,7 +26788,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H911" t="n">
         <v>9666</v>
@@ -26817,7 +26817,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H912" t="n">
         <v>17366</v>
@@ -26875,7 +26875,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G914" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H914" t="n">
         <v>24076</v>
@@ -27020,7 +27020,7 @@
         <v>36.25</v>
       </c>
       <c r="G919" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310699462891</v>
       </c>
       <c r="H919" t="n">
         <v>14186</v>
@@ -27049,7 +27049,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H920" t="n">
         <v>12456</v>
@@ -27194,7 +27194,7 @@
         <v>35.25</v>
       </c>
       <c r="G925" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H925" t="n">
         <v>24388</v>
@@ -27252,7 +27252,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>32.4575614929199</v>
+        <v>32.4575653076172</v>
       </c>
       <c r="H927" t="n">
         <v>15137</v>
@@ -27281,7 +27281,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G928" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H928" t="n">
         <v>18700</v>
@@ -27339,7 +27339,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G930" t="n">
-        <v>33.4689903259277</v>
+        <v>33.4689865112305</v>
       </c>
       <c r="H930" t="n">
         <v>54293</v>
@@ -27368,7 +27368,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>34.6643104553223</v>
+        <v>34.664306640625</v>
       </c>
       <c r="H931" t="n">
         <v>102214</v>
@@ -27426,7 +27426,7 @@
         <v>37.3499984741211</v>
       </c>
       <c r="G933" t="n">
-        <v>34.3424911499023</v>
+        <v>34.3424873352051</v>
       </c>
       <c r="H933" t="n">
         <v>31757</v>
@@ -27600,7 +27600,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>34.2965126037598</v>
+        <v>34.296516418457</v>
       </c>
       <c r="H939" t="n">
         <v>16255</v>
@@ -27977,7 +27977,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H952" t="n">
         <v>8028</v>
@@ -28035,7 +28035,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H954" t="n">
         <v>10979</v>
@@ -28093,7 +28093,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>33.7448310852051</v>
+        <v>33.7448348999023</v>
       </c>
       <c r="H956" t="n">
         <v>7086</v>
@@ -28151,7 +28151,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H958" t="n">
         <v>18202</v>
@@ -28209,7 +28209,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G960" t="n">
-        <v>32.9632759094238</v>
+        <v>32.9632720947266</v>
       </c>
       <c r="H960" t="n">
         <v>35963</v>
@@ -28325,7 +28325,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G964" t="n">
-        <v>32.2736663818359</v>
+        <v>32.2736625671387</v>
       </c>
       <c r="H964" t="n">
         <v>19495</v>
@@ -28354,7 +28354,7 @@
         <v>35.25</v>
       </c>
       <c r="G965" t="n">
-        <v>32.4115867614746</v>
+        <v>32.4115905761719</v>
       </c>
       <c r="H965" t="n">
         <v>16412</v>
@@ -28383,7 +28383,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>31.5380840301514</v>
+        <v>31.5380821228027</v>
       </c>
       <c r="H966" t="n">
         <v>27835</v>
@@ -28470,7 +28470,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G969" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H969" t="n">
         <v>26969</v>
@@ -28528,7 +28528,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G971" t="n">
-        <v>33.0552253723145</v>
+        <v>33.0552215576172</v>
       </c>
       <c r="H971" t="n">
         <v>12593</v>
@@ -28644,7 +28644,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G975" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H975" t="n">
         <v>22418</v>
@@ -28673,7 +28673,7 @@
         <v>35.75</v>
       </c>
       <c r="G976" t="n">
-        <v>32.8713264465332</v>
+        <v>32.8713302612305</v>
       </c>
       <c r="H976" t="n">
         <v>23421</v>
@@ -28789,7 +28789,7 @@
         <v>36.25</v>
       </c>
       <c r="G980" t="n">
-        <v>33.3310623168945</v>
+        <v>33.3310699462891</v>
       </c>
       <c r="H980" t="n">
         <v>18596</v>
@@ -28818,7 +28818,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>32.5495147705078</v>
+        <v>32.5495109558105</v>
       </c>
       <c r="H981" t="n">
         <v>23720</v>
@@ -28847,7 +28847,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>32.9172973632812</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H982" t="n">
         <v>17608</v>
@@ -28876,7 +28876,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>32.9172973632812</v>
+        <v>32.9173011779785</v>
       </c>
       <c r="H983" t="n">
         <v>19478</v>
@@ -28934,7 +28934,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G985" t="n">
-        <v>33.2391166687012</v>
+        <v>33.2391204833984</v>
       </c>
       <c r="H985" t="n">
         <v>10944</v>
@@ -28963,7 +28963,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G986" t="n">
-        <v>32.8253517150879</v>
+        <v>32.8253555297852</v>
       </c>
       <c r="H986" t="n">
         <v>11601</v>
@@ -29021,7 +29021,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>30.7565269470215</v>
+        <v>30.7565288543701</v>
       </c>
       <c r="H988" t="n">
         <v>19829</v>
@@ -29050,7 +29050,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>30.4347076416016</v>
+        <v>30.4347095489502</v>
       </c>
       <c r="H989" t="n">
         <v>20300</v>
@@ -29079,7 +29079,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>31.3541851043701</v>
+        <v>31.3541889190674</v>
       </c>
       <c r="H990" t="n">
         <v>16205</v>
@@ -29108,7 +29108,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G991" t="n">
-        <v>31.0783443450928</v>
+        <v>31.0783424377441</v>
       </c>
       <c r="H991" t="n">
         <v>22083</v>
@@ -29137,7 +29137,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G992" t="n">
-        <v>30.8944473266602</v>
+        <v>30.8944492340088</v>
       </c>
       <c r="H992" t="n">
         <v>20906</v>
@@ -29195,7 +29195,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G994" t="n">
-        <v>32.9632759094238</v>
+        <v>32.9632720947266</v>
       </c>
       <c r="H994" t="n">
         <v>25799</v>
@@ -29253,7 +29253,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G996" t="n">
-        <v>33.8827514648438</v>
+        <v>33.8827476501465</v>
       </c>
       <c r="H996" t="n">
         <v>15814</v>
@@ -29282,7 +29282,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>34.1585960388184</v>
+        <v>34.1585998535156</v>
       </c>
       <c r="H997" t="n">
         <v>21195</v>
@@ -29398,7 +29398,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1001" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1001" t="n">
         <v>38594</v>
@@ -29456,7 +29456,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1003" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H1003" t="n">
         <v>52594</v>
@@ -29630,7 +29630,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1009" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1009" t="n">
         <v>15324</v>
@@ -29659,7 +29659,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1010" t="n">
         <v>9446</v>
@@ -29717,7 +29717,7 @@
         <v>38.4500007629395</v>
       </c>
       <c r="G1012" t="n">
-        <v>35.3539199829102</v>
+        <v>35.3539161682129</v>
       </c>
       <c r="H1012" t="n">
         <v>19550</v>
@@ -29775,7 +29775,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>36.5952072143555</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1014" t="n">
         <v>42877</v>
@@ -29891,7 +29891,7 @@
         <v>40.75</v>
       </c>
       <c r="G1018" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1018" t="n">
         <v>22790</v>
@@ -30152,7 +30152,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1027" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1027" t="n">
         <v>33681</v>
@@ -30181,7 +30181,7 @@
         <v>42.75</v>
       </c>
       <c r="G1028" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1028" t="n">
         <v>26762</v>
@@ -30297,7 +30297,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1032" t="n">
         <v>26646</v>
@@ -30384,7 +30384,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G1035" t="n">
-        <v>38.0203971862793</v>
+        <v>38.0204010009766</v>
       </c>
       <c r="H1035" t="n">
         <v>30679</v>
@@ -30413,7 +30413,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1036" t="n">
         <v>34011</v>
@@ -30442,7 +30442,7 @@
         <v>41</v>
       </c>
       <c r="G1037" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1037" t="n">
         <v>16755</v>
@@ -30471,7 +30471,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1038" t="n">
         <v>24399</v>
@@ -30529,7 +30529,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1040" t="n">
         <v>10126</v>
@@ -30616,7 +30616,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1043" t="n">
         <v>12351</v>
@@ -30674,7 +30674,7 @@
         <v>42.8499984741211</v>
       </c>
       <c r="G1045" t="n">
-        <v>39.3996162414551</v>
+        <v>39.3996200561523</v>
       </c>
       <c r="H1045" t="n">
         <v>13666</v>
@@ -30703,7 +30703,7 @@
         <v>43.1500015258789</v>
       </c>
       <c r="G1046" t="n">
-        <v>39.675464630127</v>
+        <v>39.6754608154297</v>
       </c>
       <c r="H1046" t="n">
         <v>27206</v>
@@ -30761,7 +30761,7 @@
         <v>42.75</v>
       </c>
       <c r="G1048" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1048" t="n">
         <v>28234</v>
@@ -31109,7 +31109,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G1060" t="n">
-        <v>38.8939018249512</v>
+        <v>38.8939056396484</v>
       </c>
       <c r="H1060" t="n">
         <v>30816</v>
@@ -31138,7 +31138,7 @@
         <v>43.9500007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>40.4110450744629</v>
+        <v>40.4110412597656</v>
       </c>
       <c r="H1061" t="n">
         <v>51174</v>
@@ -31196,7 +31196,7 @@
         <v>44.5499992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>40.9627304077148</v>
+        <v>40.9627265930176</v>
       </c>
       <c r="H1063" t="n">
         <v>114652</v>
@@ -31283,7 +31283,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1066" t="n">
-        <v>40.5489654541016</v>
+        <v>40.5489616394043</v>
       </c>
       <c r="H1066" t="n">
         <v>41750</v>
@@ -31312,7 +31312,7 @@
         <v>42.75</v>
       </c>
       <c r="G1067" t="n">
-        <v>39.3076667785645</v>
+        <v>39.3076705932617</v>
       </c>
       <c r="H1067" t="n">
         <v>57559</v>
@@ -31341,7 +31341,7 @@
         <v>42.25</v>
       </c>
       <c r="G1068" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1068" t="n">
         <v>39015</v>
@@ -31370,7 +31370,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1069" t="n">
         <v>40978</v>
@@ -31399,7 +31399,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1070" t="n">
         <v>24074</v>
@@ -31515,7 +31515,7 @@
         <v>42.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1074" t="n">
         <v>19772</v>
@@ -31573,7 +31573,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1076" t="n">
         <v>35632</v>
@@ -31602,7 +31602,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1077" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1077" t="n">
         <v>48482</v>
@@ -31631,7 +31631,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1078" t="n">
         <v>21323</v>
@@ -31689,7 +31689,7 @@
         <v>41</v>
       </c>
       <c r="G1080" t="n">
-        <v>37.6985855102539</v>
+        <v>37.6985816955566</v>
       </c>
       <c r="H1080" t="n">
         <v>21026</v>
@@ -31805,7 +31805,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1084" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1084" t="n">
         <v>33932</v>
@@ -31834,7 +31834,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422164916992</v>
       </c>
       <c r="H1085" t="n">
         <v>44926</v>
@@ -32037,7 +32037,7 @@
         <v>40.75</v>
       </c>
       <c r="G1092" t="n">
-        <v>37.4687156677246</v>
+        <v>37.4687194824219</v>
       </c>
       <c r="H1092" t="n">
         <v>28651</v>
@@ -32066,7 +32066,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G1093" t="n">
-        <v>37.9744300842285</v>
+        <v>37.9744262695312</v>
       </c>
       <c r="H1093" t="n">
         <v>21149</v>
@@ -32095,7 +32095,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>37.8824806213379</v>
+        <v>37.8824844360352</v>
       </c>
       <c r="H1094" t="n">
         <v>23661</v>
@@ -32269,7 +32269,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1100" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1100" t="n">
         <v>26546</v>
@@ -32298,7 +32298,7 @@
         <v>42.25</v>
       </c>
       <c r="G1101" t="n">
-        <v>38.8479347229004</v>
+        <v>38.8479309082031</v>
       </c>
       <c r="H1101" t="n">
         <v>11787</v>
@@ -32327,7 +32327,7 @@
         <v>41.6500015258789</v>
       </c>
       <c r="G1102" t="n">
-        <v>38.2962493896484</v>
+        <v>38.2962455749512</v>
       </c>
       <c r="H1102" t="n">
         <v>17758</v>
@@ -32414,7 +32414,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G1105" t="n">
-        <v>36.5952072143555</v>
+        <v>36.59521484375</v>
       </c>
       <c r="H1105" t="n">
         <v>26729</v>
@@ -32501,7 +32501,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1108" t="n">
-        <v>36.4113159179688</v>
+        <v>36.4113121032715</v>
       </c>
       <c r="H1108" t="n">
         <v>21226</v>
@@ -32530,7 +32530,7 @@
         <v>39.4500007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>36.2733955383301</v>
+        <v>36.2733917236328</v>
       </c>
       <c r="H1109" t="n">
         <v>25222</v>
@@ -32559,7 +32559,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1110" t="n">
-        <v>35.7217063903809</v>
+        <v>35.7217102050781</v>
       </c>
       <c r="H1110" t="n">
         <v>18379</v>
@@ -32588,7 +32588,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>35.7217063903809</v>
+        <v>35.7217102050781</v>
       </c>
       <c r="H1111" t="n">
         <v>13856</v>
@@ -32617,7 +32617,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1112" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1112" t="n">
         <v>49066</v>
@@ -32675,7 +32675,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G1114" t="n">
-        <v>37.4227409362793</v>
+        <v>37.4227447509766</v>
       </c>
       <c r="H1114" t="n">
         <v>12691</v>
@@ -32704,7 +32704,7 @@
         <v>40.8499984741211</v>
       </c>
       <c r="G1115" t="n">
-        <v>37.5606651306152</v>
+        <v>37.560661315918</v>
       </c>
       <c r="H1115" t="n">
         <v>9595</v>
@@ -32733,7 +32733,7 @@
         <v>41.9500007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>38.5720901489258</v>
+        <v>38.5720863342285</v>
       </c>
       <c r="H1116" t="n">
         <v>18589</v>
@@ -32762,7 +32762,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>37.8365058898926</v>
+        <v>37.8365097045898</v>
       </c>
       <c r="H1117" t="n">
         <v>12581</v>
@@ -32907,7 +32907,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1122" t="n">
-        <v>38.9858551025391</v>
+        <v>38.9858589172363</v>
       </c>
       <c r="H1122" t="n">
         <v>13057</v>
@@ -32965,7 +32965,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>39.905330657959</v>
+        <v>39.9053344726562</v>
       </c>
       <c r="H1124" t="n">
         <v>29851</v>
@@ -32994,7 +32994,7 @@
         <v>44.4500007629395</v>
       </c>
       <c r="G1125" t="n">
-        <v>40.8707847595215</v>
+        <v>40.8707809448242</v>
       </c>
       <c r="H1125" t="n">
         <v>59380</v>
@@ -33023,7 +33023,7 @@
         <v>45.75</v>
       </c>
       <c r="G1126" t="n">
-        <v>42.066104888916</v>
+        <v>42.0661010742188</v>
       </c>
       <c r="H1126" t="n">
         <v>38246</v>
@@ -33081,7 +33081,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G1128" t="n">
-        <v>39.2616996765137</v>
+        <v>39.2616958618164</v>
       </c>
       <c r="H1128" t="n">
         <v>49587</v>
@@ -33110,7 +33110,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1129" t="n">
-        <v>38.3422203063965</v>
+        <v>38.3422164916992</v>
       </c>
       <c r="H1129" t="n">
         <v>76007</v>
@@ -33197,7 +33197,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G1132" t="n">
-        <v>39.4727058410645</v>
+        <v>39.4727020263672</v>
       </c>
       <c r="H1132" t="n">
         <v>28234</v>
@@ -33226,7 +33226,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G1133" t="n">
-        <v>39.1900825500488</v>
+        <v>39.1900787353516</v>
       </c>
       <c r="H1133" t="n">
         <v>17044</v>
@@ -33371,7 +33371,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1138" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1138" t="n">
         <v>14887</v>
@@ -33429,7 +33429,7 @@
         <v>42.1500015258789</v>
       </c>
       <c r="G1140" t="n">
-        <v>39.7082176208496</v>
+        <v>39.7082214355469</v>
       </c>
       <c r="H1140" t="n">
         <v>25485</v>
@@ -33458,7 +33458,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G1141" t="n">
-        <v>39.2842903137207</v>
+        <v>39.2842864990234</v>
       </c>
       <c r="H1141" t="n">
         <v>10680</v>
@@ -33487,7 +33487,7 @@
         <v>42.5</v>
       </c>
       <c r="G1142" t="n">
-        <v>40.0379447937012</v>
+        <v>40.0379409790039</v>
       </c>
       <c r="H1142" t="n">
         <v>21497</v>
@@ -33516,7 +33516,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G1143" t="n">
-        <v>39.7553253173828</v>
+        <v>39.7553215026855</v>
       </c>
       <c r="H1143" t="n">
         <v>17609</v>
@@ -33545,7 +33545,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G1144" t="n">
-        <v>41.5452537536621</v>
+        <v>41.5452499389648</v>
       </c>
       <c r="H1144" t="n">
         <v>77350</v>
@@ -33661,7 +33661,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G1148" t="n">
-        <v>39.9437370300293</v>
+        <v>39.9437408447266</v>
       </c>
       <c r="H1148" t="n">
         <v>26093</v>
@@ -33864,7 +33864,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G1155" t="n">
-        <v>38.8132514953613</v>
+        <v>38.8132553100586</v>
       </c>
       <c r="H1155" t="n">
         <v>17325</v>
@@ -34154,7 +34154,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1165" t="n">
         <v>25025</v>
@@ -34212,7 +34212,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1167" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1167" t="n">
         <v>17311</v>
@@ -34241,7 +34241,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>36.6935997009277</v>
+        <v>36.6935958862305</v>
       </c>
       <c r="H1168" t="n">
         <v>18709</v>
@@ -34270,7 +34270,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>36.5522842407227</v>
+        <v>36.5522880554199</v>
       </c>
       <c r="H1169" t="n">
         <v>7654</v>
@@ -34299,7 +34299,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1170" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1170" t="n">
         <v>11922</v>
@@ -34357,7 +34357,7 @@
         <v>38.8499984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>36.5993881225586</v>
+        <v>36.5993919372559</v>
       </c>
       <c r="H1172" t="n">
         <v>22854</v>
@@ -34444,7 +34444,7 @@
         <v>39.0999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>36.834903717041</v>
+        <v>36.8349075317383</v>
       </c>
       <c r="H1175" t="n">
         <v>14281</v>
@@ -34589,7 +34589,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1180" t="n">
         <v>12217</v>
@@ -34647,7 +34647,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1182" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1182" t="n">
         <v>17442</v>
@@ -34763,7 +34763,7 @@
         <v>36.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1186" t="n">
         <v>16678</v>
@@ -34850,7 +34850,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>33.5376663208008</v>
+        <v>33.5376625061035</v>
       </c>
       <c r="H1189" t="n">
         <v>13671</v>
@@ -34908,7 +34908,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G1191" t="n">
-        <v>33.8202896118164</v>
+        <v>33.8202857971191</v>
       </c>
       <c r="H1191" t="n">
         <v>14410</v>
@@ -34937,7 +34937,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1192" t="n">
         <v>21211</v>
@@ -35053,7 +35053,7 @@
         <v>37.5</v>
       </c>
       <c r="G1196" t="n">
-        <v>35.3275985717773</v>
+        <v>35.3275947570801</v>
       </c>
       <c r="H1196" t="n">
         <v>18810</v>
@@ -35198,7 +35198,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G1201" t="n">
-        <v>35.4689064025879</v>
+        <v>35.4689102172852</v>
       </c>
       <c r="H1201" t="n">
         <v>10943</v>
@@ -35227,7 +35227,7 @@
         <v>38</v>
       </c>
       <c r="G1202" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1202" t="n">
         <v>13284</v>
@@ -35372,7 +35372,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1207" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1207" t="n">
         <v>86976</v>
@@ -35401,7 +35401,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1208" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1208" t="n">
         <v>107480</v>
@@ -35459,7 +35459,7 @@
         <v>33.25</v>
       </c>
       <c r="G1210" t="n">
-        <v>31.3238010406494</v>
+        <v>31.3238048553467</v>
       </c>
       <c r="H1210" t="n">
         <v>97335</v>
@@ -35517,7 +35517,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.8890399932861</v>
+        <v>31.8890419006348</v>
       </c>
       <c r="H1212" t="n">
         <v>19682</v>
@@ -35575,7 +35575,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1214" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1214" t="n">
         <v>32700</v>
@@ -35604,7 +35604,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1215" t="n">
-        <v>31.7477340698242</v>
+        <v>31.7477359771729</v>
       </c>
       <c r="H1215" t="n">
         <v>71954</v>
@@ -35633,7 +35633,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1216" t="n">
-        <v>31.8419399261475</v>
+        <v>31.8419380187988</v>
       </c>
       <c r="H1216" t="n">
         <v>29272</v>
@@ -35662,7 +35662,7 @@
         <v>35.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1217" t="n">
         <v>40121</v>
@@ -35691,7 +35691,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1218" t="n">
         <v>88062</v>
@@ -35720,7 +35720,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.1608352661133</v>
+        <v>33.1608390808105</v>
       </c>
       <c r="H1219" t="n">
         <v>20873</v>
@@ -35807,7 +35807,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>35.2804946899414</v>
+        <v>35.2804908752441</v>
       </c>
       <c r="H1222" t="n">
         <v>55066</v>
@@ -35836,7 +35836,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>35.1391792297363</v>
+        <v>35.1391830444336</v>
       </c>
       <c r="H1223" t="n">
         <v>48119</v>
@@ -35952,7 +35952,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>34.0558013916016</v>
+        <v>34.0558052062988</v>
       </c>
       <c r="H1227" t="n">
         <v>33020</v>
@@ -36068,7 +36068,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1231" t="n">
         <v>27966</v>
@@ -36126,7 +36126,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>35.5160140991211</v>
+        <v>35.5160102844238</v>
       </c>
       <c r="H1233" t="n">
         <v>18372</v>
@@ -36155,7 +36155,7 @@
         <v>38</v>
       </c>
       <c r="G1234" t="n">
-        <v>35.7986335754395</v>
+        <v>35.7986297607422</v>
       </c>
       <c r="H1234" t="n">
         <v>21216</v>
@@ -36271,7 +36271,7 @@
         <v>39.2999992370605</v>
       </c>
       <c r="G1238" t="n">
-        <v>37.0233192443848</v>
+        <v>37.023323059082</v>
       </c>
       <c r="H1238" t="n">
         <v>31944</v>
@@ -36329,7 +36329,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G1240" t="n">
-        <v>36.1754608154297</v>
+        <v>36.1754570007324</v>
       </c>
       <c r="H1240" t="n">
         <v>21979</v>
@@ -36358,7 +36358,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G1241" t="n">
-        <v>34.5739402770996</v>
+        <v>34.5739440917969</v>
       </c>
       <c r="H1241" t="n">
         <v>36159</v>
@@ -36532,7 +36532,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1247" t="n">
-        <v>32.5955924987793</v>
+        <v>32.5955963134766</v>
       </c>
       <c r="H1247" t="n">
         <v>20275</v>
@@ -36619,7 +36619,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1250" t="n">
-        <v>32.4071846008301</v>
+        <v>32.4071807861328</v>
       </c>
       <c r="H1250" t="n">
         <v>26995</v>
@@ -36735,7 +36735,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1254" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1254" t="n">
         <v>86029</v>
@@ -36938,7 +36938,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1261" t="n">
         <v>62483</v>
@@ -37083,7 +37083,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>29.1099395751953</v>
+        <v>29.1099376678467</v>
       </c>
       <c r="H1266" t="n">
         <v>42903</v>
@@ -37257,7 +37257,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1272" t="n">
         <v>69703</v>
@@ -37286,7 +37286,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>29.5338706970215</v>
+        <v>29.5338726043701</v>
       </c>
       <c r="H1273" t="n">
         <v>51566</v>
@@ -37344,7 +37344,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1275" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1275" t="n">
         <v>39875</v>
@@ -37373,7 +37373,7 @@
         <v>32.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1276" t="n">
         <v>33069</v>
@@ -37605,7 +37605,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G1284" t="n">
-        <v>29.8164920806885</v>
+        <v>29.8164901733398</v>
       </c>
       <c r="H1284" t="n">
         <v>24216</v>
@@ -37663,7 +37663,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G1286" t="n">
-        <v>30.6643543243408</v>
+        <v>30.6643524169922</v>
       </c>
       <c r="H1286" t="n">
         <v>27493</v>
@@ -37692,7 +37692,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1287" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1287" t="n">
         <v>27163</v>
@@ -37808,7 +37808,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1291" t="n">
-        <v>30.9940795898438</v>
+        <v>30.9940776824951</v>
       </c>
       <c r="H1291" t="n">
         <v>50126</v>
@@ -37837,7 +37837,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1292" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1292" t="n">
         <v>15339</v>
@@ -37953,7 +37953,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1296" t="n">
-        <v>30.4288349151611</v>
+        <v>30.4288368225098</v>
       </c>
       <c r="H1296" t="n">
         <v>31760</v>
@@ -38127,7 +38127,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>31.9832496643066</v>
+        <v>31.9832515716553</v>
       </c>
       <c r="H1302" t="n">
         <v>58973</v>
@@ -38156,7 +38156,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.0774536132812</v>
+        <v>32.0774574279785</v>
       </c>
       <c r="H1303" t="n">
         <v>39498</v>
@@ -38330,7 +38330,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>33.3492546081543</v>
+        <v>33.349250793457</v>
       </c>
       <c r="H1309" t="n">
         <v>34631</v>
@@ -38417,7 +38417,7 @@
         <v>35.25</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2079391479492</v>
+        <v>33.2079429626465</v>
       </c>
       <c r="H1312" t="n">
         <v>27726</v>
@@ -38533,7 +38533,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1316" t="n">
-        <v>35.0449752807617</v>
+        <v>35.044979095459</v>
       </c>
       <c r="H1316" t="n">
         <v>82490</v>
@@ -38562,7 +38562,7 @@
         <v>36.25</v>
       </c>
       <c r="G1317" t="n">
-        <v>34.1500091552734</v>
+        <v>34.1500129699707</v>
       </c>
       <c r="H1317" t="n">
         <v>126426</v>
@@ -38707,7 +38707,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>30.8056659698486</v>
+        <v>30.8056640625</v>
       </c>
       <c r="H1322" t="n">
         <v>44000</v>
@@ -38765,7 +38765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1324" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1324" t="n">
         <v>42930</v>
@@ -38823,7 +38823,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>31.370906829834</v>
+        <v>31.3709030151367</v>
       </c>
       <c r="H1326" t="n">
         <v>38026</v>
@@ -38852,7 +38852,7 @@
         <v>32.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>30.6172485351562</v>
+        <v>30.6172504425049</v>
       </c>
       <c r="H1327" t="n">
         <v>61320</v>
@@ -38939,7 +38939,7 @@
         <v>31</v>
       </c>
       <c r="G1330" t="n">
-        <v>29.2041454315186</v>
+        <v>29.2041473388672</v>
       </c>
       <c r="H1330" t="n">
         <v>38634</v>
@@ -39113,7 +39113,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G1336" t="n">
-        <v>28.1207675933838</v>
+        <v>28.1207656860352</v>
       </c>
       <c r="H1336" t="n">
         <v>109851</v>
@@ -39229,7 +39229,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1340" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1340" t="n">
         <v>55268</v>
@@ -39258,7 +39258,7 @@
         <v>29</v>
       </c>
       <c r="G1341" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1341" t="n">
         <v>36968</v>
@@ -39374,7 +39374,7 @@
         <v>28.75</v>
       </c>
       <c r="G1345" t="n">
-        <v>27.0844898223877</v>
+        <v>27.0844917297363</v>
       </c>
       <c r="H1345" t="n">
         <v>66714</v>
@@ -39432,7 +39432,7 @@
         <v>29</v>
       </c>
       <c r="G1347" t="n">
-        <v>27.3200073242188</v>
+        <v>27.3200092315674</v>
       </c>
       <c r="H1347" t="n">
         <v>104150</v>
@@ -39519,7 +39519,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G1350" t="n">
-        <v>26.9902839660645</v>
+        <v>26.9902820587158</v>
       </c>
       <c r="H1350" t="n">
         <v>33485</v>
@@ -39548,7 +39548,7 @@
         <v>28</v>
       </c>
       <c r="G1351" t="n">
-        <v>26.3779373168945</v>
+        <v>26.3779392242432</v>
       </c>
       <c r="H1351" t="n">
         <v>128641</v>
@@ -39606,7 +39606,7 @@
         <v>26.5</v>
       </c>
       <c r="G1353" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1353" t="n">
         <v>181757</v>
@@ -39635,7 +39635,7 @@
         <v>26.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>24.9648342132568</v>
+        <v>24.9648361206055</v>
       </c>
       <c r="H1354" t="n">
         <v>138211</v>
@@ -39664,7 +39664,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1355" t="n">
-        <v>25.4829711914062</v>
+        <v>25.4829730987549</v>
       </c>
       <c r="H1355" t="n">
         <v>105911</v>
@@ -39838,7 +39838,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>26.0011119842529</v>
+        <v>26.0011100769043</v>
       </c>
       <c r="H1361" t="n">
         <v>64528</v>
@@ -39867,7 +39867,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1362" t="n">
-        <v>25.388765335083</v>
+        <v>25.3887672424316</v>
       </c>
       <c r="H1362" t="n">
         <v>44652</v>
@@ -39896,7 +39896,7 @@
         <v>26.75</v>
       </c>
       <c r="G1363" t="n">
-        <v>25.2003517150879</v>
+        <v>25.2003536224365</v>
       </c>
       <c r="H1363" t="n">
         <v>43761</v>
@@ -39925,7 +39925,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>26.1895236968994</v>
+        <v>26.189525604248</v>
       </c>
       <c r="H1364" t="n">
         <v>45391</v>
@@ -39954,7 +39954,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7076644897461</v>
+        <v>26.7076625823975</v>
       </c>
       <c r="H1365" t="n">
         <v>53357</v>
@@ -40157,7 +40157,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>27.5084209442139</v>
+        <v>27.5084228515625</v>
       </c>
       <c r="H1372" t="n">
         <v>44289</v>
@@ -40215,7 +40215,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.6968364715576</v>
+        <v>27.696834564209</v>
       </c>
       <c r="H1374" t="n">
         <v>43847</v>
@@ -51067,6 +51067,35 @@
         <v>19781</v>
       </c>
       <c r="I1748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1749" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>35.5999984741211</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>36.0400009155273</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>35.4599990844727</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>36.0400009155273</v>
+      </c>
+      <c r="G1749" t="n">
+        <v>36.0400009155273</v>
+      </c>
+      <c r="H1749" t="n">
+        <v>53357</v>
+      </c>
+      <c r="I1749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SL.MI.xlsx
+++ b/data/SL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5319995880127</v>
       </c>
       <c r="G2" t="n">
-        <v>13.6025457382202</v>
+        <v>13.6025447845459</v>
       </c>
       <c r="H2" t="n">
         <v>487001</v>
@@ -456,7 +456,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G3" t="n">
-        <v>13.416880607605</v>
+        <v>13.4168815612793</v>
       </c>
       <c r="H3" t="n">
         <v>251735</v>
@@ -485,7 +485,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3818502426147</v>
+        <v>13.3818492889404</v>
       </c>
       <c r="H4" t="n">
         <v>54824</v>
@@ -514,7 +514,7 @@
         <v>15.6979999542236</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7479248046875</v>
+        <v>13.7479238510132</v>
       </c>
       <c r="H5" t="n">
         <v>18109</v>
@@ -601,7 +601,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H8" t="n">
         <v>32860</v>
@@ -630,7 +630,7 @@
         <v>15.75</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7934646606445</v>
+        <v>13.7934656143188</v>
       </c>
       <c r="H9" t="n">
         <v>20006</v>
@@ -688,7 +688,7 @@
         <v>15.8020000457764</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8390054702759</v>
+        <v>13.8390045166016</v>
       </c>
       <c r="H11" t="n">
         <v>10789</v>
@@ -804,7 +804,7 @@
         <v>15.8620004653931</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8915529251099</v>
+        <v>13.8915519714355</v>
       </c>
       <c r="H15" t="n">
         <v>15065</v>
@@ -833,7 +833,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G16" t="n">
-        <v>13.9073162078857</v>
+        <v>13.9073152542114</v>
       </c>
       <c r="H16" t="n">
         <v>30923</v>
@@ -1007,7 +1007,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G22" t="n">
-        <v>14.7130279541016</v>
+        <v>14.7130289077759</v>
       </c>
       <c r="H22" t="n">
         <v>147663</v>
@@ -1036,7 +1036,7 @@
         <v>16.75</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6692380905151</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H23" t="n">
         <v>297347</v>
@@ -1065,7 +1065,7 @@
         <v>17.25</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1071271896362</v>
+        <v>15.1071262359619</v>
       </c>
       <c r="H24" t="n">
         <v>75229</v>
@@ -1094,7 +1094,7 @@
         <v>17.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3260717391968</v>
+        <v>15.3260726928711</v>
       </c>
       <c r="H25" t="n">
         <v>73618</v>
@@ -1123,7 +1123,7 @@
         <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H26" t="n">
         <v>107072</v>
@@ -1181,7 +1181,7 @@
         <v>17.003999710083</v>
       </c>
       <c r="G28" t="n">
-        <v>14.8916883468628</v>
+        <v>14.8916873931885</v>
       </c>
       <c r="H28" t="n">
         <v>63118</v>
@@ -1210,7 +1210,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9757614135742</v>
+        <v>14.9757623672485</v>
       </c>
       <c r="H29" t="n">
         <v>88659</v>
@@ -1239,7 +1239,7 @@
         <v>16.5259990692139</v>
       </c>
       <c r="G30" t="n">
-        <v>14.4730653762817</v>
+        <v>14.4730663299561</v>
       </c>
       <c r="H30" t="n">
         <v>42455</v>
@@ -1268,7 +1268,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G31" t="n">
-        <v>14.5203590393066</v>
+        <v>14.5203580856323</v>
       </c>
       <c r="H31" t="n">
         <v>43925</v>
@@ -1297,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H32" t="n">
         <v>29727</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8881826400757</v>
+        <v>14.8881845474243</v>
       </c>
       <c r="H33" t="n">
         <v>51959</v>
@@ -1355,7 +1355,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5378761291504</v>
+        <v>14.5378751754761</v>
       </c>
       <c r="H34" t="n">
         <v>28201</v>
@@ -1384,7 +1384,7 @@
         <v>16.7220001220703</v>
       </c>
       <c r="G35" t="n">
-        <v>14.6447191238403</v>
+        <v>14.6447200775146</v>
       </c>
       <c r="H35" t="n">
         <v>11249</v>
@@ -1471,7 +1471,7 @@
         <v>16.2859992980957</v>
       </c>
       <c r="G38" t="n">
-        <v>14.2628812789917</v>
+        <v>14.2628793716431</v>
       </c>
       <c r="H38" t="n">
         <v>11160</v>
@@ -1529,7 +1529,7 @@
         <v>16.3980007171631</v>
       </c>
       <c r="G40" t="n">
-        <v>14.3609666824341</v>
+        <v>14.3609676361084</v>
       </c>
       <c r="H40" t="n">
         <v>18974</v>
@@ -1558,7 +1558,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G41" t="n">
-        <v>14.6604824066162</v>
+        <v>14.6604814529419</v>
       </c>
       <c r="H41" t="n">
         <v>29941</v>
@@ -1587,7 +1587,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>14.8006038665771</v>
+        <v>14.8006076812744</v>
       </c>
       <c r="H42" t="n">
         <v>33363</v>
@@ -1616,7 +1616,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>14.8443946838379</v>
+        <v>14.8443956375122</v>
       </c>
       <c r="H43" t="n">
         <v>115888</v>
@@ -1645,7 +1645,7 @@
         <v>16.75</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6692380905151</v>
+        <v>14.6692399978638</v>
       </c>
       <c r="H44" t="n">
         <v>35731</v>
@@ -1703,7 +1703,7 @@
         <v>16.6979999542236</v>
       </c>
       <c r="G46" t="n">
-        <v>14.6237001419067</v>
+        <v>14.6237010955811</v>
       </c>
       <c r="H46" t="n">
         <v>33733</v>
@@ -1732,7 +1732,7 @@
         <v>16.8659992218018</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7708301544189</v>
+        <v>14.7708292007446</v>
       </c>
       <c r="H47" t="n">
         <v>59163</v>
@@ -1761,7 +1761,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G48" t="n">
-        <v>15.0633392333984</v>
+        <v>15.0633411407471</v>
       </c>
       <c r="H48" t="n">
         <v>87381</v>
@@ -1790,7 +1790,7 @@
         <v>17.2840003967285</v>
       </c>
       <c r="G49" t="n">
-        <v>15.136905670166</v>
+        <v>15.1369066238403</v>
       </c>
       <c r="H49" t="n">
         <v>31186</v>
@@ -1819,7 +1819,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G50" t="n">
-        <v>14.126259803772</v>
+        <v>14.1262588500977</v>
       </c>
       <c r="H50" t="n">
         <v>74499</v>
@@ -1848,7 +1848,7 @@
         <v>16.2940006256104</v>
       </c>
       <c r="G51" t="n">
-        <v>14.2698879241943</v>
+        <v>14.26988697052</v>
       </c>
       <c r="H51" t="n">
         <v>29049</v>
@@ -1877,7 +1877,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>14.44153881073</v>
+        <v>14.4415378570557</v>
       </c>
       <c r="H52" t="n">
         <v>18751</v>
@@ -1906,7 +1906,7 @@
         <v>15.996000289917</v>
       </c>
       <c r="G53" t="n">
-        <v>14.0089063644409</v>
+        <v>14.0089073181152</v>
       </c>
       <c r="H53" t="n">
         <v>23213</v>
@@ -1935,7 +1935,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H54" t="n">
         <v>34477</v>
@@ -1964,7 +1964,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G55" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H55" t="n">
         <v>37252</v>
@@ -2051,7 +2051,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G58" t="n">
-        <v>12.9527206420898</v>
+        <v>12.9527196884155</v>
       </c>
       <c r="H58" t="n">
         <v>30556</v>
@@ -2109,7 +2109,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G60" t="n">
-        <v>13.4781856536865</v>
+        <v>13.4781866073608</v>
       </c>
       <c r="H60" t="n">
         <v>34756</v>
@@ -2138,7 +2138,7 @@
         <v>14.5380001068115</v>
       </c>
       <c r="G61" t="n">
-        <v>12.7320251464844</v>
+        <v>12.7320241928101</v>
       </c>
       <c r="H61" t="n">
         <v>21255</v>
@@ -2167,7 +2167,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5602378845215</v>
+        <v>11.5602359771729</v>
       </c>
       <c r="H62" t="n">
         <v>43479</v>
@@ -2196,7 +2196,7 @@
         <v>11.5</v>
       </c>
       <c r="G63" t="n">
-        <v>10.071418762207</v>
+        <v>10.0714197158813</v>
       </c>
       <c r="H63" t="n">
         <v>21708</v>
@@ -2225,7 +2225,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>11.0347719192505</v>
+        <v>11.0347728729248</v>
       </c>
       <c r="H64" t="n">
         <v>37959</v>
@@ -2254,7 +2254,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>9.80868625640869</v>
+        <v>9.80868530273438</v>
       </c>
       <c r="H65" t="n">
         <v>49411</v>
@@ -2341,7 +2341,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>9.10806560516357</v>
+        <v>9.10806465148926</v>
       </c>
       <c r="H68" t="n">
         <v>64858</v>
@@ -2428,7 +2428,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G71" t="n">
-        <v>8.76651477813721</v>
+        <v>8.76651382446289</v>
       </c>
       <c r="H71" t="n">
         <v>44594</v>
@@ -2486,7 +2486,7 @@
         <v>9.75699996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>8.54494190216064</v>
+        <v>8.54494094848633</v>
       </c>
       <c r="H73" t="n">
         <v>9326</v>
@@ -2515,7 +2515,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6701774597168</v>
+        <v>8.67017841339111</v>
       </c>
       <c r="H74" t="n">
         <v>15416</v>
@@ -2544,7 +2544,7 @@
         <v>9.92300033569336</v>
       </c>
       <c r="G75" t="n">
-        <v>8.69032096862793</v>
+        <v>8.69032192230225</v>
       </c>
       <c r="H75" t="n">
         <v>14690</v>
@@ -2573,7 +2573,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G76" t="n">
-        <v>8.92415142059326</v>
+        <v>8.92415237426758</v>
       </c>
       <c r="H76" t="n">
         <v>26972</v>
@@ -2602,7 +2602,7 @@
         <v>10.3280000686646</v>
       </c>
       <c r="G77" t="n">
-        <v>9.04501056671143</v>
+        <v>9.04500961303711</v>
       </c>
       <c r="H77" t="n">
         <v>9539</v>
@@ -2747,7 +2747,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.8070707321167</v>
+        <v>10.8070697784424</v>
       </c>
       <c r="H82" t="n">
         <v>3945</v>
@@ -2863,7 +2863,7 @@
         <v>12.3179998397827</v>
       </c>
       <c r="G86" t="n">
-        <v>10.7878036499023</v>
+        <v>10.787802696228</v>
       </c>
       <c r="H86" t="n">
         <v>15151</v>
@@ -3008,7 +3008,7 @@
         <v>13.5</v>
       </c>
       <c r="G91" t="n">
-        <v>11.8229684829712</v>
+        <v>11.8229703903198</v>
       </c>
       <c r="H91" t="n">
         <v>16703</v>
@@ -3066,7 +3066,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>11.0347719192505</v>
+        <v>11.0347728729248</v>
       </c>
       <c r="H93" t="n">
         <v>52489</v>
@@ -3095,7 +3095,7 @@
         <v>12.4840002059937</v>
       </c>
       <c r="G94" t="n">
-        <v>10.9331817626953</v>
+        <v>10.9331827163696</v>
       </c>
       <c r="H94" t="n">
         <v>46331</v>
@@ -3153,7 +3153,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G96" t="n">
-        <v>10.6143999099731</v>
+        <v>10.6143989562988</v>
       </c>
       <c r="H96" t="n">
         <v>30171</v>
@@ -3182,7 +3182,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G97" t="n">
-        <v>10.4655179977417</v>
+        <v>10.4655170440674</v>
       </c>
       <c r="H97" t="n">
         <v>30855</v>
@@ -3211,7 +3211,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.386697769165</v>
+        <v>10.3866968154907</v>
       </c>
       <c r="H98" t="n">
         <v>22385</v>
@@ -3240,7 +3240,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3691825866699</v>
+        <v>10.3691816329956</v>
       </c>
       <c r="H99" t="n">
         <v>11865</v>
@@ -3269,7 +3269,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>10.307879447937</v>
+        <v>10.3078784942627</v>
       </c>
       <c r="H100" t="n">
         <v>7478</v>
@@ -3298,7 +3298,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2465734481812</v>
+        <v>10.2465744018555</v>
       </c>
       <c r="H101" t="n">
         <v>6381</v>
@@ -3327,7 +3327,7 @@
         <v>11.9980001449585</v>
       </c>
       <c r="G102" t="n">
-        <v>10.5075550079346</v>
+        <v>10.5075559616089</v>
       </c>
       <c r="H102" t="n">
         <v>41323</v>
@@ -3356,7 +3356,7 @@
         <v>12.173999786377</v>
       </c>
       <c r="G103" t="n">
-        <v>10.6616916656494</v>
+        <v>10.6616907119751</v>
       </c>
       <c r="H103" t="n">
         <v>12365</v>
@@ -3385,7 +3385,7 @@
         <v>11.7620000839233</v>
       </c>
       <c r="G104" t="n">
-        <v>10.3008718490601</v>
+        <v>10.3008728027344</v>
       </c>
       <c r="H104" t="n">
         <v>32832</v>
@@ -3414,7 +3414,7 @@
         <v>11.8540000915527</v>
       </c>
       <c r="G105" t="n">
-        <v>10.3814430236816</v>
+        <v>10.381443977356</v>
       </c>
       <c r="H105" t="n">
         <v>19187</v>
@@ -3501,7 +3501,7 @@
         <v>12.9280004501343</v>
       </c>
       <c r="G108" t="n">
-        <v>11.3220262527466</v>
+        <v>11.3220272064209</v>
       </c>
       <c r="H108" t="n">
         <v>36330</v>
@@ -3559,7 +3559,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>11.4726600646973</v>
+        <v>11.4726610183716</v>
       </c>
       <c r="H110" t="n">
         <v>21522</v>
@@ -3617,7 +3617,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>11.8667593002319</v>
+        <v>11.8667573928833</v>
       </c>
       <c r="H112" t="n">
         <v>27613</v>
@@ -3646,7 +3646,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G113" t="n">
-        <v>12.1119756698608</v>
+        <v>12.1119766235352</v>
       </c>
       <c r="H113" t="n">
         <v>32594</v>
@@ -3675,7 +3675,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G114" t="n">
-        <v>12.3834667205811</v>
+        <v>12.3834657669067</v>
       </c>
       <c r="H114" t="n">
         <v>29369</v>
@@ -3762,7 +3762,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G117" t="n">
-        <v>12.2258262634277</v>
+        <v>12.2258272171021</v>
       </c>
       <c r="H117" t="n">
         <v>24996</v>
@@ -3791,7 +3791,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>12.3922252655029</v>
+        <v>12.39222240448</v>
       </c>
       <c r="H118" t="n">
         <v>16297</v>
@@ -3849,7 +3849,7 @@
         <v>14.2959995269775</v>
       </c>
       <c r="G120" t="n">
-        <v>12.5200862884521</v>
+        <v>12.5200853347778</v>
       </c>
       <c r="H120" t="n">
         <v>40636</v>
@@ -3878,7 +3878,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G121" t="n">
-        <v>12.760048866272</v>
+        <v>12.7600498199463</v>
       </c>
       <c r="H121" t="n">
         <v>53970</v>
@@ -3907,7 +3907,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H122" t="n">
         <v>27467</v>
@@ -3936,7 +3936,7 @@
         <v>15.1979999542236</v>
       </c>
       <c r="G123" t="n">
-        <v>13.3100366592407</v>
+        <v>13.310037612915</v>
       </c>
       <c r="H123" t="n">
         <v>25697</v>
@@ -3965,7 +3965,7 @@
         <v>14.8360004425049</v>
       </c>
       <c r="G124" t="n">
-        <v>12.9930067062378</v>
+        <v>12.9930057525635</v>
       </c>
       <c r="H124" t="n">
         <v>20213</v>
@@ -3994,7 +3994,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>12.7863235473633</v>
+        <v>12.7863245010376</v>
       </c>
       <c r="H125" t="n">
         <v>14042</v>
@@ -4023,7 +4023,7 @@
         <v>14.3760004043579</v>
       </c>
       <c r="G126" t="n">
-        <v>12.5901489257812</v>
+        <v>12.5901498794556</v>
       </c>
       <c r="H126" t="n">
         <v>27217</v>
@@ -4052,7 +4052,7 @@
         <v>15.5</v>
       </c>
       <c r="G127" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H127" t="n">
         <v>96046</v>
@@ -4081,7 +4081,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H128" t="n">
         <v>20883</v>
@@ -4110,7 +4110,7 @@
         <v>15.0860004425049</v>
       </c>
       <c r="G129" t="n">
-        <v>13.2119512557983</v>
+        <v>13.211950302124</v>
       </c>
       <c r="H129" t="n">
         <v>8002</v>
@@ -4168,7 +4168,7 @@
         <v>15.3420000076294</v>
       </c>
       <c r="G131" t="n">
-        <v>13.4361486434937</v>
+        <v>13.4361476898193</v>
       </c>
       <c r="H131" t="n">
         <v>17251</v>
@@ -4255,7 +4255,7 @@
         <v>15.5</v>
       </c>
       <c r="G134" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H134" t="n">
         <v>10358</v>
@@ -4342,7 +4342,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H137" t="n">
         <v>5525</v>
@@ -4371,7 +4371,7 @@
         <v>15.03600025177</v>
       </c>
       <c r="G138" t="n">
-        <v>13.1681604385376</v>
+        <v>13.1681613922119</v>
       </c>
       <c r="H138" t="n">
         <v>2768</v>
@@ -4400,7 +4400,7 @@
         <v>14.9359998703003</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0805826187134</v>
+        <v>13.0805835723877</v>
       </c>
       <c r="H139" t="n">
         <v>13088</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H140" t="n">
         <v>6887</v>
@@ -4545,7 +4545,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>13.0928430557251</v>
+        <v>13.0928449630737</v>
       </c>
       <c r="H144" t="n">
         <v>3240</v>
@@ -4574,7 +4574,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0490550994873</v>
+        <v>13.0490560531616</v>
       </c>
       <c r="H145" t="n">
         <v>1877</v>
@@ -4603,7 +4603,7 @@
         <v>14.8179998397827</v>
       </c>
       <c r="G146" t="n">
-        <v>12.9772415161133</v>
+        <v>12.9772424697876</v>
       </c>
       <c r="H146" t="n">
         <v>4221</v>
@@ -4632,7 +4632,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G147" t="n">
-        <v>13.2504844665527</v>
+        <v>13.2504835128784</v>
       </c>
       <c r="H147" t="n">
         <v>20035</v>
@@ -4719,7 +4719,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H150" t="n">
         <v>1530</v>
@@ -4777,7 +4777,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H152" t="n">
         <v>9093</v>
@@ -4893,7 +4893,7 @@
         <v>15.1040000915527</v>
       </c>
       <c r="G156" t="n">
-        <v>13.2277145385742</v>
+        <v>13.2277154922485</v>
       </c>
       <c r="H156" t="n">
         <v>19524</v>
@@ -4922,7 +4922,7 @@
         <v>15.25</v>
       </c>
       <c r="G157" t="n">
-        <v>13.3555765151978</v>
+        <v>13.3555774688721</v>
       </c>
       <c r="H157" t="n">
         <v>9479</v>
@@ -5038,7 +5038,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H161" t="n">
         <v>8576</v>
@@ -5067,7 +5067,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>12.3309183120728</v>
+        <v>12.3309192657471</v>
       </c>
       <c r="H162" t="n">
         <v>17829</v>
@@ -5096,7 +5096,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>12.5673789978027</v>
+        <v>12.5673780441284</v>
       </c>
       <c r="H163" t="n">
         <v>11473</v>
@@ -5125,7 +5125,7 @@
         <v>14.3179998397827</v>
       </c>
       <c r="G164" t="n">
-        <v>12.5393533706665</v>
+        <v>12.5393543243408</v>
       </c>
       <c r="H164" t="n">
         <v>30378</v>
@@ -5154,7 +5154,7 @@
         <v>14.3979997634888</v>
       </c>
       <c r="G165" t="n">
-        <v>12.6094160079956</v>
+        <v>12.6094169616699</v>
       </c>
       <c r="H165" t="n">
         <v>15675</v>
@@ -5212,7 +5212,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G167" t="n">
-        <v>12.3484363555908</v>
+        <v>12.3484354019165</v>
       </c>
       <c r="H167" t="n">
         <v>9897</v>
@@ -5241,7 +5241,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G168" t="n">
-        <v>12.4097385406494</v>
+        <v>12.409740447998</v>
       </c>
       <c r="H168" t="n">
         <v>11733</v>
@@ -5270,7 +5270,7 @@
         <v>15</v>
       </c>
       <c r="G169" t="n">
-        <v>13.1366329193115</v>
+        <v>13.1366348266602</v>
       </c>
       <c r="H169" t="n">
         <v>3414</v>
@@ -5299,7 +5299,7 @@
         <v>15.0620002746582</v>
       </c>
       <c r="G170" t="n">
-        <v>13.1909313201904</v>
+        <v>13.1909322738647</v>
       </c>
       <c r="H170" t="n">
         <v>36613</v>
@@ -5386,7 +5386,7 @@
         <v>15.6280002593994</v>
       </c>
       <c r="G173" t="n">
-        <v>13.6866207122803</v>
+        <v>13.686619758606</v>
       </c>
       <c r="H173" t="n">
         <v>4657</v>
@@ -5444,7 +5444,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H175" t="n">
         <v>24554</v>
@@ -5502,7 +5502,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H177" t="n">
         <v>16366</v>
@@ -5531,7 +5531,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G178" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H178" t="n">
         <v>14964</v>
@@ -5618,7 +5618,7 @@
         <v>15.9280004501343</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9493541717529</v>
+        <v>13.9493551254272</v>
       </c>
       <c r="H181" t="n">
         <v>30984</v>
@@ -5937,7 +5937,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G192" t="n">
-        <v>13.6445837020874</v>
+        <v>13.6445817947388</v>
       </c>
       <c r="H192" t="n">
         <v>31164</v>
@@ -5966,7 +5966,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H193" t="n">
         <v>36033</v>
@@ -6024,7 +6024,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>13.6796140670776</v>
+        <v>13.6796131134033</v>
       </c>
       <c r="H195" t="n">
         <v>5114</v>
@@ -6082,7 +6082,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G197" t="n">
-        <v>13.2942733764648</v>
+        <v>13.2942714691162</v>
       </c>
       <c r="H197" t="n">
         <v>21767</v>
@@ -6111,7 +6111,7 @@
         <v>15</v>
       </c>
       <c r="G198" t="n">
-        <v>13.1366329193115</v>
+        <v>13.1366348266602</v>
       </c>
       <c r="H198" t="n">
         <v>5996</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>12.9614791870117</v>
+        <v>12.9614782333374</v>
       </c>
       <c r="H199" t="n">
         <v>7759</v>
@@ -6343,7 +6343,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G206" t="n">
-        <v>14.4678115844727</v>
+        <v>14.467812538147</v>
       </c>
       <c r="H206" t="n">
         <v>39648</v>
@@ -6488,7 +6488,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G211" t="n">
-        <v>14.730544090271</v>
+        <v>14.7305450439453</v>
       </c>
       <c r="H211" t="n">
         <v>9090</v>
@@ -6575,7 +6575,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="n">
-        <v>14.6955146789551</v>
+        <v>14.6955137252808</v>
       </c>
       <c r="H214" t="n">
         <v>13259</v>
@@ -6633,7 +6633,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G216" t="n">
-        <v>14.3452024459839</v>
+        <v>14.3452005386353</v>
       </c>
       <c r="H216" t="n">
         <v>9351</v>
@@ -6749,7 +6749,7 @@
         <v>15.5</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H220" t="n">
         <v>11900</v>
@@ -6778,7 +6778,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G221" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H221" t="n">
         <v>2428</v>
@@ -6836,7 +6836,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G223" t="n">
-        <v>13.5044593811035</v>
+        <v>13.5044584274292</v>
       </c>
       <c r="H223" t="n">
         <v>17777</v>
@@ -6865,7 +6865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>13.3117876052856</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H224" t="n">
         <v>45360</v>
@@ -6894,7 +6894,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G225" t="n">
-        <v>13.2592420578003</v>
+        <v>13.2592430114746</v>
       </c>
       <c r="H225" t="n">
         <v>9073</v>
@@ -6923,7 +6923,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G226" t="n">
-        <v>13.3117876052856</v>
+        <v>13.31178855896</v>
       </c>
       <c r="H226" t="n">
         <v>5423</v>
@@ -6952,7 +6952,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G227" t="n">
-        <v>13.1016025543213</v>
+        <v>13.101601600647</v>
       </c>
       <c r="H227" t="n">
         <v>2440</v>
@@ -7010,7 +7010,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H229" t="n">
         <v>11492</v>
@@ -7068,7 +7068,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>13.6620998382568</v>
+        <v>13.6620988845825</v>
       </c>
       <c r="H231" t="n">
         <v>6598</v>
@@ -7126,7 +7126,7 @@
         <v>15.5</v>
       </c>
       <c r="G233" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H233" t="n">
         <v>26206</v>
@@ -7242,7 +7242,7 @@
         <v>15.5</v>
       </c>
       <c r="G237" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H237" t="n">
         <v>17203</v>
@@ -7271,7 +7271,7 @@
         <v>15.5</v>
       </c>
       <c r="G238" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H238" t="n">
         <v>12067</v>
@@ -7300,7 +7300,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G239" t="n">
-        <v>13.6796140670776</v>
+        <v>13.6796131134033</v>
       </c>
       <c r="H239" t="n">
         <v>20611</v>
@@ -7416,7 +7416,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G243" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H243" t="n">
         <v>4468</v>
@@ -7445,7 +7445,7 @@
         <v>15.5</v>
       </c>
       <c r="G244" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H244" t="n">
         <v>25909</v>
@@ -7474,7 +7474,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G245" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H245" t="n">
         <v>13611</v>
@@ -7532,7 +7532,7 @@
         <v>15.5</v>
       </c>
       <c r="G247" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H247" t="n">
         <v>18668</v>
@@ -7561,7 +7561,7 @@
         <v>15.5</v>
       </c>
       <c r="G248" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H248" t="n">
         <v>7591</v>
@@ -7590,7 +7590,7 @@
         <v>15.5</v>
       </c>
       <c r="G249" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H249" t="n">
         <v>4482</v>
@@ -7619,7 +7619,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H250" t="n">
         <v>41070</v>
@@ -7648,7 +7648,7 @@
         <v>15.5</v>
       </c>
       <c r="G251" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H251" t="n">
         <v>2749</v>
@@ -7706,7 +7706,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>13.3993654251099</v>
+        <v>13.3993673324585</v>
       </c>
       <c r="H253" t="n">
         <v>8244</v>
@@ -7735,7 +7735,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G254" t="n">
-        <v>13.8022222518921</v>
+        <v>13.8022232055664</v>
       </c>
       <c r="H254" t="n">
         <v>8921</v>
@@ -7793,7 +7793,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G256" t="n">
-        <v>13.6270666122437</v>
+        <v>13.627067565918</v>
       </c>
       <c r="H256" t="n">
         <v>4482</v>
@@ -7822,7 +7822,7 @@
         <v>15.5</v>
       </c>
       <c r="G257" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H257" t="n">
         <v>7773</v>
@@ -7851,7 +7851,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G258" t="n">
-        <v>13.7496757507324</v>
+        <v>13.7496767044067</v>
       </c>
       <c r="H258" t="n">
         <v>4171</v>
@@ -7880,7 +7880,7 @@
         <v>15.5</v>
       </c>
       <c r="G259" t="n">
-        <v>13.5745220184326</v>
+        <v>13.574520111084</v>
       </c>
       <c r="H259" t="n">
         <v>10259</v>
@@ -7909,7 +7909,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G260" t="n">
-        <v>13.5219736099243</v>
+        <v>13.5219745635986</v>
       </c>
       <c r="H260" t="n">
         <v>15560</v>
@@ -7967,7 +7967,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G262" t="n">
-        <v>13.8197374343872</v>
+        <v>13.8197383880615</v>
       </c>
       <c r="H262" t="n">
         <v>19414</v>
@@ -7996,7 +7996,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G263" t="n">
-        <v>13.9773797988892</v>
+        <v>13.9773778915405</v>
       </c>
       <c r="H263" t="n">
         <v>14625</v>
@@ -8199,7 +8199,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G270" t="n">
-        <v>14.2576246261597</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H270" t="n">
         <v>5152</v>
@@ -8228,7 +8228,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G271" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H271" t="n">
         <v>6060</v>
@@ -8257,7 +8257,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G272" t="n">
-        <v>14.5028419494629</v>
+        <v>14.5028429031372</v>
       </c>
       <c r="H272" t="n">
         <v>8570</v>
@@ -8286,7 +8286,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G273" t="n">
-        <v>14.6079368591309</v>
+        <v>14.6079349517822</v>
       </c>
       <c r="H273" t="n">
         <v>7891</v>
@@ -8315,7 +8315,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G274" t="n">
-        <v>14.3977508544922</v>
+        <v>14.3977499008179</v>
       </c>
       <c r="H274" t="n">
         <v>5498</v>
@@ -8373,7 +8373,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G276" t="n">
-        <v>14.3276891708374</v>
+        <v>14.3276882171631</v>
       </c>
       <c r="H276" t="n">
         <v>6927</v>
@@ -8402,7 +8402,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G277" t="n">
-        <v>14.2576246261597</v>
+        <v>14.257625579834</v>
       </c>
       <c r="H277" t="n">
         <v>6898</v>
@@ -8518,7 +8518,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G281" t="n">
-        <v>15.7114133834839</v>
+        <v>15.7114114761353</v>
       </c>
       <c r="H281" t="n">
         <v>48160</v>
@@ -8547,7 +8547,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G282" t="n">
-        <v>15.7989921569824</v>
+        <v>15.7989902496338</v>
       </c>
       <c r="H282" t="n">
         <v>60104</v>
@@ -8576,7 +8576,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>15.5888042449951</v>
+        <v>15.5888032913208</v>
       </c>
       <c r="H283" t="n">
         <v>32761</v>
@@ -8605,7 +8605,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G284" t="n">
-        <v>15.8165044784546</v>
+        <v>15.8165054321289</v>
       </c>
       <c r="H284" t="n">
         <v>60606</v>
@@ -8692,7 +8692,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G287" t="n">
-        <v>16.1317844390869</v>
+        <v>16.1317863464355</v>
       </c>
       <c r="H287" t="n">
         <v>34304</v>
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="G288" t="n">
-        <v>16.6397342681885</v>
+        <v>16.6397361755371</v>
       </c>
       <c r="H288" t="n">
         <v>19711</v>
@@ -8808,7 +8808,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>16.9024677276611</v>
+        <v>16.9024658203125</v>
       </c>
       <c r="H291" t="n">
         <v>43984</v>
@@ -8837,7 +8837,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>17.3403549194336</v>
+        <v>17.3403568267822</v>
       </c>
       <c r="H292" t="n">
         <v>108964</v>
@@ -8895,7 +8895,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G294" t="n">
-        <v>17.5592975616455</v>
+        <v>17.5592994689941</v>
       </c>
       <c r="H294" t="n">
         <v>17437</v>
@@ -8953,7 +8953,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G296" t="n">
-        <v>17.6906661987305</v>
+        <v>17.6906642913818</v>
       </c>
       <c r="H296" t="n">
         <v>36908</v>
@@ -8982,7 +8982,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>17.252779006958</v>
+        <v>17.2527809143066</v>
       </c>
       <c r="H297" t="n">
         <v>43040</v>
@@ -9011,7 +9011,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>17.646879196167</v>
+        <v>17.6468772888184</v>
       </c>
       <c r="H298" t="n">
         <v>49334</v>
@@ -9127,7 +9127,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>17.4979953765869</v>
+        <v>17.4979934692383</v>
       </c>
       <c r="H302" t="n">
         <v>43697</v>
@@ -9156,7 +9156,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G303" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H303" t="n">
         <v>51778</v>
@@ -9214,7 +9214,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>18.1285533905029</v>
+        <v>18.1285552978516</v>
       </c>
       <c r="H305" t="n">
         <v>35889</v>
@@ -9243,7 +9243,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919036865234</v>
       </c>
       <c r="H306" t="n">
         <v>77246</v>
@@ -9272,7 +9272,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853870391846</v>
       </c>
       <c r="H307" t="n">
         <v>24097</v>
@@ -9417,7 +9417,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G312" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415962219238</v>
       </c>
       <c r="H312" t="n">
         <v>23897</v>
@@ -9446,7 +9446,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1356983184814</v>
+        <v>19.1356964111328</v>
       </c>
       <c r="H313" t="n">
         <v>16234</v>
@@ -9504,7 +9504,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919036865234</v>
       </c>
       <c r="H315" t="n">
         <v>9511</v>
@@ -9591,7 +9591,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853870391846</v>
       </c>
       <c r="H318" t="n">
         <v>14808</v>
@@ -9649,7 +9649,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>19.6173725128174</v>
+        <v>19.6173706054688</v>
       </c>
       <c r="H320" t="n">
         <v>55008</v>
@@ -9736,7 +9736,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794834136963</v>
       </c>
       <c r="H323" t="n">
         <v>9282</v>
@@ -9765,7 +9765,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7487392425537</v>
+        <v>19.7487373352051</v>
       </c>
       <c r="H324" t="n">
         <v>38949</v>
@@ -9823,7 +9823,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735816955566</v>
       </c>
       <c r="H326" t="n">
         <v>15812</v>
@@ -9852,7 +9852,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G327" t="n">
-        <v>19.5735855102539</v>
+        <v>19.5735816955566</v>
       </c>
       <c r="H327" t="n">
         <v>7040</v>
@@ -9881,7 +9881,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H328" t="n">
         <v>5122</v>
@@ -9910,7 +9910,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>18.8729591369629</v>
+        <v>18.8729610443115</v>
       </c>
       <c r="H329" t="n">
         <v>14665</v>
@@ -9968,7 +9968,7 @@
         <v>21.75</v>
       </c>
       <c r="G331" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H331" t="n">
         <v>11487</v>
@@ -9997,7 +9997,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G332" t="n">
-        <v>19.0919075012207</v>
+        <v>19.0919036865234</v>
       </c>
       <c r="H332" t="n">
         <v>8982</v>
@@ -10026,7 +10026,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>19.223274230957</v>
+        <v>19.2232723236084</v>
       </c>
       <c r="H333" t="n">
         <v>8384</v>
@@ -10055,7 +10055,7 @@
         <v>21.75</v>
       </c>
       <c r="G334" t="n">
-        <v>19.0481185913086</v>
+        <v>19.04811668396</v>
       </c>
       <c r="H334" t="n">
         <v>5987</v>
@@ -10084,7 +10084,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.7853851318359</v>
+        <v>18.7853870391846</v>
       </c>
       <c r="H335" t="n">
         <v>17649</v>
@@ -10142,7 +10142,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>18.7415943145752</v>
+        <v>18.7415962219238</v>
       </c>
       <c r="H337" t="n">
         <v>8572</v>
@@ -10229,7 +10229,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G340" t="n">
-        <v>19.1794853210449</v>
+        <v>19.1794834136963</v>
       </c>
       <c r="H340" t="n">
         <v>8629</v>
@@ -10287,7 +10287,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H342" t="n">
         <v>48534</v>
@@ -10316,7 +10316,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G343" t="n">
-        <v>18.0409755706787</v>
+        <v>18.0409774780273</v>
       </c>
       <c r="H343" t="n">
         <v>22326</v>
@@ -10345,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="G344" t="n">
-        <v>18.3912887573242</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H344" t="n">
         <v>18146</v>
@@ -10374,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="G345" t="n">
-        <v>18.3912887573242</v>
+        <v>18.391284942627</v>
       </c>
       <c r="H345" t="n">
         <v>7042</v>
@@ -10403,7 +10403,7 @@
         <v>21.25</v>
       </c>
       <c r="G346" t="n">
-        <v>18.8799438476562</v>
+        <v>18.8799457550049</v>
       </c>
       <c r="H346" t="n">
         <v>13430</v>
@@ -10461,7 +10461,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.7239894866943</v>
+        <v>19.723991394043</v>
       </c>
       <c r="H348" t="n">
         <v>25636</v>
@@ -10490,7 +10490,7 @@
         <v>22.75</v>
       </c>
       <c r="G349" t="n">
-        <v>20.212646484375</v>
+        <v>20.2126483917236</v>
       </c>
       <c r="H349" t="n">
         <v>34567</v>
@@ -10606,7 +10606,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>19.8572616577148</v>
+        <v>19.8572597503662</v>
       </c>
       <c r="H353" t="n">
         <v>50006</v>
@@ -10635,7 +10635,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>20.0793743133545</v>
+        <v>20.0793762207031</v>
       </c>
       <c r="H354" t="n">
         <v>30645</v>
@@ -10867,7 +10867,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>19.6351432800293</v>
+        <v>19.6351413726807</v>
       </c>
       <c r="H362" t="n">
         <v>29703</v>
@@ -10954,7 +10954,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>20.523609161377</v>
+        <v>20.5236110687256</v>
       </c>
       <c r="H365" t="n">
         <v>43029</v>
@@ -11070,7 +11070,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>21.1455364227295</v>
+        <v>21.1455383300781</v>
       </c>
       <c r="H369" t="n">
         <v>96384</v>
@@ -11099,7 +11099,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G370" t="n">
-        <v>21.2788105010986</v>
+        <v>21.27880859375</v>
       </c>
       <c r="H370" t="n">
         <v>39616</v>
@@ -11215,7 +11215,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G374" t="n">
-        <v>23.233434677124</v>
+        <v>23.2334365844727</v>
       </c>
       <c r="H374" t="n">
         <v>53913</v>
@@ -11302,7 +11302,7 @@
         <v>26.0499992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>23.1445903778076</v>
+        <v>23.144588470459</v>
       </c>
       <c r="H377" t="n">
         <v>33185</v>
@@ -11360,7 +11360,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H379" t="n">
         <v>1533317</v>
@@ -11418,7 +11418,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G381" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H381" t="n">
         <v>46241</v>
@@ -11447,7 +11447,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>21.8563117980957</v>
+        <v>21.8563098907471</v>
       </c>
       <c r="H382" t="n">
         <v>53898</v>
@@ -11476,7 +11476,7 @@
         <v>24.25</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5453472137451</v>
+        <v>21.5453491210938</v>
       </c>
       <c r="H383" t="n">
         <v>33134</v>
@@ -11505,7 +11505,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5897693634033</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H384" t="n">
         <v>31931</v>
@@ -11592,7 +11592,7 @@
         <v>23.75</v>
       </c>
       <c r="G387" t="n">
-        <v>21.1011161804199</v>
+        <v>21.1011142730713</v>
       </c>
       <c r="H387" t="n">
         <v>8616</v>
@@ -11621,7 +11621,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>21.0566940307617</v>
+        <v>21.0566902160645</v>
       </c>
       <c r="H388" t="n">
         <v>20039</v>
@@ -11708,7 +11708,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G391" t="n">
-        <v>20.7901496887207</v>
+        <v>20.7901515960693</v>
       </c>
       <c r="H391" t="n">
         <v>21903</v>
@@ -11737,7 +11737,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G392" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H392" t="n">
         <v>28978</v>
@@ -11795,7 +11795,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G394" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H394" t="n">
         <v>27878</v>
@@ -11882,7 +11882,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>20.5680332183838</v>
+        <v>20.5680313110352</v>
       </c>
       <c r="H397" t="n">
         <v>6449</v>
@@ -11969,7 +11969,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>21.2788105010986</v>
+        <v>21.27880859375</v>
       </c>
       <c r="H400" t="n">
         <v>41832</v>
@@ -11998,7 +11998,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>21.5897693634033</v>
+        <v>21.589771270752</v>
       </c>
       <c r="H401" t="n">
         <v>37886</v>
@@ -12027,7 +12027,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>21.678617477417</v>
+        <v>21.6786193847656</v>
       </c>
       <c r="H402" t="n">
         <v>58589</v>
@@ -12056,7 +12056,7 @@
         <v>24.25</v>
       </c>
       <c r="G403" t="n">
-        <v>21.5453472137451</v>
+        <v>21.5453491210938</v>
       </c>
       <c r="H403" t="n">
         <v>29308</v>
@@ -12114,7 +12114,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G405" t="n">
-        <v>21.2788105010986</v>
+        <v>21.27880859375</v>
       </c>
       <c r="H405" t="n">
         <v>18949</v>
@@ -12172,7 +12172,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>20.3459148406982</v>
+        <v>20.3459167480469</v>
       </c>
       <c r="H407" t="n">
         <v>12913</v>
@@ -12230,7 +12230,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>20.9234218597412</v>
+        <v>20.9234199523926</v>
       </c>
       <c r="H409" t="n">
         <v>11555</v>
@@ -12433,7 +12433,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>22.6115093231201</v>
+        <v>22.6115074157715</v>
       </c>
       <c r="H416" t="n">
         <v>44042</v>
@@ -12462,7 +12462,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G417" t="n">
-        <v>22.3893928527832</v>
+        <v>22.3893947601318</v>
       </c>
       <c r="H417" t="n">
         <v>9809</v>
@@ -12520,7 +12520,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5226631164551</v>
+        <v>22.5226650238037</v>
       </c>
       <c r="H419" t="n">
         <v>40477</v>
@@ -12549,7 +12549,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>22.3893928527832</v>
+        <v>22.3893947601318</v>
       </c>
       <c r="H420" t="n">
         <v>10509</v>
@@ -12578,7 +12578,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>22.9224700927734</v>
+        <v>22.9224720001221</v>
       </c>
       <c r="H421" t="n">
         <v>20723</v>
@@ -12636,7 +12636,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>24.2551765441895</v>
+        <v>24.2551746368408</v>
       </c>
       <c r="H423" t="n">
         <v>80709</v>
@@ -12694,7 +12694,7 @@
         <v>26.5</v>
       </c>
       <c r="G425" t="n">
-        <v>23.5444030761719</v>
+        <v>23.5443992614746</v>
       </c>
       <c r="H425" t="n">
         <v>13710</v>
@@ -12723,7 +12723,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>23.6332492828369</v>
+        <v>23.6332473754883</v>
       </c>
       <c r="H426" t="n">
         <v>20089</v>
@@ -12752,7 +12752,7 @@
         <v>27</v>
       </c>
       <c r="G427" t="n">
-        <v>23.9886322021484</v>
+        <v>23.9886341094971</v>
       </c>
       <c r="H427" t="n">
         <v>21987</v>
@@ -12781,7 +12781,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G428" t="n">
-        <v>24.4772911071777</v>
+        <v>24.4772930145264</v>
       </c>
       <c r="H428" t="n">
         <v>27149</v>
@@ -12810,7 +12810,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>24.1219024658203</v>
+        <v>24.1219062805176</v>
       </c>
       <c r="H429" t="n">
         <v>41301</v>
@@ -12926,7 +12926,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>24.5661392211914</v>
+        <v>24.56614112854</v>
       </c>
       <c r="H433" t="n">
         <v>14231</v>
@@ -13013,7 +13013,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>25.2324886322021</v>
+        <v>25.2324924468994</v>
       </c>
       <c r="H436" t="n">
         <v>14765</v>
@@ -13071,7 +13071,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H438" t="n">
         <v>49309</v>
@@ -13100,7 +13100,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>26.3874988555908</v>
+        <v>26.3875007629395</v>
       </c>
       <c r="H439" t="n">
         <v>22024</v>
@@ -13158,7 +13158,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G441" t="n">
-        <v>26.5207691192627</v>
+        <v>26.5207710266113</v>
       </c>
       <c r="H441" t="n">
         <v>28926</v>
@@ -13245,7 +13245,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G444" t="n">
-        <v>27.4536609649658</v>
+        <v>27.4536628723145</v>
       </c>
       <c r="H444" t="n">
         <v>42660</v>
@@ -13274,7 +13274,7 @@
         <v>31</v>
       </c>
       <c r="G445" t="n">
-        <v>27.5425090789795</v>
+        <v>27.5425052642822</v>
       </c>
       <c r="H445" t="n">
         <v>31951</v>
@@ -13332,7 +13332,7 @@
         <v>34.25</v>
       </c>
       <c r="G447" t="n">
-        <v>30.4300270080566</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H447" t="n">
         <v>138213</v>
@@ -13361,7 +13361,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>30.2967548370361</v>
+        <v>30.2967567443848</v>
       </c>
       <c r="H448" t="n">
         <v>76626</v>
@@ -13419,7 +13419,7 @@
         <v>33.5</v>
       </c>
       <c r="G450" t="n">
-        <v>29.7636737823486</v>
+        <v>29.7636795043945</v>
       </c>
       <c r="H450" t="n">
         <v>69374</v>
@@ -13448,7 +13448,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>29.1417503356934</v>
+        <v>29.1417484283447</v>
       </c>
       <c r="H451" t="n">
         <v>55282</v>
@@ -13477,7 +13477,7 @@
         <v>33.1500015258789</v>
       </c>
       <c r="G452" t="n">
-        <v>29.4527168273926</v>
+        <v>29.4527149200439</v>
       </c>
       <c r="H452" t="n">
         <v>29627</v>
@@ -13506,7 +13506,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>29.6748352050781</v>
+        <v>29.6748294830322</v>
       </c>
       <c r="H453" t="n">
         <v>18449</v>
@@ -13535,7 +13535,7 @@
         <v>34.25</v>
       </c>
       <c r="G454" t="n">
-        <v>30.4300270080566</v>
+        <v>30.4300289154053</v>
       </c>
       <c r="H454" t="n">
         <v>27063</v>
@@ -13564,7 +13564,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>30.4744491577148</v>
+        <v>30.4744529724121</v>
       </c>
       <c r="H455" t="n">
         <v>27798</v>
@@ -13622,7 +13622,7 @@
         <v>31.25</v>
       </c>
       <c r="G457" t="n">
-        <v>27.7646236419678</v>
+        <v>27.7646217346191</v>
       </c>
       <c r="H457" t="n">
         <v>101299</v>
@@ -13651,7 +13651,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G458" t="n">
-        <v>28.0311622619629</v>
+        <v>28.0311660766602</v>
       </c>
       <c r="H458" t="n">
         <v>38519</v>
@@ -13680,7 +13680,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>28.0311622619629</v>
+        <v>28.0311660766602</v>
       </c>
       <c r="H459" t="n">
         <v>26817</v>
@@ -13709,7 +13709,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>27.9423179626465</v>
+        <v>27.9423198699951</v>
       </c>
       <c r="H460" t="n">
         <v>17404</v>
@@ -13738,7 +13738,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>28.475399017334</v>
+        <v>28.4753971099854</v>
       </c>
       <c r="H461" t="n">
         <v>73902</v>
@@ -13767,7 +13767,7 @@
         <v>31.5</v>
       </c>
       <c r="G462" t="n">
-        <v>27.9867420196533</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H462" t="n">
         <v>26586</v>
@@ -13796,7 +13796,7 @@
         <v>31.5</v>
       </c>
       <c r="G463" t="n">
-        <v>27.9867420196533</v>
+        <v>27.9867401123047</v>
       </c>
       <c r="H463" t="n">
         <v>39977</v>
@@ -13825,7 +13825,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G464" t="n">
-        <v>29.230598449707</v>
+        <v>29.2305965423584</v>
       </c>
       <c r="H464" t="n">
         <v>33973</v>
@@ -13912,7 +13912,7 @@
         <v>33.75</v>
       </c>
       <c r="G467" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H467" t="n">
         <v>54363</v>
@@ -13941,7 +13941,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G468" t="n">
-        <v>29.8525199890137</v>
+        <v>29.8525218963623</v>
       </c>
       <c r="H468" t="n">
         <v>33525</v>
@@ -13999,7 +13999,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G470" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H470" t="n">
         <v>44745</v>
@@ -14028,7 +14028,7 @@
         <v>35.5</v>
       </c>
       <c r="G471" t="n">
-        <v>31.5406131744385</v>
+        <v>31.5406150817871</v>
       </c>
       <c r="H471" t="n">
         <v>48516</v>
@@ -14057,7 +14057,7 @@
         <v>35.75</v>
       </c>
       <c r="G472" t="n">
-        <v>31.7627296447754</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H472" t="n">
         <v>35631</v>
@@ -14086,7 +14086,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H473" t="n">
         <v>41695</v>
@@ -14115,7 +14115,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H474" t="n">
         <v>26719</v>
@@ -14144,7 +14144,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>32.9621620178223</v>
+        <v>32.962158203125</v>
       </c>
       <c r="H475" t="n">
         <v>22487</v>
@@ -14202,7 +14202,7 @@
         <v>37</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8733139038086</v>
+        <v>32.8733177185059</v>
       </c>
       <c r="H477" t="n">
         <v>43808</v>
@@ -14260,7 +14260,7 @@
         <v>36.25</v>
       </c>
       <c r="G479" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H479" t="n">
         <v>24196</v>
@@ -14347,7 +14347,7 @@
         <v>37.9500007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>33.7173614501953</v>
+        <v>33.717357635498</v>
       </c>
       <c r="H482" t="n">
         <v>45662</v>
@@ -14376,7 +14376,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H483" t="n">
         <v>61904</v>
@@ -14434,7 +14434,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H485" t="n">
         <v>147072</v>
@@ -14463,7 +14463,7 @@
         <v>38</v>
       </c>
       <c r="G486" t="n">
-        <v>33.7617797851562</v>
+        <v>33.7617874145508</v>
       </c>
       <c r="H486" t="n">
         <v>58518</v>
@@ -14521,7 +14521,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G488" t="n">
-        <v>33.1398506164551</v>
+        <v>33.1398544311523</v>
       </c>
       <c r="H488" t="n">
         <v>34481</v>
@@ -14550,7 +14550,7 @@
         <v>37.1500015258789</v>
       </c>
       <c r="G489" t="n">
-        <v>33.0065841674805</v>
+        <v>33.0065879821777</v>
       </c>
       <c r="H489" t="n">
         <v>27315</v>
@@ -14608,7 +14608,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H491" t="n">
         <v>10757</v>
@@ -14666,7 +14666,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G493" t="n">
-        <v>32.7844696044922</v>
+        <v>32.7844734191895</v>
       </c>
       <c r="H493" t="n">
         <v>16789</v>
@@ -14695,7 +14695,7 @@
         <v>37.25</v>
       </c>
       <c r="G494" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H494" t="n">
         <v>20925</v>
@@ -14724,7 +14724,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>33.8062057495117</v>
+        <v>33.8062019348145</v>
       </c>
       <c r="H495" t="n">
         <v>56617</v>
@@ -14753,7 +14753,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>33.8062057495117</v>
+        <v>33.8062019348145</v>
       </c>
       <c r="H496" t="n">
         <v>24430</v>
@@ -14811,7 +14811,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>32.1625442504883</v>
+        <v>32.162540435791</v>
       </c>
       <c r="H498" t="n">
         <v>32373</v>
@@ -14840,7 +14840,7 @@
         <v>36.25</v>
       </c>
       <c r="G499" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H499" t="n">
         <v>11923</v>
@@ -14898,7 +14898,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H501" t="n">
         <v>30662</v>
@@ -14927,7 +14927,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G502" t="n">
-        <v>31.9404239654541</v>
+        <v>31.9404258728027</v>
       </c>
       <c r="H502" t="n">
         <v>44140</v>
@@ -15014,7 +15014,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>31.2296504974365</v>
+        <v>31.2296485900879</v>
       </c>
       <c r="H505" t="n">
         <v>33281</v>
@@ -15101,7 +15101,7 @@
         <v>37</v>
       </c>
       <c r="G508" t="n">
-        <v>32.8733139038086</v>
+        <v>32.8733177185059</v>
       </c>
       <c r="H508" t="n">
         <v>20299</v>
@@ -15130,7 +15130,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>32.9177398681641</v>
+        <v>32.9177360534668</v>
       </c>
       <c r="H509" t="n">
         <v>34554</v>
@@ -15159,7 +15159,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>31.8071556091309</v>
+        <v>31.8071517944336</v>
       </c>
       <c r="H510" t="n">
         <v>24075</v>
@@ -15188,7 +15188,7 @@
         <v>35.75</v>
       </c>
       <c r="G511" t="n">
-        <v>31.7627296447754</v>
+        <v>31.762731552124</v>
       </c>
       <c r="H511" t="n">
         <v>25723</v>
@@ -15246,7 +15246,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G513" t="n">
-        <v>33.0510063171387</v>
+        <v>33.0510101318359</v>
       </c>
       <c r="H513" t="n">
         <v>30830</v>
@@ -15275,7 +15275,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G514" t="n">
-        <v>33.4508171081543</v>
+        <v>33.4508209228516</v>
       </c>
       <c r="H514" t="n">
         <v>66935</v>
@@ -15304,7 +15304,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>32.473503112793</v>
+        <v>32.4734992980957</v>
       </c>
       <c r="H515" t="n">
         <v>28750</v>
@@ -15333,7 +15333,7 @@
         <v>36.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>32.473503112793</v>
+        <v>32.4734992980957</v>
       </c>
       <c r="H516" t="n">
         <v>39270</v>
@@ -15507,7 +15507,7 @@
         <v>37.25</v>
       </c>
       <c r="G522" t="n">
-        <v>33.0954284667969</v>
+        <v>33.0954322814941</v>
       </c>
       <c r="H522" t="n">
         <v>24452</v>
@@ -15536,7 +15536,7 @@
         <v>37.9000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>33.6729393005371</v>
+        <v>33.6729354858398</v>
       </c>
       <c r="H523" t="n">
         <v>18883</v>
@@ -15594,7 +15594,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G525" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H525" t="n">
         <v>30151</v>
@@ -15652,7 +15652,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G527" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H527" t="n">
         <v>15724</v>
@@ -15681,7 +15681,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G528" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H528" t="n">
         <v>23614</v>
@@ -15826,7 +15826,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>33.9394798278809</v>
+        <v>33.9394721984863</v>
       </c>
       <c r="H533" t="n">
         <v>33489</v>
@@ -15855,7 +15855,7 @@
         <v>38.5</v>
       </c>
       <c r="G534" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H534" t="n">
         <v>20804</v>
@@ -15971,7 +15971,7 @@
         <v>38.3499984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>34.0727500915527</v>
+        <v>34.0727462768555</v>
       </c>
       <c r="H538" t="n">
         <v>33816</v>
@@ -16000,7 +16000,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H539" t="n">
         <v>56910</v>
@@ -16029,7 +16029,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>31.4517669677734</v>
+        <v>31.4517650604248</v>
       </c>
       <c r="H540" t="n">
         <v>30779</v>
@@ -16087,7 +16087,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>32.9621620178223</v>
+        <v>32.962158203125</v>
       </c>
       <c r="H542" t="n">
         <v>16501</v>
@@ -16145,7 +16145,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>33.9394798278809</v>
+        <v>33.9394721984863</v>
       </c>
       <c r="H544" t="n">
         <v>89245</v>
@@ -16174,7 +16174,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>33.4063949584961</v>
+        <v>33.4063911437988</v>
       </c>
       <c r="H545" t="n">
         <v>71422</v>
@@ -16261,7 +16261,7 @@
         <v>38.75</v>
       </c>
       <c r="G548" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H548" t="n">
         <v>151703</v>
@@ -16290,7 +16290,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G549" t="n">
-        <v>34.8279457092285</v>
+        <v>34.8279418945312</v>
       </c>
       <c r="H549" t="n">
         <v>115069</v>
@@ -16319,7 +16319,7 @@
         <v>38.5</v>
       </c>
       <c r="G550" t="n">
-        <v>34.2060203552246</v>
+        <v>34.2060165405273</v>
       </c>
       <c r="H550" t="n">
         <v>59281</v>
@@ -16348,7 +16348,7 @@
         <v>38.75</v>
       </c>
       <c r="G551" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H551" t="n">
         <v>43962</v>
@@ -16377,7 +16377,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>35.6275634765625</v>
+        <v>35.6275672912598</v>
       </c>
       <c r="H552" t="n">
         <v>107403</v>
@@ -16406,7 +16406,7 @@
         <v>38.75</v>
       </c>
       <c r="G553" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H553" t="n">
         <v>48943</v>
@@ -16435,7 +16435,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G554" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H554" t="n">
         <v>69956</v>
@@ -16464,7 +16464,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G555" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H555" t="n">
         <v>49369</v>
@@ -16522,7 +16522,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>33.8062057495117</v>
+        <v>33.8062019348145</v>
       </c>
       <c r="H557" t="n">
         <v>40431</v>
@@ -16551,7 +16551,7 @@
         <v>37.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>33.2731246948242</v>
+        <v>33.2731285095215</v>
       </c>
       <c r="H558" t="n">
         <v>31513</v>
@@ -16580,7 +16580,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>33.9394798278809</v>
+        <v>33.9394721984863</v>
       </c>
       <c r="H559" t="n">
         <v>87892</v>
@@ -16609,7 +16609,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G560" t="n">
-        <v>35.2721748352051</v>
+        <v>35.2721786499023</v>
       </c>
       <c r="H560" t="n">
         <v>92873</v>
@@ -16667,7 +16667,7 @@
         <v>39.8499984741211</v>
       </c>
       <c r="G562" t="n">
-        <v>35.405445098877</v>
+        <v>35.4054489135742</v>
       </c>
       <c r="H562" t="n">
         <v>123601</v>
@@ -16696,7 +16696,7 @@
         <v>41.5</v>
       </c>
       <c r="G563" t="n">
-        <v>36.8714218139648</v>
+        <v>36.8714256286621</v>
       </c>
       <c r="H563" t="n">
         <v>79980</v>
@@ -16725,7 +16725,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>34.3837127685547</v>
+        <v>34.3837089538574</v>
       </c>
       <c r="H564" t="n">
         <v>118997</v>
@@ -16754,7 +16754,7 @@
         <v>38.1500015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>33.8950538635254</v>
+        <v>33.8950576782227</v>
       </c>
       <c r="H565" t="n">
         <v>57075</v>
@@ -16812,7 +16812,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G567" t="n">
-        <v>32.9621620178223</v>
+        <v>32.962158203125</v>
       </c>
       <c r="H567" t="n">
         <v>82672</v>
@@ -16841,7 +16841,7 @@
         <v>32.25</v>
       </c>
       <c r="G568" t="n">
-        <v>28.6530933380127</v>
+        <v>28.6530914306641</v>
       </c>
       <c r="H568" t="n">
         <v>187078</v>
@@ -16870,7 +16870,7 @@
         <v>29</v>
       </c>
       <c r="G569" t="n">
-        <v>25.7655715942383</v>
+        <v>25.7655696868896</v>
       </c>
       <c r="H569" t="n">
         <v>154319</v>
@@ -16899,7 +16899,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G570" t="n">
-        <v>24.7882556915283</v>
+        <v>24.788257598877</v>
       </c>
       <c r="H570" t="n">
         <v>115179</v>
@@ -16928,7 +16928,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G571" t="n">
-        <v>26.3430767059326</v>
+        <v>26.343074798584</v>
       </c>
       <c r="H571" t="n">
         <v>102740</v>
@@ -16957,7 +16957,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G572" t="n">
-        <v>26.7873077392578</v>
+        <v>26.7873096466064</v>
       </c>
       <c r="H572" t="n">
         <v>79386</v>
@@ -16986,7 +16986,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G573" t="n">
-        <v>29.230598449707</v>
+        <v>29.2305965423584</v>
       </c>
       <c r="H573" t="n">
         <v>133949</v>
@@ -17015,7 +17015,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G574" t="n">
-        <v>30.1190624237061</v>
+        <v>30.1190643310547</v>
       </c>
       <c r="H574" t="n">
         <v>110986</v>
@@ -17044,7 +17044,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G575" t="n">
-        <v>29.8525199890137</v>
+        <v>29.8525218963623</v>
       </c>
       <c r="H575" t="n">
         <v>71925</v>
@@ -17073,7 +17073,7 @@
         <v>35.25</v>
       </c>
       <c r="G576" t="n">
-        <v>31.3184986114502</v>
+        <v>31.3184947967529</v>
       </c>
       <c r="H576" t="n">
         <v>113307</v>
@@ -17102,7 +17102,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519580841064</v>
       </c>
       <c r="H577" t="n">
         <v>60129</v>
@@ -17131,7 +17131,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G578" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H578" t="n">
         <v>447251</v>
@@ -17160,7 +17160,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H579" t="n">
         <v>47898</v>
@@ -17218,7 +17218,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G581" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H581" t="n">
         <v>35526</v>
@@ -17247,7 +17247,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>30.8298397064209</v>
+        <v>30.829833984375</v>
       </c>
       <c r="H582" t="n">
         <v>35488</v>
@@ -17276,7 +17276,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H583" t="n">
         <v>48569</v>
@@ -17305,7 +17305,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H584" t="n">
         <v>30682</v>
@@ -17334,7 +17334,7 @@
         <v>38.75</v>
       </c>
       <c r="G585" t="n">
-        <v>34.4281387329102</v>
+        <v>34.4281349182129</v>
       </c>
       <c r="H585" t="n">
         <v>89419</v>
@@ -17479,7 +17479,7 @@
         <v>36.25</v>
       </c>
       <c r="G590" t="n">
-        <v>32.2069664001465</v>
+        <v>32.2069625854492</v>
       </c>
       <c r="H590" t="n">
         <v>44682</v>
@@ -17508,7 +17508,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G591" t="n">
-        <v>31.4517669677734</v>
+        <v>31.4517650604248</v>
       </c>
       <c r="H591" t="n">
         <v>44060</v>
@@ -17537,7 +17537,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>30.4744491577148</v>
+        <v>30.4744529724121</v>
       </c>
       <c r="H592" t="n">
         <v>28557</v>
@@ -17566,7 +17566,7 @@
         <v>34.5</v>
       </c>
       <c r="G593" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H593" t="n">
         <v>18121</v>
@@ -17595,7 +17595,7 @@
         <v>33.5</v>
       </c>
       <c r="G594" t="n">
-        <v>29.7636737823486</v>
+        <v>29.7636795043945</v>
       </c>
       <c r="H594" t="n">
         <v>35604</v>
@@ -17624,7 +17624,7 @@
         <v>34.5</v>
       </c>
       <c r="G595" t="n">
-        <v>30.6521434783936</v>
+        <v>30.6521453857422</v>
       </c>
       <c r="H595" t="n">
         <v>37402</v>
@@ -17653,7 +17653,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>30.9186859130859</v>
+        <v>30.9186878204346</v>
       </c>
       <c r="H596" t="n">
         <v>28243</v>
@@ -17711,7 +17711,7 @@
         <v>34.9500007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>31.0519561767578</v>
+        <v>31.0519580841064</v>
       </c>
       <c r="H598" t="n">
         <v>20035</v>
@@ -17740,7 +17740,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G599" t="n">
-        <v>31.274076461792</v>
+        <v>31.2740745544434</v>
       </c>
       <c r="H599" t="n">
         <v>22406</v>
@@ -17769,7 +17769,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>31.3629150390625</v>
+        <v>31.3629169464111</v>
       </c>
       <c r="H600" t="n">
         <v>24723</v>
@@ -17798,7 +17798,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>31.6294574737549</v>
+        <v>31.6294612884521</v>
       </c>
       <c r="H601" t="n">
         <v>16163</v>
@@ -17827,7 +17827,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>31.1408023834229</v>
+        <v>31.1408042907715</v>
       </c>
       <c r="H602" t="n">
         <v>46419</v>
@@ -17943,7 +17943,7 @@
         <v>33.75</v>
       </c>
       <c r="G606" t="n">
-        <v>29.9857921600342</v>
+        <v>29.9857959747314</v>
       </c>
       <c r="H606" t="n">
         <v>22611</v>
@@ -18001,7 +18001,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>29.2621536254883</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H608" t="n">
         <v>42611</v>
@@ -18030,7 +18030,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H609" t="n">
         <v>29532</v>
@@ -18059,7 +18059,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G610" t="n">
-        <v>29.2621536254883</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H610" t="n">
         <v>31377</v>
@@ -18117,7 +18117,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G612" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H612" t="n">
         <v>85415</v>
@@ -18146,7 +18146,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G613" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H613" t="n">
         <v>43669</v>
@@ -18262,7 +18262,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G617" t="n">
-        <v>34.0110359191895</v>
+        <v>34.0110321044922</v>
       </c>
       <c r="H617" t="n">
         <v>48629</v>
@@ -18349,7 +18349,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G620" t="n">
-        <v>31.9758014678955</v>
+        <v>31.9758033752441</v>
       </c>
       <c r="H620" t="n">
         <v>19405</v>
@@ -18407,7 +18407,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>30.7094326019287</v>
+        <v>30.7094345092773</v>
       </c>
       <c r="H622" t="n">
         <v>13020</v>
@@ -18610,7 +18610,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>30.6189804077148</v>
+        <v>30.6189785003662</v>
       </c>
       <c r="H629" t="n">
         <v>25073</v>
@@ -18639,7 +18639,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G630" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164798736572</v>
       </c>
       <c r="H630" t="n">
         <v>9830</v>
@@ -18697,7 +18697,7 @@
         <v>34.6500015258789</v>
       </c>
       <c r="G632" t="n">
-        <v>31.3426208496094</v>
+        <v>31.3426189422607</v>
       </c>
       <c r="H632" t="n">
         <v>44384</v>
@@ -18726,7 +18726,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H633" t="n">
         <v>27780</v>
@@ -18755,7 +18755,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>31.0260257720947</v>
+        <v>31.0260276794434</v>
       </c>
       <c r="H634" t="n">
         <v>36768</v>
@@ -18813,7 +18813,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H636" t="n">
         <v>49552</v>
@@ -19045,7 +19045,7 @@
         <v>32</v>
       </c>
       <c r="G644" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H644" t="n">
         <v>31552</v>
@@ -19161,7 +19161,7 @@
         <v>32</v>
       </c>
       <c r="G648" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H648" t="n">
         <v>10722</v>
@@ -19248,7 +19248,7 @@
         <v>32</v>
       </c>
       <c r="G651" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H651" t="n">
         <v>18834</v>
@@ -19422,7 +19422,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>29.6692028045654</v>
+        <v>29.6692008972168</v>
       </c>
       <c r="H657" t="n">
         <v>10389</v>
@@ -19480,7 +19480,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H659" t="n">
         <v>11969</v>
@@ -19538,7 +19538,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H661" t="n">
         <v>16406</v>
@@ -19567,7 +19567,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.5787506103516</v>
+        <v>29.5787487030029</v>
       </c>
       <c r="H662" t="n">
         <v>11492</v>
@@ -19625,7 +19625,7 @@
         <v>32.5</v>
       </c>
       <c r="G664" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H664" t="n">
         <v>12292</v>
@@ -19683,7 +19683,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>31.0260257720947</v>
+        <v>31.0260276794434</v>
       </c>
       <c r="H666" t="n">
         <v>41810</v>
@@ -19915,7 +19915,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>30.935567855835</v>
+        <v>30.9355697631836</v>
       </c>
       <c r="H674" t="n">
         <v>5344</v>
@@ -19944,7 +19944,7 @@
         <v>34.25</v>
       </c>
       <c r="G675" t="n">
-        <v>30.9808006286621</v>
+        <v>30.9807987213135</v>
       </c>
       <c r="H675" t="n">
         <v>14000</v>
@@ -20031,7 +20031,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>29.5787506103516</v>
+        <v>29.5787487030029</v>
       </c>
       <c r="H678" t="n">
         <v>13528</v>
@@ -20089,7 +20089,7 @@
         <v>32.5</v>
       </c>
       <c r="G680" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H680" t="n">
         <v>18879</v>
@@ -20147,7 +20147,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>29.8048877716064</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H682" t="n">
         <v>13128</v>
@@ -20176,7 +20176,7 @@
         <v>32.25</v>
       </c>
       <c r="G683" t="n">
-        <v>29.1716995239258</v>
+        <v>29.1717014312744</v>
       </c>
       <c r="H683" t="n">
         <v>7419</v>
@@ -20205,7 +20205,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G684" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H684" t="n">
         <v>27461</v>
@@ -20292,7 +20292,7 @@
         <v>32</v>
       </c>
       <c r="G687" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H687" t="n">
         <v>31220</v>
@@ -20408,7 +20408,7 @@
         <v>32</v>
       </c>
       <c r="G691" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H691" t="n">
         <v>11145</v>
@@ -20437,7 +20437,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H692" t="n">
         <v>20442</v>
@@ -20698,7 +20698,7 @@
         <v>35.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>32.1567115783691</v>
+        <v>32.1567077636719</v>
       </c>
       <c r="H701" t="n">
         <v>56088</v>
@@ -20785,7 +20785,7 @@
         <v>31.75</v>
       </c>
       <c r="G704" t="n">
-        <v>28.719425201416</v>
+        <v>28.7194271087646</v>
       </c>
       <c r="H704" t="n">
         <v>29153</v>
@@ -20959,7 +20959,7 @@
         <v>30</v>
       </c>
       <c r="G710" t="n">
-        <v>27.1364669799805</v>
+        <v>27.1364650726318</v>
       </c>
       <c r="H710" t="n">
         <v>48790</v>
@@ -21075,7 +21075,7 @@
         <v>32.25</v>
       </c>
       <c r="G714" t="n">
-        <v>29.1716995239258</v>
+        <v>29.1717014312744</v>
       </c>
       <c r="H714" t="n">
         <v>28119</v>
@@ -21104,7 +21104,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>29.8048877716064</v>
+        <v>29.8048858642578</v>
       </c>
       <c r="H715" t="n">
         <v>26731</v>
@@ -21133,7 +21133,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H716" t="n">
         <v>30596</v>
@@ -21220,7 +21220,7 @@
         <v>32</v>
       </c>
       <c r="G719" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H719" t="n">
         <v>25143</v>
@@ -21249,7 +21249,7 @@
         <v>32.5</v>
       </c>
       <c r="G720" t="n">
-        <v>29.3978366851807</v>
+        <v>29.3978385925293</v>
       </c>
       <c r="H720" t="n">
         <v>19906</v>
@@ -21278,7 +21278,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>29.4430656433105</v>
+        <v>29.4430637359619</v>
       </c>
       <c r="H721" t="n">
         <v>14502</v>
@@ -21336,7 +21336,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G723" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H723" t="n">
         <v>10352</v>
@@ -21365,7 +21365,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H724" t="n">
         <v>28121</v>
@@ -21394,7 +21394,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H725" t="n">
         <v>27078</v>
@@ -21452,7 +21452,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H727" t="n">
         <v>23140</v>
@@ -21597,7 +21597,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G732" t="n">
-        <v>29.7596569061279</v>
+        <v>29.7596588134766</v>
       </c>
       <c r="H732" t="n">
         <v>39155</v>
@@ -21626,7 +21626,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="G733" t="n">
-        <v>29.2621536254883</v>
+        <v>29.2621555328369</v>
       </c>
       <c r="H733" t="n">
         <v>36285</v>
@@ -21655,7 +21655,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2169284820557</v>
+        <v>29.216926574707</v>
       </c>
       <c r="H734" t="n">
         <v>19361</v>
@@ -21684,7 +21684,7 @@
         <v>32</v>
       </c>
       <c r="G735" t="n">
-        <v>28.9455623626709</v>
+        <v>28.9455642700195</v>
       </c>
       <c r="H735" t="n">
         <v>17587</v>
@@ -21713,7 +21713,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.352611541748</v>
+        <v>29.3526096343994</v>
       </c>
       <c r="H736" t="n">
         <v>39696</v>
@@ -21742,7 +21742,7 @@
         <v>32.0499992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>28.9907913208008</v>
+        <v>28.9907894134521</v>
       </c>
       <c r="H737" t="n">
         <v>13524</v>
@@ -21771,7 +21771,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>29.1264762878418</v>
+        <v>29.1264743804932</v>
       </c>
       <c r="H738" t="n">
         <v>31102</v>
@@ -21945,7 +21945,7 @@
         <v>34.75</v>
       </c>
       <c r="G744" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H744" t="n">
         <v>24053</v>
@@ -21974,7 +21974,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>31.8401165008545</v>
+        <v>31.8401203155518</v>
       </c>
       <c r="H745" t="n">
         <v>20993</v>
@@ -22032,7 +22032,7 @@
         <v>34.0499992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>30.7998867034912</v>
+        <v>30.7998886108398</v>
       </c>
       <c r="H747" t="n">
         <v>9633</v>
@@ -22148,7 +22148,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>30.573751449585</v>
+        <v>30.5737533569336</v>
       </c>
       <c r="H751" t="n">
         <v>7222</v>
@@ -22177,7 +22177,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G752" t="n">
-        <v>30.7094326019287</v>
+        <v>30.7094345092773</v>
       </c>
       <c r="H752" t="n">
         <v>15924</v>
@@ -22264,7 +22264,7 @@
         <v>34.75</v>
       </c>
       <c r="G755" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H755" t="n">
         <v>11292</v>
@@ -22322,7 +22322,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G757" t="n">
-        <v>31.1164817810059</v>
+        <v>31.1164798736572</v>
       </c>
       <c r="H757" t="n">
         <v>15048</v>
@@ -22438,7 +22438,7 @@
         <v>34.75</v>
       </c>
       <c r="G761" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H761" t="n">
         <v>16883</v>
@@ -22612,7 +22612,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G767" t="n">
-        <v>33.1969413757324</v>
+        <v>33.1969451904297</v>
       </c>
       <c r="H767" t="n">
         <v>47582</v>
@@ -22641,7 +22641,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G768" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H768" t="n">
         <v>16759</v>
@@ -22728,7 +22728,7 @@
         <v>34.75</v>
       </c>
       <c r="G771" t="n">
-        <v>31.4330730438232</v>
+        <v>31.4330711364746</v>
       </c>
       <c r="H771" t="n">
         <v>8172</v>
@@ -22757,7 +22757,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G772" t="n">
-        <v>31.252161026001</v>
+        <v>31.2521629333496</v>
       </c>
       <c r="H772" t="n">
         <v>13060</v>
@@ -22786,7 +22786,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G773" t="n">
-        <v>32.5185317993164</v>
+        <v>32.5185356140137</v>
       </c>
       <c r="H773" t="n">
         <v>13130</v>
@@ -22815,7 +22815,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G774" t="n">
-        <v>32.8803520202637</v>
+        <v>32.8803482055664</v>
       </c>
       <c r="H774" t="n">
         <v>42655</v>
@@ -22844,7 +22844,7 @@
         <v>36</v>
       </c>
       <c r="G775" t="n">
-        <v>32.5637626647949</v>
+        <v>32.5637588500977</v>
       </c>
       <c r="H775" t="n">
         <v>13759</v>
@@ -23018,7 +23018,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>34.1919479370117</v>
+        <v>34.1919441223145</v>
       </c>
       <c r="H781" t="n">
         <v>27307</v>
@@ -23076,7 +23076,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G783" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H783" t="n">
         <v>11055</v>
@@ -23105,7 +23105,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G784" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H784" t="n">
         <v>9050</v>
@@ -23134,7 +23134,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>34.1919479370117</v>
+        <v>34.1919441223145</v>
       </c>
       <c r="H785" t="n">
         <v>16126</v>
@@ -23163,7 +23163,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G786" t="n">
-        <v>34.0110359191895</v>
+        <v>34.0110321044922</v>
       </c>
       <c r="H786" t="n">
         <v>10605</v>
@@ -23192,7 +23192,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G787" t="n">
-        <v>33.8301239013672</v>
+        <v>33.8301277160645</v>
       </c>
       <c r="H787" t="n">
         <v>11711</v>
@@ -23366,7 +23366,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>34.101490020752</v>
+        <v>34.1014938354492</v>
       </c>
       <c r="H793" t="n">
         <v>25794</v>
@@ -23424,7 +23424,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G795" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H795" t="n">
         <v>28476</v>
@@ -23453,7 +23453,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G796" t="n">
-        <v>35.4130935668945</v>
+        <v>35.4130897521973</v>
       </c>
       <c r="H796" t="n">
         <v>22692</v>
@@ -23569,7 +23569,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H800" t="n">
         <v>24431</v>
@@ -23656,7 +23656,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>37.3578643798828</v>
+        <v>37.3578681945801</v>
       </c>
       <c r="H803" t="n">
         <v>26461</v>
@@ -23685,7 +23685,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>37.2674140930176</v>
+        <v>37.2674102783203</v>
       </c>
       <c r="H804" t="n">
         <v>27876</v>
@@ -23743,7 +23743,7 @@
         <v>40.25</v>
       </c>
       <c r="G806" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H806" t="n">
         <v>19091</v>
@@ -23772,7 +23772,7 @@
         <v>39.5499992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>35.7749061584473</v>
+        <v>35.7749099731445</v>
       </c>
       <c r="H807" t="n">
         <v>30091</v>
@@ -23801,7 +23801,7 @@
         <v>40.0499992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>36.2271766662598</v>
+        <v>36.227180480957</v>
       </c>
       <c r="H808" t="n">
         <v>31459</v>
@@ -23946,7 +23946,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G813" t="n">
-        <v>36.5437774658203</v>
+        <v>36.543773651123</v>
       </c>
       <c r="H813" t="n">
         <v>27397</v>
@@ -24004,7 +24004,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H815" t="n">
         <v>35580</v>
@@ -24207,7 +24207,7 @@
         <v>42.4500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>38.3981018066406</v>
+        <v>38.3981056213379</v>
       </c>
       <c r="H822" t="n">
         <v>31744</v>
@@ -24294,7 +24294,7 @@
         <v>43.5499992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>39.3931045532227</v>
+        <v>39.3931007385254</v>
       </c>
       <c r="H825" t="n">
         <v>40999</v>
@@ -24323,7 +24323,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G826" t="n">
-        <v>38.9860572814941</v>
+        <v>38.9860534667969</v>
       </c>
       <c r="H826" t="n">
         <v>26184</v>
@@ -24497,7 +24497,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G832" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H832" t="n">
         <v>71309</v>
@@ -24671,7 +24671,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>37.0412788391113</v>
+        <v>37.0412750244141</v>
       </c>
       <c r="H838" t="n">
         <v>42162</v>
@@ -24700,7 +24700,7 @@
         <v>39.9500007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>36.1367301940918</v>
+        <v>36.1367263793945</v>
       </c>
       <c r="H839" t="n">
         <v>32321</v>
@@ -24729,7 +24729,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G840" t="n">
-        <v>35.8653678894043</v>
+        <v>35.865364074707</v>
       </c>
       <c r="H840" t="n">
         <v>24851</v>
@@ -24816,7 +24816,7 @@
         <v>39.6500015258789</v>
       </c>
       <c r="G843" t="n">
-        <v>35.8653678894043</v>
+        <v>35.865364074707</v>
       </c>
       <c r="H843" t="n">
         <v>30983</v>
@@ -24874,7 +24874,7 @@
         <v>40.25</v>
       </c>
       <c r="G845" t="n">
-        <v>36.4080924987793</v>
+        <v>36.408088684082</v>
       </c>
       <c r="H845" t="n">
         <v>19073</v>
@@ -25077,7 +25077,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>37.8101387023926</v>
+        <v>37.8101425170898</v>
       </c>
 